--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtam_prx" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +590,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.078</v>
+        <v>0.155</v>
+      </c>
+      <c r="E2">
+        <v>0.186</v>
       </c>
       <c r="F2">
-        <v>0.479</v>
+        <v>0.259</v>
       </c>
       <c r="G2">
-        <v>-0.04620652558938903</v>
+        <v>-0.001361933946203609</v>
       </c>
       <c r="H2">
-        <v>-0.05709562730409456</v>
+        <v>-0.001361933946203609</v>
       </c>
       <c r="I2">
-        <v>-0.0792529602684819</v>
+        <v>0.006639427987742594</v>
       </c>
       <c r="J2">
-        <v>-0.07887286801968629</v>
+        <v>0.006490978860743926</v>
       </c>
       <c r="K2">
-        <v>10827.9</v>
+        <v>7811</v>
       </c>
       <c r="L2">
-        <v>1.420555475381446</v>
+        <v>1.329758256724549</v>
       </c>
       <c r="M2">
-        <v>10530</v>
+        <v>6762</v>
       </c>
       <c r="N2">
-        <v>0.1367704762807782</v>
+        <v>0.07170503589493442</v>
       </c>
       <c r="O2">
-        <v>0.9724877400049872</v>
+        <v>0.8657022148252465</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="Q2">
-        <v>1.298864921944712e-05</v>
+        <v>0.002110219187088428</v>
       </c>
       <c r="R2">
-        <v>9.235401139648501e-05</v>
+        <v>0.02547689156318013</v>
       </c>
       <c r="S2">
-        <v>10529</v>
+        <v>6563</v>
       </c>
       <c r="T2">
-        <v>0.9999050332383665</v>
+        <v>0.9705708370304643</v>
       </c>
       <c r="U2">
-        <v>2686.6</v>
+        <v>9925</v>
       </c>
       <c r="V2">
-        <v>0.03489530499296664</v>
+        <v>0.1052458564414706</v>
       </c>
       <c r="W2">
-        <v>0.2921835292836863</v>
+        <v>0.1953726863431716</v>
       </c>
       <c r="X2">
-        <v>0.10153467590735</v>
+        <v>0.09284230137804994</v>
       </c>
       <c r="Y2">
-        <v>0.1906488533763363</v>
+        <v>0.1025303849651217</v>
       </c>
       <c r="Z2">
-        <v>0.1667295571116347</v>
+        <v>0.1124275077994909</v>
       </c>
       <c r="AA2">
-        <v>-0.1003270113537106</v>
+        <v>0.0007297645764926183</v>
       </c>
       <c r="AB2">
-        <v>0.07956284286843582</v>
+        <v>0.08538115683291909</v>
       </c>
       <c r="AC2">
-        <v>-0.1798898542221464</v>
+        <v>-0.08465139225642648</v>
       </c>
       <c r="AD2">
-        <v>16770.6</v>
+        <v>16558</v>
       </c>
       <c r="AE2">
-        <v>0.9491952722481881</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>16771.54919527225</v>
+        <v>16558</v>
       </c>
       <c r="AG2">
-        <v>14084.94919527225</v>
+        <v>6633</v>
       </c>
       <c r="AH2">
-        <v>0.1788739166219209</v>
+        <v>0.1493582053201757</v>
       </c>
       <c r="AI2">
-        <v>0.2979048131073915</v>
+        <v>0.2566733839714773</v>
       </c>
       <c r="AJ2">
-        <v>0.1546517777302266</v>
+        <v>0.06571490845684394</v>
       </c>
       <c r="AK2">
-        <v>0.2627213140158898</v>
+        <v>0.1215169002473207</v>
       </c>
       <c r="AL2">
-        <v>587.4</v>
+        <v>551</v>
       </c>
       <c r="AM2">
-        <v>-187.383</v>
+        <v>-393</v>
       </c>
       <c r="AN2">
-        <v>-41.79068028906055</v>
+        <v>87.60846560846561</v>
       </c>
       <c r="AO2">
-        <v>-1.029792305073204</v>
+        <v>0.07078039927404718</v>
       </c>
       <c r="AP2">
-        <v>-35.09830350179977</v>
+        <v>35.09523809523809</v>
       </c>
       <c r="AQ2">
-        <v>3.228147697496571</v>
+        <v>-0.09923664122137404</v>
       </c>
     </row>
     <row r="3">
@@ -721,247 +726,8897 @@
           <t>Retail (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.155</v>
+      </c>
+      <c r="E3">
+        <v>0.186</v>
+      </c>
       <c r="F3">
-        <v>0.479</v>
+        <v>0.259</v>
       </c>
       <c r="G3">
-        <v>-0.07617316589557172</v>
+        <v>-0.001361933946203609</v>
       </c>
       <c r="H3">
-        <v>-0.07617316589557172</v>
+        <v>-0.001361933946203609</v>
       </c>
       <c r="I3">
-        <v>-0.0950412820645158</v>
+        <v>0.006639427987742594</v>
       </c>
       <c r="J3">
-        <v>-0.09412965795594136</v>
+        <v>0.006490978860743926</v>
       </c>
       <c r="K3">
-        <v>10958</v>
+        <v>7811</v>
       </c>
       <c r="L3">
-        <v>1.810641110376735</v>
+        <v>1.329758256724549</v>
       </c>
       <c r="M3">
-        <v>10530</v>
+        <v>6762</v>
       </c>
       <c r="N3">
-        <v>0.1383058647991215</v>
+        <v>0.07170503589493442</v>
       </c>
       <c r="O3">
-        <v>0.96094177769666</v>
+        <v>0.8657022148252465</v>
       </c>
       <c r="P3">
+        <v>199</v>
+      </c>
+      <c r="Q3">
+        <v>0.002110219187088428</v>
+      </c>
+      <c r="R3">
+        <v>0.02547689156318013</v>
+      </c>
+      <c r="S3">
+        <v>6563</v>
+      </c>
+      <c r="T3">
+        <v>0.9705708370304643</v>
+      </c>
+      <c r="U3">
+        <v>9925</v>
+      </c>
+      <c r="V3">
+        <v>0.1052458564414706</v>
+      </c>
+      <c r="W3">
+        <v>0.1953726863431716</v>
+      </c>
+      <c r="X3">
+        <v>0.09284230137804994</v>
+      </c>
+      <c r="Y3">
+        <v>0.1025303849651217</v>
+      </c>
+      <c r="Z3">
+        <v>0.1124275077994909</v>
+      </c>
+      <c r="AA3">
+        <v>0.0007297645764926183</v>
+      </c>
+      <c r="AB3">
+        <v>0.08538115683291909</v>
+      </c>
+      <c r="AC3">
+        <v>-0.08465139225642648</v>
+      </c>
+      <c r="AD3">
+        <v>16558</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>16558</v>
+      </c>
+      <c r="AG3">
+        <v>6633</v>
+      </c>
+      <c r="AH3">
+        <v>0.1493582053201757</v>
+      </c>
+      <c r="AI3">
+        <v>0.2566733839714773</v>
+      </c>
+      <c r="AJ3">
+        <v>0.06571490845684394</v>
+      </c>
+      <c r="AK3">
+        <v>0.1215169002473207</v>
+      </c>
+      <c r="AL3">
+        <v>551</v>
+      </c>
+      <c r="AM3">
+        <v>-393</v>
+      </c>
+      <c r="AN3">
+        <v>87.60846560846561</v>
+      </c>
+      <c r="AO3">
+        <v>0.07078039927404718</v>
+      </c>
+      <c r="AP3">
+        <v>35.09523809523809</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.09923664122137404</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Prosus N.V. (ENXTAM:PRX)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTAM:PRX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0707803992740472</v>
+      </c>
+      <c r="F2">
+        <v>3.55203708625837</v>
+      </c>
+      <c r="G2">
+        <v>87.60846560846559</v>
+      </c>
+      <c r="H2">
+        <v>5.86566137566138</v>
+      </c>
+      <c r="I2">
+        <v>0.149358205320176</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>94303</v>
+      </c>
+      <c r="L2">
+        <v>105122.090311532</v>
+      </c>
+      <c r="M2">
+        <v>100936</v>
+      </c>
+      <c r="N2">
+        <v>96305.700311532</v>
+      </c>
+      <c r="O2">
+        <v>16558</v>
+      </c>
+      <c r="P2">
+        <v>1108.61</v>
+      </c>
+      <c r="Q2">
+        <v>0.08538115683291909</v>
+      </c>
+      <c r="R2">
+        <v>0.08728418663862959</v>
+      </c>
+      <c r="S2">
+        <v>0.0428876</v>
+      </c>
+      <c r="T2">
+        <v>0.0429618</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0928423013780499</v>
+      </c>
+      <c r="X2">
+        <v>0.0877318875137673</v>
+      </c>
+      <c r="Y2">
+        <v>1.08572880740923</v>
+      </c>
+      <c r="Z2">
+        <v>0.96778127109197</v>
+      </c>
+      <c r="AA2">
+        <v>16558</v>
+      </c>
+      <c r="AB2">
+        <v>0.0578</v>
+      </c>
+      <c r="AC2">
+        <v>0.07078039927404718</v>
+      </c>
+      <c r="AD2">
+        <v>16558</v>
+      </c>
+      <c r="AE2">
+        <v>551</v>
+      </c>
+      <c r="AF2">
+        <v>150</v>
+      </c>
+      <c r="AG2">
+        <v>189</v>
+      </c>
+      <c r="AH2">
+        <v>6.938893903907228E-18</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>94303</v>
+      </c>
+      <c r="AK2">
+        <v>0.043327855959079</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.258</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>298</v>
+      </c>
+      <c r="AR2">
+        <v>551</v>
+      </c>
+      <c r="AS2">
+        <v>16558</v>
+      </c>
+      <c r="AT2">
+        <v>9925</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
         <v>1</v>
       </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08741994810473983</v>
+      </c>
+      <c r="C2">
+        <v>105916.5576067847</v>
+      </c>
+      <c r="D2">
+        <v>95991.55760678467</v>
+      </c>
+      <c r="E2">
+        <v>-16558</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>9925</v>
+      </c>
+      <c r="H2">
+        <v>94303</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>378</v>
+      </c>
+      <c r="K2">
+        <v>150</v>
+      </c>
+      <c r="L2">
+        <v>228</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>228</v>
+      </c>
+      <c r="O2">
+        <v>58.824</v>
+      </c>
+      <c r="P2">
+        <v>169.176</v>
+      </c>
+      <c r="Q2">
+        <v>319.176</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08741994810473983</v>
+      </c>
+      <c r="T2">
+        <v>0.9605817593200962</v>
+      </c>
+      <c r="U2">
+        <v>0.05170000000000001</v>
+      </c>
+      <c r="V2">
+        <v>0.258</v>
+      </c>
+      <c r="W2">
+        <v>0.0383614</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08728418663862959</v>
+      </c>
+      <c r="C3">
+        <v>105122.090311532</v>
+      </c>
+      <c r="D3">
+        <v>96305.700311532</v>
+      </c>
+      <c r="E3">
+        <v>-15449.39</v>
+      </c>
+      <c r="F3">
+        <v>1108.61</v>
+      </c>
+      <c r="G3">
+        <v>9925</v>
+      </c>
+      <c r="H3">
+        <v>94303</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>378</v>
+      </c>
+      <c r="K3">
+        <v>150</v>
+      </c>
+      <c r="L3">
+        <v>228</v>
+      </c>
+      <c r="M3">
+        <v>64.18851900000001</v>
+      </c>
+      <c r="N3">
+        <v>163.811481</v>
+      </c>
+      <c r="O3">
+        <v>42.26336209799999</v>
+      </c>
+      <c r="P3">
+        <v>121.548118902</v>
+      </c>
       <c r="Q3">
-        <v>1.313446009488334e-05</v>
+        <v>271.548118902</v>
       </c>
       <c r="R3">
-        <v>9.125752874612155e-05</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>10529</v>
+        <v>0.08773188751376726</v>
       </c>
       <c r="T3">
-        <v>0.9999050332383665</v>
+        <v>0.96778127109197</v>
       </c>
       <c r="U3">
-        <v>2676</v>
+        <v>0.05790000000000001</v>
       </c>
       <c r="V3">
-        <v>0.03514781521390781</v>
+        <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.2677450094069929</v>
-      </c>
-      <c r="X3">
-        <v>0.08986999262069206</v>
+        <v>0.0429618</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>0.1778750167863009</v>
+        <v>3.552037086258369</v>
       </c>
       <c r="Z3">
-        <v>0.1328272227081379</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01250298104075467</v>
-      </c>
-      <c r="AB3">
-        <v>0.08116741070556274</v>
-      </c>
-      <c r="AC3">
-        <v>-0.09367039174631742</v>
-      </c>
-      <c r="AD3">
-        <v>15983</v>
-      </c>
-      <c r="AE3">
-        <v>0.9491952722481881</v>
-      </c>
-      <c r="AF3">
-        <v>15983.94919527225</v>
-      </c>
-      <c r="AG3">
-        <v>13307.94919527225</v>
-      </c>
-      <c r="AH3">
-        <v>0.1735131069887234</v>
-      </c>
-      <c r="AI3">
-        <v>0.285463606132428</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1487860143632993</v>
-      </c>
-      <c r="AK3">
-        <v>0.2496007254003254</v>
-      </c>
-      <c r="AL3">
-        <v>557</v>
-      </c>
-      <c r="AM3">
-        <v>-217</v>
-      </c>
-      <c r="AN3">
-        <v>-35.59688195991091</v>
-      </c>
-      <c r="AO3">
-        <v>-1.03411131059246</v>
-      </c>
-      <c r="AP3">
-        <v>-29.63908506742149</v>
-      </c>
-      <c r="AQ3">
-        <v>2.654377880184332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cnova N.V. (ENXTPA:CNV)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Retail (General)</t>
-        </is>
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09018700230925084</v>
+      </c>
+      <c r="C4">
+        <v>97715.29206969606</v>
       </c>
       <c r="D4">
-        <v>-0.078</v>
+        <v>90007.51206969607</v>
+      </c>
+      <c r="E4">
+        <v>-14340.78</v>
+      </c>
+      <c r="F4">
+        <v>2217.22</v>
       </c>
       <c r="G4">
-        <v>0.06928612367063619</v>
+        <v>9925</v>
       </c>
       <c r="H4">
-        <v>0.0164299815321913</v>
+        <v>94303</v>
       </c>
       <c r="I4">
-        <v>-0.01840412660001274</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.01840412660001274</v>
+        <v>378</v>
       </c>
       <c r="K4">
-        <v>-130.1</v>
+        <v>150</v>
       </c>
       <c r="L4">
-        <v>-0.08285041074953831</v>
+        <v>228</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>478.4760760000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>-250.4760760000001</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-64.62282760800002</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>-185.8532483920001</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>-35.85324839200007</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.08816491093190845</v>
+      </c>
+      <c r="T4">
+        <v>0.9777753824680363</v>
       </c>
       <c r="U4">
-        <v>10.6</v>
+        <v>0.2158</v>
       </c>
       <c r="V4">
-        <v>0.0124020124020124</v>
+        <v>0.1229403160378702</v>
       </c>
       <c r="W4">
-        <v>0.3166220491603797</v>
-      </c>
-      <c r="X4">
-        <v>0.1131993591940079</v>
+        <v>0.1892694797990276</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
       </c>
       <c r="Y4">
-        <v>0.2034226899663718</v>
+        <v>0.4765128528599619</v>
       </c>
       <c r="Z4">
-        <v>10.22330729166666</v>
-      </c>
-      <c r="AA4">
-        <v>-0.1881510416666665</v>
-      </c>
-      <c r="AB4">
-        <v>0.07795827503130888</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2661093166979754</v>
-      </c>
-      <c r="AD4">
-        <v>787.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>787.6</v>
-      </c>
-      <c r="AG4">
-        <v>777</v>
-      </c>
-      <c r="AH4">
-        <v>0.479571332886805</v>
-      </c>
-      <c r="AI4">
-        <v>2.578912901113294</v>
-      </c>
-      <c r="AJ4">
-        <v>0.4761904761904762</v>
-      </c>
-      <c r="AK4">
-        <v>2.635685210312076</v>
-      </c>
-      <c r="AL4">
-        <v>30.4</v>
-      </c>
-      <c r="AM4">
-        <v>29.617</v>
-      </c>
-      <c r="AN4">
-        <v>16.51153039832285</v>
-      </c>
-      <c r="AO4">
-        <v>-0.9506578947368421</v>
-      </c>
-      <c r="AP4">
-        <v>16.28930817610063</v>
-      </c>
-      <c r="AQ4">
-        <v>-0.9757909308842895</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09188700230925084</v>
+      </c>
+      <c r="C5">
+        <v>93286.59695129881</v>
+      </c>
+      <c r="D5">
+        <v>86687.42695129881</v>
+      </c>
+      <c r="E5">
+        <v>-13232.17</v>
+      </c>
+      <c r="F5">
+        <v>3325.83</v>
+      </c>
+      <c r="G5">
+        <v>9925</v>
+      </c>
+      <c r="H5">
+        <v>94303</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>378</v>
+      </c>
+      <c r="K5">
+        <v>150</v>
+      </c>
+      <c r="L5">
+        <v>228</v>
+      </c>
+      <c r="M5">
+        <v>717.714114</v>
+      </c>
+      <c r="N5">
+        <v>-489.714114</v>
+      </c>
+      <c r="O5">
+        <v>-126.346241412</v>
+      </c>
+      <c r="P5">
+        <v>-363.367872588</v>
+      </c>
+      <c r="Q5">
+        <v>-213.367872588</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0886016625910003</v>
+      </c>
+      <c r="T5">
+        <v>0.987855541050181</v>
+      </c>
+      <c r="U5">
+        <v>0.2158</v>
+      </c>
+      <c r="V5">
+        <v>0.08196021069191346</v>
+      </c>
+      <c r="W5">
+        <v>0.1981129865326851</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.3176752352399747</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09358700230925084</v>
+      </c>
+      <c r="C6">
+        <v>89094.12274773316</v>
+      </c>
+      <c r="D6">
+        <v>83603.56274773316</v>
+      </c>
+      <c r="E6">
+        <v>-12123.56</v>
+      </c>
+      <c r="F6">
+        <v>4434.440000000001</v>
+      </c>
+      <c r="G6">
+        <v>9925</v>
+      </c>
+      <c r="H6">
+        <v>94303</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>378</v>
+      </c>
+      <c r="K6">
+        <v>150</v>
+      </c>
+      <c r="L6">
+        <v>228</v>
+      </c>
+      <c r="M6">
+        <v>956.9521520000002</v>
+      </c>
+      <c r="N6">
+        <v>-728.9521520000002</v>
+      </c>
+      <c r="O6">
+        <v>-188.0696552160001</v>
+      </c>
+      <c r="P6">
+        <v>-540.8824967840001</v>
+      </c>
+      <c r="Q6">
+        <v>-390.8824967840001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08904751324298987</v>
+      </c>
+      <c r="T6">
+        <v>0.9981457029361204</v>
+      </c>
+      <c r="U6">
+        <v>0.2158</v>
+      </c>
+      <c r="V6">
+        <v>0.06147015801893509</v>
+      </c>
+      <c r="W6">
+        <v>0.2025347398995138</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.2382564264299809</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09679949238957666</v>
+      </c>
+      <c r="C7">
+        <v>82719.27178291362</v>
+      </c>
+      <c r="D7">
+        <v>78337.32178291363</v>
+      </c>
+      <c r="E7">
+        <v>-11014.95</v>
+      </c>
+      <c r="F7">
+        <v>5543.05</v>
+      </c>
+      <c r="G7">
+        <v>9925</v>
+      </c>
+      <c r="H7">
+        <v>94303</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>378</v>
+      </c>
+      <c r="K7">
+        <v>150</v>
+      </c>
+      <c r="L7">
+        <v>228</v>
+      </c>
+      <c r="M7">
+        <v>1362.48169</v>
+      </c>
+      <c r="N7">
+        <v>-1134.48169</v>
+      </c>
+      <c r="O7">
+        <v>-292.69627602</v>
+      </c>
+      <c r="P7">
+        <v>-841.78541398</v>
+      </c>
+      <c r="Q7">
+        <v>-691.78541398</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08951589767746959</v>
+      </c>
+      <c r="T7">
+        <v>1.008955940925327</v>
+      </c>
+      <c r="U7">
+        <v>0.2458</v>
+      </c>
+      <c r="V7">
+        <v>0.04317415817896239</v>
+      </c>
+      <c r="W7">
+        <v>0.2351877919196111</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.1673416983680712</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09879949238957667</v>
+      </c>
+      <c r="C8">
+        <v>78654.50811989023</v>
+      </c>
+      <c r="D8">
+        <v>75381.16811989024</v>
+      </c>
+      <c r="E8">
+        <v>-9906.34</v>
+      </c>
+      <c r="F8">
+        <v>6651.66</v>
+      </c>
+      <c r="G8">
+        <v>9925</v>
+      </c>
+      <c r="H8">
+        <v>94303</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>378</v>
+      </c>
+      <c r="K8">
+        <v>150</v>
+      </c>
+      <c r="L8">
+        <v>228</v>
+      </c>
+      <c r="M8">
+        <v>1634.978028</v>
+      </c>
+      <c r="N8">
+        <v>-1406.978028</v>
+      </c>
+      <c r="O8">
+        <v>-363.000331224</v>
+      </c>
+      <c r="P8">
+        <v>-1043.977696776</v>
+      </c>
+      <c r="Q8">
+        <v>-893.9776967759999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08998096041871927</v>
+      </c>
+      <c r="T8">
+        <v>1.019689514764958</v>
+      </c>
+      <c r="U8">
+        <v>0.2458</v>
+      </c>
+      <c r="V8">
+        <v>0.03597846514913532</v>
+      </c>
+      <c r="W8">
+        <v>0.2369564932663426</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.1394514153067261</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1007994923895767</v>
+      </c>
+      <c r="C9">
+        <v>74804.7394347902</v>
+      </c>
+      <c r="D9">
+        <v>72640.0094347902</v>
+      </c>
+      <c r="E9">
+        <v>-8797.73</v>
+      </c>
+      <c r="F9">
+        <v>7760.27</v>
+      </c>
+      <c r="G9">
+        <v>9925</v>
+      </c>
+      <c r="H9">
+        <v>94303</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>378</v>
+      </c>
+      <c r="K9">
+        <v>150</v>
+      </c>
+      <c r="L9">
+        <v>228</v>
+      </c>
+      <c r="M9">
+        <v>1907.474366</v>
+      </c>
+      <c r="N9">
+        <v>-1679.474366</v>
+      </c>
+      <c r="O9">
+        <v>-433.304386428</v>
+      </c>
+      <c r="P9">
+        <v>-1246.169979572</v>
+      </c>
+      <c r="Q9">
+        <v>-1096.169979572</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09045602450924313</v>
+      </c>
+      <c r="T9">
+        <v>1.030653918149528</v>
+      </c>
+      <c r="U9">
+        <v>0.2458</v>
+      </c>
+      <c r="V9">
+        <v>0.03083868441354456</v>
+      </c>
+      <c r="W9">
+        <v>0.2382198513711508</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1195297845486223</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1027994923895767</v>
+      </c>
+      <c r="C10">
+        <v>71147.33447576444</v>
+      </c>
+      <c r="D10">
+        <v>70091.21447576444</v>
+      </c>
+      <c r="E10">
+        <v>-7689.119999999999</v>
+      </c>
+      <c r="F10">
+        <v>8868.880000000001</v>
+      </c>
+      <c r="G10">
+        <v>9925</v>
+      </c>
+      <c r="H10">
+        <v>94303</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>378</v>
+      </c>
+      <c r="K10">
+        <v>150</v>
+      </c>
+      <c r="L10">
+        <v>228</v>
+      </c>
+      <c r="M10">
+        <v>2179.970704</v>
+      </c>
+      <c r="N10">
+        <v>-1951.970704</v>
+      </c>
+      <c r="O10">
+        <v>-503.6084416320001</v>
+      </c>
+      <c r="P10">
+        <v>-1448.362262368</v>
+      </c>
+      <c r="Q10">
+        <v>-1298.362262368</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09094141607999577</v>
+      </c>
+      <c r="T10">
+        <v>1.041856678129414</v>
+      </c>
+      <c r="U10">
+        <v>0.2458</v>
+      </c>
+      <c r="V10">
+        <v>0.02698384886185149</v>
+      </c>
+      <c r="W10">
+        <v>0.2391673699497569</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1045885614800446</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1047994923895766</v>
+      </c>
+      <c r="C11">
+        <v>67662.73066168388</v>
+      </c>
+      <c r="D11">
+        <v>67715.22066168388</v>
+      </c>
+      <c r="E11">
+        <v>-6580.51</v>
+      </c>
+      <c r="F11">
+        <v>9977.49</v>
+      </c>
+      <c r="G11">
+        <v>9925</v>
+      </c>
+      <c r="H11">
+        <v>94303</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>378</v>
+      </c>
+      <c r="K11">
+        <v>150</v>
+      </c>
+      <c r="L11">
+        <v>228</v>
+      </c>
+      <c r="M11">
+        <v>2452.467042</v>
+      </c>
+      <c r="N11">
+        <v>-2224.467042</v>
+      </c>
+      <c r="O11">
+        <v>-573.9124968360001</v>
+      </c>
+      <c r="P11">
+        <v>-1650.554545164</v>
+      </c>
+      <c r="Q11">
+        <v>-1500.554545164</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09143747559735835</v>
+      </c>
+      <c r="T11">
+        <v>1.053305652614352</v>
+      </c>
+      <c r="U11">
+        <v>0.2458</v>
+      </c>
+      <c r="V11">
+        <v>0.02398564343275688</v>
+      </c>
+      <c r="W11">
+        <v>0.2399043288442284</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.09296761020448407</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1067994923895767</v>
+      </c>
+      <c r="C12">
+        <v>64333.93101717937</v>
+      </c>
+      <c r="D12">
+        <v>65495.03101717938</v>
+      </c>
+      <c r="E12">
+        <v>-5471.9</v>
+      </c>
+      <c r="F12">
+        <v>11086.1</v>
+      </c>
+      <c r="G12">
+        <v>9925</v>
+      </c>
+      <c r="H12">
+        <v>94303</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>378</v>
+      </c>
+      <c r="K12">
+        <v>150</v>
+      </c>
+      <c r="L12">
+        <v>228</v>
+      </c>
+      <c r="M12">
+        <v>2724.96338</v>
+      </c>
+      <c r="N12">
+        <v>-2496.96338</v>
+      </c>
+      <c r="O12">
+        <v>-644.21655204</v>
+      </c>
+      <c r="P12">
+        <v>-1852.74682796</v>
+      </c>
+      <c r="Q12">
+        <v>-1702.74682796</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09194455865955123</v>
+      </c>
+      <c r="T12">
+        <v>1.065009048754512</v>
+      </c>
+      <c r="U12">
+        <v>0.2458</v>
+      </c>
+      <c r="V12">
+        <v>0.0215870790894812</v>
+      </c>
+      <c r="W12">
+        <v>0.2404938959598055</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.08367084918403567</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1087994923895767</v>
+      </c>
+      <c r="C13">
+        <v>61146.09693035119</v>
+      </c>
+      <c r="D13">
+        <v>63415.80693035118</v>
+      </c>
+      <c r="E13">
+        <v>-4363.289999999999</v>
+      </c>
+      <c r="F13">
+        <v>12194.71</v>
+      </c>
+      <c r="G13">
+        <v>9925</v>
+      </c>
+      <c r="H13">
+        <v>94303</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>378</v>
+      </c>
+      <c r="K13">
+        <v>150</v>
+      </c>
+      <c r="L13">
+        <v>228</v>
+      </c>
+      <c r="M13">
+        <v>2997.459718000001</v>
+      </c>
+      <c r="N13">
+        <v>-2769.459718000001</v>
+      </c>
+      <c r="O13">
+        <v>-714.5206072440002</v>
+      </c>
+      <c r="P13">
+        <v>-2054.939110756</v>
+      </c>
+      <c r="Q13">
+        <v>-1904.939110756</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09246303684673721</v>
+      </c>
+      <c r="T13">
+        <v>1.076975442560742</v>
+      </c>
+      <c r="U13">
+        <v>0.2458</v>
+      </c>
+      <c r="V13">
+        <v>0.01962461735407381</v>
+      </c>
+      <c r="W13">
+        <v>0.2409762690543687</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.07606440834912331</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1107994923895766</v>
+      </c>
+      <c r="C14">
+        <v>58086.21609425707</v>
+      </c>
+      <c r="D14">
+        <v>61464.53609425707</v>
+      </c>
+      <c r="E14">
+        <v>-3254.68</v>
+      </c>
+      <c r="F14">
+        <v>13303.32</v>
+      </c>
+      <c r="G14">
+        <v>9925</v>
+      </c>
+      <c r="H14">
+        <v>94303</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>378</v>
+      </c>
+      <c r="K14">
+        <v>150</v>
+      </c>
+      <c r="L14">
+        <v>228</v>
+      </c>
+      <c r="M14">
+        <v>3269.956056</v>
+      </c>
+      <c r="N14">
+        <v>-3041.956056</v>
+      </c>
+      <c r="O14">
+        <v>-784.824662448</v>
+      </c>
+      <c r="P14">
+        <v>-2257.131393552</v>
+      </c>
+      <c r="Q14">
+        <v>-2107.131393552</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09299329862908648</v>
+      </c>
+      <c r="T14">
+        <v>1.089213799862569</v>
+      </c>
+      <c r="U14">
+        <v>0.2458</v>
+      </c>
+      <c r="V14">
+        <v>0.01798923257456766</v>
+      </c>
+      <c r="W14">
+        <v>0.2413782466331713</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.06972570765336306</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1127994923895766</v>
+      </c>
+      <c r="C15">
+        <v>55142.82992201791</v>
+      </c>
+      <c r="D15">
+        <v>59629.75992201791</v>
+      </c>
+      <c r="E15">
+        <v>-2146.07</v>
+      </c>
+      <c r="F15">
+        <v>14411.93</v>
+      </c>
+      <c r="G15">
+        <v>9925</v>
+      </c>
+      <c r="H15">
+        <v>94303</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>378</v>
+      </c>
+      <c r="K15">
+        <v>150</v>
+      </c>
+      <c r="L15">
+        <v>228</v>
+      </c>
+      <c r="M15">
+        <v>3542.452394</v>
+      </c>
+      <c r="N15">
+        <v>-3314.452394</v>
+      </c>
+      <c r="O15">
+        <v>-855.1287176520001</v>
+      </c>
+      <c r="P15">
+        <v>-2459.323676348</v>
+      </c>
+      <c r="Q15">
+        <v>-2309.323676348</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09353575033746678</v>
+      </c>
+      <c r="T15">
+        <v>1.101733498711564</v>
+      </c>
+      <c r="U15">
+        <v>0.2458</v>
+      </c>
+      <c r="V15">
+        <v>0.01660544545344707</v>
+      </c>
+      <c r="W15">
+        <v>0.2417183815075427</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.06436219168002744</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1147994923895767</v>
+      </c>
+      <c r="C16">
+        <v>52305.80836834026</v>
+      </c>
+      <c r="D16">
+        <v>57901.34836834027</v>
+      </c>
+      <c r="E16">
+        <v>-1037.459999999999</v>
+      </c>
+      <c r="F16">
+        <v>15520.54</v>
+      </c>
+      <c r="G16">
+        <v>9925</v>
+      </c>
+      <c r="H16">
+        <v>94303</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>378</v>
+      </c>
+      <c r="K16">
+        <v>150</v>
+      </c>
+      <c r="L16">
+        <v>228</v>
+      </c>
+      <c r="M16">
+        <v>3814.948732</v>
+      </c>
+      <c r="N16">
+        <v>-3586.948732</v>
+      </c>
+      <c r="O16">
+        <v>-925.4327728560002</v>
+      </c>
+      <c r="P16">
+        <v>-2661.515959144</v>
+      </c>
+      <c r="Q16">
+        <v>-2511.515959144</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09409081720185594</v>
+      </c>
+      <c r="T16">
+        <v>1.114544353347745</v>
+      </c>
+      <c r="U16">
+        <v>0.2458</v>
+      </c>
+      <c r="V16">
+        <v>0.01541934220677228</v>
+      </c>
+      <c r="W16">
+        <v>0.2420099256855754</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.05976489227431114</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1167994923895767</v>
+      </c>
+      <c r="C17">
+        <v>49566.1628096455</v>
+      </c>
+      <c r="D17">
+        <v>56270.31280964548</v>
+      </c>
+      <c r="E17">
+        <v>71.14999999999782</v>
+      </c>
+      <c r="F17">
+        <v>16629.15</v>
+      </c>
+      <c r="G17">
+        <v>9925</v>
+      </c>
+      <c r="H17">
+        <v>94303</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>378</v>
+      </c>
+      <c r="K17">
+        <v>150</v>
+      </c>
+      <c r="L17">
+        <v>228</v>
+      </c>
+      <c r="M17">
+        <v>4087.44507</v>
+      </c>
+      <c r="N17">
+        <v>-3859.44507</v>
+      </c>
+      <c r="O17">
+        <v>-995.73682806</v>
+      </c>
+      <c r="P17">
+        <v>-2863.70824194</v>
+      </c>
+      <c r="Q17">
+        <v>-2713.70824194</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09465894446305426</v>
+      </c>
+      <c r="T17">
+        <v>1.127656639857718</v>
+      </c>
+      <c r="U17">
+        <v>0.2458</v>
+      </c>
+      <c r="V17">
+        <v>0.01439138605965413</v>
+      </c>
+      <c r="W17">
+        <v>0.242262597306537</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.05578056612269044</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1187994923895767</v>
+      </c>
+      <c r="C18">
+        <v>46915.88968384324</v>
+      </c>
+      <c r="D18">
+        <v>54728.64968384324</v>
+      </c>
+      <c r="E18">
+        <v>1179.760000000002</v>
+      </c>
+      <c r="F18">
+        <v>17737.76</v>
+      </c>
+      <c r="G18">
+        <v>9925</v>
+      </c>
+      <c r="H18">
+        <v>94303</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>378</v>
+      </c>
+      <c r="K18">
+        <v>150</v>
+      </c>
+      <c r="L18">
+        <v>228</v>
+      </c>
+      <c r="M18">
+        <v>4359.941408000001</v>
+      </c>
+      <c r="N18">
+        <v>-4131.941408000001</v>
+      </c>
+      <c r="O18">
+        <v>-1066.040883264</v>
+      </c>
+      <c r="P18">
+        <v>-3065.900524736</v>
+      </c>
+      <c r="Q18">
+        <v>-2915.900524736</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09524059856380489</v>
+      </c>
+      <c r="T18">
+        <v>1.141081123665548</v>
+      </c>
+      <c r="U18">
+        <v>0.2458</v>
+      </c>
+      <c r="V18">
+        <v>0.01349192443092575</v>
+      </c>
+      <c r="W18">
+        <v>0.2424836849748785</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.05229428074002229</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1207994923895767</v>
+      </c>
+      <c r="C19">
+        <v>44347.83914791104</v>
+      </c>
+      <c r="D19">
+        <v>53269.20914791105</v>
+      </c>
+      <c r="E19">
+        <v>2288.370000000003</v>
+      </c>
+      <c r="F19">
+        <v>18846.37</v>
+      </c>
+      <c r="G19">
+        <v>9925</v>
+      </c>
+      <c r="H19">
+        <v>94303</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>378</v>
+      </c>
+      <c r="K19">
+        <v>150</v>
+      </c>
+      <c r="L19">
+        <v>228</v>
+      </c>
+      <c r="M19">
+        <v>4632.437746000001</v>
+      </c>
+      <c r="N19">
+        <v>-4404.437746000001</v>
+      </c>
+      <c r="O19">
+        <v>-1136.344938468</v>
+      </c>
+      <c r="P19">
+        <v>-3268.092807532001</v>
+      </c>
+      <c r="Q19">
+        <v>-3118.092807532001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09583626842601942</v>
+      </c>
+      <c r="T19">
+        <v>1.154829089010917</v>
+      </c>
+      <c r="U19">
+        <v>0.2458</v>
+      </c>
+      <c r="V19">
+        <v>0.01269828181734188</v>
+      </c>
+      <c r="W19">
+        <v>0.2426787623292974</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.04921814657884449</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1227994923895767</v>
+      </c>
+      <c r="C20">
+        <v>41855.60420455695</v>
+      </c>
+      <c r="D20">
+        <v>51885.58420455694</v>
+      </c>
+      <c r="E20">
+        <v>3396.98</v>
+      </c>
+      <c r="F20">
+        <v>19954.98</v>
+      </c>
+      <c r="G20">
+        <v>9925</v>
+      </c>
+      <c r="H20">
+        <v>94303</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>378</v>
+      </c>
+      <c r="K20">
+        <v>150</v>
+      </c>
+      <c r="L20">
+        <v>228</v>
+      </c>
+      <c r="M20">
+        <v>4904.934084</v>
+      </c>
+      <c r="N20">
+        <v>-4676.934084</v>
+      </c>
+      <c r="O20">
+        <v>-1206.648993672</v>
+      </c>
+      <c r="P20">
+        <v>-3470.285090328</v>
+      </c>
+      <c r="Q20">
+        <v>-3320.285090328</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09644646682145866</v>
+      </c>
+      <c r="T20">
+        <v>1.16891237058422</v>
+      </c>
+      <c r="U20">
+        <v>0.2458</v>
+      </c>
+      <c r="V20">
+        <v>0.01199282171637844</v>
+      </c>
+      <c r="W20">
+        <v>0.2428521644221142</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.04648380510224204</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1247994923895767</v>
+      </c>
+      <c r="C21">
+        <v>39433.42667051028</v>
+      </c>
+      <c r="D21">
+        <v>50572.01667051028</v>
+      </c>
+      <c r="E21">
+        <v>4505.59</v>
+      </c>
+      <c r="F21">
+        <v>21063.59</v>
+      </c>
+      <c r="G21">
+        <v>9925</v>
+      </c>
+      <c r="H21">
+        <v>94303</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>378</v>
+      </c>
+      <c r="K21">
+        <v>150</v>
+      </c>
+      <c r="L21">
+        <v>228</v>
+      </c>
+      <c r="M21">
+        <v>5177.430422</v>
+      </c>
+      <c r="N21">
+        <v>-4949.430422</v>
+      </c>
+      <c r="O21">
+        <v>-1276.953048876</v>
+      </c>
+      <c r="P21">
+        <v>-3672.477373124</v>
+      </c>
+      <c r="Q21">
+        <v>-3522.477373124</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09707173184394581</v>
+      </c>
+      <c r="T21">
+        <v>1.183343387505013</v>
+      </c>
+      <c r="U21">
+        <v>0.2458</v>
+      </c>
+      <c r="V21">
+        <v>0.01136162057341115</v>
+      </c>
+      <c r="W21">
+        <v>0.2430073136630556</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.04403728904422932</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1267994923895767</v>
+      </c>
+      <c r="C22">
+        <v>37076.11707552325</v>
+      </c>
+      <c r="D22">
+        <v>49323.31707552324</v>
+      </c>
+      <c r="E22">
+        <v>5614.200000000001</v>
+      </c>
+      <c r="F22">
+        <v>22172.2</v>
+      </c>
+      <c r="G22">
+        <v>9925</v>
+      </c>
+      <c r="H22">
+        <v>94303</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>378</v>
+      </c>
+      <c r="K22">
+        <v>150</v>
+      </c>
+      <c r="L22">
+        <v>228</v>
+      </c>
+      <c r="M22">
+        <v>5449.92676</v>
+      </c>
+      <c r="N22">
+        <v>-5221.92676</v>
+      </c>
+      <c r="O22">
+        <v>-1347.25710408</v>
+      </c>
+      <c r="P22">
+        <v>-3874.66965592</v>
+      </c>
+      <c r="Q22">
+        <v>-3724.66965592</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09771262849199513</v>
+      </c>
+      <c r="T22">
+        <v>1.198135179848826</v>
+      </c>
+      <c r="U22">
+        <v>0.2458</v>
+      </c>
+      <c r="V22">
+        <v>0.0107935395447406</v>
+      </c>
+      <c r="W22">
+        <v>0.2431469479799028</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.04183542459201783</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1287994923895767</v>
+      </c>
+      <c r="C23">
+        <v>34778.98614231047</v>
+      </c>
+      <c r="D23">
+        <v>48134.79614231046</v>
+      </c>
+      <c r="E23">
+        <v>6722.809999999998</v>
+      </c>
+      <c r="F23">
+        <v>23280.81</v>
+      </c>
+      <c r="G23">
+        <v>9925</v>
+      </c>
+      <c r="H23">
+        <v>94303</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>378</v>
+      </c>
+      <c r="K23">
+        <v>150</v>
+      </c>
+      <c r="L23">
+        <v>228</v>
+      </c>
+      <c r="M23">
+        <v>5722.423098</v>
+      </c>
+      <c r="N23">
+        <v>-5494.423098</v>
+      </c>
+      <c r="O23">
+        <v>-1417.561159284</v>
+      </c>
+      <c r="P23">
+        <v>-4076.861938716</v>
+      </c>
+      <c r="Q23">
+        <v>-3926.861938716</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09836975037164064</v>
+      </c>
+      <c r="T23">
+        <v>1.213301447948178</v>
+      </c>
+      <c r="U23">
+        <v>0.2458</v>
+      </c>
+      <c r="V23">
+        <v>0.01027956147118152</v>
+      </c>
+      <c r="W23">
+        <v>0.2432732837903836</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.03984326151620743</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1307994923895767</v>
+      </c>
+      <c r="C24">
+        <v>32537.78593996678</v>
+      </c>
+      <c r="D24">
+        <v>47002.20593996678</v>
+      </c>
+      <c r="E24">
+        <v>7831.420000000002</v>
+      </c>
+      <c r="F24">
+        <v>24389.42</v>
+      </c>
+      <c r="G24">
+        <v>9925</v>
+      </c>
+      <c r="H24">
+        <v>94303</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>378</v>
+      </c>
+      <c r="K24">
+        <v>150</v>
+      </c>
+      <c r="L24">
+        <v>228</v>
+      </c>
+      <c r="M24">
+        <v>5994.919436000001</v>
+      </c>
+      <c r="N24">
+        <v>-5766.919436000001</v>
+      </c>
+      <c r="O24">
+        <v>-1487.865214488</v>
+      </c>
+      <c r="P24">
+        <v>-4279.054221512</v>
+      </c>
+      <c r="Q24">
+        <v>-4129.054221512</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09904372153025143</v>
+      </c>
+      <c r="T24">
+        <v>1.228856594716744</v>
+      </c>
+      <c r="U24">
+        <v>0.2458</v>
+      </c>
+      <c r="V24">
+        <v>0.009812308677036906</v>
+      </c>
+      <c r="W24">
+        <v>0.2433881345271844</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.03803220417456166</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1327994923895767</v>
+      </c>
+      <c r="C25">
+        <v>30348.65915420222</v>
+      </c>
+      <c r="D25">
+        <v>45921.68915420222</v>
+      </c>
+      <c r="E25">
+        <v>8940.030000000002</v>
+      </c>
+      <c r="F25">
+        <v>25498.03</v>
+      </c>
+      <c r="G25">
+        <v>9925</v>
+      </c>
+      <c r="H25">
+        <v>94303</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>378</v>
+      </c>
+      <c r="K25">
+        <v>150</v>
+      </c>
+      <c r="L25">
+        <v>228</v>
+      </c>
+      <c r="M25">
+        <v>6267.415774000001</v>
+      </c>
+      <c r="N25">
+        <v>-6039.415774000001</v>
+      </c>
+      <c r="O25">
+        <v>-1558.169269692</v>
+      </c>
+      <c r="P25">
+        <v>-4481.246504308001</v>
+      </c>
+      <c r="Q25">
+        <v>-4331.246504308001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.0997351984332417</v>
+      </c>
+      <c r="T25">
+        <v>1.244815771271507</v>
+      </c>
+      <c r="U25">
+        <v>0.2458</v>
+      </c>
+      <c r="V25">
+        <v>0.009385686560643997</v>
+      </c>
+      <c r="W25">
+        <v>0.2434929982433937</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.03637863008001552</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1347994923895767</v>
+      </c>
+      <c r="C26">
+        <v>28208.09519758436</v>
+      </c>
+      <c r="D26">
+        <v>44889.73519758436</v>
+      </c>
+      <c r="E26">
+        <v>10048.64</v>
+      </c>
+      <c r="F26">
+        <v>26606.64</v>
+      </c>
+      <c r="G26">
+        <v>9925</v>
+      </c>
+      <c r="H26">
+        <v>94303</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>378</v>
+      </c>
+      <c r="K26">
+        <v>150</v>
+      </c>
+      <c r="L26">
+        <v>228</v>
+      </c>
+      <c r="M26">
+        <v>6539.912112</v>
+      </c>
+      <c r="N26">
+        <v>-6311.912112</v>
+      </c>
+      <c r="O26">
+        <v>-1628.473324896</v>
+      </c>
+      <c r="P26">
+        <v>-4683.438787104</v>
+      </c>
+      <c r="Q26">
+        <v>-4533.438787104</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.100444872096837</v>
+      </c>
+      <c r="T26">
+        <v>1.261194926156659</v>
+      </c>
+      <c r="U26">
+        <v>0.2458</v>
+      </c>
+      <c r="V26">
+        <v>0.008994616287283831</v>
+      </c>
+      <c r="W26">
+        <v>0.2435891233165857</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.03486285382668153</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1367994923895766</v>
+      </c>
+      <c r="C27">
+        <v>26112.89210747334</v>
+      </c>
+      <c r="D27">
+        <v>43903.14210747334</v>
+      </c>
+      <c r="E27">
+        <v>11157.25</v>
+      </c>
+      <c r="F27">
+        <v>27715.25</v>
+      </c>
+      <c r="G27">
+        <v>9925</v>
+      </c>
+      <c r="H27">
+        <v>94303</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>378</v>
+      </c>
+      <c r="K27">
+        <v>150</v>
+      </c>
+      <c r="L27">
+        <v>228</v>
+      </c>
+      <c r="M27">
+        <v>6812.408450000001</v>
+      </c>
+      <c r="N27">
+        <v>-6584.408450000001</v>
+      </c>
+      <c r="O27">
+        <v>-1698.7773801</v>
+      </c>
+      <c r="P27">
+        <v>-4885.631069900001</v>
+      </c>
+      <c r="Q27">
+        <v>-4735.631069900001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1011734703914615</v>
+      </c>
+      <c r="T27">
+        <v>1.278010858505414</v>
+      </c>
+      <c r="U27">
+        <v>0.2458</v>
+      </c>
+      <c r="V27">
+        <v>0.008634831635792478</v>
+      </c>
+      <c r="W27">
+        <v>0.2436775583839222</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.03346833967361429</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1387994923895767</v>
+      </c>
+      <c r="C28">
+        <v>24060.12336037904</v>
+      </c>
+      <c r="D28">
+        <v>42958.98336037904</v>
+      </c>
+      <c r="E28">
+        <v>12265.86</v>
+      </c>
+      <c r="F28">
+        <v>28823.86</v>
+      </c>
+      <c r="G28">
+        <v>9925</v>
+      </c>
+      <c r="H28">
+        <v>94303</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>378</v>
+      </c>
+      <c r="K28">
+        <v>150</v>
+      </c>
+      <c r="L28">
+        <v>228</v>
+      </c>
+      <c r="M28">
+        <v>7084.904788000001</v>
+      </c>
+      <c r="N28">
+        <v>-6856.904788000001</v>
+      </c>
+      <c r="O28">
+        <v>-1769.081435304</v>
+      </c>
+      <c r="P28">
+        <v>-5087.823352696</v>
+      </c>
+      <c r="Q28">
+        <v>-4937.823352696</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1019217605318866</v>
+      </c>
+      <c r="T28">
+        <v>1.295281275512244</v>
+      </c>
+      <c r="U28">
+        <v>0.2458</v>
+      </c>
+      <c r="V28">
+        <v>0.008302722726723536</v>
+      </c>
+      <c r="W28">
+        <v>0.2437591907537714</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.03218109584001372</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1407994923895767</v>
+      </c>
+      <c r="C29">
+        <v>22047.10887821166</v>
+      </c>
+      <c r="D29">
+        <v>42054.57887821167</v>
+      </c>
+      <c r="E29">
+        <v>13374.47</v>
+      </c>
+      <c r="F29">
+        <v>29932.47</v>
+      </c>
+      <c r="G29">
+        <v>9925</v>
+      </c>
+      <c r="H29">
+        <v>94303</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>378</v>
+      </c>
+      <c r="K29">
+        <v>150</v>
+      </c>
+      <c r="L29">
+        <v>228</v>
+      </c>
+      <c r="M29">
+        <v>7357.401126000001</v>
+      </c>
+      <c r="N29">
+        <v>-7129.401126000001</v>
+      </c>
+      <c r="O29">
+        <v>-1839.385490508</v>
+      </c>
+      <c r="P29">
+        <v>-5290.015635492</v>
+      </c>
+      <c r="Q29">
+        <v>-5140.015635492</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1026905517720495</v>
+      </c>
+      <c r="T29">
+        <v>1.31302485462885</v>
+      </c>
+      <c r="U29">
+        <v>0.2458</v>
+      </c>
+      <c r="V29">
+        <v>0.007995214477585628</v>
+      </c>
+      <c r="W29">
+        <v>0.2438347762814095</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.03098920340149469</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1427994923895767</v>
+      </c>
+      <c r="C30">
+        <v>20071.3896214063</v>
+      </c>
+      <c r="D30">
+        <v>41187.4696214063</v>
+      </c>
+      <c r="E30">
+        <v>14483.08</v>
+      </c>
+      <c r="F30">
+        <v>31041.08</v>
+      </c>
+      <c r="G30">
+        <v>9925</v>
+      </c>
+      <c r="H30">
+        <v>94303</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>378</v>
+      </c>
+      <c r="K30">
+        <v>150</v>
+      </c>
+      <c r="L30">
+        <v>228</v>
+      </c>
+      <c r="M30">
+        <v>7629.897464000001</v>
+      </c>
+      <c r="N30">
+        <v>-7401.897464000001</v>
+      </c>
+      <c r="O30">
+        <v>-1909.689545712</v>
+      </c>
+      <c r="P30">
+        <v>-5492.207918288001</v>
+      </c>
+      <c r="Q30">
+        <v>-5342.207918288001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.103480698324439</v>
+      </c>
+      <c r="T30">
+        <v>1.33126131094314</v>
+      </c>
+      <c r="U30">
+        <v>0.2458</v>
+      </c>
+      <c r="V30">
+        <v>0.00770967110338614</v>
+      </c>
+      <c r="W30">
+        <v>0.2439049628427877</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.02988244613715563</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1447994923895767</v>
+      </c>
+      <c r="C31">
+        <v>18130.70526168478</v>
+      </c>
+      <c r="D31">
+        <v>40355.39526168478</v>
+      </c>
+      <c r="E31">
+        <v>15591.69</v>
+      </c>
+      <c r="F31">
+        <v>32149.69</v>
+      </c>
+      <c r="G31">
+        <v>9925</v>
+      </c>
+      <c r="H31">
+        <v>94303</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>378</v>
+      </c>
+      <c r="K31">
+        <v>150</v>
+      </c>
+      <c r="L31">
+        <v>228</v>
+      </c>
+      <c r="M31">
+        <v>7902.393802000001</v>
+      </c>
+      <c r="N31">
+        <v>-7674.393802000001</v>
+      </c>
+      <c r="O31">
+        <v>-1979.993600916</v>
+      </c>
+      <c r="P31">
+        <v>-5694.400201084</v>
+      </c>
+      <c r="Q31">
+        <v>-5544.400201084</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1042931025261917</v>
+      </c>
+      <c r="T31">
+        <v>1.350011470252198</v>
+      </c>
+      <c r="U31">
+        <v>0.2458</v>
+      </c>
+      <c r="V31">
+        <v>0.007443820375683171</v>
+      </c>
+      <c r="W31">
+        <v>0.2439703089516571</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.02885201696001227</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1467994923895767</v>
+      </c>
+      <c r="C32">
+        <v>16222.97450757198</v>
+      </c>
+      <c r="D32">
+        <v>39556.27450757197</v>
+      </c>
+      <c r="E32">
+        <v>16700.3</v>
+      </c>
+      <c r="F32">
+        <v>33258.3</v>
+      </c>
+      <c r="G32">
+        <v>9925</v>
+      </c>
+      <c r="H32">
+        <v>94303</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>378</v>
+      </c>
+      <c r="K32">
+        <v>150</v>
+      </c>
+      <c r="L32">
+        <v>228</v>
+      </c>
+      <c r="M32">
+        <v>8174.89014</v>
+      </c>
+      <c r="N32">
+        <v>-7946.89014</v>
+      </c>
+      <c r="O32">
+        <v>-2050.29765612</v>
+      </c>
+      <c r="P32">
+        <v>-5896.59248388</v>
+      </c>
+      <c r="Q32">
+        <v>-5746.59248388</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1051287182765659</v>
+      </c>
+      <c r="T32">
+        <v>1.369297348398658</v>
+      </c>
+      <c r="U32">
+        <v>0.2458</v>
+      </c>
+      <c r="V32">
+        <v>0.007195693029827066</v>
+      </c>
+      <c r="W32">
+        <v>0.2440312986532685</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.02789028306134522</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1487994923895767</v>
+      </c>
+      <c r="C33">
+        <v>14346.27772209623</v>
+      </c>
+      <c r="D33">
+        <v>38788.18772209623</v>
+      </c>
+      <c r="E33">
+        <v>17808.91</v>
+      </c>
+      <c r="F33">
+        <v>34366.91</v>
+      </c>
+      <c r="G33">
+        <v>9925</v>
+      </c>
+      <c r="H33">
+        <v>94303</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>378</v>
+      </c>
+      <c r="K33">
+        <v>150</v>
+      </c>
+      <c r="L33">
+        <v>228</v>
+      </c>
+      <c r="M33">
+        <v>8447.386478</v>
+      </c>
+      <c r="N33">
+        <v>-8219.386478</v>
+      </c>
+      <c r="O33">
+        <v>-2120.601711324</v>
+      </c>
+      <c r="P33">
+        <v>-6098.784766676001</v>
+      </c>
+      <c r="Q33">
+        <v>-5948.784766676001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1059885547733277</v>
+      </c>
+      <c r="T33">
+        <v>1.389142237505885</v>
+      </c>
+      <c r="U33">
+        <v>0.2458</v>
+      </c>
+      <c r="V33">
+        <v>0.006963573899832643</v>
+      </c>
+      <c r="W33">
+        <v>0.2440883535354212</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.02699059651097924</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1507994923895767</v>
+      </c>
+      <c r="C34">
+        <v>12498.84152704794</v>
+      </c>
+      <c r="D34">
+        <v>38049.36152704794</v>
+      </c>
+      <c r="E34">
+        <v>18917.52</v>
+      </c>
+      <c r="F34">
+        <v>35475.52</v>
+      </c>
+      <c r="G34">
+        <v>9925</v>
+      </c>
+      <c r="H34">
+        <v>94303</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>378</v>
+      </c>
+      <c r="K34">
+        <v>150</v>
+      </c>
+      <c r="L34">
+        <v>228</v>
+      </c>
+      <c r="M34">
+        <v>8719.882816000001</v>
+      </c>
+      <c r="N34">
+        <v>-8491.882816000001</v>
+      </c>
+      <c r="O34">
+        <v>-2190.905766528</v>
+      </c>
+      <c r="P34">
+        <v>-6300.977049472001</v>
+      </c>
+      <c r="Q34">
+        <v>-6150.977049472001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1068736805788178</v>
+      </c>
+      <c r="T34">
+        <v>1.409570799822148</v>
+      </c>
+      <c r="U34">
+        <v>0.2458</v>
+      </c>
+      <c r="V34">
+        <v>0.006745962215462874</v>
+      </c>
+      <c r="W34">
+        <v>0.2441418424874393</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.02614714037001109</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1527994923895767</v>
+      </c>
+      <c r="C35">
+        <v>10679.02513387154</v>
+      </c>
+      <c r="D35">
+        <v>37338.15513387154</v>
+      </c>
+      <c r="E35">
+        <v>20026.13</v>
+      </c>
+      <c r="F35">
+        <v>36584.13</v>
+      </c>
+      <c r="G35">
+        <v>9925</v>
+      </c>
+      <c r="H35">
+        <v>94303</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>378</v>
+      </c>
+      <c r="K35">
+        <v>150</v>
+      </c>
+      <c r="L35">
+        <v>228</v>
+      </c>
+      <c r="M35">
+        <v>8992.379154000002</v>
+      </c>
+      <c r="N35">
+        <v>-8764.379154000002</v>
+      </c>
+      <c r="O35">
+        <v>-2261.209821732</v>
+      </c>
+      <c r="P35">
+        <v>-6503.169332268002</v>
+      </c>
+      <c r="Q35">
+        <v>-6353.169332268002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1077852280501434</v>
+      </c>
+      <c r="T35">
+        <v>1.430609169968747</v>
+      </c>
+      <c r="U35">
+        <v>0.2458</v>
+      </c>
+      <c r="V35">
+        <v>0.006541539118024603</v>
+      </c>
+      <c r="W35">
+        <v>0.2441920896847896</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.02535480278304114</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1547994923895767</v>
+      </c>
+      <c r="C36">
+        <v>8885.30817942039</v>
+      </c>
+      <c r="D36">
+        <v>36653.0481794204</v>
+      </c>
+      <c r="E36">
+        <v>21134.74000000001</v>
+      </c>
+      <c r="F36">
+        <v>37692.74000000001</v>
+      </c>
+      <c r="G36">
+        <v>9925</v>
+      </c>
+      <c r="H36">
+        <v>94303</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>378</v>
+      </c>
+      <c r="K36">
+        <v>150</v>
+      </c>
+      <c r="L36">
+        <v>228</v>
+      </c>
+      <c r="M36">
+        <v>9264.875492000003</v>
+      </c>
+      <c r="N36">
+        <v>-9036.875492000003</v>
+      </c>
+      <c r="O36">
+        <v>-2331.513876936001</v>
+      </c>
+      <c r="P36">
+        <v>-6705.361615064002</v>
+      </c>
+      <c r="Q36">
+        <v>-6555.361615064002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1087243981721153</v>
+      </c>
+      <c r="T36">
+        <v>1.452285066483425</v>
+      </c>
+      <c r="U36">
+        <v>0.2458</v>
+      </c>
+      <c r="V36">
+        <v>0.006349140908670938</v>
+      </c>
+      <c r="W36">
+        <v>0.2442393811646487</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.02460907328942219</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1567994923895767</v>
+      </c>
+      <c r="C37">
+        <v>7116.279876771259</v>
+      </c>
+      <c r="D37">
+        <v>35992.62987677127</v>
+      </c>
+      <c r="E37">
+        <v>22243.35000000001</v>
+      </c>
+      <c r="F37">
+        <v>38801.35000000001</v>
+      </c>
+      <c r="G37">
+        <v>9925</v>
+      </c>
+      <c r="H37">
+        <v>94303</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>378</v>
+      </c>
+      <c r="K37">
+        <v>150</v>
+      </c>
+      <c r="L37">
+        <v>228</v>
+      </c>
+      <c r="M37">
+        <v>9537.371830000002</v>
+      </c>
+      <c r="N37">
+        <v>-9309.371830000002</v>
+      </c>
+      <c r="O37">
+        <v>-2401.817932140001</v>
+      </c>
+      <c r="P37">
+        <v>-6907.553897860002</v>
+      </c>
+      <c r="Q37">
+        <v>-6757.553897860002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1096924658363017</v>
+      </c>
+      <c r="T37">
+        <v>1.474627913660093</v>
+      </c>
+      <c r="U37">
+        <v>0.2458</v>
+      </c>
+      <c r="V37">
+        <v>0.006167736882708912</v>
+      </c>
+      <c r="W37">
+        <v>0.2442839702742302</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.02390595690972441</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1587994923895767</v>
+      </c>
+      <c r="C38">
+        <v>5370.629318169747</v>
+      </c>
+      <c r="D38">
+        <v>35355.58931816975</v>
+      </c>
+      <c r="E38">
+        <v>23351.96</v>
+      </c>
+      <c r="F38">
+        <v>39909.96</v>
+      </c>
+      <c r="G38">
+        <v>9925</v>
+      </c>
+      <c r="H38">
+        <v>94303</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>378</v>
+      </c>
+      <c r="K38">
+        <v>150</v>
+      </c>
+      <c r="L38">
+        <v>228</v>
+      </c>
+      <c r="M38">
+        <v>9809.868168000001</v>
+      </c>
+      <c r="N38">
+        <v>-9581.868168000001</v>
+      </c>
+      <c r="O38">
+        <v>-2472.121987344</v>
+      </c>
+      <c r="P38">
+        <v>-7109.746180656</v>
+      </c>
+      <c r="Q38">
+        <v>-6959.746180656</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1106907856149939</v>
+      </c>
+      <c r="T38">
+        <v>1.497668974811032</v>
+      </c>
+      <c r="U38">
+        <v>0.2458</v>
+      </c>
+      <c r="V38">
+        <v>0.00599641085818922</v>
+      </c>
+      <c r="W38">
+        <v>0.2443260822110571</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.02324190255112102</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1607994923895767</v>
+      </c>
+      <c r="C39">
+        <v>3647.136789846962</v>
+      </c>
+      <c r="D39">
+        <v>34740.70678984696</v>
+      </c>
+      <c r="E39">
+        <v>24460.57</v>
+      </c>
+      <c r="F39">
+        <v>41018.57</v>
+      </c>
+      <c r="G39">
+        <v>9925</v>
+      </c>
+      <c r="H39">
+        <v>94303</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>378</v>
+      </c>
+      <c r="K39">
+        <v>150</v>
+      </c>
+      <c r="L39">
+        <v>228</v>
+      </c>
+      <c r="M39">
+        <v>10082.364506</v>
+      </c>
+      <c r="N39">
+        <v>-9854.364506</v>
+      </c>
+      <c r="O39">
+        <v>-2542.426042548</v>
+      </c>
+      <c r="P39">
+        <v>-7311.938463451999</v>
+      </c>
+      <c r="Q39">
+        <v>-7161.938463451999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1117207980850732</v>
+      </c>
+      <c r="T39">
+        <v>1.521441498220731</v>
+      </c>
+      <c r="U39">
+        <v>0.2458</v>
+      </c>
+      <c r="V39">
+        <v>0.005834345699859782</v>
+      </c>
+      <c r="W39">
+        <v>0.2443659178269745</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.02261374302271235</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1627994923895767</v>
+      </c>
+      <c r="C40">
+        <v>1944.66597762789</v>
+      </c>
+      <c r="D40">
+        <v>34146.84597762789</v>
+      </c>
+      <c r="E40">
+        <v>25569.18</v>
+      </c>
+      <c r="F40">
+        <v>42127.18</v>
+      </c>
+      <c r="G40">
+        <v>9925</v>
+      </c>
+      <c r="H40">
+        <v>94303</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>378</v>
+      </c>
+      <c r="K40">
+        <v>150</v>
+      </c>
+      <c r="L40">
+        <v>228</v>
+      </c>
+      <c r="M40">
+        <v>10354.860844</v>
+      </c>
+      <c r="N40">
+        <v>-10126.860844</v>
+      </c>
+      <c r="O40">
+        <v>-2612.730097752</v>
+      </c>
+      <c r="P40">
+        <v>-7514.130746248</v>
+      </c>
+      <c r="Q40">
+        <v>-7364.130746248</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1127840367638647</v>
+      </c>
+      <c r="T40">
+        <v>1.545980877224291</v>
+      </c>
+      <c r="U40">
+        <v>0.2458</v>
+      </c>
+      <c r="V40">
+        <v>0.005680810286705577</v>
+      </c>
+      <c r="W40">
+        <v>0.2444036568315278</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.02201864452211466</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1647994923895767</v>
+      </c>
+      <c r="C41">
+        <v>262.1569585322577</v>
+      </c>
+      <c r="D41">
+        <v>33572.94695853226</v>
+      </c>
+      <c r="E41">
+        <v>26677.79</v>
+      </c>
+      <c r="F41">
+        <v>43235.79</v>
+      </c>
+      <c r="G41">
+        <v>9925</v>
+      </c>
+      <c r="H41">
+        <v>94303</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>378</v>
+      </c>
+      <c r="K41">
+        <v>150</v>
+      </c>
+      <c r="L41">
+        <v>228</v>
+      </c>
+      <c r="M41">
+        <v>10627.357182</v>
+      </c>
+      <c r="N41">
+        <v>-10399.357182</v>
+      </c>
+      <c r="O41">
+        <v>-2683.034152956001</v>
+      </c>
+      <c r="P41">
+        <v>-7716.323029044001</v>
+      </c>
+      <c r="Q41">
+        <v>-7566.323029044001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1138821357272067</v>
+      </c>
+      <c r="T41">
+        <v>1.571324826031247</v>
+      </c>
+      <c r="U41">
+        <v>0.2458</v>
+      </c>
+      <c r="V41">
+        <v>0.005535148484482357</v>
+      </c>
+      <c r="W41">
+        <v>0.2444394605025142</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.02145406389334248</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1667994923895767</v>
+      </c>
+      <c r="C42">
+        <v>-1401.380112573774</v>
+      </c>
+      <c r="D42">
+        <v>33018.01988742623</v>
+      </c>
+      <c r="E42">
+        <v>27786.4</v>
+      </c>
+      <c r="F42">
+        <v>44344.4</v>
+      </c>
+      <c r="G42">
+        <v>9925</v>
+      </c>
+      <c r="H42">
+        <v>94303</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>378</v>
+      </c>
+      <c r="K42">
+        <v>150</v>
+      </c>
+      <c r="L42">
+        <v>228</v>
+      </c>
+      <c r="M42">
+        <v>10899.85352</v>
+      </c>
+      <c r="N42">
+        <v>-10671.85352</v>
+      </c>
+      <c r="O42">
+        <v>-2753.33820816</v>
+      </c>
+      <c r="P42">
+        <v>-7918.51531184</v>
+      </c>
+      <c r="Q42">
+        <v>-7768.51531184</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1150168379893269</v>
+      </c>
+      <c r="T42">
+        <v>1.597513573131768</v>
+      </c>
+      <c r="U42">
+        <v>0.2458</v>
+      </c>
+      <c r="V42">
+        <v>0.005396769772370299</v>
+      </c>
+      <c r="W42">
+        <v>0.2444734739899514</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.02091771229600892</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1687994923895766</v>
+      </c>
+      <c r="C43">
+        <v>-3046.870700387059</v>
+      </c>
+      <c r="D43">
+        <v>32481.13929961294</v>
+      </c>
+      <c r="E43">
+        <v>28895.01</v>
+      </c>
+      <c r="F43">
+        <v>45453.01</v>
+      </c>
+      <c r="G43">
+        <v>9925</v>
+      </c>
+      <c r="H43">
+        <v>94303</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>378</v>
+      </c>
+      <c r="K43">
+        <v>150</v>
+      </c>
+      <c r="L43">
+        <v>228</v>
+      </c>
+      <c r="M43">
+        <v>11172.349858</v>
+      </c>
+      <c r="N43">
+        <v>-10944.349858</v>
+      </c>
+      <c r="O43">
+        <v>-2823.642263364</v>
+      </c>
+      <c r="P43">
+        <v>-8120.707594636001</v>
+      </c>
+      <c r="Q43">
+        <v>-7970.707594636001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1161900047349086</v>
+      </c>
+      <c r="T43">
+        <v>1.624590074371289</v>
+      </c>
+      <c r="U43">
+        <v>0.2458</v>
+      </c>
+      <c r="V43">
+        <v>0.005265141241336877</v>
+      </c>
+      <c r="W43">
+        <v>0.2445058282828794</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.02040752419122815</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1707994923895766</v>
+      </c>
+      <c r="C44">
+        <v>-4675.181039623334</v>
+      </c>
+      <c r="D44">
+        <v>31961.43896037666</v>
+      </c>
+      <c r="E44">
+        <v>30003.62</v>
+      </c>
+      <c r="F44">
+        <v>46561.62</v>
+      </c>
+      <c r="G44">
+        <v>9925</v>
+      </c>
+      <c r="H44">
+        <v>94303</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>378</v>
+      </c>
+      <c r="K44">
+        <v>150</v>
+      </c>
+      <c r="L44">
+        <v>228</v>
+      </c>
+      <c r="M44">
+        <v>11444.846196</v>
+      </c>
+      <c r="N44">
+        <v>-11216.846196</v>
+      </c>
+      <c r="O44">
+        <v>-2893.946318568</v>
+      </c>
+      <c r="P44">
+        <v>-8322.899877432001</v>
+      </c>
+      <c r="Q44">
+        <v>-8172.899877432001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1174036255062002</v>
+      </c>
+      <c r="T44">
+        <v>1.652600248067346</v>
+      </c>
+      <c r="U44">
+        <v>0.2458</v>
+      </c>
+      <c r="V44">
+        <v>0.005139780735590761</v>
+      </c>
+      <c r="W44">
+        <v>0.2445366418951918</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.01992163075810371</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1727994923895766</v>
+      </c>
+      <c r="C45">
+        <v>-6287.122798813885</v>
+      </c>
+      <c r="D45">
+        <v>31458.10720118611</v>
+      </c>
+      <c r="E45">
+        <v>31112.23</v>
+      </c>
+      <c r="F45">
+        <v>47670.23</v>
+      </c>
+      <c r="G45">
+        <v>9925</v>
+      </c>
+      <c r="H45">
+        <v>94303</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>378</v>
+      </c>
+      <c r="K45">
+        <v>150</v>
+      </c>
+      <c r="L45">
+        <v>228</v>
+      </c>
+      <c r="M45">
+        <v>11717.342534</v>
+      </c>
+      <c r="N45">
+        <v>-11489.342534</v>
+      </c>
+      <c r="O45">
+        <v>-2964.250373772</v>
+      </c>
+      <c r="P45">
+        <v>-8525.092160228</v>
+      </c>
+      <c r="Q45">
+        <v>-8375.092160228</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1186598294624493</v>
+      </c>
+      <c r="T45">
+        <v>1.681593234875545</v>
+      </c>
+      <c r="U45">
+        <v>0.2458</v>
+      </c>
+      <c r="V45">
+        <v>0.005020250951042139</v>
+      </c>
+      <c r="W45">
+        <v>0.2445660223162338</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01945833701954314</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1747994923895766</v>
+      </c>
+      <c r="C46">
+        <v>-7883.457310259</v>
+      </c>
+      <c r="D46">
+        <v>30970.382689741</v>
+      </c>
+      <c r="E46">
+        <v>32220.84</v>
+      </c>
+      <c r="F46">
+        <v>48778.84</v>
+      </c>
+      <c r="G46">
+        <v>9925</v>
+      </c>
+      <c r="H46">
+        <v>94303</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>378</v>
+      </c>
+      <c r="K46">
+        <v>150</v>
+      </c>
+      <c r="L46">
+        <v>228</v>
+      </c>
+      <c r="M46">
+        <v>11989.838872</v>
+      </c>
+      <c r="N46">
+        <v>-11761.838872</v>
+      </c>
+      <c r="O46">
+        <v>-3034.554428976001</v>
+      </c>
+      <c r="P46">
+        <v>-8727.284443024002</v>
+      </c>
+      <c r="Q46">
+        <v>-8577.284443024002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1199608978457073</v>
+      </c>
+      <c r="T46">
+        <v>1.711621685498322</v>
+      </c>
+      <c r="U46">
+        <v>0.2458</v>
+      </c>
+      <c r="V46">
+        <v>0.004906154338518453</v>
+      </c>
+      <c r="W46">
+        <v>0.2445940672635922</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01901610208728077</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1767994923895767</v>
+      </c>
+      <c r="C47">
+        <v>-9464.899412503182</v>
+      </c>
+      <c r="D47">
+        <v>30497.55058749682</v>
+      </c>
+      <c r="E47">
+        <v>33329.45</v>
+      </c>
+      <c r="F47">
+        <v>49887.45</v>
+      </c>
+      <c r="G47">
+        <v>9925</v>
+      </c>
+      <c r="H47">
+        <v>94303</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>378</v>
+      </c>
+      <c r="K47">
+        <v>150</v>
+      </c>
+      <c r="L47">
+        <v>228</v>
+      </c>
+      <c r="M47">
+        <v>12262.33521</v>
+      </c>
+      <c r="N47">
+        <v>-12034.33521</v>
+      </c>
+      <c r="O47">
+        <v>-3104.85848418</v>
+      </c>
+      <c r="P47">
+        <v>-8929.476725820001</v>
+      </c>
+      <c r="Q47">
+        <v>-8779.476725820001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1213092778065384</v>
+      </c>
+      <c r="T47">
+        <v>1.74274207978011</v>
+      </c>
+      <c r="U47">
+        <v>0.2458</v>
+      </c>
+      <c r="V47">
+        <v>0.004797128686551377</v>
+      </c>
+      <c r="W47">
+        <v>0.2446208657688457</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.01859352204089681</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1787994923895767</v>
+      </c>
+      <c r="C48">
+        <v>-11032.12094611962</v>
+      </c>
+      <c r="D48">
+        <v>30038.93905388039</v>
+      </c>
+      <c r="E48">
+        <v>34438.06</v>
+      </c>
+      <c r="F48">
+        <v>50996.06</v>
+      </c>
+      <c r="G48">
+        <v>9925</v>
+      </c>
+      <c r="H48">
+        <v>94303</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>378</v>
+      </c>
+      <c r="K48">
+        <v>150</v>
+      </c>
+      <c r="L48">
+        <v>228</v>
+      </c>
+      <c r="M48">
+        <v>12534.831548</v>
+      </c>
+      <c r="N48">
+        <v>-12306.831548</v>
+      </c>
+      <c r="O48">
+        <v>-3175.162539384</v>
+      </c>
+      <c r="P48">
+        <v>-9131.669008616002</v>
+      </c>
+      <c r="Q48">
+        <v>-8981.669008616002</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1227075977659187</v>
+      </c>
+      <c r="T48">
+        <v>1.77501508125752</v>
+      </c>
+      <c r="U48">
+        <v>0.2458</v>
+      </c>
+      <c r="V48">
+        <v>0.004692843280321999</v>
+      </c>
+      <c r="W48">
+        <v>0.2446464991216969</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.01818931504000776</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1807994923895767</v>
+      </c>
+      <c r="C49">
+        <v>-12585.75393875718</v>
+      </c>
+      <c r="D49">
+        <v>29593.91606124282</v>
+      </c>
+      <c r="E49">
+        <v>35546.67000000001</v>
+      </c>
+      <c r="F49">
+        <v>52104.67000000001</v>
+      </c>
+      <c r="G49">
+        <v>9925</v>
+      </c>
+      <c r="H49">
+        <v>94303</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>378</v>
+      </c>
+      <c r="K49">
+        <v>150</v>
+      </c>
+      <c r="L49">
+        <v>228</v>
+      </c>
+      <c r="M49">
+        <v>12807.327886</v>
+      </c>
+      <c r="N49">
+        <v>-12579.327886</v>
+      </c>
+      <c r="O49">
+        <v>-3245.466594588001</v>
+      </c>
+      <c r="P49">
+        <v>-9333.861291412002</v>
+      </c>
+      <c r="Q49">
+        <v>-9183.861291412002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1241586845162191</v>
+      </c>
+      <c r="T49">
+        <v>1.808505931847284</v>
+      </c>
+      <c r="U49">
+        <v>0.2458</v>
+      </c>
+      <c r="V49">
+        <v>0.004592995550953445</v>
+      </c>
+      <c r="W49">
+        <v>0.2446710416935756</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.01780230833702889</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1827994923895767</v>
+      </c>
+      <c r="C50">
+        <v>-14126.39351120389</v>
+      </c>
+      <c r="D50">
+        <v>29161.88648879611</v>
+      </c>
+      <c r="E50">
+        <v>36655.28</v>
+      </c>
+      <c r="F50">
+        <v>53213.28</v>
+      </c>
+      <c r="G50">
+        <v>9925</v>
+      </c>
+      <c r="H50">
+        <v>94303</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>378</v>
+      </c>
+      <c r="K50">
+        <v>150</v>
+      </c>
+      <c r="L50">
+        <v>228</v>
+      </c>
+      <c r="M50">
+        <v>13079.824224</v>
+      </c>
+      <c r="N50">
+        <v>-12851.824224</v>
+      </c>
+      <c r="O50">
+        <v>-3315.770649792</v>
+      </c>
+      <c r="P50">
+        <v>-9536.053574207999</v>
+      </c>
+      <c r="Q50">
+        <v>-9386.053574207999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1256655822953771</v>
+      </c>
+      <c r="T50">
+        <v>1.843284892075116</v>
+      </c>
+      <c r="U50">
+        <v>0.2458</v>
+      </c>
+      <c r="V50">
+        <v>0.004497308143641915</v>
+      </c>
+      <c r="W50">
+        <v>0.2446945616582928</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01743142691334076</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1847994923895767</v>
+      </c>
+      <c r="C51">
+        <v>-15654.60053256658</v>
+      </c>
+      <c r="D51">
+        <v>28742.28946743343</v>
+      </c>
+      <c r="E51">
+        <v>37763.89</v>
+      </c>
+      <c r="F51">
+        <v>54321.89</v>
+      </c>
+      <c r="G51">
+        <v>9925</v>
+      </c>
+      <c r="H51">
+        <v>94303</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>378</v>
+      </c>
+      <c r="K51">
+        <v>150</v>
+      </c>
+      <c r="L51">
+        <v>228</v>
+      </c>
+      <c r="M51">
+        <v>13352.320562</v>
+      </c>
+      <c r="N51">
+        <v>-13124.320562</v>
+      </c>
+      <c r="O51">
+        <v>-3386.074704996</v>
+      </c>
+      <c r="P51">
+        <v>-9738.245857004</v>
+      </c>
+      <c r="Q51">
+        <v>-9588.245857004</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1272315741050904</v>
+      </c>
+      <c r="T51">
+        <v>1.879427733096197</v>
+      </c>
+      <c r="U51">
+        <v>0.2458</v>
+      </c>
+      <c r="V51">
+        <v>0.004405526344792081</v>
+      </c>
+      <c r="W51">
+        <v>0.2447171216244501</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.01707568350694599</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1867994923895767</v>
+      </c>
+      <c r="C52">
+        <v>-17170.90404947683</v>
+      </c>
+      <c r="D52">
+        <v>28334.59595052317</v>
+      </c>
+      <c r="E52">
+        <v>38872.5</v>
+      </c>
+      <c r="F52">
+        <v>55430.5</v>
+      </c>
+      <c r="G52">
+        <v>9925</v>
+      </c>
+      <c r="H52">
+        <v>94303</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>378</v>
+      </c>
+      <c r="K52">
+        <v>150</v>
+      </c>
+      <c r="L52">
+        <v>228</v>
+      </c>
+      <c r="M52">
+        <v>13624.8169</v>
+      </c>
+      <c r="N52">
+        <v>-13396.8169</v>
+      </c>
+      <c r="O52">
+        <v>-3456.378760200001</v>
+      </c>
+      <c r="P52">
+        <v>-9940.4381398</v>
+      </c>
+      <c r="Q52">
+        <v>-9790.4381398</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1288602055871922</v>
+      </c>
+      <c r="T52">
+        <v>1.917016287758121</v>
+      </c>
+      <c r="U52">
+        <v>0.2458</v>
+      </c>
+      <c r="V52">
+        <v>0.004317415817896239</v>
+      </c>
+      <c r="W52">
+        <v>0.2447387791919611</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.01673416983680709</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1887994923895767</v>
+      </c>
+      <c r="C53">
+        <v>-18675.80351144681</v>
+      </c>
+      <c r="D53">
+        <v>27938.30648855319</v>
+      </c>
+      <c r="E53">
+        <v>39981.11</v>
+      </c>
+      <c r="F53">
+        <v>56539.11</v>
+      </c>
+      <c r="G53">
+        <v>9925</v>
+      </c>
+      <c r="H53">
+        <v>94303</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>378</v>
+      </c>
+      <c r="K53">
+        <v>150</v>
+      </c>
+      <c r="L53">
+        <v>228</v>
+      </c>
+      <c r="M53">
+        <v>13897.313238</v>
+      </c>
+      <c r="N53">
+        <v>-13669.313238</v>
+      </c>
+      <c r="O53">
+        <v>-3526.682815404</v>
+      </c>
+      <c r="P53">
+        <v>-10142.630422596</v>
+      </c>
+      <c r="Q53">
+        <v>-9992.630422596001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1305553118236655</v>
+      </c>
+      <c r="T53">
+        <v>1.95613906914094</v>
+      </c>
+      <c r="U53">
+        <v>0.2458</v>
+      </c>
+      <c r="V53">
+        <v>0.004232760605780627</v>
+      </c>
+      <c r="W53">
+        <v>0.2447595874430991</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.01640604885961483</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1907994923895767</v>
+      </c>
+      <c r="C54">
+        <v>-20169.77081205708</v>
+      </c>
+      <c r="D54">
+        <v>27552.94918794292</v>
+      </c>
+      <c r="E54">
+        <v>41089.72</v>
+      </c>
+      <c r="F54">
+        <v>57647.72</v>
+      </c>
+      <c r="G54">
+        <v>9925</v>
+      </c>
+      <c r="H54">
+        <v>94303</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>378</v>
+      </c>
+      <c r="K54">
+        <v>150</v>
+      </c>
+      <c r="L54">
+        <v>228</v>
+      </c>
+      <c r="M54">
+        <v>14169.809576</v>
+      </c>
+      <c r="N54">
+        <v>-13941.809576</v>
+      </c>
+      <c r="O54">
+        <v>-3596.986870608001</v>
+      </c>
+      <c r="P54">
+        <v>-10344.822705392</v>
+      </c>
+      <c r="Q54">
+        <v>-10194.822705392</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1323210474866586</v>
+      </c>
+      <c r="T54">
+        <v>1.99689196641471</v>
+      </c>
+      <c r="U54">
+        <v>0.2458</v>
+      </c>
+      <c r="V54">
+        <v>0.004151361363361768</v>
+      </c>
+      <c r="W54">
+        <v>0.2447795953768857</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.01609054792000686</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1927994923895767</v>
+      </c>
+      <c r="C55">
+        <v>-21653.25216351621</v>
+      </c>
+      <c r="D55">
+        <v>27178.07783648379</v>
+      </c>
+      <c r="E55">
+        <v>42198.33</v>
+      </c>
+      <c r="F55">
+        <v>58756.33</v>
+      </c>
+      <c r="G55">
+        <v>9925</v>
+      </c>
+      <c r="H55">
+        <v>94303</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>378</v>
+      </c>
+      <c r="K55">
+        <v>150</v>
+      </c>
+      <c r="L55">
+        <v>228</v>
+      </c>
+      <c r="M55">
+        <v>14442.305914</v>
+      </c>
+      <c r="N55">
+        <v>-14214.305914</v>
+      </c>
+      <c r="O55">
+        <v>-3667.290925812001</v>
+      </c>
+      <c r="P55">
+        <v>-10547.014988188</v>
+      </c>
+      <c r="Q55">
+        <v>-10397.014988188</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1341619208374385</v>
+      </c>
+      <c r="T55">
+        <v>2.039379029529916</v>
+      </c>
+      <c r="U55">
+        <v>0.2458</v>
+      </c>
+      <c r="V55">
+        <v>0.00407303379046815</v>
+      </c>
+      <c r="W55">
+        <v>0.2447988482943029</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.01578695267623309</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1947994923895767</v>
+      </c>
+      <c r="C56">
+        <v>-23126.66982024867</v>
+      </c>
+      <c r="D56">
+        <v>26813.27017975133</v>
+      </c>
+      <c r="E56">
+        <v>43306.94</v>
+      </c>
+      <c r="F56">
+        <v>59864.94</v>
+      </c>
+      <c r="G56">
+        <v>9925</v>
+      </c>
+      <c r="H56">
+        <v>94303</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>378</v>
+      </c>
+      <c r="K56">
+        <v>150</v>
+      </c>
+      <c r="L56">
+        <v>228</v>
+      </c>
+      <c r="M56">
+        <v>14714.802252</v>
+      </c>
+      <c r="N56">
+        <v>-14486.802252</v>
+      </c>
+      <c r="O56">
+        <v>-3737.594981016</v>
+      </c>
+      <c r="P56">
+        <v>-10749.207270984</v>
+      </c>
+      <c r="Q56">
+        <v>-10599.207270984</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1360828321599916</v>
+      </c>
+      <c r="T56">
+        <v>2.083713356258828</v>
+      </c>
+      <c r="U56">
+        <v>0.2458</v>
+      </c>
+      <c r="V56">
+        <v>0.003997607238792814</v>
+      </c>
+      <c r="W56">
+        <v>0.2448173881407048</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.01549460170074735</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1967994923895767</v>
+      </c>
+      <c r="C57">
+        <v>-24590.42366550841</v>
+      </c>
+      <c r="D57">
+        <v>26458.12633449159</v>
+      </c>
+      <c r="E57">
+        <v>44415.55</v>
+      </c>
+      <c r="F57">
+        <v>60973.55</v>
+      </c>
+      <c r="G57">
+        <v>9925</v>
+      </c>
+      <c r="H57">
+        <v>94303</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>378</v>
+      </c>
+      <c r="K57">
+        <v>150</v>
+      </c>
+      <c r="L57">
+        <v>228</v>
+      </c>
+      <c r="M57">
+        <v>14987.29859</v>
+      </c>
+      <c r="N57">
+        <v>-14759.29859</v>
+      </c>
+      <c r="O57">
+        <v>-3807.899036220001</v>
+      </c>
+      <c r="P57">
+        <v>-10951.39955378</v>
+      </c>
+      <c r="Q57">
+        <v>-10801.39955378</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1380891173191025</v>
+      </c>
+      <c r="T57">
+        <v>2.130018097509024</v>
+      </c>
+      <c r="U57">
+        <v>0.2458</v>
+      </c>
+      <c r="V57">
+        <v>0.003924923470814762</v>
+      </c>
+      <c r="W57">
+        <v>0.2448352538108738</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.01521288166982471</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1987994923895767</v>
+      </c>
+      <c r="C58">
+        <v>-26044.89267355169</v>
+      </c>
+      <c r="D58">
+        <v>26112.26732644832</v>
+      </c>
+      <c r="E58">
+        <v>45524.16</v>
+      </c>
+      <c r="F58">
+        <v>62082.16</v>
+      </c>
+      <c r="G58">
+        <v>9925</v>
+      </c>
+      <c r="H58">
+        <v>94303</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>378</v>
+      </c>
+      <c r="K58">
+        <v>150</v>
+      </c>
+      <c r="L58">
+        <v>228</v>
+      </c>
+      <c r="M58">
+        <v>15259.794928</v>
+      </c>
+      <c r="N58">
+        <v>-15031.794928</v>
+      </c>
+      <c r="O58">
+        <v>-3878.203091424</v>
+      </c>
+      <c r="P58">
+        <v>-11153.591836576</v>
+      </c>
+      <c r="Q58">
+        <v>-11003.591836576</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.140186597258173</v>
+      </c>
+      <c r="T58">
+        <v>2.178427599725138</v>
+      </c>
+      <c r="U58">
+        <v>0.2458</v>
+      </c>
+      <c r="V58">
+        <v>0.00385483555169307</v>
+      </c>
+      <c r="W58">
+        <v>0.2448524814213938</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.01494122306857781</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2007994923895767</v>
+      </c>
+      <c r="C59">
+        <v>-27490.43625860909</v>
+      </c>
+      <c r="D59">
+        <v>25775.33374139092</v>
+      </c>
+      <c r="E59">
+        <v>46632.77</v>
+      </c>
+      <c r="F59">
+        <v>63190.77</v>
+      </c>
+      <c r="G59">
+        <v>9925</v>
+      </c>
+      <c r="H59">
+        <v>94303</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>378</v>
+      </c>
+      <c r="K59">
+        <v>150</v>
+      </c>
+      <c r="L59">
+        <v>228</v>
+      </c>
+      <c r="M59">
+        <v>15532.291266</v>
+      </c>
+      <c r="N59">
+        <v>-15304.291266</v>
+      </c>
+      <c r="O59">
+        <v>-3948.507146628001</v>
+      </c>
+      <c r="P59">
+        <v>-11355.784119372</v>
+      </c>
+      <c r="Q59">
+        <v>-11205.784119372</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1423816344037119</v>
+      </c>
+      <c r="T59">
+        <v>2.22908870669549</v>
+      </c>
+      <c r="U59">
+        <v>0.2458</v>
+      </c>
+      <c r="V59">
+        <v>0.003787206857803718</v>
+      </c>
+      <c r="W59">
+        <v>0.2448691045543518</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.0146790963480764</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2027994923895767</v>
+      </c>
+      <c r="C60">
+        <v>-28927.39552075105</v>
+      </c>
+      <c r="D60">
+        <v>25446.98447924894</v>
+      </c>
+      <c r="E60">
+        <v>47741.38</v>
+      </c>
+      <c r="F60">
+        <v>64299.38</v>
+      </c>
+      <c r="G60">
+        <v>9925</v>
+      </c>
+      <c r="H60">
+        <v>94303</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>378</v>
+      </c>
+      <c r="K60">
+        <v>150</v>
+      </c>
+      <c r="L60">
+        <v>228</v>
+      </c>
+      <c r="M60">
+        <v>15804.787604</v>
+      </c>
+      <c r="N60">
+        <v>-15576.787604</v>
+      </c>
+      <c r="O60">
+        <v>-4018.811201832</v>
+      </c>
+      <c r="P60">
+        <v>-11557.976402168</v>
+      </c>
+      <c r="Q60">
+        <v>-11407.976402168</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1446811971276098</v>
+      </c>
+      <c r="T60">
+        <v>2.282162247331096</v>
+      </c>
+      <c r="U60">
+        <v>0.2458</v>
+      </c>
+      <c r="V60">
+        <v>0.003721910187841585</v>
+      </c>
+      <c r="W60">
+        <v>0.2448851544758285</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.01442600848000619</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2047994923895767</v>
+      </c>
+      <c r="C61">
+        <v>-30356.09439772557</v>
+      </c>
+      <c r="D61">
+        <v>25126.89560227443</v>
+      </c>
+      <c r="E61">
+        <v>48849.99</v>
+      </c>
+      <c r="F61">
+        <v>65407.99</v>
+      </c>
+      <c r="G61">
+        <v>9925</v>
+      </c>
+      <c r="H61">
+        <v>94303</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>378</v>
+      </c>
+      <c r="K61">
+        <v>150</v>
+      </c>
+      <c r="L61">
+        <v>228</v>
+      </c>
+      <c r="M61">
+        <v>16077.283942</v>
+      </c>
+      <c r="N61">
+        <v>-15849.283942</v>
+      </c>
+      <c r="O61">
+        <v>-4089.115257036</v>
+      </c>
+      <c r="P61">
+        <v>-11760.168684964</v>
+      </c>
+      <c r="Q61">
+        <v>-11610.168684964</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1470929336429173</v>
+      </c>
+      <c r="T61">
+        <v>2.33782474116844</v>
+      </c>
+      <c r="U61">
+        <v>0.2458</v>
+      </c>
+      <c r="V61">
+        <v>0.003658826964318847</v>
+      </c>
+      <c r="W61">
+        <v>0.2449006603321705</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.01418149986170092</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2067994923895767</v>
+      </c>
+      <c r="C62">
+        <v>-31776.84073094423</v>
+      </c>
+      <c r="D62">
+        <v>24814.75926905576</v>
+      </c>
+      <c r="E62">
+        <v>49958.59999999999</v>
+      </c>
+      <c r="F62">
+        <v>66516.59999999999</v>
+      </c>
+      <c r="G62">
+        <v>9925</v>
+      </c>
+      <c r="H62">
+        <v>94303</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>378</v>
+      </c>
+      <c r="K62">
+        <v>150</v>
+      </c>
+      <c r="L62">
+        <v>228</v>
+      </c>
+      <c r="M62">
+        <v>16349.78028</v>
+      </c>
+      <c r="N62">
+        <v>-16121.78028</v>
+      </c>
+      <c r="O62">
+        <v>-4159.41931224</v>
+      </c>
+      <c r="P62">
+        <v>-11962.36096776</v>
+      </c>
+      <c r="Q62">
+        <v>-11812.36096776</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1496252569839903</v>
+      </c>
+      <c r="T62">
+        <v>2.396270359697651</v>
+      </c>
+      <c r="U62">
+        <v>0.2458</v>
+      </c>
+      <c r="V62">
+        <v>0.003597846514913533</v>
+      </c>
+      <c r="W62">
+        <v>0.2449156493266343</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.01394514153067261</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2087994923895767</v>
+      </c>
+      <c r="C63">
+        <v>-33189.92725299066</v>
+      </c>
+      <c r="D63">
+        <v>24510.28274700934</v>
+      </c>
+      <c r="E63">
+        <v>51067.20999999999</v>
+      </c>
+      <c r="F63">
+        <v>67625.20999999999</v>
+      </c>
+      <c r="G63">
+        <v>9925</v>
+      </c>
+      <c r="H63">
+        <v>94303</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>378</v>
+      </c>
+      <c r="K63">
+        <v>150</v>
+      </c>
+      <c r="L63">
+        <v>228</v>
+      </c>
+      <c r="M63">
+        <v>16622.276618</v>
+      </c>
+      <c r="N63">
+        <v>-16394.276618</v>
+      </c>
+      <c r="O63">
+        <v>-4229.723367444</v>
+      </c>
+      <c r="P63">
+        <v>-12164.553250556</v>
+      </c>
+      <c r="Q63">
+        <v>-12014.553250556</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1522874430605028</v>
+      </c>
+      <c r="T63">
+        <v>2.457713189433488</v>
+      </c>
+      <c r="U63">
+        <v>0.2458</v>
+      </c>
+      <c r="V63">
+        <v>0.003538865424505114</v>
+      </c>
+      <c r="W63">
+        <v>0.2449301468786567</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.01371653265312056</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2107994923895767</v>
+      </c>
+      <c r="C64">
+        <v>-34595.63250330983</v>
+      </c>
+      <c r="D64">
+        <v>24213.18749669017</v>
+      </c>
+      <c r="E64">
+        <v>52175.81999999999</v>
+      </c>
+      <c r="F64">
+        <v>68733.81999999999</v>
+      </c>
+      <c r="G64">
+        <v>9925</v>
+      </c>
+      <c r="H64">
+        <v>94303</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>378</v>
+      </c>
+      <c r="K64">
+        <v>150</v>
+      </c>
+      <c r="L64">
+        <v>228</v>
+      </c>
+      <c r="M64">
+        <v>16894.772956</v>
+      </c>
+      <c r="N64">
+        <v>-16666.772956</v>
+      </c>
+      <c r="O64">
+        <v>-4300.027422648001</v>
+      </c>
+      <c r="P64">
+        <v>-12366.745533352</v>
+      </c>
+      <c r="Q64">
+        <v>-12216.745533352</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1550897441936739</v>
+      </c>
+      <c r="T64">
+        <v>2.522389852313317</v>
+      </c>
+      <c r="U64">
+        <v>0.2458</v>
+      </c>
+      <c r="V64">
+        <v>0.003481786949916322</v>
+      </c>
+      <c r="W64">
+        <v>0.2449441767677106</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.01349529825548967</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2127994923895767</v>
+      </c>
+      <c r="C65">
+        <v>-35994.22167809926</v>
+      </c>
+      <c r="D65">
+        <v>23923.20832190074</v>
+      </c>
+      <c r="E65">
+        <v>53284.43000000001</v>
+      </c>
+      <c r="F65">
+        <v>69842.43000000001</v>
+      </c>
+      <c r="G65">
+        <v>9925</v>
+      </c>
+      <c r="H65">
+        <v>94303</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>378</v>
+      </c>
+      <c r="K65">
+        <v>150</v>
+      </c>
+      <c r="L65">
+        <v>228</v>
+      </c>
+      <c r="M65">
+        <v>17167.269294</v>
+      </c>
+      <c r="N65">
+        <v>-16939.269294</v>
+      </c>
+      <c r="O65">
+        <v>-4370.331477852001</v>
+      </c>
+      <c r="P65">
+        <v>-12568.937816148</v>
+      </c>
+      <c r="Q65">
+        <v>-12418.937816148</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1580435210637733</v>
+      </c>
+      <c r="T65">
+        <v>2.590562551024488</v>
+      </c>
+      <c r="U65">
+        <v>0.2458</v>
+      </c>
+      <c r="V65">
+        <v>0.00342652049039384</v>
+      </c>
+      <c r="W65">
+        <v>0.2449577612634612</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.01328108717206911</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2147994923895767</v>
+      </c>
+      <c r="C66">
+        <v>-37385.94741985254</v>
+      </c>
+      <c r="D66">
+        <v>23640.09258014746</v>
+      </c>
+      <c r="E66">
+        <v>54393.04000000001</v>
+      </c>
+      <c r="F66">
+        <v>70951.04000000001</v>
+      </c>
+      <c r="G66">
+        <v>9925</v>
+      </c>
+      <c r="H66">
+        <v>94303</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>378</v>
+      </c>
+      <c r="K66">
+        <v>150</v>
+      </c>
+      <c r="L66">
+        <v>228</v>
+      </c>
+      <c r="M66">
+        <v>17439.765632</v>
+      </c>
+      <c r="N66">
+        <v>-17211.765632</v>
+      </c>
+      <c r="O66">
+        <v>-4440.635533056001</v>
+      </c>
+      <c r="P66">
+        <v>-12771.130098944</v>
+      </c>
+      <c r="Q66">
+        <v>-12621.130098944</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1611613966488781</v>
+      </c>
+      <c r="T66">
+        <v>2.662522621886279</v>
+      </c>
+      <c r="U66">
+        <v>0.2458</v>
+      </c>
+      <c r="V66">
+        <v>0.003372981107731437</v>
+      </c>
+      <c r="W66">
+        <v>0.2449709212437196</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.01307357018500555</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2167994923895767</v>
+      </c>
+      <c r="C67">
+        <v>-38771.05055149633</v>
+      </c>
+      <c r="D67">
+        <v>23363.59944850368</v>
+      </c>
+      <c r="E67">
+        <v>55501.65000000001</v>
+      </c>
+      <c r="F67">
+        <v>72059.65000000001</v>
+      </c>
+      <c r="G67">
+        <v>9925</v>
+      </c>
+      <c r="H67">
+        <v>94303</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>378</v>
+      </c>
+      <c r="K67">
+        <v>150</v>
+      </c>
+      <c r="L67">
+        <v>228</v>
+      </c>
+      <c r="M67">
+        <v>17712.26197</v>
+      </c>
+      <c r="N67">
+        <v>-17484.26197</v>
+      </c>
+      <c r="O67">
+        <v>-4510.939588260001</v>
+      </c>
+      <c r="P67">
+        <v>-12973.32238174</v>
+      </c>
+      <c r="Q67">
+        <v>-12823.32238174</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1644574365531317</v>
+      </c>
+      <c r="T67">
+        <v>2.738594696797316</v>
+      </c>
+      <c r="U67">
+        <v>0.2458</v>
+      </c>
+      <c r="V67">
+        <v>0.003321089090689414</v>
+      </c>
+      <c r="W67">
+        <v>0.2449836763015086</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.01287243833600549</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2187994923895767</v>
+      </c>
+      <c r="C68">
+        <v>-40149.76075960437</v>
+      </c>
+      <c r="D68">
+        <v>23093.49924039563</v>
+      </c>
+      <c r="E68">
+        <v>56610.26000000001</v>
+      </c>
+      <c r="F68">
+        <v>73168.26000000001</v>
+      </c>
+      <c r="G68">
+        <v>9925</v>
+      </c>
+      <c r="H68">
+        <v>94303</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>378</v>
+      </c>
+      <c r="K68">
+        <v>150</v>
+      </c>
+      <c r="L68">
+        <v>228</v>
+      </c>
+      <c r="M68">
+        <v>17984.758308</v>
+      </c>
+      <c r="N68">
+        <v>-17756.758308</v>
+      </c>
+      <c r="O68">
+        <v>-4581.243643464001</v>
+      </c>
+      <c r="P68">
+        <v>-13175.514664536</v>
+      </c>
+      <c r="Q68">
+        <v>-13025.514664536</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1679473611576356</v>
+      </c>
+      <c r="T68">
+        <v>2.819141599644296</v>
+      </c>
+      <c r="U68">
+        <v>0.2458</v>
+      </c>
+      <c r="V68">
+        <v>0.003270769559012301</v>
+      </c>
+      <c r="W68">
+        <v>0.2449960448423948</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.01267740139152052</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2207994923895767</v>
+      </c>
+      <c r="C69">
+        <v>-41522.2972307622</v>
+      </c>
+      <c r="D69">
+        <v>22829.57276923782</v>
+      </c>
+      <c r="E69">
+        <v>57718.87000000001</v>
+      </c>
+      <c r="F69">
+        <v>74276.87000000001</v>
+      </c>
+      <c r="G69">
+        <v>9925</v>
+      </c>
+      <c r="H69">
+        <v>94303</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>378</v>
+      </c>
+      <c r="K69">
+        <v>150</v>
+      </c>
+      <c r="L69">
+        <v>228</v>
+      </c>
+      <c r="M69">
+        <v>18257.254646</v>
+      </c>
+      <c r="N69">
+        <v>-18029.254646</v>
+      </c>
+      <c r="O69">
+        <v>-4651.547698668001</v>
+      </c>
+      <c r="P69">
+        <v>-13377.706947332</v>
+      </c>
+      <c r="Q69">
+        <v>-13227.706947332</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1716487963442307</v>
+      </c>
+      <c r="T69">
+        <v>2.904570132966851</v>
+      </c>
+      <c r="U69">
+        <v>0.2458</v>
+      </c>
+      <c r="V69">
+        <v>0.00322195210290764</v>
+      </c>
+      <c r="W69">
+        <v>0.2450080441731053</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01248818644537841</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2227994923895767</v>
+      </c>
+      <c r="C70">
+        <v>-42888.86924478866</v>
+      </c>
+      <c r="D70">
+        <v>22571.61075521136</v>
+      </c>
+      <c r="E70">
+        <v>58827.48000000001</v>
+      </c>
+      <c r="F70">
+        <v>75385.48000000001</v>
+      </c>
+      <c r="G70">
+        <v>9925</v>
+      </c>
+      <c r="H70">
+        <v>94303</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>378</v>
+      </c>
+      <c r="K70">
+        <v>150</v>
+      </c>
+      <c r="L70">
+        <v>228</v>
+      </c>
+      <c r="M70">
+        <v>18529.75098400001</v>
+      </c>
+      <c r="N70">
+        <v>-18301.75098400001</v>
+      </c>
+      <c r="O70">
+        <v>-4721.851753872002</v>
+      </c>
+      <c r="P70">
+        <v>-13579.89923012801</v>
+      </c>
+      <c r="Q70">
+        <v>-13429.89923012801</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1755815712299879</v>
+      </c>
+      <c r="T70">
+        <v>2.995337949622065</v>
+      </c>
+      <c r="U70">
+        <v>0.2458</v>
+      </c>
+      <c r="V70">
+        <v>0.003174570454335469</v>
+      </c>
+      <c r="W70">
+        <v>0.2450196905823244</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01230453664471109</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2247994923895767</v>
+      </c>
+      <c r="C71">
+        <v>-44249.67672818806</v>
+      </c>
+      <c r="D71">
+        <v>22319.41327181195</v>
+      </c>
+      <c r="E71">
+        <v>59936.09000000001</v>
+      </c>
+      <c r="F71">
+        <v>76494.09000000001</v>
+      </c>
+      <c r="G71">
+        <v>9925</v>
+      </c>
+      <c r="H71">
+        <v>94303</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>378</v>
+      </c>
+      <c r="K71">
+        <v>150</v>
+      </c>
+      <c r="L71">
+        <v>228</v>
+      </c>
+      <c r="M71">
+        <v>18802.247322</v>
+      </c>
+      <c r="N71">
+        <v>-18574.247322</v>
+      </c>
+      <c r="O71">
+        <v>-4792.155809076001</v>
+      </c>
+      <c r="P71">
+        <v>-13782.091512924</v>
+      </c>
+      <c r="Q71">
+        <v>-13632.091512924</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1797680735277294</v>
+      </c>
+      <c r="T71">
+        <v>3.091961754448584</v>
+      </c>
+      <c r="U71">
+        <v>0.2458</v>
+      </c>
+      <c r="V71">
+        <v>0.003128562186881332</v>
+      </c>
+      <c r="W71">
+        <v>0.2450309994144646</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.0121262100266718</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2267994923895767</v>
+      </c>
+      <c r="C72">
+        <v>-45604.91077090939</v>
+      </c>
+      <c r="D72">
+        <v>22072.78922909062</v>
+      </c>
+      <c r="E72">
+        <v>61044.70000000001</v>
+      </c>
+      <c r="F72">
+        <v>77602.70000000001</v>
+      </c>
+      <c r="G72">
+        <v>9925</v>
+      </c>
+      <c r="H72">
+        <v>94303</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>378</v>
+      </c>
+      <c r="K72">
+        <v>150</v>
+      </c>
+      <c r="L72">
+        <v>228</v>
+      </c>
+      <c r="M72">
+        <v>19074.74366</v>
+      </c>
+      <c r="N72">
+        <v>-18846.74366</v>
+      </c>
+      <c r="O72">
+        <v>-4862.459864280001</v>
+      </c>
+      <c r="P72">
+        <v>-13984.28379572</v>
+      </c>
+      <c r="Q72">
+        <v>-13834.28379572</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1842336759786537</v>
+      </c>
+      <c r="T72">
+        <v>3.195027146263536</v>
+      </c>
+      <c r="U72">
+        <v>0.2458</v>
+      </c>
+      <c r="V72">
+        <v>0.003083868441354456</v>
+      </c>
+      <c r="W72">
+        <v>0.2450419851371151</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01195297845486221</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2287994923895767</v>
+      </c>
+      <c r="C73">
+        <v>-46954.75410921939</v>
+      </c>
+      <c r="D73">
+        <v>21831.5558907806</v>
+      </c>
+      <c r="E73">
+        <v>62153.31</v>
+      </c>
+      <c r="F73">
+        <v>78711.31</v>
+      </c>
+      <c r="G73">
+        <v>9925</v>
+      </c>
+      <c r="H73">
+        <v>94303</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>378</v>
+      </c>
+      <c r="K73">
+        <v>150</v>
+      </c>
+      <c r="L73">
+        <v>228</v>
+      </c>
+      <c r="M73">
+        <v>19347.239998</v>
+      </c>
+      <c r="N73">
+        <v>-19119.239998</v>
+      </c>
+      <c r="O73">
+        <v>-4932.763919484</v>
+      </c>
+      <c r="P73">
+        <v>-14186.476078516</v>
+      </c>
+      <c r="Q73">
+        <v>-14036.476078516</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1890072510124004</v>
+      </c>
+      <c r="T73">
+        <v>3.305200496134691</v>
+      </c>
+      <c r="U73">
+        <v>0.2458</v>
+      </c>
+      <c r="V73">
+        <v>0.003040433674574816</v>
+      </c>
+      <c r="W73">
+        <v>0.2450526614027895</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.01178462664563884</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2307994923895767</v>
+      </c>
+      <c r="C74">
+        <v>-48299.38157725446</v>
+      </c>
+      <c r="D74">
+        <v>21595.53842274553</v>
+      </c>
+      <c r="E74">
+        <v>63261.92</v>
+      </c>
+      <c r="F74">
+        <v>79819.92</v>
+      </c>
+      <c r="G74">
+        <v>9925</v>
+      </c>
+      <c r="H74">
+        <v>94303</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>378</v>
+      </c>
+      <c r="K74">
+        <v>150</v>
+      </c>
+      <c r="L74">
+        <v>228</v>
+      </c>
+      <c r="M74">
+        <v>19619.736336</v>
+      </c>
+      <c r="N74">
+        <v>-19391.736336</v>
+      </c>
+      <c r="O74">
+        <v>-5003.067974688001</v>
+      </c>
+      <c r="P74">
+        <v>-14388.668361312</v>
+      </c>
+      <c r="Q74">
+        <v>-14238.668361312</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1941217956914147</v>
+      </c>
+      <c r="T74">
+        <v>3.423243370996645</v>
+      </c>
+      <c r="U74">
+        <v>0.2458</v>
+      </c>
+      <c r="V74">
+        <v>0.00299820542909461</v>
+      </c>
+      <c r="W74">
+        <v>0.2450630411055286</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01162095127556051</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2327994923895767</v>
+      </c>
+      <c r="C75">
+        <v>-49638.96052959532</v>
+      </c>
+      <c r="D75">
+        <v>21364.56947040468</v>
+      </c>
+      <c r="E75">
+        <v>64370.53</v>
+      </c>
+      <c r="F75">
+        <v>80928.53</v>
+      </c>
+      <c r="G75">
+        <v>9925</v>
+      </c>
+      <c r="H75">
+        <v>94303</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>378</v>
+      </c>
+      <c r="K75">
+        <v>150</v>
+      </c>
+      <c r="L75">
+        <v>228</v>
+      </c>
+      <c r="M75">
+        <v>19892.232674</v>
+      </c>
+      <c r="N75">
+        <v>-19664.232674</v>
+      </c>
+      <c r="O75">
+        <v>-5073.372029892001</v>
+      </c>
+      <c r="P75">
+        <v>-14590.860644108</v>
+      </c>
+      <c r="Q75">
+        <v>-14440.860644108</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1996151955318374</v>
+      </c>
+      <c r="T75">
+        <v>3.550030162515039</v>
+      </c>
+      <c r="U75">
+        <v>0.2458</v>
+      </c>
+      <c r="V75">
+        <v>0.002957134121846739</v>
+      </c>
+      <c r="W75">
+        <v>0.2450731364328501</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.01146176016219669</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2347994923895767</v>
+      </c>
+      <c r="C76">
+        <v>-50973.65123701189</v>
+      </c>
+      <c r="D76">
+        <v>21138.48876298811</v>
+      </c>
+      <c r="E76">
+        <v>65479.14</v>
+      </c>
+      <c r="F76">
+        <v>82037.14</v>
+      </c>
+      <c r="G76">
+        <v>9925</v>
+      </c>
+      <c r="H76">
+        <v>94303</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>378</v>
+      </c>
+      <c r="K76">
+        <v>150</v>
+      </c>
+      <c r="L76">
+        <v>228</v>
+      </c>
+      <c r="M76">
+        <v>20164.729012</v>
+      </c>
+      <c r="N76">
+        <v>-19936.729012</v>
+      </c>
+      <c r="O76">
+        <v>-5143.676085096</v>
+      </c>
+      <c r="P76">
+        <v>-14793.052926904</v>
+      </c>
+      <c r="Q76">
+        <v>-14643.052926904</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2055311645907543</v>
+      </c>
+      <c r="T76">
+        <v>3.686569784150233</v>
+      </c>
+      <c r="U76">
+        <v>0.2458</v>
+      </c>
+      <c r="V76">
+        <v>0.002917172849929891</v>
+      </c>
+      <c r="W76">
+        <v>0.2450829589134872</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.01130687151135612</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2367994923895767</v>
+      </c>
+      <c r="C77">
+        <v>-52303.60725734448</v>
+      </c>
+      <c r="D77">
+        <v>20917.14274265552</v>
+      </c>
+      <c r="E77">
+        <v>66587.75</v>
+      </c>
+      <c r="F77">
+        <v>83145.75</v>
+      </c>
+      <c r="G77">
+        <v>9925</v>
+      </c>
+      <c r="H77">
+        <v>94303</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>378</v>
+      </c>
+      <c r="K77">
+        <v>150</v>
+      </c>
+      <c r="L77">
+        <v>228</v>
+      </c>
+      <c r="M77">
+        <v>20437.22535</v>
+      </c>
+      <c r="N77">
+        <v>-20209.22535</v>
+      </c>
+      <c r="O77">
+        <v>-5213.9801403</v>
+      </c>
+      <c r="P77">
+        <v>-14995.2452097</v>
+      </c>
+      <c r="Q77">
+        <v>-14845.2452097</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2119204111743845</v>
+      </c>
+      <c r="T77">
+        <v>3.834032575516242</v>
+      </c>
+      <c r="U77">
+        <v>0.2458</v>
+      </c>
+      <c r="V77">
+        <v>0.002878277211930826</v>
+      </c>
+      <c r="W77">
+        <v>0.2450925194613074</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.01115611322453813</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2387994923895767</v>
+      </c>
+      <c r="C78">
+        <v>-53628.97578332477</v>
+      </c>
+      <c r="D78">
+        <v>20700.38421667523</v>
+      </c>
+      <c r="E78">
+        <v>67696.36</v>
+      </c>
+      <c r="F78">
+        <v>84254.36</v>
+      </c>
+      <c r="G78">
+        <v>9925</v>
+      </c>
+      <c r="H78">
+        <v>94303</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>378</v>
+      </c>
+      <c r="K78">
+        <v>150</v>
+      </c>
+      <c r="L78">
+        <v>228</v>
+      </c>
+      <c r="M78">
+        <v>20709.721688</v>
+      </c>
+      <c r="N78">
+        <v>-20481.721688</v>
+      </c>
+      <c r="O78">
+        <v>-5284.284195504</v>
+      </c>
+      <c r="P78">
+        <v>-15197.437492496</v>
+      </c>
+      <c r="Q78">
+        <v>-15047.437492496</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2188420949733171</v>
+      </c>
+      <c r="T78">
+        <v>3.993783932829419</v>
+      </c>
+      <c r="U78">
+        <v>0.2458</v>
+      </c>
+      <c r="V78">
+        <v>0.002840405143352789</v>
+      </c>
+      <c r="W78">
+        <v>0.2451018284157639</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01100932226105733</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2407994923895767</v>
+      </c>
+      <c r="C79">
+        <v>-54949.89796899262</v>
+      </c>
+      <c r="D79">
+        <v>20488.07203100738</v>
+      </c>
+      <c r="E79">
+        <v>68804.97</v>
+      </c>
+      <c r="F79">
+        <v>85362.97</v>
+      </c>
+      <c r="G79">
+        <v>9925</v>
+      </c>
+      <c r="H79">
+        <v>94303</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>378</v>
+      </c>
+      <c r="K79">
+        <v>150</v>
+      </c>
+      <c r="L79">
+        <v>228</v>
+      </c>
+      <c r="M79">
+        <v>20982.218026</v>
+      </c>
+      <c r="N79">
+        <v>-20754.218026</v>
+      </c>
+      <c r="O79">
+        <v>-5354.588250708</v>
+      </c>
+      <c r="P79">
+        <v>-15399.629775292</v>
+      </c>
+      <c r="Q79">
+        <v>-15249.629775292</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2263656643199831</v>
+      </c>
+      <c r="T79">
+        <v>4.167426712517655</v>
+      </c>
+      <c r="U79">
+        <v>0.2458</v>
+      </c>
+      <c r="V79">
+        <v>0.002803516764867687</v>
+      </c>
+      <c r="W79">
+        <v>0.2451108955791955</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.01086634404987474</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2427994923895767</v>
+      </c>
+      <c r="C80">
+        <v>-56266.50923622931</v>
+      </c>
+      <c r="D80">
+        <v>20280.07076377069</v>
+      </c>
+      <c r="E80">
+        <v>69913.58</v>
+      </c>
+      <c r="F80">
+        <v>86471.58</v>
+      </c>
+      <c r="G80">
+        <v>9925</v>
+      </c>
+      <c r="H80">
+        <v>94303</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>378</v>
+      </c>
+      <c r="K80">
+        <v>150</v>
+      </c>
+      <c r="L80">
+        <v>228</v>
+      </c>
+      <c r="M80">
+        <v>21254.714364</v>
+      </c>
+      <c r="N80">
+        <v>-21026.714364</v>
+      </c>
+      <c r="O80">
+        <v>-5424.892305912001</v>
+      </c>
+      <c r="P80">
+        <v>-15601.822058088</v>
+      </c>
+      <c r="Q80">
+        <v>-15451.822058088</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.234573194516346</v>
+      </c>
+      <c r="T80">
+        <v>4.356855199450275</v>
+      </c>
+      <c r="U80">
+        <v>0.2458</v>
+      </c>
+      <c r="V80">
+        <v>0.002767574242241179</v>
+      </c>
+      <c r="W80">
+        <v>0.2451197302512571</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.01072703194667124</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2447994923895767</v>
+      </c>
+      <c r="C81">
+        <v>-57578.93956280652</v>
+      </c>
+      <c r="D81">
+        <v>20076.25043719348</v>
+      </c>
+      <c r="E81">
+        <v>71022.19</v>
+      </c>
+      <c r="F81">
+        <v>87580.19</v>
+      </c>
+      <c r="G81">
+        <v>9925</v>
+      </c>
+      <c r="H81">
+        <v>94303</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>378</v>
+      </c>
+      <c r="K81">
+        <v>150</v>
+      </c>
+      <c r="L81">
+        <v>228</v>
+      </c>
+      <c r="M81">
+        <v>21527.210702</v>
+      </c>
+      <c r="N81">
+        <v>-21299.210702</v>
+      </c>
+      <c r="O81">
+        <v>-5495.196361116001</v>
+      </c>
+      <c r="P81">
+        <v>-15804.014340884</v>
+      </c>
+      <c r="Q81">
+        <v>-15654.014340884</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2435623942552196</v>
+      </c>
+      <c r="T81">
+        <v>4.564324494662194</v>
+      </c>
+      <c r="U81">
+        <v>0.2458</v>
+      </c>
+      <c r="V81">
+        <v>0.002732541656896354</v>
+      </c>
+      <c r="W81">
+        <v>0.2451283412607349</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.01059124673215639</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2467994923895767</v>
+      </c>
+      <c r="C82">
+        <v>-58887.31375323822</v>
+      </c>
+      <c r="D82">
+        <v>19876.48624676178</v>
+      </c>
+      <c r="E82">
+        <v>72130.8</v>
+      </c>
+      <c r="F82">
+        <v>88688.8</v>
+      </c>
+      <c r="G82">
+        <v>9925</v>
+      </c>
+      <c r="H82">
+        <v>94303</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>378</v>
+      </c>
+      <c r="K82">
+        <v>150</v>
+      </c>
+      <c r="L82">
+        <v>228</v>
+      </c>
+      <c r="M82">
+        <v>21799.70704</v>
+      </c>
+      <c r="N82">
+        <v>-21571.70704</v>
+      </c>
+      <c r="O82">
+        <v>-5565.50041632</v>
+      </c>
+      <c r="P82">
+        <v>-16006.20662368</v>
+      </c>
+      <c r="Q82">
+        <v>-15856.20662368</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2534505139679806</v>
+      </c>
+      <c r="T82">
+        <v>4.792540719395304</v>
+      </c>
+      <c r="U82">
+        <v>0.2458</v>
+      </c>
+      <c r="V82">
+        <v>0.002698384886185149</v>
+      </c>
+      <c r="W82">
+        <v>0.2451367369949757</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01045885614800446</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2487994923895767</v>
+      </c>
+      <c r="C83">
+        <v>-60191.75169362161</v>
+      </c>
+      <c r="D83">
+        <v>19680.65830637839</v>
+      </c>
+      <c r="E83">
+        <v>73239.41</v>
+      </c>
+      <c r="F83">
+        <v>89797.41</v>
+      </c>
+      <c r="G83">
+        <v>9925</v>
+      </c>
+      <c r="H83">
+        <v>94303</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>378</v>
+      </c>
+      <c r="K83">
+        <v>150</v>
+      </c>
+      <c r="L83">
+        <v>228</v>
+      </c>
+      <c r="M83">
+        <v>22072.203378</v>
+      </c>
+      <c r="N83">
+        <v>-21844.203378</v>
+      </c>
+      <c r="O83">
+        <v>-5635.804471524</v>
+      </c>
+      <c r="P83">
+        <v>-16208.398906476</v>
+      </c>
+      <c r="Q83">
+        <v>-16058.398906476</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.264379488387348</v>
+      </c>
+      <c r="T83">
+        <v>5.044779704626635</v>
+      </c>
+      <c r="U83">
+        <v>0.2458</v>
+      </c>
+      <c r="V83">
+        <v>0.002665071492528542</v>
+      </c>
+      <c r="W83">
+        <v>0.2451449254271365</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.0103297344671649</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2507994923895767</v>
+      </c>
+      <c r="C84">
+        <v>-61492.36859156044</v>
+      </c>
+      <c r="D84">
+        <v>19488.65140843956</v>
+      </c>
+      <c r="E84">
+        <v>74348.02</v>
+      </c>
+      <c r="F84">
+        <v>90906.02</v>
+      </c>
+      <c r="G84">
+        <v>9925</v>
+      </c>
+      <c r="H84">
+        <v>94303</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>378</v>
+      </c>
+      <c r="K84">
+        <v>150</v>
+      </c>
+      <c r="L84">
+        <v>228</v>
+      </c>
+      <c r="M84">
+        <v>22344.699716</v>
+      </c>
+      <c r="N84">
+        <v>-22116.699716</v>
+      </c>
+      <c r="O84">
+        <v>-5706.108526728</v>
+      </c>
+      <c r="P84">
+        <v>-16410.591189272</v>
+      </c>
+      <c r="Q84">
+        <v>-16260.591189272</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2765227932977562</v>
+      </c>
+      <c r="T84">
+        <v>5.32504524377256</v>
+      </c>
+      <c r="U84">
+        <v>0.2458</v>
+      </c>
+      <c r="V84">
+        <v>0.002632570620668438</v>
+      </c>
+      <c r="W84">
+        <v>0.2451529141414397</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01020376209561413</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2527994923895767</v>
+      </c>
+      <c r="C85">
+        <v>-62789.27520217977</v>
+      </c>
+      <c r="D85">
+        <v>19300.35479782023</v>
+      </c>
+      <c r="E85">
+        <v>75456.63</v>
+      </c>
+      <c r="F85">
+        <v>92014.63</v>
+      </c>
+      <c r="G85">
+        <v>9925</v>
+      </c>
+      <c r="H85">
+        <v>94303</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>378</v>
+      </c>
+      <c r="K85">
+        <v>150</v>
+      </c>
+      <c r="L85">
+        <v>228</v>
+      </c>
+      <c r="M85">
+        <v>22617.196054</v>
+      </c>
+      <c r="N85">
+        <v>-22389.196054</v>
+      </c>
+      <c r="O85">
+        <v>-5776.412581932001</v>
+      </c>
+      <c r="P85">
+        <v>-16612.783472068</v>
+      </c>
+      <c r="Q85">
+        <v>-16462.783472068</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2900947223152713</v>
+      </c>
+      <c r="T85">
+        <v>5.638283199288593</v>
+      </c>
+      <c r="U85">
+        <v>0.2458</v>
+      </c>
+      <c r="V85">
+        <v>0.002600852902347131</v>
+      </c>
+      <c r="W85">
+        <v>0.2451607103566031</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.01008082520289588</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2547994923895767</v>
+      </c>
+      <c r="C86">
+        <v>-64082.57804116373</v>
+      </c>
+      <c r="D86">
+        <v>19115.66195883626</v>
+      </c>
+      <c r="E86">
+        <v>76565.23999999999</v>
+      </c>
+      <c r="F86">
+        <v>93123.23999999999</v>
+      </c>
+      <c r="G86">
+        <v>9925</v>
+      </c>
+      <c r="H86">
+        <v>94303</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>378</v>
+      </c>
+      <c r="K86">
+        <v>150</v>
+      </c>
+      <c r="L86">
+        <v>228</v>
+      </c>
+      <c r="M86">
+        <v>22889.692392</v>
+      </c>
+      <c r="N86">
+        <v>-22661.692392</v>
+      </c>
+      <c r="O86">
+        <v>-5846.716637136001</v>
+      </c>
+      <c r="P86">
+        <v>-16814.975754864</v>
+      </c>
+      <c r="Q86">
+        <v>-16664.975754864</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3053631424599756</v>
+      </c>
+      <c r="T86">
+        <v>5.990675899244128</v>
+      </c>
+      <c r="U86">
+        <v>0.2458</v>
+      </c>
+      <c r="V86">
+        <v>0.002569890367795381</v>
+      </c>
+      <c r="W86">
+        <v>0.2451683209475959</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.009960815379051913</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2567994923895767</v>
+      </c>
+      <c r="C87">
+        <v>-65372.37958567742</v>
+      </c>
+      <c r="D87">
+        <v>18934.47041432257</v>
+      </c>
+      <c r="E87">
+        <v>77673.84999999999</v>
+      </c>
+      <c r="F87">
+        <v>94231.84999999999</v>
+      </c>
+      <c r="G87">
+        <v>9925</v>
+      </c>
+      <c r="H87">
+        <v>94303</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>378</v>
+      </c>
+      <c r="K87">
+        <v>150</v>
+      </c>
+      <c r="L87">
+        <v>228</v>
+      </c>
+      <c r="M87">
+        <v>23162.18873</v>
+      </c>
+      <c r="N87">
+        <v>-22934.18873</v>
+      </c>
+      <c r="O87">
+        <v>-5917.02069234</v>
+      </c>
+      <c r="P87">
+        <v>-17017.16803766</v>
+      </c>
+      <c r="Q87">
+        <v>-16867.16803766</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3226673519573073</v>
+      </c>
+      <c r="T87">
+        <v>6.390054292527069</v>
+      </c>
+      <c r="U87">
+        <v>0.2458</v>
+      </c>
+      <c r="V87">
+        <v>0.002539656363468376</v>
+      </c>
+      <c r="W87">
+        <v>0.2451757524658595</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.009843629315768876</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2587994923895767</v>
+      </c>
+      <c r="C88">
+        <v>-66658.77846396912</v>
+      </c>
+      <c r="D88">
+        <v>18756.68153603086</v>
+      </c>
+      <c r="E88">
+        <v>78782.45999999999</v>
+      </c>
+      <c r="F88">
+        <v>95340.45999999999</v>
+      </c>
+      <c r="G88">
+        <v>9925</v>
+      </c>
+      <c r="H88">
+        <v>94303</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>378</v>
+      </c>
+      <c r="K88">
+        <v>150</v>
+      </c>
+      <c r="L88">
+        <v>228</v>
+      </c>
+      <c r="M88">
+        <v>23434.685068</v>
+      </c>
+      <c r="N88">
+        <v>-23206.685068</v>
+      </c>
+      <c r="O88">
+        <v>-5987.324747544</v>
+      </c>
+      <c r="P88">
+        <v>-17219.360320456</v>
+      </c>
+      <c r="Q88">
+        <v>-17069.360320456</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3424435913828293</v>
+      </c>
+      <c r="T88">
+        <v>6.846486741993289</v>
+      </c>
+      <c r="U88">
+        <v>0.2458</v>
+      </c>
+      <c r="V88">
+        <v>0.002510125475521069</v>
+      </c>
+      <c r="W88">
+        <v>0.2451830111581169</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.009729168509771569</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2607994923895767</v>
+      </c>
+      <c r="C89">
+        <v>-67941.86963439017</v>
+      </c>
+      <c r="D89">
+        <v>18582.20036560983</v>
+      </c>
+      <c r="E89">
+        <v>79891.06999999999</v>
+      </c>
+      <c r="F89">
+        <v>96449.06999999999</v>
+      </c>
+      <c r="G89">
+        <v>9925</v>
+      </c>
+      <c r="H89">
+        <v>94303</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>378</v>
+      </c>
+      <c r="K89">
+        <v>150</v>
+      </c>
+      <c r="L89">
+        <v>228</v>
+      </c>
+      <c r="M89">
+        <v>23707.181406</v>
+      </c>
+      <c r="N89">
+        <v>-23479.181406</v>
+      </c>
+      <c r="O89">
+        <v>-6057.628802748</v>
+      </c>
+      <c r="P89">
+        <v>-17421.552603252</v>
+      </c>
+      <c r="Q89">
+        <v>-17271.552603252</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3652623291815085</v>
+      </c>
+      <c r="T89">
+        <v>7.373139568300465</v>
+      </c>
+      <c r="U89">
+        <v>0.2458</v>
+      </c>
+      <c r="V89">
+        <v>0.002481273458561057</v>
+      </c>
+      <c r="W89">
+        <v>0.2451901029838857</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.00961733898667072</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2627994923895767</v>
+      </c>
+      <c r="C90">
+        <v>-69221.74455451495</v>
+      </c>
+      <c r="D90">
+        <v>18410.93544548505</v>
+      </c>
+      <c r="E90">
+        <v>80999.68000000001</v>
+      </c>
+      <c r="F90">
+        <v>97557.68000000001</v>
+      </c>
+      <c r="G90">
+        <v>9925</v>
+      </c>
+      <c r="H90">
+        <v>94303</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>378</v>
+      </c>
+      <c r="K90">
+        <v>150</v>
+      </c>
+      <c r="L90">
+        <v>228</v>
+      </c>
+      <c r="M90">
+        <v>23979.677744</v>
+      </c>
+      <c r="N90">
+        <v>-23751.677744</v>
+      </c>
+      <c r="O90">
+        <v>-6127.932857952002</v>
+      </c>
+      <c r="P90">
+        <v>-17623.744886048</v>
+      </c>
+      <c r="Q90">
+        <v>-17473.744886048</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3918841899466343</v>
+      </c>
+      <c r="T90">
+        <v>7.987567865658838</v>
+      </c>
+      <c r="U90">
+        <v>0.2458</v>
+      </c>
+      <c r="V90">
+        <v>0.002453077169259227</v>
+      </c>
+      <c r="W90">
+        <v>0.2451970336317961</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.009508051043640386</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2647994923895767</v>
+      </c>
+      <c r="C91">
+        <v>-70498.49134099422</v>
+      </c>
+      <c r="D91">
+        <v>18242.79865900579</v>
+      </c>
+      <c r="E91">
+        <v>82108.29000000001</v>
+      </c>
+      <c r="F91">
+        <v>98666.29000000001</v>
+      </c>
+      <c r="G91">
+        <v>9925</v>
+      </c>
+      <c r="H91">
+        <v>94303</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>378</v>
+      </c>
+      <c r="K91">
+        <v>150</v>
+      </c>
+      <c r="L91">
+        <v>228</v>
+      </c>
+      <c r="M91">
+        <v>24252.17408200001</v>
+      </c>
+      <c r="N91">
+        <v>-24024.17408200001</v>
+      </c>
+      <c r="O91">
+        <v>-6198.236913156002</v>
+      </c>
+      <c r="P91">
+        <v>-17825.937168844</v>
+      </c>
+      <c r="Q91">
+        <v>-17675.937168844</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4233463890326919</v>
+      </c>
+      <c r="T91">
+        <v>8.713710398900551</v>
+      </c>
+      <c r="U91">
+        <v>0.2458</v>
+      </c>
+      <c r="V91">
+        <v>0.002425514504436089</v>
+      </c>
+      <c r="W91">
+        <v>0.2452038085348096</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.009401219009442241</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2667994923895767</v>
+      </c>
+      <c r="C92">
+        <v>-71772.1949207283</v>
+      </c>
+      <c r="D92">
+        <v>18077.70507927171</v>
+      </c>
+      <c r="E92">
+        <v>83216.90000000001</v>
+      </c>
+      <c r="F92">
+        <v>99774.90000000001</v>
+      </c>
+      <c r="G92">
+        <v>9925</v>
+      </c>
+      <c r="H92">
+        <v>94303</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>378</v>
+      </c>
+      <c r="K92">
+        <v>150</v>
+      </c>
+      <c r="L92">
+        <v>228</v>
+      </c>
+      <c r="M92">
+        <v>24524.67042</v>
+      </c>
+      <c r="N92">
+        <v>-24296.67042</v>
+      </c>
+      <c r="O92">
+        <v>-6268.540968360001</v>
+      </c>
+      <c r="P92">
+        <v>-18028.12945164</v>
+      </c>
+      <c r="Q92">
+        <v>-17878.12945164</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4611010279359611</v>
+      </c>
+      <c r="T92">
+        <v>9.585081438790606</v>
+      </c>
+      <c r="U92">
+        <v>0.2458</v>
+      </c>
+      <c r="V92">
+        <v>0.002398564343275688</v>
+      </c>
+      <c r="W92">
+        <v>0.2452104328844228</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.009296761020448407</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2687994923895767</v>
+      </c>
+      <c r="C93">
+        <v>-73042.93717390572</v>
+      </c>
+      <c r="D93">
+        <v>17915.57282609428</v>
+      </c>
+      <c r="E93">
+        <v>84325.51000000001</v>
+      </c>
+      <c r="F93">
+        <v>100883.51</v>
+      </c>
+      <c r="G93">
+        <v>9925</v>
+      </c>
+      <c r="H93">
+        <v>94303</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>378</v>
+      </c>
+      <c r="K93">
+        <v>150</v>
+      </c>
+      <c r="L93">
+        <v>228</v>
+      </c>
+      <c r="M93">
+        <v>24797.166758</v>
+      </c>
+      <c r="N93">
+        <v>-24569.166758</v>
+      </c>
+      <c r="O93">
+        <v>-6338.845023564001</v>
+      </c>
+      <c r="P93">
+        <v>-18230.321734436</v>
+      </c>
+      <c r="Q93">
+        <v>-18080.321734436</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5072455865955123</v>
+      </c>
+      <c r="T93">
+        <v>10.65009048754512</v>
+      </c>
+      <c r="U93">
+        <v>0.2458</v>
+      </c>
+      <c r="V93">
+        <v>0.002372206493349582</v>
+      </c>
+      <c r="W93">
+        <v>0.2452169116439347</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.009194598811432475</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2707994923895767</v>
+      </c>
+      <c r="C94">
+        <v>-74310.79706941282</v>
+      </c>
+      <c r="D94">
+        <v>17756.3229305872</v>
+      </c>
+      <c r="E94">
+        <v>85434.12000000001</v>
+      </c>
+      <c r="F94">
+        <v>101992.12</v>
+      </c>
+      <c r="G94">
+        <v>9925</v>
+      </c>
+      <c r="H94">
+        <v>94303</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>378</v>
+      </c>
+      <c r="K94">
+        <v>150</v>
+      </c>
+      <c r="L94">
+        <v>228</v>
+      </c>
+      <c r="M94">
+        <v>25069.663096</v>
+      </c>
+      <c r="N94">
+        <v>-24841.663096</v>
+      </c>
+      <c r="O94">
+        <v>-6409.149078768001</v>
+      </c>
+      <c r="P94">
+        <v>-18432.514017232</v>
+      </c>
+      <c r="Q94">
+        <v>-18282.514017232</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5649262849199516</v>
+      </c>
+      <c r="T94">
+        <v>11.98135179848826</v>
+      </c>
+      <c r="U94">
+        <v>0.2458</v>
+      </c>
+      <c r="V94">
+        <v>0.002346421640160999</v>
+      </c>
+      <c r="W94">
+        <v>0.2452232495608485</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.009094657520003824</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2727994923895767</v>
+      </c>
+      <c r="C95">
+        <v>-75575.85079308524</v>
+      </c>
+      <c r="D95">
+        <v>17599.87920691477</v>
+      </c>
+      <c r="E95">
+        <v>86542.73000000001</v>
+      </c>
+      <c r="F95">
+        <v>103100.73</v>
+      </c>
+      <c r="G95">
+        <v>9925</v>
+      </c>
+      <c r="H95">
+        <v>94303</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>378</v>
+      </c>
+      <c r="K95">
+        <v>150</v>
+      </c>
+      <c r="L95">
+        <v>228</v>
+      </c>
+      <c r="M95">
+        <v>25342.159434</v>
+      </c>
+      <c r="N95">
+        <v>-25114.159434</v>
+      </c>
+      <c r="O95">
+        <v>-6479.453133972002</v>
+      </c>
+      <c r="P95">
+        <v>-18634.706300028</v>
+      </c>
+      <c r="Q95">
+        <v>-18484.706300028</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.639087182765659</v>
+      </c>
+      <c r="T95">
+        <v>13.69297348398659</v>
+      </c>
+      <c r="U95">
+        <v>0.2458</v>
+      </c>
+      <c r="V95">
+        <v>0.002321191299944214</v>
+      </c>
+      <c r="W95">
+        <v>0.2452294511784737</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.008996865503659746</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2747994923895767</v>
+      </c>
+      <c r="C96">
+        <v>-76838.17186923884</v>
+      </c>
+      <c r="D96">
+        <v>17446.16813076118</v>
+      </c>
+      <c r="E96">
+        <v>87651.34000000001</v>
+      </c>
+      <c r="F96">
+        <v>104209.34</v>
+      </c>
+      <c r="G96">
+        <v>9925</v>
+      </c>
+      <c r="H96">
+        <v>94303</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>378</v>
+      </c>
+      <c r="K96">
+        <v>150</v>
+      </c>
+      <c r="L96">
+        <v>228</v>
+      </c>
+      <c r="M96">
+        <v>25614.65577200001</v>
+      </c>
+      <c r="N96">
+        <v>-25386.65577200001</v>
+      </c>
+      <c r="O96">
+        <v>-6549.757189176002</v>
+      </c>
+      <c r="P96">
+        <v>-18836.898582824</v>
+      </c>
+      <c r="Q96">
+        <v>-18686.898582824</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.737968379893269</v>
+      </c>
+      <c r="T96">
+        <v>15.97513573131769</v>
+      </c>
+      <c r="U96">
+        <v>0.2458</v>
+      </c>
+      <c r="V96">
+        <v>0.002296497775476723</v>
+      </c>
+      <c r="W96">
+        <v>0.2452355208467878</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.008901154168514447</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2767994923895767</v>
+      </c>
+      <c r="C97">
+        <v>-78097.83127588721</v>
+      </c>
+      <c r="D97">
+        <v>17295.1187241128</v>
+      </c>
+      <c r="E97">
+        <v>88759.95000000001</v>
+      </c>
+      <c r="F97">
+        <v>105317.95</v>
+      </c>
+      <c r="G97">
+        <v>9925</v>
+      </c>
+      <c r="H97">
+        <v>94303</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>378</v>
+      </c>
+      <c r="K97">
+        <v>150</v>
+      </c>
+      <c r="L97">
+        <v>228</v>
+      </c>
+      <c r="M97">
+        <v>25887.15211000001</v>
+      </c>
+      <c r="N97">
+        <v>-25659.15211000001</v>
+      </c>
+      <c r="O97">
+        <v>-6620.061244380002</v>
+      </c>
+      <c r="P97">
+        <v>-19039.09086562</v>
+      </c>
+      <c r="Q97">
+        <v>-18889.09086562</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8764020558719232</v>
+      </c>
+      <c r="T97">
+        <v>19.17016287758124</v>
+      </c>
+      <c r="U97">
+        <v>0.2458</v>
+      </c>
+      <c r="V97">
+        <v>0.00227232411468223</v>
+      </c>
+      <c r="W97">
+        <v>0.2452414627326111</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.008807457808845842</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2787994923895767</v>
+      </c>
+      <c r="C98">
+        <v>-79354.89755402532</v>
+      </c>
+      <c r="D98">
+        <v>17146.66244597469</v>
+      </c>
+      <c r="E98">
+        <v>89868.56</v>
+      </c>
+      <c r="F98">
+        <v>106426.56</v>
+      </c>
+      <c r="G98">
+        <v>9925</v>
+      </c>
+      <c r="H98">
+        <v>94303</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>378</v>
+      </c>
+      <c r="K98">
+        <v>150</v>
+      </c>
+      <c r="L98">
+        <v>228</v>
+      </c>
+      <c r="M98">
+        <v>26159.648448</v>
+      </c>
+      <c r="N98">
+        <v>-25931.648448</v>
+      </c>
+      <c r="O98">
+        <v>-6690.365299584</v>
+      </c>
+      <c r="P98">
+        <v>-19241.283148416</v>
+      </c>
+      <c r="Q98">
+        <v>-19091.283148416</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.084052569839902</v>
+      </c>
+      <c r="T98">
+        <v>23.96270359697649</v>
+      </c>
+      <c r="U98">
+        <v>0.2458</v>
+      </c>
+      <c r="V98">
+        <v>0.002248654071820958</v>
+      </c>
+      <c r="W98">
+        <v>0.2452472808291464</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.008715713456670326</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2807994923895767</v>
+      </c>
+      <c r="C99">
+        <v>-80609.4369113326</v>
+      </c>
+      <c r="D99">
+        <v>17000.73308866741</v>
+      </c>
+      <c r="E99">
+        <v>90977.17</v>
+      </c>
+      <c r="F99">
+        <v>107535.17</v>
+      </c>
+      <c r="G99">
+        <v>9925</v>
+      </c>
+      <c r="H99">
+        <v>94303</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>378</v>
+      </c>
+      <c r="K99">
+        <v>150</v>
+      </c>
+      <c r="L99">
+        <v>228</v>
+      </c>
+      <c r="M99">
+        <v>26432.144786</v>
+      </c>
+      <c r="N99">
+        <v>-26204.144786</v>
+      </c>
+      <c r="O99">
+        <v>-6760.669354788</v>
+      </c>
+      <c r="P99">
+        <v>-19443.475431212</v>
+      </c>
+      <c r="Q99">
+        <v>-19293.475431212</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.430136759786536</v>
+      </c>
+      <c r="T99">
+        <v>31.95027146263533</v>
+      </c>
+      <c r="U99">
+        <v>0.2458</v>
+      </c>
+      <c r="V99">
+        <v>0.002225472071080536</v>
+      </c>
+      <c r="W99">
+        <v>0.2452529789649284</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.008625860740622215</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2827994923895766</v>
+      </c>
+      <c r="C100">
+        <v>-81861.51332062534</v>
+      </c>
+      <c r="D100">
+        <v>16857.26667937466</v>
+      </c>
+      <c r="E100">
+        <v>92085.78</v>
+      </c>
+      <c r="F100">
+        <v>108643.78</v>
+      </c>
+      <c r="G100">
+        <v>9925</v>
+      </c>
+      <c r="H100">
+        <v>94303</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>378</v>
+      </c>
+      <c r="K100">
+        <v>150</v>
+      </c>
+      <c r="L100">
+        <v>228</v>
+      </c>
+      <c r="M100">
+        <v>26704.641124</v>
+      </c>
+      <c r="N100">
+        <v>-26476.641124</v>
+      </c>
+      <c r="O100">
+        <v>-6830.973409992001</v>
+      </c>
+      <c r="P100">
+        <v>-19645.667714008</v>
+      </c>
+      <c r="Q100">
+        <v>-19495.667714008</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.122305139679803</v>
+      </c>
+      <c r="T100">
+        <v>47.92540719395299</v>
+      </c>
+      <c r="U100">
+        <v>0.2458</v>
+      </c>
+      <c r="V100">
+        <v>0.002202763172396041</v>
+      </c>
+      <c r="W100">
+        <v>0.2452585608122251</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.008537841753473052</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2847994923895767</v>
+      </c>
+      <c r="C101">
+        <v>-83111.18861336577</v>
+      </c>
+      <c r="D101">
+        <v>16716.20138663423</v>
+      </c>
+      <c r="E101">
+        <v>93194.39</v>
+      </c>
+      <c r="F101">
+        <v>109752.39</v>
+      </c>
+      <c r="G101">
+        <v>9925</v>
+      </c>
+      <c r="H101">
+        <v>94303</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>378</v>
+      </c>
+      <c r="K101">
+        <v>150</v>
+      </c>
+      <c r="L101">
+        <v>228</v>
+      </c>
+      <c r="M101">
+        <v>26977.137462</v>
+      </c>
+      <c r="N101">
+        <v>-26749.137462</v>
+      </c>
+      <c r="O101">
+        <v>-6901.277465196001</v>
+      </c>
+      <c r="P101">
+        <v>-19847.859996804</v>
+      </c>
+      <c r="Q101">
+        <v>-19697.859996804</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.198810279359606</v>
+      </c>
+      <c r="T101">
+        <v>95.85081438790597</v>
+      </c>
+      <c r="U101">
+        <v>0.2458</v>
+      </c>
+      <c r="V101">
+        <v>0.002180513039341535</v>
+      </c>
+      <c r="W101">
+        <v>0.2452640298949299</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.008451600927680381</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.155</v>
+        <v>0.011</v>
       </c>
       <c r="E2">
         <v>0.186</v>
@@ -599,40 +599,40 @@
         <v>0.259</v>
       </c>
       <c r="G2">
-        <v>-0.001361933946203609</v>
+        <v>0.01624166228151266</v>
       </c>
       <c r="H2">
-        <v>-0.001361933946203609</v>
+        <v>0.007395502965312247</v>
       </c>
       <c r="I2">
-        <v>0.006639427987742594</v>
+        <v>0.003086200275909149</v>
       </c>
       <c r="J2">
-        <v>0.006490978860743926</v>
+        <v>0.003051698528352916</v>
       </c>
       <c r="K2">
-        <v>7811</v>
+        <v>7687.7</v>
       </c>
       <c r="L2">
-        <v>1.329758256724549</v>
+        <v>1.09335400281598</v>
       </c>
       <c r="M2">
         <v>6762</v>
       </c>
       <c r="N2">
-        <v>0.07170503589493442</v>
+        <v>0.07166415139131467</v>
       </c>
       <c r="O2">
-        <v>0.8657022148252465</v>
+        <v>0.8795868725366495</v>
       </c>
       <c r="P2">
         <v>199</v>
       </c>
       <c r="Q2">
-        <v>0.002110219187088428</v>
+        <v>0.002109015990368474</v>
       </c>
       <c r="R2">
-        <v>0.02547689156318013</v>
+        <v>0.02588550541774523</v>
       </c>
       <c r="S2">
         <v>6563</v>
@@ -641,73 +641,73 @@
         <v>0.9705708370304643</v>
       </c>
       <c r="U2">
-        <v>9925</v>
+        <v>9945.1</v>
       </c>
       <c r="V2">
-        <v>0.1052458564414706</v>
+        <v>0.1053988689739372</v>
       </c>
       <c r="W2">
-        <v>0.1953726863431716</v>
+        <v>0.2079923013036309</v>
       </c>
       <c r="X2">
-        <v>0.09284230137804994</v>
+        <v>0.3391509726337838</v>
       </c>
       <c r="Y2">
-        <v>0.1025303849651217</v>
+        <v>-0.1311586713301529</v>
       </c>
       <c r="Z2">
-        <v>0.1124275077994909</v>
+        <v>0.1341881875157446</v>
       </c>
       <c r="AA2">
-        <v>0.0007297645764926183</v>
+        <v>-0.05661798991201718</v>
       </c>
       <c r="AB2">
-        <v>0.08538115683291909</v>
+        <v>0.07995060246155389</v>
       </c>
       <c r="AC2">
-        <v>-0.08465139225642648</v>
+        <v>-0.1365685923735711</v>
       </c>
       <c r="AD2">
-        <v>16558</v>
+        <v>17426.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16558</v>
+        <v>17426.3</v>
       </c>
       <c r="AG2">
-        <v>6633</v>
+        <v>7481.199999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1493582053201757</v>
+        <v>0.1558938694668514</v>
       </c>
       <c r="AI2">
-        <v>0.2566733839714773</v>
+        <v>0.2690248518736936</v>
       </c>
       <c r="AJ2">
-        <v>0.06571490845684394</v>
+        <v>0.07346177261925803</v>
       </c>
       <c r="AK2">
-        <v>0.1215169002473207</v>
+        <v>0.136441810883319</v>
       </c>
       <c r="AL2">
-        <v>551</v>
+        <v>589.2</v>
       </c>
       <c r="AM2">
-        <v>-393</v>
+        <v>-355.3969999999999</v>
       </c>
       <c r="AN2">
-        <v>87.60846560846561</v>
+        <v>71.44854448544486</v>
       </c>
       <c r="AO2">
-        <v>0.07078039927404718</v>
+        <v>0.0368295994568907</v>
       </c>
       <c r="AP2">
-        <v>35.09523809523809</v>
+        <v>30.67322673226732</v>
       </c>
       <c r="AQ2">
-        <v>-0.09923664122137404</v>
+        <v>-0.06105847826515137</v>
       </c>
     </row>
     <row r="3">
@@ -787,10 +787,10 @@
         <v>0.1953726863431716</v>
       </c>
       <c r="X3">
-        <v>0.09284230137804994</v>
+        <v>0.09281205736081985</v>
       </c>
       <c r="Y3">
-        <v>0.1025303849651217</v>
+        <v>0.1025606289823517</v>
       </c>
       <c r="Z3">
         <v>0.1124275077994909</v>
@@ -799,10 +799,10 @@
         <v>0.0007297645764926183</v>
       </c>
       <c r="AB3">
-        <v>0.08538115683291909</v>
+        <v>0.08535543000782417</v>
       </c>
       <c r="AC3">
-        <v>-0.08465139225642648</v>
+        <v>-0.08462566543133154</v>
       </c>
       <c r="AD3">
         <v>16558</v>
@@ -845,6 +845,134 @@
       </c>
       <c r="AQ3">
         <v>-0.09923664122137404</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cnova N.V. (ENXTPA:CNV)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Retail (General)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.133</v>
+      </c>
+      <c r="G4">
+        <v>0.1055905988075694</v>
+      </c>
+      <c r="H4">
+        <v>0.05184481119847922</v>
+      </c>
+      <c r="I4">
+        <v>-0.01494858722889484</v>
+      </c>
+      <c r="J4">
+        <v>-0.01494858722889484</v>
+      </c>
+      <c r="K4">
+        <v>-123.3</v>
+      </c>
+      <c r="L4">
+        <v>-0.1065410870128748</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>20.1</v>
+      </c>
+      <c r="V4">
+        <v>0.3736059479553904</v>
+      </c>
+      <c r="W4">
+        <v>0.2206119162640902</v>
+      </c>
+      <c r="X4">
+        <v>0.5854898879067477</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3648779716426576</v>
+      </c>
+      <c r="Z4">
+        <v>7.623847167325424</v>
+      </c>
+      <c r="AA4">
+        <v>-0.113965744400527</v>
+      </c>
+      <c r="AB4">
+        <v>0.07454577491528362</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1885115193158106</v>
+      </c>
+      <c r="AD4">
+        <v>868.3</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>868.3</v>
+      </c>
+      <c r="AG4">
+        <v>848.1999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.9416549181216788</v>
+      </c>
+      <c r="AI4">
+        <v>3.266741911211438</v>
+      </c>
+      <c r="AJ4">
+        <v>0.9403547671840355</v>
+      </c>
+      <c r="AK4">
+        <v>3.452177452177453</v>
+      </c>
+      <c r="AL4">
+        <v>38.2</v>
+      </c>
+      <c r="AM4">
+        <v>37.603</v>
+      </c>
+      <c r="AN4">
+        <v>15.816029143898</v>
+      </c>
+      <c r="AO4">
+        <v>-0.4528795811518325</v>
+      </c>
+      <c r="AP4">
+        <v>15.44990892531876</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.460069675291865</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1267,7 @@
         <v>0.0707803992740472</v>
       </c>
       <c r="F2">
-        <v>3.55203708625837</v>
+        <v>3.71904063823435</v>
       </c>
       <c r="G2">
         <v>87.60846560846559</v>
@@ -1157,13 +1285,13 @@
         <v>94303</v>
       </c>
       <c r="L2">
-        <v>105122.090311532</v>
+        <v>105166.287665927</v>
       </c>
       <c r="M2">
         <v>100936</v>
       </c>
       <c r="N2">
-        <v>96305.700311532</v>
+        <v>96349.8976659269</v>
       </c>
       <c r="O2">
         <v>16558</v>
@@ -1172,16 +1300,16 @@
         <v>1108.61</v>
       </c>
       <c r="Q2">
-        <v>0.08538115683291909</v>
+        <v>0.0853554300078242</v>
       </c>
       <c r="R2">
-        <v>0.08728418663862959</v>
+        <v>0.08723820574789951</v>
       </c>
       <c r="S2">
         <v>0.0428876</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1322,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0928423013780499</v>
+        <v>0.09281205736081979</v>
       </c>
       <c r="X2">
-        <v>0.0877318875137673</v>
+        <v>0.08770492903828229</v>
       </c>
       <c r="Y2">
         <v>1.08572880740923</v>
@@ -1236,7 +1364,7 @@
         <v>94303</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1552,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08741994810473983</v>
+        <v>0.08739319017856015</v>
       </c>
       <c r="C2">
-        <v>105916.5576067847</v>
+        <v>105915.8789426729</v>
       </c>
       <c r="D2">
-        <v>95991.55760678467</v>
+        <v>95990.87894267295</v>
       </c>
       <c r="E2">
         <v>-16558</v>
@@ -1475,19 +1603,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08741994810473983</v>
+        <v>0.08739319017856015</v>
       </c>
       <c r="T2">
         <v>0.9605817593200962</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1634,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08728418663862959</v>
+        <v>0.08723820574789948</v>
       </c>
       <c r="C3">
-        <v>105122.090311532</v>
+        <v>105166.2876659269</v>
       </c>
       <c r="D3">
-        <v>96305.700311532</v>
+        <v>96349.89766592694</v>
       </c>
       <c r="E3">
         <v>-15449.39</v>
@@ -1539,37 +1667,37 @@
         <v>228</v>
       </c>
       <c r="M3">
-        <v>64.18851900000001</v>
+        <v>61.30613300000002</v>
       </c>
       <c r="N3">
-        <v>163.811481</v>
+        <v>166.693867</v>
       </c>
       <c r="O3">
-        <v>42.26336209799999</v>
+        <v>43.007017686</v>
       </c>
       <c r="P3">
-        <v>121.548118902</v>
+        <v>123.686849314</v>
       </c>
       <c r="Q3">
-        <v>271.548118902</v>
+        <v>273.686849314</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08773188751376726</v>
+        <v>0.08770492903828229</v>
       </c>
       <c r="T3">
         <v>0.96778127109197</v>
       </c>
       <c r="U3">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>3.552037086258369</v>
+        <v>3.71904063823435</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1716,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09018700230925084</v>
+        <v>0.08813249394448081</v>
       </c>
       <c r="C4">
-        <v>97715.29206969606</v>
+        <v>102022.2536170282</v>
       </c>
       <c r="D4">
-        <v>90007.51206969607</v>
+        <v>94314.47361702818</v>
       </c>
       <c r="E4">
         <v>-14340.78</v>
@@ -1621,45 +1749,45 @@
         <v>228</v>
       </c>
       <c r="M4">
-        <v>478.4760760000001</v>
+        <v>262.962292</v>
       </c>
       <c r="N4">
-        <v>-250.4760760000001</v>
+        <v>-34.96229200000005</v>
       </c>
       <c r="O4">
-        <v>-64.62282760800002</v>
+        <v>-9.020271336000013</v>
       </c>
       <c r="P4">
-        <v>-185.8532483920001</v>
+        <v>-25.94202066400003</v>
       </c>
       <c r="Q4">
-        <v>-35.85324839200007</v>
+        <v>124.057979336</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08816491093190845</v>
+        <v>0.08805214729438801</v>
       </c>
       <c r="T4">
-        <v>0.9777753824680363</v>
+        <v>0.9758001684616172</v>
       </c>
       <c r="U4">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V4">
-        <v>0.1229403160378702</v>
+        <v>0.2236974721835783</v>
       </c>
       <c r="W4">
-        <v>0.1892694797990276</v>
+        <v>0.09206947979902763</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y4">
-        <v>0.4765128528599619</v>
+        <v>0.8670444658278228</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1798,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09188700230925084</v>
+        <v>0.09140267051435594</v>
       </c>
       <c r="C5">
-        <v>93286.59695129881</v>
+        <v>94150.33396117331</v>
       </c>
       <c r="D5">
-        <v>86687.42695129881</v>
+        <v>87551.16396117331</v>
       </c>
       <c r="E5">
         <v>-13232.17</v>
@@ -1703,37 +1831,37 @@
         <v>228</v>
       </c>
       <c r="M5">
-        <v>717.714114</v>
+        <v>667.8266640000001</v>
       </c>
       <c r="N5">
-        <v>-489.714114</v>
+        <v>-439.8266640000001</v>
       </c>
       <c r="O5">
-        <v>-126.346241412</v>
+        <v>-113.475279312</v>
       </c>
       <c r="P5">
-        <v>-363.367872588</v>
+        <v>-326.3513846880001</v>
       </c>
       <c r="Q5">
-        <v>-213.367872588</v>
+        <v>-176.3513846880001</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0886016625910003</v>
+        <v>0.08856626898801585</v>
       </c>
       <c r="T5">
-        <v>0.987855541050181</v>
+        <v>0.9876736486839691</v>
       </c>
       <c r="U5">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V5">
-        <v>0.08196021069191346</v>
+        <v>0.08808273639101058</v>
       </c>
       <c r="W5">
-        <v>0.1981129865326851</v>
+        <v>0.1831129865326851</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.3176752352399747</v>
+        <v>0.341405955003917</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1880,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09358700230925084</v>
+        <v>0.09295267051435592</v>
       </c>
       <c r="C6">
-        <v>89094.12274773316</v>
+        <v>90163.74689943931</v>
       </c>
       <c r="D6">
-        <v>83603.56274773316</v>
+        <v>84673.18689943932</v>
       </c>
       <c r="E6">
         <v>-12123.56</v>
@@ -1785,37 +1913,37 @@
         <v>228</v>
       </c>
       <c r="M6">
-        <v>956.9521520000002</v>
+        <v>890.4355520000001</v>
       </c>
       <c r="N6">
-        <v>-728.9521520000002</v>
+        <v>-662.4355520000001</v>
       </c>
       <c r="O6">
-        <v>-188.0696552160001</v>
+        <v>-170.908372416</v>
       </c>
       <c r="P6">
-        <v>-540.8824967840001</v>
+        <v>-491.5271795840001</v>
       </c>
       <c r="Q6">
-        <v>-390.8824967840001</v>
+        <v>-341.5271795840001</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08904751324298987</v>
+        <v>0.08901175095664102</v>
       </c>
       <c r="T6">
-        <v>0.9981457029361204</v>
+        <v>0.9979619158577603</v>
       </c>
       <c r="U6">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V6">
-        <v>0.06147015801893509</v>
+        <v>0.06606205229325793</v>
       </c>
       <c r="W6">
-        <v>0.2025347398995138</v>
+        <v>0.1875347398995138</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.2382564264299809</v>
+        <v>0.2560544662529377</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1962,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09679949238957666</v>
+        <v>0.09450267051435593</v>
       </c>
       <c r="C7">
-        <v>82719.27178291362</v>
+        <v>86360.34751093041</v>
       </c>
       <c r="D7">
-        <v>78337.32178291363</v>
+        <v>81978.39751093042</v>
       </c>
       <c r="E7">
         <v>-11014.95</v>
@@ -1867,45 +1995,45 @@
         <v>228</v>
       </c>
       <c r="M7">
-        <v>1362.48169</v>
+        <v>1113.04444</v>
       </c>
       <c r="N7">
-        <v>-1134.48169</v>
+        <v>-885.0444400000001</v>
       </c>
       <c r="O7">
-        <v>-292.69627602</v>
+        <v>-228.34146552</v>
       </c>
       <c r="P7">
-        <v>-841.78541398</v>
+        <v>-656.7029744800001</v>
       </c>
       <c r="Q7">
-        <v>-691.78541398</v>
+        <v>-506.7029744800001</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08951589767746959</v>
+        <v>0.08946661149302672</v>
       </c>
       <c r="T7">
-        <v>1.008955940925327</v>
+        <v>1.008466778129947</v>
       </c>
       <c r="U7">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V7">
-        <v>0.04317415817896239</v>
+        <v>0.05284964183460635</v>
       </c>
       <c r="W7">
-        <v>0.2351877919196111</v>
+        <v>0.190187791919611</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y7">
-        <v>0.1673416983680712</v>
+        <v>0.2048435730023502</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +2044,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09879949238957667</v>
+        <v>0.09816898444186427</v>
       </c>
       <c r="C8">
-        <v>78654.50811989023</v>
+        <v>79512.49044031375</v>
       </c>
       <c r="D8">
-        <v>75381.16811989024</v>
+        <v>76239.15044031375</v>
       </c>
       <c r="E8">
         <v>-9906.34</v>
@@ -1949,37 +2077,37 @@
         <v>228</v>
       </c>
       <c r="M8">
-        <v>1634.978028</v>
+        <v>1568.461428</v>
       </c>
       <c r="N8">
-        <v>-1406.978028</v>
+        <v>-1340.461428</v>
       </c>
       <c r="O8">
-        <v>-363.000331224</v>
+        <v>-345.8390484240001</v>
       </c>
       <c r="P8">
-        <v>-1043.977696776</v>
+        <v>-994.622379576</v>
       </c>
       <c r="Q8">
-        <v>-893.9776967759999</v>
+        <v>-844.622379576</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08998096041871927</v>
+        <v>0.08994850515519545</v>
       </c>
       <c r="T8">
-        <v>1.019689514764958</v>
+        <v>1.019595962013752</v>
       </c>
       <c r="U8">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.03597846514913532</v>
+        <v>0.0375042694387509</v>
       </c>
       <c r="W8">
-        <v>0.2369564932663426</v>
+        <v>0.2269564932663426</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.1394514153067261</v>
+        <v>0.1453653854215151</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +2126,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1007994923895767</v>
+        <v>0.1000689844418643</v>
       </c>
       <c r="C9">
-        <v>74804.7394347902</v>
+        <v>75734.68757948602</v>
       </c>
       <c r="D9">
-        <v>72640.0094347902</v>
+        <v>73569.95757948603</v>
       </c>
       <c r="E9">
         <v>-8797.73</v>
@@ -2031,37 +2159,37 @@
         <v>228</v>
       </c>
       <c r="M9">
-        <v>1907.474366</v>
+        <v>1829.871666</v>
       </c>
       <c r="N9">
-        <v>-1679.474366</v>
+        <v>-1601.871666</v>
       </c>
       <c r="O9">
-        <v>-433.304386428</v>
+        <v>-413.2828898280001</v>
       </c>
       <c r="P9">
-        <v>-1246.169979572</v>
+        <v>-1188.588776172</v>
       </c>
       <c r="Q9">
-        <v>-1096.169979572</v>
+        <v>-1038.588776172</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09045602450924313</v>
+        <v>0.09042322026439109</v>
       </c>
       <c r="T9">
-        <v>1.030653918149528</v>
+        <v>1.03055935945476</v>
       </c>
       <c r="U9">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.03083868441354456</v>
+        <v>0.03214651666178649</v>
       </c>
       <c r="W9">
-        <v>0.2382198513711508</v>
+        <v>0.2282198513711508</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.1195297845486223</v>
+        <v>0.1245989017898701</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2208,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1027994923895767</v>
+        <v>0.1019689844418643</v>
       </c>
       <c r="C10">
-        <v>71147.33447576444</v>
+        <v>72137.46360880435</v>
       </c>
       <c r="D10">
-        <v>70091.21447576444</v>
+        <v>71081.34360880435</v>
       </c>
       <c r="E10">
         <v>-7689.119999999999</v>
@@ -2113,37 +2241,37 @@
         <v>228</v>
       </c>
       <c r="M10">
-        <v>2179.970704</v>
+        <v>2091.281904</v>
       </c>
       <c r="N10">
-        <v>-1951.970704</v>
+        <v>-1863.281904</v>
       </c>
       <c r="O10">
-        <v>-503.6084416320001</v>
+        <v>-480.7267312320001</v>
       </c>
       <c r="P10">
-        <v>-1448.362262368</v>
+        <v>-1382.555172768</v>
       </c>
       <c r="Q10">
-        <v>-1298.362262368</v>
+        <v>-1232.555172768</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09094141607999577</v>
+        <v>0.09090825526726491</v>
       </c>
       <c r="T10">
-        <v>1.041856678129414</v>
+        <v>1.041761091622746</v>
       </c>
       <c r="U10">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.02698384886185149</v>
+        <v>0.02812820207906317</v>
       </c>
       <c r="W10">
-        <v>0.2391673699497569</v>
+        <v>0.2291673699497569</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.1045885614800446</v>
+        <v>0.1090240390661363</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2290,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1047994923895766</v>
+        <v>0.1038689844418643</v>
       </c>
       <c r="C11">
-        <v>67662.73066168388</v>
+        <v>68703.09306460305</v>
       </c>
       <c r="D11">
-        <v>67715.22066168388</v>
+        <v>68755.58306460305</v>
       </c>
       <c r="E11">
         <v>-6580.51</v>
@@ -2195,37 +2323,37 @@
         <v>228</v>
       </c>
       <c r="M11">
-        <v>2452.467042</v>
+        <v>2352.692142</v>
       </c>
       <c r="N11">
-        <v>-2224.467042</v>
+        <v>-2124.692142</v>
       </c>
       <c r="O11">
-        <v>-573.9124968360001</v>
+        <v>-548.170572636</v>
       </c>
       <c r="P11">
-        <v>-1650.554545164</v>
+        <v>-1576.521569364</v>
       </c>
       <c r="Q11">
-        <v>-1500.554545164</v>
+        <v>-1426.521569364</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09143747559735835</v>
+        <v>0.091403950380092</v>
       </c>
       <c r="T11">
-        <v>1.053305652614352</v>
+        <v>1.053209015706513</v>
       </c>
       <c r="U11">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.02398564343275688</v>
+        <v>0.0250028462925006</v>
       </c>
       <c r="W11">
-        <v>0.2399043288442284</v>
+        <v>0.2299043288442284</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.09296761020448407</v>
+        <v>0.09691025694767674</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2372,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1067994923895767</v>
+        <v>0.1057689844418643</v>
       </c>
       <c r="C12">
-        <v>64333.93101717937</v>
+        <v>65416.09686982951</v>
       </c>
       <c r="D12">
-        <v>65495.03101717938</v>
+        <v>66577.19686982951</v>
       </c>
       <c r="E12">
         <v>-5471.9</v>
@@ -2277,37 +2405,37 @@
         <v>228</v>
       </c>
       <c r="M12">
-        <v>2724.96338</v>
+        <v>2614.10238</v>
       </c>
       <c r="N12">
-        <v>-2496.96338</v>
+        <v>-2386.10238</v>
       </c>
       <c r="O12">
-        <v>-644.21655204</v>
+        <v>-615.61441404</v>
       </c>
       <c r="P12">
-        <v>-1852.74682796</v>
+        <v>-1770.48796596</v>
       </c>
       <c r="Q12">
-        <v>-1702.74682796</v>
+        <v>-1620.48796596</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09194455865955123</v>
+        <v>0.0919106609398708</v>
       </c>
       <c r="T12">
-        <v>1.065009048754512</v>
+        <v>1.064911338103252</v>
       </c>
       <c r="U12">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.0215870790894812</v>
+        <v>0.02250256166325054</v>
       </c>
       <c r="W12">
-        <v>0.2404938959598055</v>
+        <v>0.2304938959598055</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.08367084918403567</v>
+        <v>0.08721923125290909</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2454,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1087994923895767</v>
+        <v>0.1076689844418643</v>
       </c>
       <c r="C13">
-        <v>61146.09693035119</v>
+        <v>62262.89740074681</v>
       </c>
       <c r="D13">
-        <v>63415.80693035118</v>
+        <v>64532.60740074681</v>
       </c>
       <c r="E13">
         <v>-4363.289999999999</v>
@@ -2359,37 +2487,37 @@
         <v>228</v>
       </c>
       <c r="M13">
-        <v>2997.459718000001</v>
+        <v>2875.512618</v>
       </c>
       <c r="N13">
-        <v>-2769.459718000001</v>
+        <v>-2647.512618</v>
       </c>
       <c r="O13">
-        <v>-714.5206072440002</v>
+        <v>-683.0582554440001</v>
       </c>
       <c r="P13">
-        <v>-2054.939110756</v>
+        <v>-1964.454362556</v>
       </c>
       <c r="Q13">
-        <v>-1904.939110756</v>
+        <v>-1814.454362556</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09246303684673721</v>
+        <v>0.09242875825380194</v>
       </c>
       <c r="T13">
-        <v>1.076975442560742</v>
+        <v>1.076876634036996</v>
       </c>
       <c r="U13">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.01962461735407381</v>
+        <v>0.02045687423931867</v>
       </c>
       <c r="W13">
-        <v>0.2409762690543687</v>
+        <v>0.2309762690543687</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.07606440834912331</v>
+        <v>0.07929021022991734</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2536,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1107994923895766</v>
+        <v>0.1095689844418643</v>
       </c>
       <c r="C14">
-        <v>58086.21609425707</v>
+        <v>59231.53521746249</v>
       </c>
       <c r="D14">
-        <v>61464.53609425707</v>
+        <v>62609.85521746249</v>
       </c>
       <c r="E14">
         <v>-3254.68</v>
@@ -2441,37 +2569,37 @@
         <v>228</v>
       </c>
       <c r="M14">
-        <v>3269.956056</v>
+        <v>3136.922856</v>
       </c>
       <c r="N14">
-        <v>-3041.956056</v>
+        <v>-2908.922856</v>
       </c>
       <c r="O14">
-        <v>-784.824662448</v>
+        <v>-750.5020968480001</v>
       </c>
       <c r="P14">
-        <v>-2257.131393552</v>
+        <v>-2158.420759152</v>
       </c>
       <c r="Q14">
-        <v>-2107.131393552</v>
+        <v>-2008.420759152</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09299329862908648</v>
+        <v>0.09295863050668604</v>
       </c>
       <c r="T14">
-        <v>1.089213799862569</v>
+        <v>1.089113868514689</v>
       </c>
       <c r="U14">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.01798923257456766</v>
+        <v>0.01875213471937545</v>
       </c>
       <c r="W14">
-        <v>0.2413782466331713</v>
+        <v>0.2313782466331713</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.06972570765336306</v>
+        <v>0.07268269271075756</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2618,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1127994923895766</v>
+        <v>0.1114689844418643</v>
       </c>
       <c r="C15">
-        <v>55142.82992201791</v>
+        <v>56311.43496945217</v>
       </c>
       <c r="D15">
-        <v>59629.75992201791</v>
+        <v>60798.36496945217</v>
       </c>
       <c r="E15">
         <v>-2146.07</v>
@@ -2523,37 +2651,37 @@
         <v>228</v>
       </c>
       <c r="M15">
-        <v>3542.452394</v>
+        <v>3398.333094</v>
       </c>
       <c r="N15">
-        <v>-3314.452394</v>
+        <v>-3170.333094</v>
       </c>
       <c r="O15">
-        <v>-855.1287176520001</v>
+        <v>-817.945938252</v>
       </c>
       <c r="P15">
-        <v>-2459.323676348</v>
+        <v>-2352.387155748</v>
       </c>
       <c r="Q15">
-        <v>-2309.323676348</v>
+        <v>-2202.387155748</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09353575033746678</v>
+        <v>0.09350068373090083</v>
       </c>
       <c r="T15">
-        <v>1.101733498711564</v>
+        <v>1.101632418727502</v>
       </c>
       <c r="U15">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.01660544545344707</v>
+        <v>0.01730966281788503</v>
       </c>
       <c r="W15">
-        <v>0.2417183815075427</v>
+        <v>0.2317183815075427</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.06436219168002744</v>
+        <v>0.06709171634839162</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2700,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1147994923895767</v>
+        <v>0.1133689844418643</v>
       </c>
       <c r="C16">
-        <v>52305.80836834026</v>
+        <v>53493.21079667519</v>
       </c>
       <c r="D16">
-        <v>57901.34836834027</v>
+        <v>59088.75079667518</v>
       </c>
       <c r="E16">
         <v>-1037.459999999999</v>
@@ -2605,37 +2733,37 @@
         <v>228</v>
       </c>
       <c r="M16">
-        <v>3814.948732</v>
+        <v>3659.743332</v>
       </c>
       <c r="N16">
-        <v>-3586.948732</v>
+        <v>-3431.743332</v>
       </c>
       <c r="O16">
-        <v>-925.4327728560002</v>
+        <v>-885.3897796560002</v>
       </c>
       <c r="P16">
-        <v>-2661.515959144</v>
+        <v>-2546.353552344</v>
       </c>
       <c r="Q16">
-        <v>-2511.515959144</v>
+        <v>-2396.353552344</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09409081720185594</v>
+        <v>0.09405534284405083</v>
       </c>
       <c r="T16">
-        <v>1.114544353347745</v>
+        <v>1.114442098015031</v>
       </c>
       <c r="U16">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.01541934220677228</v>
+        <v>0.01607325833089324</v>
       </c>
       <c r="W16">
-        <v>0.2420099256855754</v>
+        <v>0.2320099256855754</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.05976489227431114</v>
+        <v>0.06229945089493505</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2782,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1167994923895767</v>
+        <v>0.1152689844418643</v>
       </c>
       <c r="C17">
-        <v>49566.1628096455</v>
+        <v>50768.5036647582</v>
       </c>
       <c r="D17">
-        <v>56270.31280964548</v>
+        <v>57472.6536647582</v>
       </c>
       <c r="E17">
         <v>71.14999999999782</v>
@@ -2687,37 +2815,37 @@
         <v>228</v>
       </c>
       <c r="M17">
-        <v>4087.44507</v>
+        <v>3921.153569999999</v>
       </c>
       <c r="N17">
-        <v>-3859.44507</v>
+        <v>-3693.153569999999</v>
       </c>
       <c r="O17">
-        <v>-995.73682806</v>
+        <v>-952.8336210599999</v>
       </c>
       <c r="P17">
-        <v>-2863.70824194</v>
+        <v>-2740.319948939999</v>
       </c>
       <c r="Q17">
-        <v>-2713.70824194</v>
+        <v>-2590.319948939999</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09465894446305426</v>
+        <v>0.09462305275986319</v>
       </c>
       <c r="T17">
-        <v>1.127656639857718</v>
+        <v>1.12755318152109</v>
       </c>
       <c r="U17">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01439138605965413</v>
+        <v>0.01500170777550036</v>
       </c>
       <c r="W17">
-        <v>0.242262597306537</v>
+        <v>0.232262597306537</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.05578056612269044</v>
+        <v>0.05814615416860602</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2864,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1187994923895767</v>
+        <v>0.1171689844418643</v>
       </c>
       <c r="C18">
-        <v>46915.88968384324</v>
+        <v>48129.84468315902</v>
       </c>
       <c r="D18">
-        <v>54728.64968384324</v>
+        <v>55942.60468315902</v>
       </c>
       <c r="E18">
         <v>1179.760000000002</v>
@@ -2769,37 +2897,37 @@
         <v>228</v>
       </c>
       <c r="M18">
-        <v>4359.941408000001</v>
+        <v>4182.563808000001</v>
       </c>
       <c r="N18">
-        <v>-4131.941408000001</v>
+        <v>-3954.563808000001</v>
       </c>
       <c r="O18">
-        <v>-1066.040883264</v>
+        <v>-1020.277462464</v>
       </c>
       <c r="P18">
-        <v>-3065.900524736</v>
+        <v>-2934.286345536001</v>
       </c>
       <c r="Q18">
-        <v>-2915.900524736</v>
+        <v>-2784.286345536001</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09524059856380489</v>
+        <v>0.095204279578433</v>
       </c>
       <c r="T18">
-        <v>1.141081123665548</v>
+        <v>1.140976433682056</v>
       </c>
       <c r="U18">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01349192443092575</v>
+        <v>0.01406410103953159</v>
       </c>
       <c r="W18">
-        <v>0.2424836849748785</v>
+        <v>0.2324836849748785</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.05229428074002229</v>
+        <v>0.05451201953306817</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2946,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1207994923895767</v>
+        <v>0.1190689844418643</v>
       </c>
       <c r="C19">
-        <v>44347.83914791104</v>
+        <v>45570.53968980422</v>
       </c>
       <c r="D19">
-        <v>53269.20914791105</v>
+        <v>54491.90968980423</v>
       </c>
       <c r="E19">
         <v>2288.370000000003</v>
@@ -2851,37 +2979,37 @@
         <v>228</v>
       </c>
       <c r="M19">
-        <v>4632.437746000001</v>
+        <v>4443.974046000001</v>
       </c>
       <c r="N19">
-        <v>-4404.437746000001</v>
+        <v>-4215.974046000001</v>
       </c>
       <c r="O19">
-        <v>-1136.344938468</v>
+        <v>-1087.721303868</v>
       </c>
       <c r="P19">
-        <v>-3268.092807532001</v>
+        <v>-3128.252742132001</v>
       </c>
       <c r="Q19">
-        <v>-3118.092807532001</v>
+        <v>-2978.252742132001</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09583626842601942</v>
+        <v>0.09579951186251051</v>
       </c>
       <c r="T19">
-        <v>1.154829089010917</v>
+        <v>1.154723137702321</v>
       </c>
       <c r="U19">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01269828181734188</v>
+        <v>0.01323680097838267</v>
       </c>
       <c r="W19">
-        <v>0.2426787623292974</v>
+        <v>0.2326787623292974</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.04921814657884449</v>
+        <v>0.05130543014876998</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +3028,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1227994923895767</v>
+        <v>0.1209689844418643</v>
       </c>
       <c r="C20">
-        <v>41855.60420455695</v>
+        <v>43084.57133942368</v>
       </c>
       <c r="D20">
-        <v>51885.58420455694</v>
+        <v>53114.55133942368</v>
       </c>
       <c r="E20">
         <v>3396.98</v>
@@ -2933,37 +3061,37 @@
         <v>228</v>
       </c>
       <c r="M20">
-        <v>4904.934084</v>
+        <v>4705.384284</v>
       </c>
       <c r="N20">
-        <v>-4676.934084</v>
+        <v>-4477.384284</v>
       </c>
       <c r="O20">
-        <v>-1206.648993672</v>
+        <v>-1155.165145272</v>
       </c>
       <c r="P20">
-        <v>-3470.285090328</v>
+        <v>-3322.219138728</v>
       </c>
       <c r="Q20">
-        <v>-3320.285090328</v>
+        <v>-3172.219138728</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09644646682145866</v>
+        <v>0.09640926200717526</v>
       </c>
       <c r="T20">
-        <v>1.16891237058422</v>
+        <v>1.168805127186496</v>
       </c>
       <c r="U20">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01199282171637844</v>
+        <v>0.0125014231462503</v>
       </c>
       <c r="W20">
-        <v>0.2428521644221142</v>
+        <v>0.2328521644221142</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.04648380510224204</v>
+        <v>0.04845512847383837</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +3110,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1247994923895767</v>
+        <v>0.1228689844418643</v>
       </c>
       <c r="C21">
-        <v>39433.42667051028</v>
+        <v>40666.51567492253</v>
       </c>
       <c r="D21">
-        <v>50572.01667051028</v>
+        <v>51805.10567492253</v>
       </c>
       <c r="E21">
         <v>4505.59</v>
@@ -3015,37 +3143,37 @@
         <v>228</v>
       </c>
       <c r="M21">
-        <v>5177.430422</v>
+        <v>4966.794522</v>
       </c>
       <c r="N21">
-        <v>-4949.430422</v>
+        <v>-4738.794522</v>
       </c>
       <c r="O21">
-        <v>-1276.953048876</v>
+        <v>-1222.608986676</v>
       </c>
       <c r="P21">
-        <v>-3672.477373124</v>
+        <v>-3516.185535324</v>
       </c>
       <c r="Q21">
-        <v>-3522.477373124</v>
+        <v>-3366.185535324</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09707173184394581</v>
+        <v>0.09703406771096756</v>
       </c>
       <c r="T21">
-        <v>1.183343387505013</v>
+        <v>1.183234820114724</v>
       </c>
       <c r="U21">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.01136162057341115</v>
+        <v>0.01184345350697397</v>
       </c>
       <c r="W21">
-        <v>0.2430073136630556</v>
+        <v>0.2330073136630555</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.04403728904422932</v>
+        <v>0.04590485855416271</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3192,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1267994923895767</v>
+        <v>0.1247689844418643</v>
       </c>
       <c r="C22">
-        <v>37076.11707552325</v>
+        <v>38311.47074254963</v>
       </c>
       <c r="D22">
-        <v>49323.31707552324</v>
+        <v>50558.67074254963</v>
       </c>
       <c r="E22">
         <v>5614.200000000001</v>
@@ -3097,37 +3225,37 @@
         <v>228</v>
       </c>
       <c r="M22">
-        <v>5449.92676</v>
+        <v>5228.204760000001</v>
       </c>
       <c r="N22">
-        <v>-5221.92676</v>
+        <v>-5000.204760000001</v>
       </c>
       <c r="O22">
-        <v>-1347.25710408</v>
+        <v>-1290.05282808</v>
       </c>
       <c r="P22">
-        <v>-3874.66965592</v>
+        <v>-3710.151931920001</v>
       </c>
       <c r="Q22">
-        <v>-3724.66965592</v>
+        <v>-3560.151931920001</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09771262849199513</v>
+        <v>0.09767449355735464</v>
       </c>
       <c r="T22">
-        <v>1.198135179848826</v>
+        <v>1.198025255366158</v>
       </c>
       <c r="U22">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0107935395447406</v>
+        <v>0.01125128083162527</v>
       </c>
       <c r="W22">
-        <v>0.2431469479799028</v>
+        <v>0.2331469479799028</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.04183542459201783</v>
+        <v>0.04360961562645449</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3274,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1287994923895767</v>
+        <v>0.1266689844418643</v>
       </c>
       <c r="C23">
-        <v>34778.98614231047</v>
+        <v>36014.99527009646</v>
       </c>
       <c r="D23">
-        <v>48134.79614231046</v>
+        <v>49370.80527009645</v>
       </c>
       <c r="E23">
         <v>6722.809999999998</v>
@@ -3179,37 +3307,37 @@
         <v>228</v>
       </c>
       <c r="M23">
-        <v>5722.423098</v>
+        <v>5489.614998</v>
       </c>
       <c r="N23">
-        <v>-5494.423098</v>
+        <v>-5261.614998</v>
       </c>
       <c r="O23">
-        <v>-1417.561159284</v>
+        <v>-1357.496669484</v>
       </c>
       <c r="P23">
-        <v>-4076.861938716</v>
+        <v>-3904.118328516</v>
       </c>
       <c r="Q23">
-        <v>-3926.861938716</v>
+        <v>-3754.118328516</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09836975037164064</v>
+        <v>0.0983311327163085</v>
       </c>
       <c r="T23">
-        <v>1.213301447948178</v>
+        <v>1.213190132016363</v>
       </c>
       <c r="U23">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01027956147118152</v>
+        <v>0.01071550555392883</v>
       </c>
       <c r="W23">
-        <v>0.2432732837903836</v>
+        <v>0.2332732837903836</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.03984326151620743</v>
+        <v>0.04153296726329003</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3356,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1307994923895767</v>
+        <v>0.1285689844418643</v>
       </c>
       <c r="C24">
-        <v>32537.78593996678</v>
+        <v>33773.05579111667</v>
       </c>
       <c r="D24">
-        <v>47002.20593996678</v>
+        <v>48237.47579111667</v>
       </c>
       <c r="E24">
         <v>7831.420000000002</v>
@@ -3261,37 +3389,37 @@
         <v>228</v>
       </c>
       <c r="M24">
-        <v>5994.919436000001</v>
+        <v>5751.025236</v>
       </c>
       <c r="N24">
-        <v>-5766.919436000001</v>
+        <v>-5523.025236</v>
       </c>
       <c r="O24">
-        <v>-1487.865214488</v>
+        <v>-1424.940510888</v>
       </c>
       <c r="P24">
-        <v>-4279.054221512</v>
+        <v>-4098.084725112</v>
       </c>
       <c r="Q24">
-        <v>-4129.054221512</v>
+        <v>-3948.084725112</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09904372153025143</v>
+        <v>0.099004608776774</v>
       </c>
       <c r="T24">
-        <v>1.228856594716744</v>
+        <v>1.228743851657598</v>
       </c>
       <c r="U24">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.009812308677036906</v>
+        <v>0.01022843711965934</v>
       </c>
       <c r="W24">
-        <v>0.2433881345271844</v>
+        <v>0.2333881345271843</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.03803220417456166</v>
+        <v>0.03964510511495867</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3438,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1327994923895767</v>
+        <v>0.1304689844418643</v>
       </c>
       <c r="C25">
-        <v>30348.65915420222</v>
+        <v>31581.98088844558</v>
       </c>
       <c r="D25">
-        <v>45921.68915420222</v>
+        <v>47155.01088844558</v>
       </c>
       <c r="E25">
         <v>8940.030000000002</v>
@@ -3343,37 +3471,37 @@
         <v>228</v>
       </c>
       <c r="M25">
-        <v>6267.415774000001</v>
+        <v>6012.435474000001</v>
       </c>
       <c r="N25">
-        <v>-6039.415774000001</v>
+        <v>-5784.435474000001</v>
       </c>
       <c r="O25">
-        <v>-1558.169269692</v>
+        <v>-1492.384352292</v>
       </c>
       <c r="P25">
-        <v>-4481.246504308001</v>
+        <v>-4292.051121708</v>
       </c>
       <c r="Q25">
-        <v>-4331.246504308001</v>
+        <v>-4142.051121708</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0997351984332417</v>
+        <v>0.09969557772192691</v>
       </c>
       <c r="T25">
-        <v>1.244815771271507</v>
+        <v>1.244701564016788</v>
       </c>
       <c r="U25">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.009385686560643997</v>
+        <v>0.009783722462282842</v>
       </c>
       <c r="W25">
-        <v>0.2434929982433937</v>
+        <v>0.2334929982433937</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.03637863008001552</v>
+        <v>0.03792140489256912</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3520,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1347994923895767</v>
+        <v>0.1323689844418643</v>
       </c>
       <c r="C26">
-        <v>28208.09519758436</v>
+        <v>29438.421463248</v>
       </c>
       <c r="D26">
-        <v>44889.73519758436</v>
+        <v>46120.061463248</v>
       </c>
       <c r="E26">
         <v>10048.64</v>
@@ -3425,37 +3553,37 @@
         <v>228</v>
       </c>
       <c r="M26">
-        <v>6539.912112</v>
+        <v>6273.845712</v>
       </c>
       <c r="N26">
-        <v>-6311.912112</v>
+        <v>-6045.845712</v>
       </c>
       <c r="O26">
-        <v>-1628.473324896</v>
+        <v>-1559.828193696</v>
       </c>
       <c r="P26">
-        <v>-4683.438787104</v>
+        <v>-4486.017518304</v>
       </c>
       <c r="Q26">
-        <v>-4533.438787104</v>
+        <v>-4336.017518304</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.100444872096837</v>
+        <v>0.1004047300603733</v>
       </c>
       <c r="T26">
-        <v>1.261194926156659</v>
+        <v>1.261079216174903</v>
       </c>
       <c r="U26">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.008994616287283831</v>
+        <v>0.009376067359687726</v>
       </c>
       <c r="W26">
-        <v>0.2435891233165857</v>
+        <v>0.2335891233165856</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.03486285382668153</v>
+        <v>0.03634134635537878</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3602,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1367994923895766</v>
+        <v>0.1342689844418643</v>
       </c>
       <c r="C27">
-        <v>26112.89210747334</v>
+        <v>27339.31612374566</v>
       </c>
       <c r="D27">
-        <v>43903.14210747334</v>
+        <v>45129.56612374566</v>
       </c>
       <c r="E27">
         <v>11157.25</v>
@@ -3507,37 +3635,37 @@
         <v>228</v>
       </c>
       <c r="M27">
-        <v>6812.408450000001</v>
+        <v>6535.255950000001</v>
       </c>
       <c r="N27">
-        <v>-6584.408450000001</v>
+        <v>-6307.255950000001</v>
       </c>
       <c r="O27">
-        <v>-1698.7773801</v>
+        <v>-1627.2720351</v>
       </c>
       <c r="P27">
-        <v>-4885.631069900001</v>
+        <v>-4679.9839149</v>
       </c>
       <c r="Q27">
-        <v>-4735.631069900001</v>
+        <v>-4529.9839149</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1011734703914615</v>
+        <v>0.101132793127845</v>
       </c>
       <c r="T27">
-        <v>1.278010858505414</v>
+        <v>1.277893605723902</v>
       </c>
       <c r="U27">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.008634831635792478</v>
+        <v>0.009001024665300216</v>
       </c>
       <c r="W27">
-        <v>0.2436775583839222</v>
+        <v>0.2336775583839222</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.03346833967361429</v>
+        <v>0.03488769250116364</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3684,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1387994923895767</v>
+        <v>0.1361689844418643</v>
       </c>
       <c r="C28">
-        <v>24060.12336037904</v>
+        <v>25281.86094013869</v>
       </c>
       <c r="D28">
-        <v>42958.98336037904</v>
+        <v>44180.72094013869</v>
       </c>
       <c r="E28">
         <v>12265.86</v>
@@ -3589,37 +3717,37 @@
         <v>228</v>
       </c>
       <c r="M28">
-        <v>7084.904788000001</v>
+        <v>6796.666188</v>
       </c>
       <c r="N28">
-        <v>-6856.904788000001</v>
+        <v>-6568.666188</v>
       </c>
       <c r="O28">
-        <v>-1769.081435304</v>
+        <v>-1694.715876504</v>
       </c>
       <c r="P28">
-        <v>-5087.823352696</v>
+        <v>-4873.950311496</v>
       </c>
       <c r="Q28">
-        <v>-4937.823352696</v>
+        <v>-4723.950311496</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1019217605318866</v>
+        <v>0.1018805335755185</v>
       </c>
       <c r="T28">
-        <v>1.295281275512244</v>
+        <v>1.295162438233685</v>
       </c>
       <c r="U28">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.008302722726723536</v>
+        <v>0.008654831408942517</v>
       </c>
       <c r="W28">
-        <v>0.2437591907537714</v>
+        <v>0.2337591907537714</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.03218109584001372</v>
+        <v>0.03354585817419575</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3766,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1407994923895767</v>
+        <v>0.1380689844418643</v>
       </c>
       <c r="C29">
-        <v>22047.10887821166</v>
+        <v>23263.48293636106</v>
       </c>
       <c r="D29">
-        <v>42054.57887821167</v>
+        <v>43270.95293636106</v>
       </c>
       <c r="E29">
         <v>13374.47</v>
@@ -3671,37 +3799,37 @@
         <v>228</v>
       </c>
       <c r="M29">
-        <v>7357.401126000001</v>
+        <v>7058.076426000001</v>
       </c>
       <c r="N29">
-        <v>-7129.401126000001</v>
+        <v>-6830.076426000001</v>
       </c>
       <c r="O29">
-        <v>-1839.385490508</v>
+        <v>-1762.159717908</v>
       </c>
       <c r="P29">
-        <v>-5290.015635492</v>
+        <v>-5067.916708092001</v>
       </c>
       <c r="Q29">
-        <v>-5140.015635492</v>
+        <v>-4917.916708092001</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1026905517720495</v>
+        <v>0.1026487600628544</v>
       </c>
       <c r="T29">
-        <v>1.31302485462885</v>
+        <v>1.312904389442365</v>
       </c>
       <c r="U29">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.007995214477585628</v>
+        <v>0.008334282097500201</v>
       </c>
       <c r="W29">
-        <v>0.2438347762814095</v>
+        <v>0.2338347762814095</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.03098920340149469</v>
+        <v>0.03230341898255895</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3848,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1427994923895767</v>
+        <v>0.1399689844418643</v>
       </c>
       <c r="C30">
-        <v>20071.3896214063</v>
+        <v>21281.81679089692</v>
       </c>
       <c r="D30">
-        <v>41187.4696214063</v>
+        <v>42397.89679089692</v>
       </c>
       <c r="E30">
         <v>14483.08</v>
@@ -3753,37 +3881,37 @@
         <v>228</v>
       </c>
       <c r="M30">
-        <v>7629.897464000001</v>
+        <v>7319.486664000001</v>
       </c>
       <c r="N30">
-        <v>-7401.897464000001</v>
+        <v>-7091.486664000001</v>
       </c>
       <c r="O30">
-        <v>-1909.689545712</v>
+        <v>-1829.603559312</v>
       </c>
       <c r="P30">
-        <v>-5492.207918288001</v>
+        <v>-5261.883104688</v>
       </c>
       <c r="Q30">
-        <v>-5342.207918288001</v>
+        <v>-5111.883104688</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.103480698324439</v>
+        <v>0.1034383261748385</v>
       </c>
       <c r="T30">
-        <v>1.33126131094314</v>
+        <v>1.331139172629065</v>
       </c>
       <c r="U30">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.00770967110338614</v>
+        <v>0.008036629165446622</v>
       </c>
       <c r="W30">
-        <v>0.2439049628427877</v>
+        <v>0.2339049628427877</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.02988244613715563</v>
+        <v>0.03114972544746752</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3930,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1447994923895767</v>
+        <v>0.1418689844418642</v>
       </c>
       <c r="C31">
-        <v>18130.70526168478</v>
+        <v>19334.68430238816</v>
       </c>
       <c r="D31">
-        <v>40355.39526168478</v>
+        <v>41559.37430238815</v>
       </c>
       <c r="E31">
         <v>15591.69</v>
@@ -3835,37 +3963,37 @@
         <v>228</v>
       </c>
       <c r="M31">
-        <v>7902.393802000001</v>
+        <v>7580.896902</v>
       </c>
       <c r="N31">
-        <v>-7674.393802000001</v>
+        <v>-7352.896902</v>
       </c>
       <c r="O31">
-        <v>-1979.993600916</v>
+        <v>-1897.047400716</v>
       </c>
       <c r="P31">
-        <v>-5694.400201084</v>
+        <v>-5455.849501284</v>
       </c>
       <c r="Q31">
-        <v>-5544.400201084</v>
+        <v>-5305.849501284</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1042931025261917</v>
+        <v>0.1042501335857517</v>
       </c>
       <c r="T31">
-        <v>1.350011470252198</v>
+        <v>1.349887611680179</v>
       </c>
       <c r="U31">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.007443820375683171</v>
+        <v>0.007759504021810531</v>
       </c>
       <c r="W31">
-        <v>0.2439703089516571</v>
+        <v>0.2339703089516571</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.02885201696001227</v>
+        <v>0.03007559698376172</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +4012,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1467994923895767</v>
+        <v>0.1437689844418643</v>
       </c>
       <c r="C32">
-        <v>16222.97450757198</v>
+        <v>17420.0762446927</v>
       </c>
       <c r="D32">
-        <v>39556.27450757197</v>
+        <v>40753.3762446927</v>
       </c>
       <c r="E32">
         <v>16700.3</v>
@@ -3917,37 +4045,37 @@
         <v>228</v>
       </c>
       <c r="M32">
-        <v>8174.89014</v>
+        <v>7842.307139999999</v>
       </c>
       <c r="N32">
-        <v>-7946.89014</v>
+        <v>-7614.307139999999</v>
       </c>
       <c r="O32">
-        <v>-2050.29765612</v>
+        <v>-1964.49124212</v>
       </c>
       <c r="P32">
-        <v>-5896.59248388</v>
+        <v>-5649.815897879999</v>
       </c>
       <c r="Q32">
-        <v>-5746.59248388</v>
+        <v>-5499.815897879999</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1051287182765659</v>
+        <v>0.1050851354941196</v>
       </c>
       <c r="T32">
-        <v>1.369297348398658</v>
+        <v>1.369171720418467</v>
       </c>
       <c r="U32">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.007195693029827066</v>
+        <v>0.007500853887750182</v>
       </c>
       <c r="W32">
-        <v>0.2440312986532685</v>
+        <v>0.2340312986532685</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.02789028306134522</v>
+        <v>0.02907307708430307</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +4094,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1487994923895767</v>
+        <v>0.1456689844418643</v>
       </c>
       <c r="C33">
-        <v>14346.27772209623</v>
+        <v>15536.13629318017</v>
       </c>
       <c r="D33">
-        <v>38788.18772209623</v>
+        <v>39978.04629318017</v>
       </c>
       <c r="E33">
         <v>17808.91</v>
@@ -3999,37 +4127,37 @@
         <v>228</v>
       </c>
       <c r="M33">
-        <v>8447.386478</v>
+        <v>8103.717377999999</v>
       </c>
       <c r="N33">
-        <v>-8219.386478</v>
+        <v>-7875.717377999999</v>
       </c>
       <c r="O33">
-        <v>-2120.601711324</v>
+        <v>-2031.935083524</v>
       </c>
       <c r="P33">
-        <v>-6098.784766676001</v>
+        <v>-5843.782294475999</v>
       </c>
       <c r="Q33">
-        <v>-5948.784766676001</v>
+        <v>-5693.782294475999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1059885547733277</v>
+        <v>0.1059443403563532</v>
       </c>
       <c r="T33">
-        <v>1.389142237505885</v>
+        <v>1.389014788830329</v>
       </c>
       <c r="U33">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.006963573899832643</v>
+        <v>0.007258890859113079</v>
       </c>
       <c r="W33">
-        <v>0.2440883535354212</v>
+        <v>0.2340883535354211</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.02699059651097924</v>
+        <v>0.02813523588803524</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4176,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1507994923895767</v>
+        <v>0.1475689844418643</v>
       </c>
       <c r="C34">
-        <v>12498.84152704794</v>
+        <v>13681.14675157794</v>
       </c>
       <c r="D34">
-        <v>38049.36152704794</v>
+        <v>39231.66675157795</v>
       </c>
       <c r="E34">
         <v>18917.52</v>
@@ -4081,37 +4209,37 @@
         <v>228</v>
       </c>
       <c r="M34">
-        <v>8719.882816000001</v>
+        <v>8365.127616000002</v>
       </c>
       <c r="N34">
-        <v>-8491.882816000001</v>
+        <v>-8137.127616000002</v>
       </c>
       <c r="O34">
-        <v>-2190.905766528</v>
+        <v>-2099.378924928</v>
       </c>
       <c r="P34">
-        <v>-6300.977049472001</v>
+        <v>-6037.748691072002</v>
       </c>
       <c r="Q34">
-        <v>-6150.977049472001</v>
+        <v>-5887.748691072002</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1068736805788178</v>
+        <v>0.106828815949829</v>
       </c>
       <c r="T34">
-        <v>1.409570799822148</v>
+        <v>1.409441476901363</v>
       </c>
       <c r="U34">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.006745962215462874</v>
+        <v>0.007032050519765793</v>
       </c>
       <c r="W34">
-        <v>0.2441418424874393</v>
+        <v>0.2341418424874392</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.02614714037001109</v>
+        <v>0.02725600976653408</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4258,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1527994923895767</v>
+        <v>0.1494689844418643</v>
       </c>
       <c r="C35">
-        <v>10679.02513387154</v>
+        <v>11853.51584837039</v>
       </c>
       <c r="D35">
-        <v>37338.15513387154</v>
+        <v>38512.6458483704</v>
       </c>
       <c r="E35">
         <v>20026.13</v>
@@ -4163,37 +4291,37 @@
         <v>228</v>
       </c>
       <c r="M35">
-        <v>8992.379154000002</v>
+        <v>8626.537854000002</v>
       </c>
       <c r="N35">
-        <v>-8764.379154000002</v>
+        <v>-8398.537854000002</v>
       </c>
       <c r="O35">
-        <v>-2261.209821732</v>
+        <v>-2166.822766332</v>
       </c>
       <c r="P35">
-        <v>-6503.169332268002</v>
+        <v>-6231.715087668002</v>
       </c>
       <c r="Q35">
-        <v>-6353.169332268002</v>
+        <v>-6081.715087668002</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1077852280501434</v>
+        <v>0.1077396937998265</v>
       </c>
       <c r="T35">
-        <v>1.430609169968747</v>
+        <v>1.430477916855114</v>
       </c>
       <c r="U35">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.006541539118024603</v>
+        <v>0.006818958079772891</v>
       </c>
       <c r="W35">
-        <v>0.2441920896847896</v>
+        <v>0.2341920896847896</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.02535480278304114</v>
+        <v>0.02643007007663911</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4340,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1547994923895767</v>
+        <v>0.1513689844418643</v>
       </c>
       <c r="C36">
-        <v>8885.30817942039</v>
+        <v>10051.76640501239</v>
       </c>
       <c r="D36">
-        <v>36653.0481794204</v>
+        <v>37819.5064050124</v>
       </c>
       <c r="E36">
         <v>21134.74000000001</v>
@@ -4245,37 +4373,37 @@
         <v>228</v>
       </c>
       <c r="M36">
-        <v>9264.875492000003</v>
+        <v>8887.948092000002</v>
       </c>
       <c r="N36">
-        <v>-9036.875492000003</v>
+        <v>-8659.948092000002</v>
       </c>
       <c r="O36">
-        <v>-2331.513876936001</v>
+        <v>-2234.266607736001</v>
       </c>
       <c r="P36">
-        <v>-6705.361615064002</v>
+        <v>-6425.681484264001</v>
       </c>
       <c r="Q36">
-        <v>-6555.361615064002</v>
+        <v>-6275.681484264001</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1087243981721153</v>
+        <v>0.1086781740089147</v>
       </c>
       <c r="T36">
-        <v>1.452285066483425</v>
+        <v>1.452151824686253</v>
       </c>
       <c r="U36">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.006349140908670938</v>
+        <v>0.006618400489191334</v>
       </c>
       <c r="W36">
-        <v>0.2442393811646487</v>
+        <v>0.2342393811646487</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.02460907328942219</v>
+        <v>0.02565271507438505</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4422,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1567994923895767</v>
+        <v>0.1532689844418643</v>
       </c>
       <c r="C37">
-        <v>7116.279876771259</v>
+        <v>8274.525706186025</v>
       </c>
       <c r="D37">
-        <v>35992.62987677127</v>
+        <v>37150.87570618603</v>
       </c>
       <c r="E37">
         <v>22243.35000000001</v>
@@ -4327,37 +4455,37 @@
         <v>228</v>
       </c>
       <c r="M37">
-        <v>9537.371830000002</v>
+        <v>9149.358330000001</v>
       </c>
       <c r="N37">
-        <v>-9309.371830000002</v>
+        <v>-8921.358330000001</v>
       </c>
       <c r="O37">
-        <v>-2401.817932140001</v>
+        <v>-2301.71044914</v>
       </c>
       <c r="P37">
-        <v>-6907.553897860002</v>
+        <v>-6619.64788086</v>
       </c>
       <c r="Q37">
-        <v>-6757.553897860002</v>
+        <v>-6469.64788086</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1096924658363017</v>
+        <v>0.1096455305321288</v>
       </c>
       <c r="T37">
-        <v>1.474627913660093</v>
+        <v>1.474492621989118</v>
       </c>
       <c r="U37">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.006167736882708912</v>
+        <v>0.006429303332357298</v>
       </c>
       <c r="W37">
-        <v>0.2442839702742302</v>
+        <v>0.2342839702742302</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.02390595690972441</v>
+        <v>0.02491978035797404</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4504,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1587994923895767</v>
+        <v>0.1551689844418643</v>
       </c>
       <c r="C38">
-        <v>5370.629318169747</v>
+        <v>6520.516425924128</v>
       </c>
       <c r="D38">
-        <v>35355.58931816975</v>
+        <v>36505.47642592413</v>
       </c>
       <c r="E38">
         <v>23351.96</v>
@@ -4409,37 +4537,37 @@
         <v>228</v>
       </c>
       <c r="M38">
-        <v>9809.868168000001</v>
+        <v>9410.768568</v>
       </c>
       <c r="N38">
-        <v>-9581.868168000001</v>
+        <v>-9182.768568</v>
       </c>
       <c r="O38">
-        <v>-2472.121987344</v>
+        <v>-2369.154290544</v>
       </c>
       <c r="P38">
-        <v>-7109.746180656</v>
+        <v>-6813.614277455999</v>
       </c>
       <c r="Q38">
-        <v>-6959.746180656</v>
+        <v>-6663.614277455999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1106907856149939</v>
+        <v>0.1106431169466933</v>
       </c>
       <c r="T38">
-        <v>1.497668974811032</v>
+        <v>1.497531569207698</v>
       </c>
       <c r="U38">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.00599641085818922</v>
+        <v>0.006250711573125151</v>
       </c>
       <c r="W38">
-        <v>0.2443260822110571</v>
+        <v>0.2343260822110571</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.02324190255112102</v>
+        <v>0.02422756423691919</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4586,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1607994923895767</v>
+        <v>0.1570689844418642</v>
       </c>
       <c r="C39">
-        <v>3647.136789846962</v>
+        <v>4788.548483392588</v>
       </c>
       <c r="D39">
-        <v>34740.70678984696</v>
+        <v>35882.11848339259</v>
       </c>
       <c r="E39">
         <v>24460.57</v>
@@ -4491,37 +4619,37 @@
         <v>228</v>
       </c>
       <c r="M39">
-        <v>10082.364506</v>
+        <v>9672.178806</v>
       </c>
       <c r="N39">
-        <v>-9854.364506</v>
+        <v>-9444.178806</v>
       </c>
       <c r="O39">
-        <v>-2542.426042548</v>
+        <v>-2436.598131948</v>
       </c>
       <c r="P39">
-        <v>-7311.938463451999</v>
+        <v>-7007.580674052</v>
       </c>
       <c r="Q39">
-        <v>-7161.938463451999</v>
+        <v>-6857.580674052</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1117207980850732</v>
+        <v>0.111672372771244</v>
       </c>
       <c r="T39">
-        <v>1.521441498220731</v>
+        <v>1.521301911576074</v>
       </c>
       <c r="U39">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.005834345699859782</v>
+        <v>0.006081773422500146</v>
       </c>
       <c r="W39">
-        <v>0.2443659178269745</v>
+        <v>0.2343659178269745</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.02261374302271235</v>
+        <v>0.02357276520348894</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4668,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1627994923895767</v>
+        <v>0.1589689844418643</v>
       </c>
       <c r="C40">
-        <v>1944.66597762789</v>
+        <v>3077.511719074762</v>
       </c>
       <c r="D40">
-        <v>34146.84597762789</v>
+        <v>35279.69171907476</v>
       </c>
       <c r="E40">
         <v>25569.18</v>
@@ -4573,37 +4701,37 @@
         <v>228</v>
       </c>
       <c r="M40">
-        <v>10354.860844</v>
+        <v>9933.589044</v>
       </c>
       <c r="N40">
-        <v>-10126.860844</v>
+        <v>-9705.589044</v>
       </c>
       <c r="O40">
-        <v>-2612.730097752</v>
+        <v>-2504.041973352</v>
       </c>
       <c r="P40">
-        <v>-7514.130746248</v>
+        <v>-7201.547070648</v>
       </c>
       <c r="Q40">
-        <v>-7364.130746248</v>
+        <v>-7051.547070648</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1127840367638647</v>
+        <v>0.1127348303965866</v>
       </c>
       <c r="T40">
-        <v>1.545980877224291</v>
+        <v>1.54583903918214</v>
       </c>
       <c r="U40">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.005680810286705577</v>
+        <v>0.005921726753486985</v>
       </c>
       <c r="W40">
-        <v>0.2444036568315278</v>
+        <v>0.2344036568315278</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.02201864452211466</v>
+        <v>0.0229524292770813</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4750,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1647994923895767</v>
+        <v>0.1608689844418643</v>
       </c>
       <c r="C41">
-        <v>262.1569585322577</v>
+        <v>1386.369296533849</v>
       </c>
       <c r="D41">
-        <v>33572.94695853226</v>
+        <v>34697.15929653385</v>
       </c>
       <c r="E41">
         <v>26677.79</v>
@@ -4655,37 +4783,37 @@
         <v>228</v>
       </c>
       <c r="M41">
-        <v>10627.357182</v>
+        <v>10194.999282</v>
       </c>
       <c r="N41">
-        <v>-10399.357182</v>
+        <v>-9966.999282000001</v>
       </c>
       <c r="O41">
-        <v>-2683.034152956001</v>
+        <v>-2571.485814756</v>
       </c>
       <c r="P41">
-        <v>-7716.323029044001</v>
+        <v>-7395.513467244</v>
       </c>
       <c r="Q41">
-        <v>-7566.323029044001</v>
+        <v>-7245.513467244</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1138821357272067</v>
+        <v>0.11383212269817</v>
       </c>
       <c r="T41">
-        <v>1.571324826031247</v>
+        <v>1.57118066277529</v>
       </c>
       <c r="U41">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.005535148484482357</v>
+        <v>0.005769887605961677</v>
       </c>
       <c r="W41">
-        <v>0.2444394605025142</v>
+        <v>0.2344394605025142</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.02145406389334248</v>
+        <v>0.02236390544946387</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4832,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1667994923895767</v>
+        <v>0.1627689844418643</v>
       </c>
       <c r="C42">
-        <v>-1401.380112573774</v>
+        <v>-285.8482527492743</v>
       </c>
       <c r="D42">
-        <v>33018.01988742623</v>
+        <v>34133.55174725073</v>
       </c>
       <c r="E42">
         <v>27786.4</v>
@@ -4737,37 +4865,37 @@
         <v>228</v>
       </c>
       <c r="M42">
-        <v>10899.85352</v>
+        <v>10456.40952</v>
       </c>
       <c r="N42">
-        <v>-10671.85352</v>
+        <v>-10228.40952</v>
       </c>
       <c r="O42">
-        <v>-2753.33820816</v>
+        <v>-2638.92965616</v>
       </c>
       <c r="P42">
-        <v>-7918.51531184</v>
+        <v>-7589.479863840001</v>
       </c>
       <c r="Q42">
-        <v>-7768.51531184</v>
+        <v>-7439.479863840001</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1150168379893269</v>
+        <v>0.1149659914098062</v>
       </c>
       <c r="T42">
-        <v>1.597513573131768</v>
+        <v>1.597367007154878</v>
       </c>
       <c r="U42">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.005396769772370299</v>
+        <v>0.005625640415812635</v>
       </c>
       <c r="W42">
-        <v>0.2444734739899514</v>
+        <v>0.2344734739899514</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.02091771229600892</v>
+        <v>0.02180480781322724</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4914,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1687994923895766</v>
+        <v>0.1646689844418643</v>
       </c>
       <c r="C43">
-        <v>-3046.870700387059</v>
+        <v>-1940.048413414734</v>
       </c>
       <c r="D43">
-        <v>32481.13929961294</v>
+        <v>33587.96158658527</v>
       </c>
       <c r="E43">
         <v>28895.01</v>
@@ -4819,37 +4947,37 @@
         <v>228</v>
       </c>
       <c r="M43">
-        <v>11172.349858</v>
+        <v>10717.819758</v>
       </c>
       <c r="N43">
-        <v>-10944.349858</v>
+        <v>-10489.819758</v>
       </c>
       <c r="O43">
-        <v>-2823.642263364</v>
+        <v>-2706.373497564</v>
       </c>
       <c r="P43">
-        <v>-8120.707594636001</v>
+        <v>-7783.446260436001</v>
       </c>
       <c r="Q43">
-        <v>-7970.707594636001</v>
+        <v>-7633.446260436001</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1161900047349086</v>
+        <v>0.1161382963489554</v>
       </c>
       <c r="T43">
-        <v>1.624590074371289</v>
+        <v>1.6244410242253</v>
       </c>
       <c r="U43">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.005265141241336877</v>
+        <v>0.005488429673963546</v>
       </c>
       <c r="W43">
-        <v>0.2445058282828794</v>
+        <v>0.2345058282828794</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.02040752419122815</v>
+        <v>0.02127298323241689</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4996,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1707994923895766</v>
+        <v>0.1665689844418643</v>
       </c>
       <c r="C44">
-        <v>-4675.181039623334</v>
+        <v>-3577.081562035579</v>
       </c>
       <c r="D44">
-        <v>31961.43896037666</v>
+        <v>33059.53843796442</v>
       </c>
       <c r="E44">
         <v>30003.62</v>
@@ -4901,37 +5029,37 @@
         <v>228</v>
       </c>
       <c r="M44">
-        <v>11444.846196</v>
+        <v>10979.229996</v>
       </c>
       <c r="N44">
-        <v>-11216.846196</v>
+        <v>-10751.229996</v>
       </c>
       <c r="O44">
-        <v>-2893.946318568</v>
+        <v>-2773.817338968</v>
       </c>
       <c r="P44">
-        <v>-8322.899877432001</v>
+        <v>-7977.412657032</v>
       </c>
       <c r="Q44">
-        <v>-8172.899877432001</v>
+        <v>-7827.412657032</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1174036255062002</v>
+        <v>0.1173510255963512</v>
       </c>
       <c r="T44">
-        <v>1.652600248067346</v>
+        <v>1.652448628091253</v>
       </c>
       <c r="U44">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.005139780735590761</v>
+        <v>0.005357752776964415</v>
       </c>
       <c r="W44">
-        <v>0.2445366418951918</v>
+        <v>0.2345366418951918</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.01992163075810371</v>
+        <v>0.02076648363164502</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +5078,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1727994923895766</v>
+        <v>0.1684689844418643</v>
       </c>
       <c r="C45">
-        <v>-6287.122798813885</v>
+        <v>-5197.745389805707</v>
       </c>
       <c r="D45">
-        <v>31458.10720118611</v>
+        <v>32547.48461019429</v>
       </c>
       <c r="E45">
         <v>31112.23</v>
@@ -4983,37 +5111,37 @@
         <v>228</v>
       </c>
       <c r="M45">
-        <v>11717.342534</v>
+        <v>11240.640234</v>
       </c>
       <c r="N45">
-        <v>-11489.342534</v>
+        <v>-11012.640234</v>
       </c>
       <c r="O45">
-        <v>-2964.250373772</v>
+        <v>-2841.261180372</v>
       </c>
       <c r="P45">
-        <v>-8525.092160228</v>
+        <v>-8171.379053627999</v>
       </c>
       <c r="Q45">
-        <v>-8375.092160228</v>
+        <v>-8021.379053627999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1186598294624493</v>
+        <v>0.1186063067471644</v>
       </c>
       <c r="T45">
-        <v>1.681593234875545</v>
+        <v>1.681438954899871</v>
       </c>
       <c r="U45">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.005020250951042139</v>
+        <v>0.005233153875174546</v>
       </c>
       <c r="W45">
-        <v>0.2445660223162338</v>
+        <v>0.2345660223162339</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.01945833701954314</v>
+        <v>0.02028354215183936</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5160,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1747994923895766</v>
+        <v>0.1703689844418643</v>
       </c>
       <c r="C46">
-        <v>-7883.457310259</v>
+        <v>-6802.788920483079</v>
       </c>
       <c r="D46">
-        <v>30970.382689741</v>
+        <v>32051.05107951692</v>
       </c>
       <c r="E46">
         <v>32220.84</v>
@@ -5065,37 +5193,37 @@
         <v>228</v>
       </c>
       <c r="M46">
-        <v>11989.838872</v>
+        <v>11502.050472</v>
       </c>
       <c r="N46">
-        <v>-11761.838872</v>
+        <v>-11274.050472</v>
       </c>
       <c r="O46">
-        <v>-3034.554428976001</v>
+        <v>-2908.705021776</v>
       </c>
       <c r="P46">
-        <v>-8727.284443024002</v>
+        <v>-8365.345450224</v>
       </c>
       <c r="Q46">
-        <v>-8577.284443024002</v>
+        <v>-8215.345450224</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1199608978457073</v>
+        <v>0.1199064193676495</v>
       </c>
       <c r="T46">
-        <v>1.711621685498322</v>
+        <v>1.711464650523083</v>
       </c>
       <c r="U46">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.004906154338518453</v>
+        <v>0.005114218559829668</v>
       </c>
       <c r="W46">
-        <v>0.2445940672635922</v>
+        <v>0.2345940672635922</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.01901610208728077</v>
+        <v>0.01982255255747933</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5242,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1767994923895767</v>
+        <v>0.1722689844418643</v>
       </c>
       <c r="C47">
-        <v>-9464.899412503182</v>
+        <v>-8392.916166152725</v>
       </c>
       <c r="D47">
-        <v>30497.55058749682</v>
+        <v>31569.53383384728</v>
       </c>
       <c r="E47">
         <v>33329.45</v>
@@ -5147,37 +5275,37 @@
         <v>228</v>
       </c>
       <c r="M47">
-        <v>12262.33521</v>
+        <v>11763.46071</v>
       </c>
       <c r="N47">
-        <v>-12034.33521</v>
+        <v>-11535.46071</v>
       </c>
       <c r="O47">
-        <v>-3104.85848418</v>
+        <v>-2976.14886318</v>
       </c>
       <c r="P47">
-        <v>-8929.476725820001</v>
+        <v>-8559.311846820001</v>
       </c>
       <c r="Q47">
-        <v>-8779.476725820001</v>
+        <v>-8409.311846820001</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1213092778065384</v>
+        <v>0.1212538088106977</v>
       </c>
       <c r="T47">
-        <v>1.74274207978011</v>
+        <v>1.742582189623503</v>
       </c>
       <c r="U47">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.004797128686551377</v>
+        <v>0.00500056925850012</v>
       </c>
       <c r="W47">
-        <v>0.2446208657688457</v>
+        <v>0.2346208657688457</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.01859352204089681</v>
+        <v>0.0193820513895353</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5324,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1787994923895767</v>
+        <v>0.1741689844418643</v>
       </c>
       <c r="C48">
-        <v>-11032.12094611962</v>
+        <v>-9968.789458334293</v>
       </c>
       <c r="D48">
-        <v>30038.93905388039</v>
+        <v>31102.27054166571</v>
       </c>
       <c r="E48">
         <v>34438.06</v>
@@ -5229,37 +5357,37 @@
         <v>228</v>
       </c>
       <c r="M48">
-        <v>12534.831548</v>
+        <v>12024.870948</v>
       </c>
       <c r="N48">
-        <v>-12306.831548</v>
+        <v>-11796.870948</v>
       </c>
       <c r="O48">
-        <v>-3175.162539384</v>
+        <v>-3043.592704584</v>
       </c>
       <c r="P48">
-        <v>-9131.669008616002</v>
+        <v>-8753.278243416002</v>
       </c>
       <c r="Q48">
-        <v>-8981.669008616002</v>
+        <v>-8603.278243416002</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1227075977659187</v>
+        <v>0.1226511015664513</v>
       </c>
       <c r="T48">
-        <v>1.77501508125752</v>
+        <v>1.774852230172087</v>
       </c>
       <c r="U48">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.004692843280321999</v>
+        <v>0.004891861231141421</v>
       </c>
       <c r="W48">
-        <v>0.2446464991216969</v>
+        <v>0.2346464991216969</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.01818931504000776</v>
+        <v>0.01896070244628456</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5406,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1807994923895767</v>
+        <v>0.1760689844418643</v>
       </c>
       <c r="C49">
-        <v>-12585.75393875718</v>
+        <v>-11531.0324875803</v>
       </c>
       <c r="D49">
-        <v>29593.91606124282</v>
+        <v>30648.6375124197</v>
       </c>
       <c r="E49">
         <v>35546.67000000001</v>
@@ -5311,37 +5439,37 @@
         <v>228</v>
       </c>
       <c r="M49">
-        <v>12807.327886</v>
+        <v>12286.281186</v>
       </c>
       <c r="N49">
-        <v>-12579.327886</v>
+        <v>-12058.281186</v>
       </c>
       <c r="O49">
-        <v>-3245.466594588001</v>
+        <v>-3111.036545988</v>
       </c>
       <c r="P49">
-        <v>-9333.861291412002</v>
+        <v>-8947.244640012002</v>
       </c>
       <c r="Q49">
-        <v>-9183.861291412002</v>
+        <v>-8797.244640012002</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1241586845162191</v>
+        <v>0.124101122350724</v>
       </c>
       <c r="T49">
-        <v>1.808505931847284</v>
+        <v>1.808340008099862</v>
       </c>
       <c r="U49">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.004592995550953445</v>
+        <v>0.004787779077287349</v>
       </c>
       <c r="W49">
-        <v>0.2446710416935756</v>
+        <v>0.2346710416935757</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.01780230833702889</v>
+        <v>0.01855728324529982</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5488,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1827994923895767</v>
+        <v>0.1779689844418643</v>
       </c>
       <c r="C50">
-        <v>-14126.39351120389</v>
+        <v>-13080.2330808992</v>
       </c>
       <c r="D50">
-        <v>29161.88648879611</v>
+        <v>30208.0469191008</v>
       </c>
       <c r="E50">
         <v>36655.28</v>
@@ -5393,37 +5521,37 @@
         <v>228</v>
       </c>
       <c r="M50">
-        <v>13079.824224</v>
+        <v>12547.691424</v>
       </c>
       <c r="N50">
-        <v>-12851.824224</v>
+        <v>-12319.691424</v>
       </c>
       <c r="O50">
-        <v>-3315.770649792</v>
+        <v>-3178.480387392</v>
       </c>
       <c r="P50">
-        <v>-9536.053574207999</v>
+        <v>-9141.211036608001</v>
       </c>
       <c r="Q50">
-        <v>-9386.053574207999</v>
+        <v>-8991.211036608001</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1256655822953771</v>
+        <v>0.125606913165161</v>
       </c>
       <c r="T50">
-        <v>1.843284892075116</v>
+        <v>1.843115777486397</v>
       </c>
       <c r="U50">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.004497308143641915</v>
+        <v>0.004688033679843863</v>
       </c>
       <c r="W50">
-        <v>0.2446945616582928</v>
+        <v>0.2346945616582928</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.01743142691334076</v>
+        <v>0.01817067317768939</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5570,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1847994923895767</v>
+        <v>0.1798689844418643</v>
       </c>
       <c r="C51">
-        <v>-15654.60053256658</v>
+        <v>-14616.94574301178</v>
       </c>
       <c r="D51">
-        <v>28742.28946743343</v>
+        <v>29779.94425698822</v>
       </c>
       <c r="E51">
         <v>37763.89</v>
@@ -5475,37 +5603,37 @@
         <v>228</v>
       </c>
       <c r="M51">
-        <v>13352.320562</v>
+        <v>12809.101662</v>
       </c>
       <c r="N51">
-        <v>-13124.320562</v>
+        <v>-12581.101662</v>
       </c>
       <c r="O51">
-        <v>-3386.074704996</v>
+        <v>-3245.924228796001</v>
       </c>
       <c r="P51">
-        <v>-9738.245857004</v>
+        <v>-9335.177433204</v>
       </c>
       <c r="Q51">
-        <v>-9588.245857004</v>
+        <v>-9185.177433204</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1272315741050904</v>
+        <v>0.127171754599772</v>
       </c>
       <c r="T51">
-        <v>1.879427733096197</v>
+        <v>1.87925530253515</v>
       </c>
       <c r="U51">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.004405526344792081</v>
+        <v>0.004592359523112355</v>
       </c>
       <c r="W51">
-        <v>0.2447171216244501</v>
+        <v>0.2347171216244501</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.01707568350694599</v>
+        <v>0.01779984311283855</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5652,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1867994923895767</v>
+        <v>0.1817689844418643</v>
       </c>
       <c r="C52">
-        <v>-17170.90404947683</v>
+        <v>-16141.69398454193</v>
       </c>
       <c r="D52">
-        <v>28334.59595052317</v>
+        <v>29363.80601545808</v>
       </c>
       <c r="E52">
         <v>38872.5</v>
@@ -5557,37 +5685,37 @@
         <v>228</v>
       </c>
       <c r="M52">
-        <v>13624.8169</v>
+        <v>13070.5119</v>
       </c>
       <c r="N52">
-        <v>-13396.8169</v>
+        <v>-12842.5119</v>
       </c>
       <c r="O52">
-        <v>-3456.378760200001</v>
+        <v>-3313.368070200001</v>
       </c>
       <c r="P52">
-        <v>-9940.4381398</v>
+        <v>-9529.143829800001</v>
       </c>
       <c r="Q52">
-        <v>-9790.4381398</v>
+        <v>-9379.143829800001</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1288602055871922</v>
+        <v>0.1287991896917674</v>
       </c>
       <c r="T52">
-        <v>1.917016287758121</v>
+        <v>1.916840408585853</v>
       </c>
       <c r="U52">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.004317415817896239</v>
+        <v>0.004500512332650108</v>
       </c>
       <c r="W52">
-        <v>0.2447387791919611</v>
+        <v>0.2347387791919611</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.01673416983680709</v>
+        <v>0.01744384625058182</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5734,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1887994923895767</v>
+        <v>0.1836689844418643</v>
       </c>
       <c r="C53">
-        <v>-18675.80351144681</v>
+        <v>-17654.97245769585</v>
       </c>
       <c r="D53">
-        <v>27938.30648855319</v>
+        <v>28959.13754230415</v>
       </c>
       <c r="E53">
         <v>39981.11</v>
@@ -5639,37 +5767,37 @@
         <v>228</v>
       </c>
       <c r="M53">
-        <v>13897.313238</v>
+        <v>13331.922138</v>
       </c>
       <c r="N53">
-        <v>-13669.313238</v>
+        <v>-13103.922138</v>
       </c>
       <c r="O53">
-        <v>-3526.682815404</v>
+        <v>-3380.811911604</v>
       </c>
       <c r="P53">
-        <v>-10142.630422596</v>
+        <v>-9723.110226396</v>
       </c>
       <c r="Q53">
-        <v>-9992.630422596001</v>
+        <v>-9573.110226396</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1305553118236655</v>
+        <v>0.1304930507058852</v>
       </c>
       <c r="T53">
-        <v>1.95613906914094</v>
+        <v>1.95595960059781</v>
       </c>
       <c r="U53">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.004232760605780627</v>
+        <v>0.004412266992794224</v>
       </c>
       <c r="W53">
-        <v>0.2447595874430991</v>
+        <v>0.2347595874430991</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.01640604885961483</v>
+        <v>0.01710181004958999</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5816,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1907994923895767</v>
+        <v>0.1855689844418643</v>
       </c>
       <c r="C54">
-        <v>-20169.77081205708</v>
+        <v>-19157.24891774847</v>
       </c>
       <c r="D54">
-        <v>27552.94918794292</v>
+        <v>28565.47108225154</v>
       </c>
       <c r="E54">
         <v>41089.72</v>
@@ -5721,37 +5849,37 @@
         <v>228</v>
       </c>
       <c r="M54">
-        <v>14169.809576</v>
+        <v>13593.332376</v>
       </c>
       <c r="N54">
-        <v>-13941.809576</v>
+        <v>-13365.332376</v>
       </c>
       <c r="O54">
-        <v>-3596.986870608001</v>
+        <v>-3448.255753008</v>
       </c>
       <c r="P54">
-        <v>-10344.822705392</v>
+        <v>-9917.076622992001</v>
       </c>
       <c r="Q54">
-        <v>-10194.822705392</v>
+        <v>-9767.076622992001</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1323210474866586</v>
+        <v>0.1322574892622577</v>
       </c>
       <c r="T54">
-        <v>1.99689196641471</v>
+        <v>1.996708758943597</v>
       </c>
       <c r="U54">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.004151361363361768</v>
+        <v>0.004327415704471258</v>
       </c>
       <c r="W54">
-        <v>0.2447795953768857</v>
+        <v>0.2347795953768857</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.01609054792000686</v>
+        <v>0.01677292908709793</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5898,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1927994923895767</v>
+        <v>0.1874689844418643</v>
       </c>
       <c r="C55">
-        <v>-21653.25216351621</v>
+        <v>-20648.9660266905</v>
       </c>
       <c r="D55">
-        <v>27178.07783648379</v>
+        <v>28182.3639733095</v>
       </c>
       <c r="E55">
         <v>42198.33</v>
@@ -5803,37 +5931,37 @@
         <v>228</v>
       </c>
       <c r="M55">
-        <v>14442.305914</v>
+        <v>13854.742614</v>
       </c>
       <c r="N55">
-        <v>-14214.305914</v>
+        <v>-13626.742614</v>
       </c>
       <c r="O55">
-        <v>-3667.290925812001</v>
+        <v>-3515.699594412</v>
       </c>
       <c r="P55">
-        <v>-10547.014988188</v>
+        <v>-10111.043019588</v>
       </c>
       <c r="Q55">
-        <v>-10397.014988188</v>
+        <v>-9961.043019588</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1341619208374385</v>
+        <v>0.1340970103103909</v>
       </c>
       <c r="T55">
-        <v>2.039379029529916</v>
+        <v>2.039191924027504</v>
       </c>
       <c r="U55">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.00407303379046815</v>
+        <v>0.004245766351556705</v>
       </c>
       <c r="W55">
-        <v>0.2447988482943029</v>
+        <v>0.2347988482943029</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.01578695267623309</v>
+        <v>0.016456458726964</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5980,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1947994923895767</v>
+        <v>0.1893689844418643</v>
       </c>
       <c r="C56">
-        <v>-23126.66982024867</v>
+        <v>-22130.54301365816</v>
       </c>
       <c r="D56">
-        <v>26813.27017975133</v>
+        <v>27809.39698634184</v>
       </c>
       <c r="E56">
         <v>43306.94</v>
@@ -5885,37 +6013,37 @@
         <v>228</v>
       </c>
       <c r="M56">
-        <v>14714.802252</v>
+        <v>14116.152852</v>
       </c>
       <c r="N56">
-        <v>-14486.802252</v>
+        <v>-13888.152852</v>
       </c>
       <c r="O56">
-        <v>-3737.594981016</v>
+        <v>-3583.143435816</v>
       </c>
       <c r="P56">
-        <v>-10749.207270984</v>
+        <v>-10305.009416184</v>
       </c>
       <c r="Q56">
-        <v>-10599.207270984</v>
+        <v>-10155.009416184</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1360828321599916</v>
+        <v>0.1360165105345298</v>
       </c>
       <c r="T56">
-        <v>2.083713356258828</v>
+        <v>2.083522183245493</v>
       </c>
       <c r="U56">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.003997607238792814</v>
+        <v>0.0041671410487501</v>
       </c>
       <c r="W56">
-        <v>0.2448173881407048</v>
+        <v>0.2348173881407047</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.01549460170074735</v>
+        <v>0.01615170949127942</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +6062,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1967994923895767</v>
+        <v>0.1912689844418643</v>
       </c>
       <c r="C57">
-        <v>-24590.42366550841</v>
+        <v>-23602.37720523946</v>
       </c>
       <c r="D57">
-        <v>26458.12633449159</v>
+        <v>27446.17279476054</v>
       </c>
       <c r="E57">
         <v>44415.55</v>
@@ -5967,37 +6095,37 @@
         <v>228</v>
       </c>
       <c r="M57">
-        <v>14987.29859</v>
+        <v>14377.56309</v>
       </c>
       <c r="N57">
-        <v>-14759.29859</v>
+        <v>-14149.56309</v>
       </c>
       <c r="O57">
-        <v>-3807.899036220001</v>
+        <v>-3650.58727722</v>
       </c>
       <c r="P57">
-        <v>-10951.39955378</v>
+        <v>-10498.97581278</v>
       </c>
       <c r="Q57">
-        <v>-10801.39955378</v>
+        <v>-10348.97581278</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1380891173191025</v>
+        <v>0.1380213218797416</v>
       </c>
       <c r="T57">
-        <v>2.130018097509024</v>
+        <v>2.129822676206504</v>
       </c>
       <c r="U57">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.003924923470814762</v>
+        <v>0.004091374847863734</v>
       </c>
       <c r="W57">
-        <v>0.2448352538108738</v>
+        <v>0.2348352538108738</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.01521288166982471</v>
+        <v>0.01585804204598351</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6144,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1987994923895767</v>
+        <v>0.1931689844418643</v>
       </c>
       <c r="C58">
-        <v>-26044.89267355169</v>
+        <v>-25064.84543740105</v>
       </c>
       <c r="D58">
-        <v>26112.26732644832</v>
+        <v>27092.31456259896</v>
       </c>
       <c r="E58">
         <v>45524.16</v>
@@ -6049,37 +6177,37 @@
         <v>228</v>
       </c>
       <c r="M58">
-        <v>15259.794928</v>
+        <v>14638.973328</v>
       </c>
       <c r="N58">
-        <v>-15031.794928</v>
+        <v>-14410.973328</v>
       </c>
       <c r="O58">
-        <v>-3878.203091424</v>
+        <v>-3718.031118624001</v>
       </c>
       <c r="P58">
-        <v>-11153.591836576</v>
+        <v>-10692.942209376</v>
       </c>
       <c r="Q58">
-        <v>-11003.591836576</v>
+        <v>-10542.942209376</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.140186597258173</v>
+        <v>0.1401172610133721</v>
       </c>
       <c r="T58">
-        <v>2.178427599725138</v>
+        <v>2.178227737029379</v>
       </c>
       <c r="U58">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.00385483555169307</v>
+        <v>0.004018314582723311</v>
       </c>
       <c r="W58">
-        <v>0.2448524814213938</v>
+        <v>0.2348524814213939</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.01494122306857781</v>
+        <v>0.01557486272373376</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6226,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2007994923895767</v>
+        <v>0.1950689844418643</v>
       </c>
       <c r="C59">
-        <v>-27490.43625860909</v>
+        <v>-26518.30535958288</v>
       </c>
       <c r="D59">
-        <v>25775.33374139092</v>
+        <v>26747.46464041713</v>
       </c>
       <c r="E59">
         <v>46632.77</v>
@@ -6131,37 +6259,37 @@
         <v>228</v>
       </c>
       <c r="M59">
-        <v>15532.291266</v>
+        <v>14900.383566</v>
       </c>
       <c r="N59">
-        <v>-15304.291266</v>
+        <v>-14672.383566</v>
       </c>
       <c r="O59">
-        <v>-3948.507146628001</v>
+        <v>-3785.474960028001</v>
       </c>
       <c r="P59">
-        <v>-11355.784119372</v>
+        <v>-10886.908605972</v>
       </c>
       <c r="Q59">
-        <v>-11205.784119372</v>
+        <v>-10736.908605972</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1423816344037119</v>
+        <v>0.1423106856881017</v>
       </c>
       <c r="T59">
-        <v>2.22908870669549</v>
+        <v>2.228884196030062</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.003787206857803718</v>
+        <v>0.003947817835657989</v>
       </c>
       <c r="W59">
-        <v>0.2448691045543518</v>
+        <v>0.2348691045543519</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.0146790963480764</v>
+        <v>0.0153016195180542</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6308,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2027994923895767</v>
+        <v>0.1969689844418642</v>
       </c>
       <c r="C60">
-        <v>-28927.39552075105</v>
+        <v>-27963.0966404483</v>
       </c>
       <c r="D60">
-        <v>25446.98447924894</v>
+        <v>26411.2833595517</v>
       </c>
       <c r="E60">
         <v>47741.38</v>
@@ -6213,37 +6341,37 @@
         <v>228</v>
       </c>
       <c r="M60">
-        <v>15804.787604</v>
+        <v>15161.793804</v>
       </c>
       <c r="N60">
-        <v>-15576.787604</v>
+        <v>-14933.793804</v>
       </c>
       <c r="O60">
-        <v>-4018.811201832</v>
+        <v>-3852.918801432</v>
       </c>
       <c r="P60">
-        <v>-11557.976402168</v>
+        <v>-11080.875002568</v>
       </c>
       <c r="Q60">
-        <v>-11407.976402168</v>
+        <v>-10930.875002568</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1446811971276098</v>
+        <v>0.144608559156866</v>
       </c>
       <c r="T60">
-        <v>2.282162247331096</v>
+        <v>2.281952867364111</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.003721910187841585</v>
+        <v>0.003879752010905266</v>
       </c>
       <c r="W60">
-        <v>0.2448851544758285</v>
+        <v>0.2348851544758285</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.01442600848000619</v>
+        <v>0.01503779849188092</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6390,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2047994923895767</v>
+        <v>0.1988689844418643</v>
       </c>
       <c r="C61">
-        <v>-30356.09439772557</v>
+        <v>-29399.54208383433</v>
       </c>
       <c r="D61">
-        <v>25126.89560227443</v>
+        <v>26083.44791616567</v>
       </c>
       <c r="E61">
         <v>48849.99</v>
@@ -6295,37 +6423,37 @@
         <v>228</v>
       </c>
       <c r="M61">
-        <v>16077.283942</v>
+        <v>15423.204042</v>
       </c>
       <c r="N61">
-        <v>-15849.283942</v>
+        <v>-15195.204042</v>
       </c>
       <c r="O61">
-        <v>-4089.115257036</v>
+        <v>-3920.362642836</v>
       </c>
       <c r="P61">
-        <v>-11760.168684964</v>
+        <v>-11274.841399164</v>
       </c>
       <c r="Q61">
-        <v>-11610.168684964</v>
+        <v>-11124.841399164</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1470929336429173</v>
+        <v>0.1470185240143505</v>
       </c>
       <c r="T61">
-        <v>2.33782474116844</v>
+        <v>2.337610254372991</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.003658826964318847</v>
+        <v>0.003813993502245855</v>
       </c>
       <c r="W61">
-        <v>0.2449006603321705</v>
+        <v>0.2349006603321704</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.01418149986170092</v>
+        <v>0.01478292055134056</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6472,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2067994923895767</v>
+        <v>0.2007689844418643</v>
       </c>
       <c r="C62">
-        <v>-31776.84073094423</v>
+        <v>-30827.94866260914</v>
       </c>
       <c r="D62">
-        <v>24814.75926905576</v>
+        <v>25763.65133739085</v>
       </c>
       <c r="E62">
         <v>49958.59999999999</v>
@@ -6377,37 +6505,37 @@
         <v>228</v>
       </c>
       <c r="M62">
-        <v>16349.78028</v>
+        <v>15684.61428</v>
       </c>
       <c r="N62">
-        <v>-16121.78028</v>
+        <v>-15456.61428</v>
       </c>
       <c r="O62">
-        <v>-4159.41931224</v>
+        <v>-3987.806484239999</v>
       </c>
       <c r="P62">
-        <v>-11962.36096776</v>
+        <v>-11468.80779576</v>
       </c>
       <c r="Q62">
-        <v>-11812.36096776</v>
+        <v>-11318.80779576</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1496252569839903</v>
+        <v>0.1495489871147093</v>
       </c>
       <c r="T62">
-        <v>2.396270359697651</v>
+        <v>2.396050510732317</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.003597846514913533</v>
+        <v>0.003750426943875091</v>
       </c>
       <c r="W62">
-        <v>0.2449156493266343</v>
+        <v>0.2349156493266343</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.01394514153067261</v>
+        <v>0.01453653854215153</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6554,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2087994923895767</v>
+        <v>0.2026689844418643</v>
       </c>
       <c r="C63">
-        <v>-33189.92725299066</v>
+        <v>-32248.60847739699</v>
       </c>
       <c r="D63">
-        <v>24510.28274700934</v>
+        <v>25451.60152260301</v>
       </c>
       <c r="E63">
         <v>51067.20999999999</v>
@@ -6459,37 +6587,37 @@
         <v>228</v>
       </c>
       <c r="M63">
-        <v>16622.276618</v>
+        <v>15946.024518</v>
       </c>
       <c r="N63">
-        <v>-16394.276618</v>
+        <v>-15718.024518</v>
       </c>
       <c r="O63">
-        <v>-4229.723367444</v>
+        <v>-4055.250325644</v>
       </c>
       <c r="P63">
-        <v>-12164.553250556</v>
+        <v>-11662.774192356</v>
       </c>
       <c r="Q63">
-        <v>-12014.553250556</v>
+        <v>-11512.774192356</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1522874430605028</v>
+        <v>0.152209217553548</v>
       </c>
       <c r="T63">
-        <v>2.457713189433488</v>
+        <v>2.457487703315197</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.003538865424505114</v>
+        <v>0.003688944534959106</v>
       </c>
       <c r="W63">
-        <v>0.2449301468786567</v>
+        <v>0.2349301468786566</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.01371653265312056</v>
+        <v>0.0142982346316245</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6636,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2107994923895767</v>
+        <v>0.2045689844418643</v>
       </c>
       <c r="C64">
-        <v>-34595.63250330983</v>
+        <v>-33661.79964646439</v>
       </c>
       <c r="D64">
-        <v>24213.18749669017</v>
+        <v>25147.0203535356</v>
       </c>
       <c r="E64">
         <v>52175.81999999999</v>
@@ -6541,37 +6669,37 @@
         <v>228</v>
       </c>
       <c r="M64">
-        <v>16894.772956</v>
+        <v>16207.434756</v>
       </c>
       <c r="N64">
-        <v>-16666.772956</v>
+        <v>-15979.434756</v>
       </c>
       <c r="O64">
-        <v>-4300.027422648001</v>
+        <v>-4122.694167048</v>
       </c>
       <c r="P64">
-        <v>-12366.745533352</v>
+        <v>-11856.740588952</v>
       </c>
       <c r="Q64">
-        <v>-12216.745533352</v>
+        <v>-11706.740588952</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1550897441936739</v>
+        <v>0.1550094601207466</v>
       </c>
       <c r="T64">
-        <v>2.522389852313317</v>
+        <v>2.522158432349807</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.003481786949916322</v>
+        <v>0.003629445429556539</v>
       </c>
       <c r="W64">
-        <v>0.2449441767677106</v>
+        <v>0.2349441767677106</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.01349529825548967</v>
+        <v>0.01406761794401756</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6718,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2127994923895767</v>
+        <v>0.2064689844418643</v>
       </c>
       <c r="C65">
-        <v>-35994.22167809926</v>
+        <v>-35067.78713246578</v>
       </c>
       <c r="D65">
-        <v>23923.20832190074</v>
+        <v>24849.64286753423</v>
       </c>
       <c r="E65">
         <v>53284.43000000001</v>
@@ -6623,37 +6751,37 @@
         <v>228</v>
       </c>
       <c r="M65">
-        <v>17167.269294</v>
+        <v>16468.844994</v>
       </c>
       <c r="N65">
-        <v>-16939.269294</v>
+        <v>-16240.844994</v>
       </c>
       <c r="O65">
-        <v>-4370.331477852001</v>
+        <v>-4190.138008452001</v>
       </c>
       <c r="P65">
-        <v>-12568.937816148</v>
+        <v>-12050.706985548</v>
       </c>
       <c r="Q65">
-        <v>-12418.937816148</v>
+        <v>-11900.706985548</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1580435210637733</v>
+        <v>0.1579610671510371</v>
       </c>
       <c r="T65">
-        <v>2.590562551024488</v>
+        <v>2.590324876467369</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.00342652049039384</v>
+        <v>0.003571835184642943</v>
       </c>
       <c r="W65">
-        <v>0.2449577612634612</v>
+        <v>0.2349577612634612</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.01328108717206911</v>
+        <v>0.01384432242109668</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6800,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2147994923895767</v>
+        <v>0.2083689844418643</v>
       </c>
       <c r="C66">
-        <v>-37385.94741985254</v>
+        <v>-36466.82351121456</v>
       </c>
       <c r="D66">
-        <v>23640.09258014746</v>
+        <v>24559.21648878545</v>
       </c>
       <c r="E66">
         <v>54393.04000000001</v>
@@ -6705,37 +6833,37 @@
         <v>228</v>
       </c>
       <c r="M66">
-        <v>17439.765632</v>
+        <v>16730.255232</v>
       </c>
       <c r="N66">
-        <v>-17211.765632</v>
+        <v>-16502.255232</v>
       </c>
       <c r="O66">
-        <v>-4440.635533056001</v>
+        <v>-4257.581849856001</v>
       </c>
       <c r="P66">
-        <v>-12771.130098944</v>
+        <v>-12244.673382144</v>
       </c>
       <c r="Q66">
-        <v>-12621.130098944</v>
+        <v>-12094.673382144</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1611613966488781</v>
+        <v>0.161076652349677</v>
       </c>
       <c r="T66">
-        <v>2.662522621886279</v>
+        <v>2.66227834525813</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.003372981107731437</v>
+        <v>0.003516025259882896</v>
       </c>
       <c r="W66">
-        <v>0.2449709212437196</v>
+        <v>0.2349709212437196</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.01307357018500555</v>
+        <v>0.01362800488326699</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6882,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2167994923895767</v>
+        <v>0.2102689844418643</v>
       </c>
       <c r="C67">
-        <v>-38771.05055149633</v>
+        <v>-37859.14968716739</v>
       </c>
       <c r="D67">
-        <v>23363.59944850368</v>
+        <v>24275.50031283262</v>
       </c>
       <c r="E67">
         <v>55501.65000000001</v>
@@ -6787,37 +6915,37 @@
         <v>228</v>
       </c>
       <c r="M67">
-        <v>17712.26197</v>
+        <v>16991.66547</v>
       </c>
       <c r="N67">
-        <v>-17484.26197</v>
+        <v>-16763.66547</v>
       </c>
       <c r="O67">
-        <v>-4510.939588260001</v>
+        <v>-4325.025691260001</v>
       </c>
       <c r="P67">
-        <v>-12973.32238174</v>
+        <v>-12438.63977874</v>
       </c>
       <c r="Q67">
-        <v>-12823.32238174</v>
+        <v>-12288.63977874</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1644574365531317</v>
+        <v>0.1643702709882392</v>
       </c>
       <c r="T67">
-        <v>2.738594696797316</v>
+        <v>2.738343440836934</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.003321089090689414</v>
+        <v>0.003461932563577006</v>
       </c>
       <c r="W67">
-        <v>0.2449836763015086</v>
+        <v>0.2349836763015086</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.01287243833600549</v>
+        <v>0.01341834326967828</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6964,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2187994923895767</v>
+        <v>0.2121689844418643</v>
       </c>
       <c r="C68">
-        <v>-40149.76075960437</v>
+        <v>-39244.99555988199</v>
       </c>
       <c r="D68">
-        <v>23093.49924039563</v>
+        <v>23998.26444011802</v>
       </c>
       <c r="E68">
         <v>56610.26000000001</v>
@@ -6869,37 +6997,37 @@
         <v>228</v>
       </c>
       <c r="M68">
-        <v>17984.758308</v>
+        <v>17253.075708</v>
       </c>
       <c r="N68">
-        <v>-17756.758308</v>
+        <v>-17025.075708</v>
       </c>
       <c r="O68">
-        <v>-4581.243643464001</v>
+        <v>-4392.469532664001</v>
       </c>
       <c r="P68">
-        <v>-13175.514664536</v>
+        <v>-12632.606175336</v>
       </c>
       <c r="Q68">
-        <v>-13025.514664536</v>
+        <v>-12482.606175336</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1679473611576356</v>
+        <v>0.167857631899658</v>
       </c>
       <c r="T68">
-        <v>2.819141599644296</v>
+        <v>2.818882953802726</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.003270769559012301</v>
+        <v>0.003409479039886445</v>
       </c>
       <c r="W68">
-        <v>0.2449960448423948</v>
+        <v>0.2349960448423948</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.01267740139152052</v>
+        <v>0.01321503503831956</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +7046,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2207994923895767</v>
+        <v>0.2140689844418643</v>
       </c>
       <c r="C69">
-        <v>-41522.2972307622</v>
+        <v>-40624.58064532311</v>
       </c>
       <c r="D69">
-        <v>22829.57276923782</v>
+        <v>23727.2893546769</v>
       </c>
       <c r="E69">
         <v>57718.87000000001</v>
@@ -6951,37 +7079,37 @@
         <v>228</v>
       </c>
       <c r="M69">
-        <v>18257.254646</v>
+        <v>17514.485946</v>
       </c>
       <c r="N69">
-        <v>-18029.254646</v>
+        <v>-17286.485946</v>
       </c>
       <c r="O69">
-        <v>-4651.547698668001</v>
+        <v>-4459.913374068001</v>
       </c>
       <c r="P69">
-        <v>-13377.706947332</v>
+        <v>-12826.572571932</v>
       </c>
       <c r="Q69">
-        <v>-13227.706947332</v>
+        <v>-12676.572571932</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1716487963442307</v>
+        <v>0.1715563480178295</v>
       </c>
       <c r="T69">
-        <v>2.904570132966851</v>
+        <v>2.904303649372506</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.00322195210290764</v>
+        <v>0.003358591293022468</v>
       </c>
       <c r="W69">
-        <v>0.2450080441731053</v>
+        <v>0.2350080441731053</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.01248818644537841</v>
+        <v>0.01301779570938943</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7128,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2227994923895767</v>
+        <v>0.2159689844418643</v>
       </c>
       <c r="C70">
-        <v>-42888.86924478866</v>
+        <v>-41998.11465554594</v>
       </c>
       <c r="D70">
-        <v>22571.61075521136</v>
+        <v>23462.36534445407</v>
       </c>
       <c r="E70">
         <v>58827.48000000001</v>
@@ -7033,37 +7161,37 @@
         <v>228</v>
       </c>
       <c r="M70">
-        <v>18529.75098400001</v>
+        <v>17775.896184</v>
       </c>
       <c r="N70">
-        <v>-18301.75098400001</v>
+        <v>-17547.896184</v>
       </c>
       <c r="O70">
-        <v>-4721.851753872002</v>
+        <v>-4527.357215472001</v>
       </c>
       <c r="P70">
-        <v>-13579.89923012801</v>
+        <v>-13020.538968528</v>
       </c>
       <c r="Q70">
-        <v>-13429.89923012801</v>
+        <v>-12870.538968528</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1755815712299879</v>
+        <v>0.1754862338933867</v>
       </c>
       <c r="T70">
-        <v>2.995337949622065</v>
+        <v>2.995063138415397</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.003174570454335469</v>
+        <v>0.003309200244595667</v>
       </c>
       <c r="W70">
-        <v>0.2450196905823244</v>
+        <v>0.2350196905823244</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.01230453664471109</v>
+        <v>0.01282635753719252</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7210,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2247994923895767</v>
+        <v>0.2178689844418643</v>
       </c>
       <c r="C71">
-        <v>-44249.67672818806</v>
+        <v>-43365.79803997406</v>
       </c>
       <c r="D71">
-        <v>22319.41327181195</v>
+        <v>23203.29196002595</v>
       </c>
       <c r="E71">
         <v>59936.09000000001</v>
@@ -7115,37 +7243,37 @@
         <v>228</v>
       </c>
       <c r="M71">
-        <v>18802.247322</v>
+        <v>18037.30642200001</v>
       </c>
       <c r="N71">
-        <v>-18574.247322</v>
+        <v>-17809.30642200001</v>
       </c>
       <c r="O71">
-        <v>-4792.155809076001</v>
+        <v>-4594.801056876002</v>
       </c>
       <c r="P71">
-        <v>-13782.091512924</v>
+        <v>-13214.505365124</v>
       </c>
       <c r="Q71">
-        <v>-13632.091512924</v>
+        <v>-13064.505365124</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1797680735277294</v>
+        <v>0.1796696607931733</v>
       </c>
       <c r="T71">
-        <v>3.091961754448584</v>
+        <v>3.091678078364281</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.003128562186881332</v>
+        <v>0.003261240820760947</v>
       </c>
       <c r="W71">
-        <v>0.2450309994144646</v>
+        <v>0.2350309994144646</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0121262100266718</v>
+        <v>0.01264046829752308</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7292,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2267994923895767</v>
+        <v>0.2197689844418643</v>
       </c>
       <c r="C72">
-        <v>-45604.91077090939</v>
+        <v>-44727.82249120793</v>
       </c>
       <c r="D72">
-        <v>22072.78922909062</v>
+        <v>22949.87750879208</v>
       </c>
       <c r="E72">
         <v>61044.70000000001</v>
@@ -7197,37 +7325,37 @@
         <v>228</v>
       </c>
       <c r="M72">
-        <v>19074.74366</v>
+        <v>18298.71666</v>
       </c>
       <c r="N72">
-        <v>-18846.74366</v>
+        <v>-18070.71666</v>
       </c>
       <c r="O72">
-        <v>-4862.459864280001</v>
+        <v>-4662.244898280001</v>
       </c>
       <c r="P72">
-        <v>-13984.28379572</v>
+        <v>-13408.47176172</v>
       </c>
       <c r="Q72">
-        <v>-13834.28379572</v>
+        <v>-13258.47176172</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1842336759786537</v>
+        <v>0.1841319828196124</v>
       </c>
       <c r="T72">
-        <v>3.195027146263536</v>
+        <v>3.194734014309756</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.003083868441354456</v>
+        <v>0.003214651666178649</v>
       </c>
       <c r="W72">
-        <v>0.2450419851371151</v>
+        <v>0.2350419851371151</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.01195297845486221</v>
+        <v>0.01245989017898697</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7374,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2287994923895767</v>
+        <v>0.2216689844418643</v>
       </c>
       <c r="C73">
-        <v>-46954.75410921939</v>
+        <v>-46084.37141804649</v>
       </c>
       <c r="D73">
-        <v>21831.5558907806</v>
+        <v>22701.93858195351</v>
       </c>
       <c r="E73">
         <v>62153.31</v>
@@ -7279,37 +7407,37 @@
         <v>228</v>
       </c>
       <c r="M73">
-        <v>19347.239998</v>
+        <v>18560.126898</v>
       </c>
       <c r="N73">
-        <v>-19119.239998</v>
+        <v>-18332.126898</v>
       </c>
       <c r="O73">
-        <v>-4932.763919484</v>
+        <v>-4729.688739684</v>
       </c>
       <c r="P73">
-        <v>-14186.476078516</v>
+        <v>-13602.438158316</v>
       </c>
       <c r="Q73">
-        <v>-14036.476078516</v>
+        <v>-13452.438158316</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1890072510124004</v>
+        <v>0.1889020511927025</v>
       </c>
       <c r="T73">
-        <v>3.305200496134691</v>
+        <v>3.304897256182506</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.003040433674574816</v>
+        <v>0.003169374882147964</v>
       </c>
       <c r="W73">
-        <v>0.2450526614027895</v>
+        <v>0.2350526614027895</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.01178462664563884</v>
+        <v>0.01228439876801535</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7456,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2307994923895767</v>
+        <v>0.2235689844418643</v>
       </c>
       <c r="C74">
-        <v>-48299.38157725446</v>
+        <v>-47435.62038817471</v>
       </c>
       <c r="D74">
-        <v>21595.53842274553</v>
+        <v>22459.29961182529</v>
       </c>
       <c r="E74">
         <v>63261.92</v>
@@ -7361,37 +7489,37 @@
         <v>228</v>
       </c>
       <c r="M74">
-        <v>19619.736336</v>
+        <v>18821.537136</v>
       </c>
       <c r="N74">
-        <v>-19391.736336</v>
+        <v>-18593.537136</v>
       </c>
       <c r="O74">
-        <v>-5003.067974688001</v>
+        <v>-4797.132581088</v>
       </c>
       <c r="P74">
-        <v>-14388.668361312</v>
+        <v>-13796.404554912</v>
       </c>
       <c r="Q74">
-        <v>-14238.668361312</v>
+        <v>-13646.404554912</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1941217956914147</v>
+        <v>0.194012838735299</v>
       </c>
       <c r="T74">
-        <v>3.423243370996645</v>
+        <v>3.422929301046167</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.00299820542909461</v>
+        <v>0.003125355786562575</v>
       </c>
       <c r="W74">
-        <v>0.2450630411055286</v>
+        <v>0.2350630411055286</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.01162095127556051</v>
+        <v>0.01211378211845959</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7538,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2327994923895767</v>
+        <v>0.2254689844418643</v>
       </c>
       <c r="C75">
-        <v>-49638.96052959532</v>
+        <v>-48781.73754276251</v>
       </c>
       <c r="D75">
-        <v>21364.56947040468</v>
+        <v>22221.79245723749</v>
       </c>
       <c r="E75">
         <v>64370.53</v>
@@ -7443,37 +7571,37 @@
         <v>228</v>
       </c>
       <c r="M75">
-        <v>19892.232674</v>
+        <v>19082.947374</v>
       </c>
       <c r="N75">
-        <v>-19664.232674</v>
+        <v>-18854.947374</v>
       </c>
       <c r="O75">
-        <v>-5073.372029892001</v>
+        <v>-4864.576422492</v>
       </c>
       <c r="P75">
-        <v>-14590.860644108</v>
+        <v>-13990.370951508</v>
       </c>
       <c r="Q75">
-        <v>-14440.860644108</v>
+        <v>-13840.370951508</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1996151955318374</v>
+        <v>0.1995022031329027</v>
       </c>
       <c r="T75">
-        <v>3.550030162515039</v>
+        <v>3.549704460344173</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.002957134121846739</v>
+        <v>0.003082542693595965</v>
       </c>
       <c r="W75">
-        <v>0.2450731364328501</v>
+        <v>0.2350731364328501</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.01146176016219669</v>
+        <v>0.0119478398976588</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7620,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2347994923895767</v>
+        <v>0.2273689844418643</v>
       </c>
       <c r="C76">
-        <v>-50973.65123701189</v>
+        <v>-50122.88398503287</v>
       </c>
       <c r="D76">
-        <v>21138.48876298811</v>
+        <v>21989.25601496714</v>
       </c>
       <c r="E76">
         <v>65479.14</v>
@@ -7525,37 +7653,37 @@
         <v>228</v>
       </c>
       <c r="M76">
-        <v>20164.729012</v>
+        <v>19344.357612</v>
       </c>
       <c r="N76">
-        <v>-19936.729012</v>
+        <v>-19116.357612</v>
       </c>
       <c r="O76">
-        <v>-5143.676085096</v>
+        <v>-4932.020263896</v>
       </c>
       <c r="P76">
-        <v>-14793.052926904</v>
+        <v>-14184.337348104</v>
       </c>
       <c r="Q76">
-        <v>-14643.052926904</v>
+        <v>-14034.337348104</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2055311645907543</v>
+        <v>0.205413826330322</v>
       </c>
       <c r="T76">
-        <v>3.686569784150233</v>
+        <v>3.686231554972795</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.002917172849929891</v>
+        <v>0.003040886711250073</v>
       </c>
       <c r="W76">
-        <v>0.2450829589134872</v>
+        <v>0.2350829589134873</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.01130687151135612</v>
+        <v>0.01178638260174447</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7702,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2367994923895767</v>
+        <v>0.2292689844418643</v>
       </c>
       <c r="C77">
-        <v>-52303.60725734448</v>
+        <v>-51459.21414468565</v>
       </c>
       <c r="D77">
-        <v>20917.14274265552</v>
+        <v>21761.53585531435</v>
       </c>
       <c r="E77">
         <v>66587.75</v>
@@ -7607,37 +7735,37 @@
         <v>228</v>
       </c>
       <c r="M77">
-        <v>20437.22535</v>
+        <v>19605.76785</v>
       </c>
       <c r="N77">
-        <v>-20209.22535</v>
+        <v>-19377.76785</v>
       </c>
       <c r="O77">
-        <v>-5213.9801403</v>
+        <v>-4999.4641053</v>
       </c>
       <c r="P77">
-        <v>-14995.2452097</v>
+        <v>-14378.3037447</v>
       </c>
       <c r="Q77">
-        <v>-14845.2452097</v>
+        <v>-14228.3037447</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2119204111743845</v>
+        <v>0.2117983793835349</v>
       </c>
       <c r="T77">
-        <v>3.834032575516242</v>
+        <v>3.833680817171707</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.002878277211930826</v>
+        <v>0.003000341555100072</v>
       </c>
       <c r="W77">
-        <v>0.2450925194613074</v>
+        <v>0.2350925194613074</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.01115611322453813</v>
+        <v>0.01162923083372125</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7784,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2387994923895767</v>
+        <v>0.2311689844418643</v>
       </c>
       <c r="C78">
-        <v>-53628.97578332477</v>
+        <v>-52790.87611991006</v>
       </c>
       <c r="D78">
-        <v>20700.38421667523</v>
+        <v>21538.48388008995</v>
       </c>
       <c r="E78">
         <v>67696.36</v>
@@ -7689,37 +7817,37 @@
         <v>228</v>
       </c>
       <c r="M78">
-        <v>20709.721688</v>
+        <v>19867.178088</v>
       </c>
       <c r="N78">
-        <v>-20481.721688</v>
+        <v>-19639.178088</v>
       </c>
       <c r="O78">
-        <v>-5284.284195504</v>
+        <v>-5066.907946704</v>
       </c>
       <c r="P78">
-        <v>-15197.437492496</v>
+        <v>-14572.270141296</v>
       </c>
       <c r="Q78">
-        <v>-15047.437492496</v>
+        <v>-14422.270141296</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2188420949733171</v>
+        <v>0.2187149785245155</v>
       </c>
       <c r="T78">
-        <v>3.993783932829419</v>
+        <v>3.993417517887194</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.002840405143352789</v>
+        <v>0.002960863376743493</v>
       </c>
       <c r="W78">
-        <v>0.2451018284157639</v>
+        <v>0.2351018284157639</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.01100932226105733</v>
+        <v>0.01147621463854065</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7866,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2407994923895767</v>
+        <v>0.2330689844418643</v>
       </c>
       <c r="C79">
-        <v>-54949.89796899262</v>
+        <v>-54118.0119985767</v>
       </c>
       <c r="D79">
-        <v>20488.07203100738</v>
+        <v>21319.9580014233</v>
       </c>
       <c r="E79">
         <v>68804.97</v>
@@ -7771,37 +7899,37 @@
         <v>228</v>
       </c>
       <c r="M79">
-        <v>20982.218026</v>
+        <v>20128.588326</v>
       </c>
       <c r="N79">
-        <v>-20754.218026</v>
+        <v>-19900.588326</v>
       </c>
       <c r="O79">
-        <v>-5354.588250708</v>
+        <v>-5134.351788108001</v>
       </c>
       <c r="P79">
-        <v>-15399.629775292</v>
+        <v>-14766.236537892</v>
       </c>
       <c r="Q79">
-        <v>-15249.629775292</v>
+        <v>-14616.236537892</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2263656643199831</v>
+        <v>0.2262330210690597</v>
       </c>
       <c r="T79">
-        <v>4.167426712517655</v>
+        <v>4.167044366490986</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.002803516764867687</v>
+        <v>0.002922410605616953</v>
       </c>
       <c r="W79">
-        <v>0.2451108955791955</v>
+        <v>0.2351108955791955</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.01086634404987474</v>
+        <v>0.01132717288998819</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7948,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2427994923895767</v>
+        <v>0.2349689844418643</v>
       </c>
       <c r="C80">
-        <v>-56266.50923622931</v>
+        <v>-55440.75816007391</v>
       </c>
       <c r="D80">
-        <v>20280.07076377069</v>
+        <v>21105.82183992609</v>
       </c>
       <c r="E80">
         <v>69913.58</v>
@@ -7853,37 +7981,37 @@
         <v>228</v>
       </c>
       <c r="M80">
-        <v>21254.714364</v>
+        <v>20389.998564</v>
       </c>
       <c r="N80">
-        <v>-21026.714364</v>
+        <v>-20161.998564</v>
       </c>
       <c r="O80">
-        <v>-5424.892305912001</v>
+        <v>-5201.795629512</v>
       </c>
       <c r="P80">
-        <v>-15601.822058088</v>
+        <v>-14960.202934488</v>
       </c>
       <c r="Q80">
-        <v>-15451.822058088</v>
+        <v>-14810.202934488</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.234573194516346</v>
+        <v>0.2344345220267442</v>
       </c>
       <c r="T80">
-        <v>4.356855199450275</v>
+        <v>4.356455474058758</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.002767574242241179</v>
+        <v>0.002884943802980839</v>
       </c>
       <c r="W80">
-        <v>0.2451197302512571</v>
+        <v>0.2351197302512571</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.01072703194667124</v>
+        <v>0.01118195272473188</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +8030,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2447994923895767</v>
+        <v>0.2368689844418643</v>
       </c>
       <c r="C81">
-        <v>-57578.93956280652</v>
+        <v>-56759.24555913477</v>
       </c>
       <c r="D81">
-        <v>20076.25043719348</v>
+        <v>20895.94444086523</v>
       </c>
       <c r="E81">
         <v>71022.19</v>
@@ -7935,37 +8063,37 @@
         <v>228</v>
       </c>
       <c r="M81">
-        <v>21527.210702</v>
+        <v>20651.408802</v>
       </c>
       <c r="N81">
-        <v>-21299.210702</v>
+        <v>-20423.408802</v>
       </c>
       <c r="O81">
-        <v>-5495.196361116001</v>
+        <v>-5269.239470916001</v>
       </c>
       <c r="P81">
-        <v>-15804.014340884</v>
+        <v>-15154.169331084</v>
       </c>
       <c r="Q81">
-        <v>-15654.014340884</v>
+        <v>-15004.169331084</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2435623942552196</v>
+        <v>0.243417118313732</v>
       </c>
       <c r="T81">
-        <v>4.564324494662194</v>
+        <v>4.563905734728223</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.002732541656896354</v>
+        <v>0.002848425526993739</v>
       </c>
       <c r="W81">
-        <v>0.2451283412607349</v>
+        <v>0.2351283412607349</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.01059124673215639</v>
+        <v>0.01104040901935555</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +8112,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2467994923895767</v>
+        <v>0.2387689844418643</v>
       </c>
       <c r="C82">
-        <v>-58887.31375323822</v>
+        <v>-58073.5999928969</v>
       </c>
       <c r="D82">
-        <v>19876.48624676178</v>
+        <v>20690.20000710311</v>
       </c>
       <c r="E82">
         <v>72130.8</v>
@@ -8017,37 +8145,37 @@
         <v>228</v>
       </c>
       <c r="M82">
-        <v>21799.70704</v>
+        <v>20912.81904</v>
       </c>
       <c r="N82">
-        <v>-21571.70704</v>
+        <v>-20684.81904</v>
       </c>
       <c r="O82">
-        <v>-5565.50041632</v>
+        <v>-5336.68331232</v>
       </c>
       <c r="P82">
-        <v>-16006.20662368</v>
+        <v>-15348.13572768</v>
       </c>
       <c r="Q82">
-        <v>-15856.20662368</v>
+        <v>-15198.13572768</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2534505139679806</v>
+        <v>0.2532979742294186</v>
       </c>
       <c r="T82">
-        <v>4.792540719395304</v>
+        <v>4.792101021464634</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.002698384886185149</v>
+        <v>0.002812820207906317</v>
       </c>
       <c r="W82">
-        <v>0.2451367369949757</v>
+        <v>0.2351367369949757</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.01045885614800446</v>
+        <v>0.01090240390661368</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8194,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2487994923895767</v>
+        <v>0.2406689844418643</v>
       </c>
       <c r="C83">
-        <v>-60191.75169362161</v>
+        <v>-59383.94235233876</v>
       </c>
       <c r="D83">
-        <v>19680.65830637839</v>
+        <v>20488.46764766124</v>
       </c>
       <c r="E83">
         <v>73239.41</v>
@@ -8099,37 +8227,37 @@
         <v>228</v>
       </c>
       <c r="M83">
-        <v>22072.203378</v>
+        <v>21174.229278</v>
       </c>
       <c r="N83">
-        <v>-21844.203378</v>
+        <v>-20946.229278</v>
       </c>
       <c r="O83">
-        <v>-5635.804471524</v>
+        <v>-5404.127153724001</v>
       </c>
       <c r="P83">
-        <v>-16208.398906476</v>
+        <v>-15542.102124276</v>
       </c>
       <c r="Q83">
-        <v>-16058.398906476</v>
+        <v>-15392.102124276</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.264379488387348</v>
+        <v>0.2642189202414933</v>
       </c>
       <c r="T83">
-        <v>5.044779704626635</v>
+        <v>5.044316864699615</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.002665071492528542</v>
+        <v>0.002778094032500066</v>
       </c>
       <c r="W83">
-        <v>0.2451449254271365</v>
+        <v>0.2351449254271365</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0103297344671649</v>
+        <v>0.01076780632751961</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8276,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2507994923895767</v>
+        <v>0.2425689844418643</v>
       </c>
       <c r="C84">
-        <v>-61492.36859156044</v>
+        <v>-60690.38885914889</v>
       </c>
       <c r="D84">
-        <v>19488.65140843956</v>
+        <v>20290.63114085111</v>
       </c>
       <c r="E84">
         <v>74348.02</v>
@@ -8181,37 +8309,37 @@
         <v>228</v>
       </c>
       <c r="M84">
-        <v>22344.699716</v>
+        <v>21435.639516</v>
       </c>
       <c r="N84">
-        <v>-22116.699716</v>
+        <v>-21207.639516</v>
       </c>
       <c r="O84">
-        <v>-5706.108526728</v>
+        <v>-5471.570995128001</v>
       </c>
       <c r="P84">
-        <v>-16410.591189272</v>
+        <v>-15736.068520872</v>
       </c>
       <c r="Q84">
-        <v>-16260.591189272</v>
+        <v>-15586.068520872</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2765227932977562</v>
+        <v>0.276353304699354</v>
       </c>
       <c r="T84">
-        <v>5.32504524377256</v>
+        <v>5.324556690516261</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.002632570620668438</v>
+        <v>0.002744214836981773</v>
       </c>
       <c r="W84">
-        <v>0.2451529141414397</v>
+        <v>0.2351529141414397</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01020376209561413</v>
+        <v>0.01063649161620839</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8358,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2527994923895767</v>
+        <v>0.2444689844418643</v>
       </c>
       <c r="C85">
-        <v>-62789.27520217977</v>
+        <v>-61993.05128900314</v>
       </c>
       <c r="D85">
-        <v>19300.35479782023</v>
+        <v>20096.57871099687</v>
       </c>
       <c r="E85">
         <v>75456.63</v>
@@ -8263,37 +8391,37 @@
         <v>228</v>
       </c>
       <c r="M85">
-        <v>22617.196054</v>
+        <v>21697.049754</v>
       </c>
       <c r="N85">
-        <v>-22389.196054</v>
+        <v>-21469.049754</v>
       </c>
       <c r="O85">
-        <v>-5776.412581932001</v>
+        <v>-5539.014836532001</v>
       </c>
       <c r="P85">
-        <v>-16612.783472068</v>
+        <v>-15930.034917468</v>
       </c>
       <c r="Q85">
-        <v>-16462.783472068</v>
+        <v>-15780.034917468</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2900947223152713</v>
+        <v>0.2899152637993161</v>
       </c>
       <c r="T85">
-        <v>5.638283199288593</v>
+        <v>5.637765907605454</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.002600852902347131</v>
+        <v>0.002711152007620547</v>
       </c>
       <c r="W85">
-        <v>0.2451607103566031</v>
+        <v>0.2351607103566031</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.01008082520289588</v>
+        <v>0.01050834111480836</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8440,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2547994923895767</v>
+        <v>0.2463689844418643</v>
       </c>
       <c r="C86">
-        <v>-64082.57804116373</v>
+        <v>-63292.03718215105</v>
       </c>
       <c r="D86">
-        <v>19115.66195883626</v>
+        <v>19906.20281784894</v>
       </c>
       <c r="E86">
         <v>76565.23999999999</v>
@@ -8345,37 +8473,37 @@
         <v>228</v>
       </c>
       <c r="M86">
-        <v>22889.692392</v>
+        <v>21958.459992</v>
       </c>
       <c r="N86">
-        <v>-22661.692392</v>
+        <v>-21730.459992</v>
       </c>
       <c r="O86">
-        <v>-5846.716637136001</v>
+        <v>-5606.458677936</v>
       </c>
       <c r="P86">
-        <v>-16814.975754864</v>
+        <v>-16124.001314064</v>
       </c>
       <c r="Q86">
-        <v>-16664.975754864</v>
+        <v>-15974.001314064</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3053631424599756</v>
+        <v>0.3051724677867732</v>
       </c>
       <c r="T86">
-        <v>5.990675899244128</v>
+        <v>5.990126276830791</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.002569890367795381</v>
+        <v>0.002678876388482208</v>
       </c>
       <c r="W86">
-        <v>0.2451683209475959</v>
+        <v>0.2351683209475959</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.009960815379051913</v>
+        <v>0.01038324181582251</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8522,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2567994923895767</v>
+        <v>0.2482689844418643</v>
       </c>
       <c r="C87">
-        <v>-65372.37958567742</v>
+        <v>-64587.45004214551</v>
       </c>
       <c r="D87">
-        <v>18934.47041432257</v>
+        <v>19719.39995785448</v>
       </c>
       <c r="E87">
         <v>77673.84999999999</v>
@@ -8427,37 +8555,37 @@
         <v>228</v>
       </c>
       <c r="M87">
-        <v>23162.18873</v>
+        <v>22219.87023</v>
       </c>
       <c r="N87">
-        <v>-22934.18873</v>
+        <v>-21991.87023</v>
       </c>
       <c r="O87">
-        <v>-5917.02069234</v>
+        <v>-5673.90251934</v>
       </c>
       <c r="P87">
-        <v>-17017.16803766</v>
+        <v>-16317.96771066</v>
       </c>
       <c r="Q87">
-        <v>-16867.16803766</v>
+        <v>-16167.96771066</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3226673519573073</v>
+        <v>0.3224639656392248</v>
       </c>
       <c r="T87">
-        <v>6.390054292527069</v>
+        <v>6.389468028619511</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.002539656363468376</v>
+        <v>0.002647360195676535</v>
       </c>
       <c r="W87">
-        <v>0.2451757524658595</v>
+        <v>0.2351757524658595</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.009843629315768876</v>
+        <v>0.01026108602975406</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8604,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2587994923895767</v>
+        <v>0.2501689844418643</v>
       </c>
       <c r="C88">
-        <v>-66658.77846396912</v>
+        <v>-65879.38952348655</v>
       </c>
       <c r="D88">
-        <v>18756.68153603086</v>
+        <v>19536.07047651345</v>
       </c>
       <c r="E88">
         <v>78782.45999999999</v>
@@ -8509,37 +8637,37 @@
         <v>228</v>
       </c>
       <c r="M88">
-        <v>23434.685068</v>
+        <v>22481.280468</v>
       </c>
       <c r="N88">
-        <v>-23206.685068</v>
+        <v>-22253.280468</v>
       </c>
       <c r="O88">
-        <v>-5987.324747544</v>
+        <v>-5741.346360744</v>
       </c>
       <c r="P88">
-        <v>-17219.360320456</v>
+        <v>-16511.934107256</v>
       </c>
       <c r="Q88">
-        <v>-17069.360320456</v>
+        <v>-16361.934107256</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3424435913828293</v>
+        <v>0.342225677470598</v>
       </c>
       <c r="T88">
-        <v>6.846486741993289</v>
+        <v>6.845858602092333</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.002510125475521069</v>
+        <v>0.002616576937587273</v>
       </c>
       <c r="W88">
-        <v>0.2451830111581169</v>
+        <v>0.2351830111581169</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.009729168509771569</v>
+        <v>0.01014177107591963</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8686,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2607994923895767</v>
+        <v>0.2520689844418643</v>
       </c>
       <c r="C89">
-        <v>-67941.86963439017</v>
+        <v>-67167.9516088949</v>
       </c>
       <c r="D89">
-        <v>18582.20036560983</v>
+        <v>19356.11839110509</v>
       </c>
       <c r="E89">
         <v>79891.06999999999</v>
@@ -8591,37 +8719,37 @@
         <v>228</v>
       </c>
       <c r="M89">
-        <v>23707.181406</v>
+        <v>22742.690706</v>
       </c>
       <c r="N89">
-        <v>-23479.181406</v>
+        <v>-22514.690706</v>
       </c>
       <c r="O89">
-        <v>-6057.628802748</v>
+        <v>-5808.790202147999</v>
       </c>
       <c r="P89">
-        <v>-17421.552603252</v>
+        <v>-16705.900503852</v>
       </c>
       <c r="Q89">
-        <v>-17271.552603252</v>
+        <v>-16555.900503852</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3652623291815085</v>
+        <v>0.365027652660644</v>
       </c>
       <c r="T89">
-        <v>7.373139568300465</v>
+        <v>7.372463109945589</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.002481273458561057</v>
+        <v>0.002586501340603511</v>
       </c>
       <c r="W89">
-        <v>0.2451901029838857</v>
+        <v>0.2351901029838857</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.00961733898667072</v>
+        <v>0.0100251989945872</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8768,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2627994923895767</v>
+        <v>0.2539689844418643</v>
       </c>
       <c r="C90">
-        <v>-69221.74455451495</v>
+        <v>-68453.22877687722</v>
       </c>
       <c r="D90">
-        <v>18410.93544548505</v>
+        <v>19179.45122312278</v>
       </c>
       <c r="E90">
         <v>80999.68000000001</v>
@@ -8673,37 +8801,37 @@
         <v>228</v>
       </c>
       <c r="M90">
-        <v>23979.677744</v>
+        <v>23004.100944</v>
       </c>
       <c r="N90">
-        <v>-23751.677744</v>
+        <v>-22776.100944</v>
       </c>
       <c r="O90">
-        <v>-6127.932857952002</v>
+        <v>-5876.234043552001</v>
       </c>
       <c r="P90">
-        <v>-17623.744886048</v>
+        <v>-16899.866900448</v>
       </c>
       <c r="Q90">
-        <v>-17473.744886048</v>
+        <v>-16749.866900448</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3918841899466343</v>
+        <v>0.391629957049031</v>
       </c>
       <c r="T90">
-        <v>7.987567865658838</v>
+        <v>7.986835035774389</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.002453077169259227</v>
+        <v>0.002557109279914834</v>
       </c>
       <c r="W90">
-        <v>0.2451970336317961</v>
+        <v>0.2351970336317961</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.009508051043640386</v>
+        <v>0.009911276278739667</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8850,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2647994923895767</v>
+        <v>0.2558689844418643</v>
       </c>
       <c r="C91">
-        <v>-70498.49134099422</v>
+        <v>-69735.31016019807</v>
       </c>
       <c r="D91">
-        <v>18242.79865900579</v>
+        <v>19005.97983980194</v>
       </c>
       <c r="E91">
         <v>82108.29000000001</v>
@@ -8755,37 +8883,37 @@
         <v>228</v>
       </c>
       <c r="M91">
-        <v>24252.17408200001</v>
+        <v>23265.511182</v>
       </c>
       <c r="N91">
-        <v>-24024.17408200001</v>
+        <v>-23037.511182</v>
       </c>
       <c r="O91">
-        <v>-6198.236913156002</v>
+        <v>-5943.677884956001</v>
       </c>
       <c r="P91">
-        <v>-17825.937168844</v>
+        <v>-17093.833297044</v>
       </c>
       <c r="Q91">
-        <v>-17675.937168844</v>
+        <v>-16943.833297044</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4233463890326919</v>
+        <v>0.4230690440534884</v>
       </c>
       <c r="T91">
-        <v>8.713710398900551</v>
+        <v>8.712910948117516</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.002425514504436089</v>
+        <v>0.002528377714971971</v>
       </c>
       <c r="W91">
-        <v>0.2452038085348096</v>
+        <v>0.2352038085348096</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.009401219009442241</v>
+        <v>0.009799913623922407</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8932,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2667994923895767</v>
+        <v>0.2577689844418642</v>
       </c>
       <c r="C92">
-        <v>-71772.1949207283</v>
+        <v>-71014.2816958289</v>
       </c>
       <c r="D92">
-        <v>18077.70507927171</v>
+        <v>18835.6183041711</v>
       </c>
       <c r="E92">
         <v>83216.90000000001</v>
@@ -8837,37 +8965,37 @@
         <v>228</v>
       </c>
       <c r="M92">
-        <v>24524.67042</v>
+        <v>23526.92142</v>
       </c>
       <c r="N92">
-        <v>-24296.67042</v>
+        <v>-23298.92142</v>
       </c>
       <c r="O92">
-        <v>-6268.540968360001</v>
+        <v>-6011.121726360001</v>
       </c>
       <c r="P92">
-        <v>-18028.12945164</v>
+        <v>-17287.79969364</v>
       </c>
       <c r="Q92">
-        <v>-17878.12945164</v>
+        <v>-17137.79969364</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4611010279359611</v>
+        <v>0.4607959484588373</v>
       </c>
       <c r="T92">
-        <v>9.585081438790606</v>
+        <v>9.584202042929268</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.002398564343275688</v>
+        <v>0.00250028462925006</v>
       </c>
       <c r="W92">
-        <v>0.2452104328844228</v>
+        <v>0.2352104328844228</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.009296761020448407</v>
+        <v>0.009691025694767652</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +9014,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2687994923895767</v>
+        <v>0.2596689844418643</v>
       </c>
       <c r="C93">
-        <v>-73042.93717390572</v>
+        <v>-72290.22626690436</v>
       </c>
       <c r="D93">
-        <v>17915.57282609428</v>
+        <v>18668.28373309565</v>
       </c>
       <c r="E93">
         <v>84325.51000000001</v>
@@ -8919,37 +9047,37 @@
         <v>228</v>
       </c>
       <c r="M93">
-        <v>24797.166758</v>
+        <v>23788.331658</v>
       </c>
       <c r="N93">
-        <v>-24569.166758</v>
+        <v>-23560.331658</v>
       </c>
       <c r="O93">
-        <v>-6338.845023564001</v>
+        <v>-6078.565567764001</v>
       </c>
       <c r="P93">
-        <v>-18230.321734436</v>
+        <v>-17481.766090236</v>
       </c>
       <c r="Q93">
-        <v>-18080.321734436</v>
+        <v>-17331.766090236</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5072455865955123</v>
+        <v>0.506906609398708</v>
       </c>
       <c r="T93">
-        <v>10.65009048754512</v>
+        <v>10.64911338103252</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.002372206493349582</v>
+        <v>0.002472808973983576</v>
       </c>
       <c r="W93">
-        <v>0.2452169116439347</v>
+        <v>0.2352169116439347</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.009194598811432475</v>
+        <v>0.009584530906913136</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +9096,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2707994923895767</v>
+        <v>0.2615689844418643</v>
       </c>
       <c r="C94">
-        <v>-74310.79706941282</v>
+        <v>-73563.22383717835</v>
       </c>
       <c r="D94">
-        <v>17756.3229305872</v>
+        <v>18503.89616282166</v>
       </c>
       <c r="E94">
         <v>85434.12000000001</v>
@@ -9001,37 +9129,37 @@
         <v>228</v>
       </c>
       <c r="M94">
-        <v>25069.663096</v>
+        <v>24049.741896</v>
       </c>
       <c r="N94">
-        <v>-24841.663096</v>
+        <v>-23821.741896</v>
       </c>
       <c r="O94">
-        <v>-6409.149078768001</v>
+        <v>-6146.009409168001</v>
       </c>
       <c r="P94">
-        <v>-18432.514017232</v>
+        <v>-17675.732486832</v>
       </c>
       <c r="Q94">
-        <v>-18282.514017232</v>
+        <v>-17525.732486832</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5649262849199516</v>
+        <v>0.5645449355735468</v>
       </c>
       <c r="T94">
-        <v>11.98135179848826</v>
+        <v>11.98025255366159</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.002346421640160999</v>
+        <v>0.002445930615570711</v>
       </c>
       <c r="W94">
-        <v>0.2452232495608485</v>
+        <v>0.2352232495608484</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.009094657520003824</v>
+        <v>0.00948035122314228</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9178,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2727994923895767</v>
+        <v>0.2634689844418643</v>
       </c>
       <c r="C95">
-        <v>-75575.85079308524</v>
+        <v>-74833.35157843813</v>
       </c>
       <c r="D95">
-        <v>17599.87920691477</v>
+        <v>18342.37842156188</v>
       </c>
       <c r="E95">
         <v>86542.73000000001</v>
@@ -9083,37 +9211,37 @@
         <v>228</v>
       </c>
       <c r="M95">
-        <v>25342.159434</v>
+        <v>24311.152134</v>
       </c>
       <c r="N95">
-        <v>-25114.159434</v>
+        <v>-24083.152134</v>
       </c>
       <c r="O95">
-        <v>-6479.453133972002</v>
+        <v>-6213.453250572001</v>
       </c>
       <c r="P95">
-        <v>-18634.706300028</v>
+        <v>-17869.698883428</v>
       </c>
       <c r="Q95">
-        <v>-18484.706300028</v>
+        <v>-17719.698883428</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.639087182765659</v>
+        <v>0.6386513549411963</v>
       </c>
       <c r="T95">
-        <v>13.69297348398659</v>
+        <v>13.69171720418468</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.002321191299944214</v>
+        <v>0.002419630286371026</v>
       </c>
       <c r="W95">
-        <v>0.2452294511784737</v>
+        <v>0.2352294511784737</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.008996865503659746</v>
+        <v>0.009378411962678412</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9260,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2747994923895767</v>
+        <v>0.2653689844418642</v>
       </c>
       <c r="C96">
-        <v>-76838.17186923884</v>
+        <v>-76100.6839913033</v>
       </c>
       <c r="D96">
-        <v>17446.16813076118</v>
+        <v>18183.65600869671</v>
       </c>
       <c r="E96">
         <v>87651.34000000001</v>
@@ -9165,37 +9293,37 @@
         <v>228</v>
       </c>
       <c r="M96">
-        <v>25614.65577200001</v>
+        <v>24572.562372</v>
       </c>
       <c r="N96">
-        <v>-25386.65577200001</v>
+        <v>-24344.562372</v>
       </c>
       <c r="O96">
-        <v>-6549.757189176002</v>
+        <v>-6280.897091976001</v>
       </c>
       <c r="P96">
-        <v>-18836.898582824</v>
+        <v>-18063.665280024</v>
       </c>
       <c r="Q96">
-        <v>-18686.898582824</v>
+        <v>-17913.665280024</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.737968379893269</v>
+        <v>0.7374599140980626</v>
       </c>
       <c r="T96">
-        <v>15.97513573131769</v>
+        <v>15.97367007154879</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.002296497775476723</v>
+        <v>0.002393889538643675</v>
       </c>
       <c r="W96">
-        <v>0.2452355208467878</v>
+        <v>0.2352355208467878</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.008901154168514447</v>
+        <v>0.009278641622649908</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9342,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2767994923895767</v>
+        <v>0.2672689844418643</v>
       </c>
       <c r="C97">
-        <v>-78097.83127588721</v>
+        <v>-77365.29301980652</v>
       </c>
       <c r="D97">
-        <v>17295.1187241128</v>
+        <v>18027.6569801935</v>
       </c>
       <c r="E97">
         <v>88759.95000000001</v>
@@ -9247,37 +9375,37 @@
         <v>228</v>
       </c>
       <c r="M97">
-        <v>25887.15211000001</v>
+        <v>24833.97261</v>
       </c>
       <c r="N97">
-        <v>-25659.15211000001</v>
+        <v>-24605.97261</v>
       </c>
       <c r="O97">
-        <v>-6620.061244380002</v>
+        <v>-6348.340933380001</v>
       </c>
       <c r="P97">
-        <v>-19039.09086562</v>
+        <v>-18257.63167662</v>
       </c>
       <c r="Q97">
-        <v>-18889.09086562</v>
+        <v>-18107.63167662</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8764020558719232</v>
+        <v>0.8757918969176756</v>
       </c>
       <c r="T97">
-        <v>19.17016287758124</v>
+        <v>19.16840408585856</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.00227232411468223</v>
+        <v>0.002368690701394793</v>
       </c>
       <c r="W97">
-        <v>0.2452414627326111</v>
+        <v>0.2352414627326111</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.008807457808845842</v>
+        <v>0.009180971710832542</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9424,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2787994923895767</v>
+        <v>0.2691689844418643</v>
       </c>
       <c r="C98">
-        <v>-79354.89755402532</v>
+        <v>-78627.24816012647</v>
       </c>
       <c r="D98">
-        <v>17146.66244597469</v>
+        <v>17874.31183987352</v>
       </c>
       <c r="E98">
         <v>89868.56</v>
@@ -9329,37 +9457,37 @@
         <v>228</v>
       </c>
       <c r="M98">
-        <v>26159.648448</v>
+        <v>25095.382848</v>
       </c>
       <c r="N98">
-        <v>-25931.648448</v>
+        <v>-24867.382848</v>
       </c>
       <c r="O98">
-        <v>-6690.365299584</v>
+        <v>-6415.784774784001</v>
       </c>
       <c r="P98">
-        <v>-19241.283148416</v>
+        <v>-18451.598073216</v>
       </c>
       <c r="Q98">
-        <v>-19091.283148416</v>
+        <v>-18301.598073216</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.084052569839902</v>
+        <v>1.083289871147092</v>
       </c>
       <c r="T98">
-        <v>23.96270359697649</v>
+        <v>23.96050510732315</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002248654071820958</v>
+        <v>0.002344016839921931</v>
       </c>
       <c r="W98">
-        <v>0.2452472808291464</v>
+        <v>0.2352472808291464</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.008715713456670326</v>
+        <v>0.009085336588844695</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9506,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2807994923895767</v>
+        <v>0.2710689844418643</v>
       </c>
       <c r="C99">
-        <v>-80609.4369113326</v>
+        <v>-79886.61656381842</v>
       </c>
       <c r="D99">
-        <v>17000.73308866741</v>
+        <v>17723.55343618158</v>
       </c>
       <c r="E99">
         <v>90977.17</v>
@@ -9411,37 +9539,37 @@
         <v>228</v>
       </c>
       <c r="M99">
-        <v>26432.144786</v>
+        <v>25356.793086</v>
       </c>
       <c r="N99">
-        <v>-26204.144786</v>
+        <v>-25128.793086</v>
       </c>
       <c r="O99">
-        <v>-6760.669354788</v>
+        <v>-6483.228616188</v>
       </c>
       <c r="P99">
-        <v>-19443.475431212</v>
+        <v>-18645.564469812</v>
       </c>
       <c r="Q99">
-        <v>-19293.475431212</v>
+        <v>-18495.564469812</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.430136759786536</v>
+        <v>1.429119828196123</v>
       </c>
       <c r="T99">
-        <v>31.95027146263533</v>
+        <v>31.94734014309753</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.002225472071080536</v>
+        <v>0.00231985171786088</v>
       </c>
       <c r="W99">
-        <v>0.2452529789649284</v>
+        <v>0.2352529789649284</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.008625860740622215</v>
+        <v>0.008991673325042138</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9588,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2827994923895766</v>
+        <v>0.2729689844418643</v>
       </c>
       <c r="C100">
-        <v>-81861.51332062534</v>
+        <v>-81143.46313586403</v>
       </c>
       <c r="D100">
-        <v>16857.26667937466</v>
+        <v>17575.31686413597</v>
       </c>
       <c r="E100">
         <v>92085.78</v>
@@ -9493,37 +9621,37 @@
         <v>228</v>
       </c>
       <c r="M100">
-        <v>26704.641124</v>
+        <v>25618.203324</v>
       </c>
       <c r="N100">
-        <v>-26476.641124</v>
+        <v>-25390.203324</v>
       </c>
       <c r="O100">
-        <v>-6830.973409992001</v>
+        <v>-6550.672457592001</v>
       </c>
       <c r="P100">
-        <v>-19645.667714008</v>
+        <v>-18839.530866408</v>
       </c>
       <c r="Q100">
-        <v>-19495.667714008</v>
+        <v>-18689.530866408</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.122305139679803</v>
+        <v>2.120779742294184</v>
       </c>
       <c r="T100">
-        <v>47.92540719395299</v>
+        <v>47.92101021464629</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002202763172396041</v>
+        <v>0.002296179761556178</v>
       </c>
       <c r="W100">
-        <v>0.2452585608122251</v>
+        <v>0.2352585608122251</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9659,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.008537841753473052</v>
+        <v>0.008899921556419277</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9670,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2847994923895767</v>
+        <v>0.2748689844418643</v>
       </c>
       <c r="C101">
-        <v>-83111.18861336577</v>
+        <v>-82397.85062784192</v>
       </c>
       <c r="D101">
-        <v>16716.20138663423</v>
+        <v>17429.53937215808</v>
       </c>
       <c r="E101">
         <v>93194.39</v>
@@ -9575,37 +9703,37 @@
         <v>228</v>
       </c>
       <c r="M101">
-        <v>26977.137462</v>
+        <v>25879.613562</v>
       </c>
       <c r="N101">
-        <v>-26749.137462</v>
+        <v>-25651.613562</v>
       </c>
       <c r="O101">
-        <v>-6901.277465196001</v>
+        <v>-6618.116298996001</v>
       </c>
       <c r="P101">
-        <v>-19847.859996804</v>
+        <v>-19033.497263004</v>
       </c>
       <c r="Q101">
-        <v>-19697.859996804</v>
+        <v>-18883.497263004</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.198810279359606</v>
+        <v>4.195759484588368</v>
       </c>
       <c r="T101">
-        <v>95.85081438790597</v>
+        <v>95.84202042929259</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.002180513039341535</v>
+        <v>0.002272986026590964</v>
       </c>
       <c r="W101">
-        <v>0.2452640298949299</v>
+        <v>0.2352640298949299</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9741,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.008451600927680381</v>
+        <v>0.008810023358879704</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_general.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08739319017856015</v>
+        <v>0.08723820574789948</v>
       </c>
       <c r="C2">
-        <v>105915.8789426729</v>
+        <v>105166.2876659269</v>
       </c>
       <c r="D2">
-        <v>95990.87894267295</v>
+        <v>96349.89766592694</v>
       </c>
       <c r="E2">
-        <v>-16558</v>
+        <v>-15449.39</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1108.61</v>
       </c>
       <c r="G2">
         <v>9925</v>
@@ -1585,45 +1585,45 @@
         <v>228</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>61.30613300000002</v>
       </c>
       <c r="N2">
-        <v>228</v>
+        <v>166.693867</v>
       </c>
       <c r="O2">
-        <v>58.824</v>
+        <v>43.007017686</v>
       </c>
       <c r="P2">
-        <v>169.176</v>
+        <v>123.686849314</v>
       </c>
       <c r="Q2">
-        <v>319.176</v>
+        <v>273.686849314</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08739319017856015</v>
+        <v>0.08770492903828229</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200962</v>
+        <v>0.96778127109197</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0373226</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>3.71904063823435</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08723820574789948</v>
+        <v>0.08813249394448081</v>
       </c>
       <c r="C3">
-        <v>105166.2876659269</v>
+        <v>102022.2536170282</v>
       </c>
       <c r="D3">
-        <v>96349.89766592694</v>
+        <v>94314.47361702818</v>
       </c>
       <c r="E3">
-        <v>-15449.39</v>
+        <v>-14340.78</v>
       </c>
       <c r="F3">
-        <v>1108.61</v>
+        <v>2217.22</v>
       </c>
       <c r="G3">
         <v>9925</v>
@@ -1667,45 +1667,45 @@
         <v>228</v>
       </c>
       <c r="M3">
-        <v>61.30613300000002</v>
+        <v>262.962292</v>
       </c>
       <c r="N3">
-        <v>166.693867</v>
+        <v>-34.96229200000005</v>
       </c>
       <c r="O3">
-        <v>43.007017686</v>
+        <v>-9.020271336000013</v>
       </c>
       <c r="P3">
-        <v>123.686849314</v>
+        <v>-25.94202066400003</v>
       </c>
       <c r="Q3">
-        <v>273.686849314</v>
+        <v>124.057979336</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08770492903828229</v>
+        <v>0.08805214729438801</v>
       </c>
       <c r="T3">
-        <v>0.96778127109197</v>
+        <v>0.9758001684616172</v>
       </c>
       <c r="U3">
-        <v>0.05530000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V3">
-        <v>0.258</v>
+        <v>0.2236974721835783</v>
       </c>
       <c r="W3">
-        <v>0.04103260000000001</v>
+        <v>0.09206947979902763</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y3">
-        <v>3.71904063823435</v>
+        <v>0.8670444658278228</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08813249394448081</v>
+        <v>0.09140267051435594</v>
       </c>
       <c r="C4">
-        <v>102022.2536170282</v>
+        <v>94150.33396117331</v>
       </c>
       <c r="D4">
-        <v>94314.47361702818</v>
+        <v>87551.16396117331</v>
       </c>
       <c r="E4">
-        <v>-14340.78</v>
+        <v>-13232.17</v>
       </c>
       <c r="F4">
-        <v>2217.22</v>
+        <v>3325.83</v>
       </c>
       <c r="G4">
         <v>9925</v>
@@ -1749,45 +1749,45 @@
         <v>228</v>
       </c>
       <c r="M4">
-        <v>262.962292</v>
+        <v>667.8266640000001</v>
       </c>
       <c r="N4">
-        <v>-34.96229200000005</v>
+        <v>-439.8266640000001</v>
       </c>
       <c r="O4">
-        <v>-9.020271336000013</v>
+        <v>-113.475279312</v>
       </c>
       <c r="P4">
-        <v>-25.94202066400003</v>
+        <v>-326.3513846880001</v>
       </c>
       <c r="Q4">
-        <v>124.057979336</v>
+        <v>-176.3513846880001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08805214729438801</v>
+        <v>0.08856626898801585</v>
       </c>
       <c r="T4">
-        <v>0.9758001684616172</v>
+        <v>0.9876736486839691</v>
       </c>
       <c r="U4">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V4">
-        <v>0.2236974721835783</v>
+        <v>0.08808273639101058</v>
       </c>
       <c r="W4">
-        <v>0.09206947979902763</v>
+        <v>0.1831129865326851</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y4">
-        <v>0.8670444658278228</v>
+        <v>0.341405955003917</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09140267051435594</v>
+        <v>0.09295267051435592</v>
       </c>
       <c r="C5">
-        <v>94150.33396117331</v>
+        <v>90163.74689943931</v>
       </c>
       <c r="D5">
-        <v>87551.16396117331</v>
+        <v>84673.18689943932</v>
       </c>
       <c r="E5">
-        <v>-13232.17</v>
+        <v>-12123.56</v>
       </c>
       <c r="F5">
-        <v>3325.83</v>
+        <v>4434.440000000001</v>
       </c>
       <c r="G5">
         <v>9925</v>
@@ -1831,37 +1831,37 @@
         <v>228</v>
       </c>
       <c r="M5">
-        <v>667.8266640000001</v>
+        <v>890.4355520000001</v>
       </c>
       <c r="N5">
-        <v>-439.8266640000001</v>
+        <v>-662.4355520000001</v>
       </c>
       <c r="O5">
-        <v>-113.475279312</v>
+        <v>-170.908372416</v>
       </c>
       <c r="P5">
-        <v>-326.3513846880001</v>
+        <v>-491.5271795840001</v>
       </c>
       <c r="Q5">
-        <v>-176.3513846880001</v>
+        <v>-341.5271795840001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08856626898801585</v>
+        <v>0.08901175095664102</v>
       </c>
       <c r="T5">
-        <v>0.9876736486839691</v>
+        <v>0.9979619158577603</v>
       </c>
       <c r="U5">
         <v>0.2008</v>
       </c>
       <c r="V5">
-        <v>0.08808273639101058</v>
+        <v>0.06606205229325793</v>
       </c>
       <c r="W5">
-        <v>0.1831129865326851</v>
+        <v>0.1875347398995138</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.341405955003917</v>
+        <v>0.2560544662529377</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09295267051435592</v>
+        <v>0.09450267051435593</v>
       </c>
       <c r="C6">
-        <v>90163.74689943931</v>
+        <v>86360.34751093041</v>
       </c>
       <c r="D6">
-        <v>84673.18689943932</v>
+        <v>81978.39751093042</v>
       </c>
       <c r="E6">
-        <v>-12123.56</v>
+        <v>-11014.95</v>
       </c>
       <c r="F6">
-        <v>4434.440000000001</v>
+        <v>5543.05</v>
       </c>
       <c r="G6">
         <v>9925</v>
@@ -1913,37 +1913,37 @@
         <v>228</v>
       </c>
       <c r="M6">
-        <v>890.4355520000001</v>
+        <v>1113.04444</v>
       </c>
       <c r="N6">
-        <v>-662.4355520000001</v>
+        <v>-885.0444400000001</v>
       </c>
       <c r="O6">
-        <v>-170.908372416</v>
+        <v>-228.34146552</v>
       </c>
       <c r="P6">
-        <v>-491.5271795840001</v>
+        <v>-656.7029744800001</v>
       </c>
       <c r="Q6">
-        <v>-341.5271795840001</v>
+        <v>-506.7029744800001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08901175095664102</v>
+        <v>0.08946661149302672</v>
       </c>
       <c r="T6">
-        <v>0.9979619158577603</v>
+        <v>1.008466778129947</v>
       </c>
       <c r="U6">
         <v>0.2008</v>
       </c>
       <c r="V6">
-        <v>0.06606205229325793</v>
+        <v>0.05284964183460635</v>
       </c>
       <c r="W6">
-        <v>0.1875347398995138</v>
+        <v>0.190187791919611</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.2560544662529377</v>
+        <v>0.2048435730023502</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09450267051435593</v>
+        <v>0.09816898444186427</v>
       </c>
       <c r="C7">
-        <v>86360.34751093041</v>
+        <v>79512.49044031375</v>
       </c>
       <c r="D7">
-        <v>81978.39751093042</v>
+        <v>76239.15044031375</v>
       </c>
       <c r="E7">
-        <v>-11014.95</v>
+        <v>-9906.34</v>
       </c>
       <c r="F7">
-        <v>5543.05</v>
+        <v>6651.660000000001</v>
       </c>
       <c r="G7">
         <v>9925</v>
@@ -1995,45 +1995,45 @@
         <v>228</v>
       </c>
       <c r="M7">
-        <v>1113.04444</v>
+        <v>1568.461428</v>
       </c>
       <c r="N7">
-        <v>-885.0444400000001</v>
+        <v>-1340.461428</v>
       </c>
       <c r="O7">
-        <v>-228.34146552</v>
+        <v>-345.8390484240001</v>
       </c>
       <c r="P7">
-        <v>-656.7029744800001</v>
+        <v>-994.6223795760002</v>
       </c>
       <c r="Q7">
-        <v>-506.7029744800001</v>
+        <v>-844.6223795760002</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08946661149302672</v>
+        <v>0.08994850515519545</v>
       </c>
       <c r="T7">
-        <v>1.008466778129947</v>
+        <v>1.019595962013752</v>
       </c>
       <c r="U7">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.05284964183460635</v>
+        <v>0.0375042694387509</v>
       </c>
       <c r="W7">
-        <v>0.190187791919611</v>
+        <v>0.2269564932663426</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y7">
-        <v>0.2048435730023502</v>
+        <v>0.1453653854215151</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09816898444186427</v>
+        <v>0.1000689844418643</v>
       </c>
       <c r="C8">
-        <v>79512.49044031375</v>
+        <v>75734.68757948601</v>
       </c>
       <c r="D8">
-        <v>76239.15044031375</v>
+        <v>73569.95757948601</v>
       </c>
       <c r="E8">
-        <v>-9906.34</v>
+        <v>-8797.73</v>
       </c>
       <c r="F8">
-        <v>6651.66</v>
+        <v>7760.27</v>
       </c>
       <c r="G8">
         <v>9925</v>
@@ -2077,37 +2077,37 @@
         <v>228</v>
       </c>
       <c r="M8">
-        <v>1568.461428</v>
+        <v>1829.871666</v>
       </c>
       <c r="N8">
-        <v>-1340.461428</v>
+        <v>-1601.871666</v>
       </c>
       <c r="O8">
-        <v>-345.8390484240001</v>
+        <v>-413.282889828</v>
       </c>
       <c r="P8">
-        <v>-994.622379576</v>
+        <v>-1188.588776172</v>
       </c>
       <c r="Q8">
-        <v>-844.622379576</v>
+        <v>-1038.588776172</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08994850515519545</v>
+        <v>0.09042322026439109</v>
       </c>
       <c r="T8">
-        <v>1.019595962013752</v>
+        <v>1.03055935945476</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.0375042694387509</v>
+        <v>0.03214651666178649</v>
       </c>
       <c r="W8">
-        <v>0.2269564932663426</v>
+        <v>0.2282198513711508</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.1453653854215151</v>
+        <v>0.1245989017898701</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1000689844418643</v>
+        <v>0.1019689844418643</v>
       </c>
       <c r="C9">
-        <v>75734.68757948602</v>
+        <v>72137.46360880435</v>
       </c>
       <c r="D9">
-        <v>73569.95757948603</v>
+        <v>71081.34360880435</v>
       </c>
       <c r="E9">
-        <v>-8797.73</v>
+        <v>-7689.119999999999</v>
       </c>
       <c r="F9">
-        <v>7760.27</v>
+        <v>8868.880000000001</v>
       </c>
       <c r="G9">
         <v>9925</v>
@@ -2159,37 +2159,37 @@
         <v>228</v>
       </c>
       <c r="M9">
-        <v>1829.871666</v>
+        <v>2091.281904</v>
       </c>
       <c r="N9">
-        <v>-1601.871666</v>
+        <v>-1863.281904</v>
       </c>
       <c r="O9">
-        <v>-413.2828898280001</v>
+        <v>-480.7267312320001</v>
       </c>
       <c r="P9">
-        <v>-1188.588776172</v>
+        <v>-1382.555172768</v>
       </c>
       <c r="Q9">
-        <v>-1038.588776172</v>
+        <v>-1232.555172768</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09042322026439109</v>
+        <v>0.09090825526726491</v>
       </c>
       <c r="T9">
-        <v>1.03055935945476</v>
+        <v>1.041761091622746</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.03214651666178649</v>
+        <v>0.02812820207906317</v>
       </c>
       <c r="W9">
-        <v>0.2282198513711508</v>
+        <v>0.2291673699497569</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.1245989017898701</v>
+        <v>0.1090240390661363</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1019689844418643</v>
+        <v>0.1038689844418643</v>
       </c>
       <c r="C10">
-        <v>72137.46360880435</v>
+        <v>68703.09306460305</v>
       </c>
       <c r="D10">
-        <v>71081.34360880435</v>
+        <v>68755.58306460305</v>
       </c>
       <c r="E10">
-        <v>-7689.119999999999</v>
+        <v>-6580.51</v>
       </c>
       <c r="F10">
-        <v>8868.880000000001</v>
+        <v>9977.49</v>
       </c>
       <c r="G10">
         <v>9925</v>
@@ -2241,37 +2241,37 @@
         <v>228</v>
       </c>
       <c r="M10">
-        <v>2091.281904</v>
+        <v>2352.692142</v>
       </c>
       <c r="N10">
-        <v>-1863.281904</v>
+        <v>-2124.692142</v>
       </c>
       <c r="O10">
-        <v>-480.7267312320001</v>
+        <v>-548.170572636</v>
       </c>
       <c r="P10">
-        <v>-1382.555172768</v>
+        <v>-1576.521569364</v>
       </c>
       <c r="Q10">
-        <v>-1232.555172768</v>
+        <v>-1426.521569364</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09090825526726491</v>
+        <v>0.091403950380092</v>
       </c>
       <c r="T10">
-        <v>1.041761091622746</v>
+        <v>1.053209015706513</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.02812820207906317</v>
+        <v>0.0250028462925006</v>
       </c>
       <c r="W10">
-        <v>0.2291673699497569</v>
+        <v>0.2299043288442284</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.1090240390661363</v>
+        <v>0.09691025694767674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1038689844418643</v>
+        <v>0.1057689844418643</v>
       </c>
       <c r="C11">
-        <v>68703.09306460305</v>
+        <v>65416.09686982951</v>
       </c>
       <c r="D11">
-        <v>68755.58306460305</v>
+        <v>66577.19686982951</v>
       </c>
       <c r="E11">
-        <v>-6580.51</v>
+        <v>-5471.900000000001</v>
       </c>
       <c r="F11">
-        <v>9977.49</v>
+        <v>11086.1</v>
       </c>
       <c r="G11">
         <v>9925</v>
@@ -2323,37 +2323,37 @@
         <v>228</v>
       </c>
       <c r="M11">
-        <v>2352.692142</v>
+        <v>2614.10238</v>
       </c>
       <c r="N11">
-        <v>-2124.692142</v>
+        <v>-2386.10238</v>
       </c>
       <c r="O11">
-        <v>-548.170572636</v>
+        <v>-615.6144140399999</v>
       </c>
       <c r="P11">
-        <v>-1576.521569364</v>
+        <v>-1770.48796596</v>
       </c>
       <c r="Q11">
-        <v>-1426.521569364</v>
+        <v>-1620.48796596</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.091403950380092</v>
+        <v>0.0919106609398708</v>
       </c>
       <c r="T11">
-        <v>1.053209015706513</v>
+        <v>1.064911338103252</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.0250028462925006</v>
+        <v>0.02250256166325054</v>
       </c>
       <c r="W11">
-        <v>0.2299043288442284</v>
+        <v>0.2304938959598055</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.09691025694767674</v>
+        <v>0.08721923125290909</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1057689844418643</v>
+        <v>0.1076689844418643</v>
       </c>
       <c r="C12">
-        <v>65416.09686982951</v>
+        <v>62262.89740074681</v>
       </c>
       <c r="D12">
-        <v>66577.19686982951</v>
+        <v>64532.60740074681</v>
       </c>
       <c r="E12">
-        <v>-5471.9</v>
+        <v>-4363.289999999999</v>
       </c>
       <c r="F12">
-        <v>11086.1</v>
+        <v>12194.71</v>
       </c>
       <c r="G12">
         <v>9925</v>
@@ -2405,37 +2405,37 @@
         <v>228</v>
       </c>
       <c r="M12">
-        <v>2614.10238</v>
+        <v>2875.512618</v>
       </c>
       <c r="N12">
-        <v>-2386.10238</v>
+        <v>-2647.512618</v>
       </c>
       <c r="O12">
-        <v>-615.61441404</v>
+        <v>-683.0582554440001</v>
       </c>
       <c r="P12">
-        <v>-1770.48796596</v>
+        <v>-1964.454362556</v>
       </c>
       <c r="Q12">
-        <v>-1620.48796596</v>
+        <v>-1814.454362556</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0919106609398708</v>
+        <v>0.09242875825380194</v>
       </c>
       <c r="T12">
-        <v>1.064911338103252</v>
+        <v>1.076876634036996</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.02250256166325054</v>
+        <v>0.02045687423931867</v>
       </c>
       <c r="W12">
-        <v>0.2304938959598055</v>
+        <v>0.2309762690543687</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.08721923125290909</v>
+        <v>0.07929021022991734</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1076689844418643</v>
+        <v>0.1095689844418643</v>
       </c>
       <c r="C13">
-        <v>62262.89740074681</v>
+        <v>59231.53521746249</v>
       </c>
       <c r="D13">
-        <v>64532.60740074681</v>
+        <v>62609.85521746249</v>
       </c>
       <c r="E13">
-        <v>-4363.289999999999</v>
+        <v>-3254.68</v>
       </c>
       <c r="F13">
-        <v>12194.71</v>
+        <v>13303.32</v>
       </c>
       <c r="G13">
         <v>9925</v>
@@ -2487,37 +2487,37 @@
         <v>228</v>
       </c>
       <c r="M13">
-        <v>2875.512618</v>
+        <v>3136.922856</v>
       </c>
       <c r="N13">
-        <v>-2647.512618</v>
+        <v>-2908.922856</v>
       </c>
       <c r="O13">
-        <v>-683.0582554440001</v>
+        <v>-750.5020968480001</v>
       </c>
       <c r="P13">
-        <v>-1964.454362556</v>
+        <v>-2158.420759152</v>
       </c>
       <c r="Q13">
-        <v>-1814.454362556</v>
+        <v>-2008.420759152</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09242875825380194</v>
+        <v>0.09295863050668604</v>
       </c>
       <c r="T13">
-        <v>1.076876634036996</v>
+        <v>1.089113868514689</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.02045687423931867</v>
+        <v>0.01875213471937545</v>
       </c>
       <c r="W13">
-        <v>0.2309762690543687</v>
+        <v>0.2313782466331713</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.07929021022991734</v>
+        <v>0.07268269271075756</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1095689844418643</v>
+        <v>0.1114689844418643</v>
       </c>
       <c r="C14">
-        <v>59231.53521746249</v>
+        <v>56311.43496945217</v>
       </c>
       <c r="D14">
-        <v>62609.85521746249</v>
+        <v>60798.36496945217</v>
       </c>
       <c r="E14">
-        <v>-3254.68</v>
+        <v>-2146.07</v>
       </c>
       <c r="F14">
-        <v>13303.32</v>
+        <v>14411.93</v>
       </c>
       <c r="G14">
         <v>9925</v>
@@ -2569,37 +2569,37 @@
         <v>228</v>
       </c>
       <c r="M14">
-        <v>3136.922856</v>
+        <v>3398.333094</v>
       </c>
       <c r="N14">
-        <v>-2908.922856</v>
+        <v>-3170.333094</v>
       </c>
       <c r="O14">
-        <v>-750.5020968480001</v>
+        <v>-817.945938252</v>
       </c>
       <c r="P14">
-        <v>-2158.420759152</v>
+        <v>-2352.387155748</v>
       </c>
       <c r="Q14">
-        <v>-2008.420759152</v>
+        <v>-2202.387155748</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09295863050668604</v>
+        <v>0.09350068373090083</v>
       </c>
       <c r="T14">
-        <v>1.089113868514689</v>
+        <v>1.101632418727502</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.01875213471937545</v>
+        <v>0.01730966281788503</v>
       </c>
       <c r="W14">
-        <v>0.2313782466331713</v>
+        <v>0.2317183815075427</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.07268269271075756</v>
+        <v>0.06709171634839162</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1114689844418643</v>
+        <v>0.1133689844418643</v>
       </c>
       <c r="C15">
-        <v>56311.43496945217</v>
+        <v>53493.21079667519</v>
       </c>
       <c r="D15">
-        <v>60798.36496945217</v>
+        <v>59088.75079667518</v>
       </c>
       <c r="E15">
-        <v>-2146.07</v>
+        <v>-1037.459999999999</v>
       </c>
       <c r="F15">
-        <v>14411.93</v>
+        <v>15520.54</v>
       </c>
       <c r="G15">
         <v>9925</v>
@@ -2651,37 +2651,37 @@
         <v>228</v>
       </c>
       <c r="M15">
-        <v>3398.333094</v>
+        <v>3659.743332</v>
       </c>
       <c r="N15">
-        <v>-3170.333094</v>
+        <v>-3431.743332</v>
       </c>
       <c r="O15">
-        <v>-817.945938252</v>
+        <v>-885.3897796560002</v>
       </c>
       <c r="P15">
-        <v>-2352.387155748</v>
+        <v>-2546.353552344</v>
       </c>
       <c r="Q15">
-        <v>-2202.387155748</v>
+        <v>-2396.353552344</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09350068373090083</v>
+        <v>0.09405534284405083</v>
       </c>
       <c r="T15">
-        <v>1.101632418727502</v>
+        <v>1.114442098015031</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.01730966281788503</v>
+        <v>0.01607325833089324</v>
       </c>
       <c r="W15">
-        <v>0.2317183815075427</v>
+        <v>0.2320099256855754</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.06709171634839162</v>
+        <v>0.06229945089493505</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1133689844418643</v>
+        <v>0.1152689844418643</v>
       </c>
       <c r="C16">
-        <v>53493.21079667519</v>
+        <v>50768.50366475817</v>
       </c>
       <c r="D16">
-        <v>59088.75079667518</v>
+        <v>57472.65366475817</v>
       </c>
       <c r="E16">
-        <v>-1037.459999999999</v>
+        <v>71.15000000000146</v>
       </c>
       <c r="F16">
-        <v>15520.54</v>
+        <v>16629.15</v>
       </c>
       <c r="G16">
         <v>9925</v>
@@ -2733,37 +2733,37 @@
         <v>228</v>
       </c>
       <c r="M16">
-        <v>3659.743332</v>
+        <v>3921.15357</v>
       </c>
       <c r="N16">
-        <v>-3431.743332</v>
+        <v>-3693.15357</v>
       </c>
       <c r="O16">
-        <v>-885.3897796560002</v>
+        <v>-952.8336210600002</v>
       </c>
       <c r="P16">
-        <v>-2546.353552344</v>
+        <v>-2740.31994894</v>
       </c>
       <c r="Q16">
-        <v>-2396.353552344</v>
+        <v>-2590.31994894</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09405534284405083</v>
+        <v>0.09462305275986321</v>
       </c>
       <c r="T16">
-        <v>1.114442098015031</v>
+        <v>1.12755318152109</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.01607325833089324</v>
+        <v>0.01500170777550036</v>
       </c>
       <c r="W16">
-        <v>0.2320099256855754</v>
+        <v>0.232262597306537</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.06229945089493505</v>
+        <v>0.05814615416860602</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1152689844418643</v>
+        <v>0.1171689844418643</v>
       </c>
       <c r="C17">
-        <v>50768.5036647582</v>
+        <v>48129.84468315902</v>
       </c>
       <c r="D17">
-        <v>57472.6536647582</v>
+        <v>55942.60468315902</v>
       </c>
       <c r="E17">
-        <v>71.14999999999782</v>
+        <v>1179.760000000002</v>
       </c>
       <c r="F17">
-        <v>16629.15</v>
+        <v>17737.76</v>
       </c>
       <c r="G17">
         <v>9925</v>
@@ -2815,37 +2815,37 @@
         <v>228</v>
       </c>
       <c r="M17">
-        <v>3921.153569999999</v>
+        <v>4182.563808000001</v>
       </c>
       <c r="N17">
-        <v>-3693.153569999999</v>
+        <v>-3954.563808000001</v>
       </c>
       <c r="O17">
-        <v>-952.8336210599999</v>
+        <v>-1020.277462464</v>
       </c>
       <c r="P17">
-        <v>-2740.319948939999</v>
+        <v>-2934.286345536001</v>
       </c>
       <c r="Q17">
-        <v>-2590.319948939999</v>
+        <v>-2784.286345536001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09462305275986319</v>
+        <v>0.095204279578433</v>
       </c>
       <c r="T17">
-        <v>1.12755318152109</v>
+        <v>1.140976433682056</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01500170777550036</v>
+        <v>0.01406410103953159</v>
       </c>
       <c r="W17">
-        <v>0.232262597306537</v>
+        <v>0.2324836849748785</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.05814615416860602</v>
+        <v>0.05451201953306817</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1171689844418643</v>
+        <v>0.1190689844418643</v>
       </c>
       <c r="C18">
-        <v>48129.84468315902</v>
+        <v>45570.53968980422</v>
       </c>
       <c r="D18">
-        <v>55942.60468315902</v>
+        <v>54491.90968980423</v>
       </c>
       <c r="E18">
-        <v>1179.760000000002</v>
+        <v>2288.370000000003</v>
       </c>
       <c r="F18">
-        <v>17737.76</v>
+        <v>18846.37</v>
       </c>
       <c r="G18">
         <v>9925</v>
@@ -2897,37 +2897,37 @@
         <v>228</v>
       </c>
       <c r="M18">
-        <v>4182.563808000001</v>
+        <v>4443.974046000001</v>
       </c>
       <c r="N18">
-        <v>-3954.563808000001</v>
+        <v>-4215.974046000001</v>
       </c>
       <c r="O18">
-        <v>-1020.277462464</v>
+        <v>-1087.721303868</v>
       </c>
       <c r="P18">
-        <v>-2934.286345536001</v>
+        <v>-3128.252742132001</v>
       </c>
       <c r="Q18">
-        <v>-2784.286345536001</v>
+        <v>-2978.252742132001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.095204279578433</v>
+        <v>0.09579951186251051</v>
       </c>
       <c r="T18">
-        <v>1.140976433682056</v>
+        <v>1.154723137702321</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01406410103953159</v>
+        <v>0.01323680097838267</v>
       </c>
       <c r="W18">
-        <v>0.2324836849748785</v>
+        <v>0.2326787623292974</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.05451201953306817</v>
+        <v>0.05130543014876998</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1190689844418643</v>
+        <v>0.1209689844418643</v>
       </c>
       <c r="C19">
-        <v>45570.53968980422</v>
+        <v>43084.57133942368</v>
       </c>
       <c r="D19">
-        <v>54491.90968980423</v>
+        <v>53114.55133942368</v>
       </c>
       <c r="E19">
-        <v>2288.370000000003</v>
+        <v>3396.980000000003</v>
       </c>
       <c r="F19">
-        <v>18846.37</v>
+        <v>19954.98</v>
       </c>
       <c r="G19">
         <v>9925</v>
@@ -2979,37 +2979,37 @@
         <v>228</v>
       </c>
       <c r="M19">
-        <v>4443.974046000001</v>
+        <v>4705.384284000001</v>
       </c>
       <c r="N19">
-        <v>-4215.974046000001</v>
+        <v>-4477.384284000001</v>
       </c>
       <c r="O19">
-        <v>-1087.721303868</v>
+        <v>-1155.165145272</v>
       </c>
       <c r="P19">
-        <v>-3128.252742132001</v>
+        <v>-3322.219138728</v>
       </c>
       <c r="Q19">
-        <v>-2978.252742132001</v>
+        <v>-3172.219138728</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09579951186251051</v>
+        <v>0.09640926200717527</v>
       </c>
       <c r="T19">
-        <v>1.154723137702321</v>
+        <v>1.168805127186496</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01323680097838267</v>
+        <v>0.0125014231462503</v>
       </c>
       <c r="W19">
-        <v>0.2326787623292974</v>
+        <v>0.2328521644221142</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.05130543014876998</v>
+        <v>0.04845512847383837</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1209689844418643</v>
+        <v>0.1228689844418643</v>
       </c>
       <c r="C20">
-        <v>43084.57133942368</v>
+        <v>40666.51567492253</v>
       </c>
       <c r="D20">
-        <v>53114.55133942368</v>
+        <v>51805.10567492253</v>
       </c>
       <c r="E20">
-        <v>3396.98</v>
+        <v>4505.59</v>
       </c>
       <c r="F20">
-        <v>19954.98</v>
+        <v>21063.59</v>
       </c>
       <c r="G20">
         <v>9925</v>
@@ -3061,37 +3061,37 @@
         <v>228</v>
       </c>
       <c r="M20">
-        <v>4705.384284</v>
+        <v>4966.794522</v>
       </c>
       <c r="N20">
-        <v>-4477.384284</v>
+        <v>-4738.794522</v>
       </c>
       <c r="O20">
-        <v>-1155.165145272</v>
+        <v>-1222.608986676</v>
       </c>
       <c r="P20">
-        <v>-3322.219138728</v>
+        <v>-3516.185535324</v>
       </c>
       <c r="Q20">
-        <v>-3172.219138728</v>
+        <v>-3366.185535324</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09640926200717526</v>
+        <v>0.09703406771096756</v>
       </c>
       <c r="T20">
-        <v>1.168805127186496</v>
+        <v>1.183234820114724</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.0125014231462503</v>
+        <v>0.01184345350697397</v>
       </c>
       <c r="W20">
-        <v>0.2328521644221142</v>
+        <v>0.2330073136630555</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.04845512847383837</v>
+        <v>0.04590485855416271</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1228689844418643</v>
+        <v>0.1247689844418643</v>
       </c>
       <c r="C21">
-        <v>40666.51567492253</v>
+        <v>38311.47074254963</v>
       </c>
       <c r="D21">
-        <v>51805.10567492253</v>
+        <v>50558.67074254963</v>
       </c>
       <c r="E21">
-        <v>4505.59</v>
+        <v>5614.200000000001</v>
       </c>
       <c r="F21">
-        <v>21063.59</v>
+        <v>22172.2</v>
       </c>
       <c r="G21">
         <v>9925</v>
@@ -3143,37 +3143,37 @@
         <v>228</v>
       </c>
       <c r="M21">
-        <v>4966.794522</v>
+        <v>5228.204760000001</v>
       </c>
       <c r="N21">
-        <v>-4738.794522</v>
+        <v>-5000.204760000001</v>
       </c>
       <c r="O21">
-        <v>-1222.608986676</v>
+        <v>-1290.05282808</v>
       </c>
       <c r="P21">
-        <v>-3516.185535324</v>
+        <v>-3710.151931920001</v>
       </c>
       <c r="Q21">
-        <v>-3366.185535324</v>
+        <v>-3560.151931920001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09703406771096756</v>
+        <v>0.09767449355735464</v>
       </c>
       <c r="T21">
-        <v>1.183234820114724</v>
+        <v>1.198025255366158</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.01184345350697397</v>
+        <v>0.01125128083162527</v>
       </c>
       <c r="W21">
-        <v>0.2330073136630555</v>
+        <v>0.2331469479799028</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.04590485855416271</v>
+        <v>0.04360961562645449</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1247689844418643</v>
+        <v>0.1266689844418643</v>
       </c>
       <c r="C22">
-        <v>38311.47074254963</v>
+        <v>36014.99527009643</v>
       </c>
       <c r="D22">
-        <v>50558.67074254963</v>
+        <v>49370.80527009643</v>
       </c>
       <c r="E22">
-        <v>5614.200000000001</v>
+        <v>6722.810000000001</v>
       </c>
       <c r="F22">
-        <v>22172.2</v>
+        <v>23280.81</v>
       </c>
       <c r="G22">
         <v>9925</v>
@@ -3225,37 +3225,37 @@
         <v>228</v>
       </c>
       <c r="M22">
-        <v>5228.204760000001</v>
+        <v>5489.614998000001</v>
       </c>
       <c r="N22">
-        <v>-5000.204760000001</v>
+        <v>-5261.614998000001</v>
       </c>
       <c r="O22">
-        <v>-1290.05282808</v>
+        <v>-1357.496669484</v>
       </c>
       <c r="P22">
-        <v>-3710.151931920001</v>
+        <v>-3904.118328516</v>
       </c>
       <c r="Q22">
-        <v>-3560.151931920001</v>
+        <v>-3754.118328516</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09767449355735464</v>
+        <v>0.0983311327163085</v>
       </c>
       <c r="T22">
-        <v>1.198025255366158</v>
+        <v>1.213190132016363</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.01125128083162527</v>
+        <v>0.01071550555392883</v>
       </c>
       <c r="W22">
-        <v>0.2331469479799028</v>
+        <v>0.2332732837903836</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.04360961562645449</v>
+        <v>0.04153296726329003</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1266689844418643</v>
+        <v>0.1285689844418643</v>
       </c>
       <c r="C23">
-        <v>36014.99527009646</v>
+        <v>33773.05579111667</v>
       </c>
       <c r="D23">
-        <v>49370.80527009645</v>
+        <v>48237.47579111667</v>
       </c>
       <c r="E23">
-        <v>6722.809999999998</v>
+        <v>7831.420000000002</v>
       </c>
       <c r="F23">
-        <v>23280.81</v>
+        <v>24389.42</v>
       </c>
       <c r="G23">
         <v>9925</v>
@@ -3307,37 +3307,37 @@
         <v>228</v>
       </c>
       <c r="M23">
-        <v>5489.614998</v>
+        <v>5751.025236</v>
       </c>
       <c r="N23">
-        <v>-5261.614998</v>
+        <v>-5523.025236</v>
       </c>
       <c r="O23">
-        <v>-1357.496669484</v>
+        <v>-1424.940510888</v>
       </c>
       <c r="P23">
-        <v>-3904.118328516</v>
+        <v>-4098.084725112</v>
       </c>
       <c r="Q23">
-        <v>-3754.118328516</v>
+        <v>-3948.084725112</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0983311327163085</v>
+        <v>0.099004608776774</v>
       </c>
       <c r="T23">
-        <v>1.213190132016363</v>
+        <v>1.228743851657598</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01071550555392883</v>
+        <v>0.01022843711965934</v>
       </c>
       <c r="W23">
-        <v>0.2332732837903836</v>
+        <v>0.2333881345271843</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.04153296726329003</v>
+        <v>0.03964510511495867</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1285689844418643</v>
+        <v>0.1304689844418643</v>
       </c>
       <c r="C24">
-        <v>33773.05579111667</v>
+        <v>31581.98088844558</v>
       </c>
       <c r="D24">
-        <v>48237.47579111667</v>
+        <v>47155.01088844558</v>
       </c>
       <c r="E24">
-        <v>7831.420000000002</v>
+        <v>8940.030000000002</v>
       </c>
       <c r="F24">
-        <v>24389.42</v>
+        <v>25498.03</v>
       </c>
       <c r="G24">
         <v>9925</v>
@@ -3389,37 +3389,37 @@
         <v>228</v>
       </c>
       <c r="M24">
-        <v>5751.025236</v>
+        <v>6012.435474000001</v>
       </c>
       <c r="N24">
-        <v>-5523.025236</v>
+        <v>-5784.435474000001</v>
       </c>
       <c r="O24">
-        <v>-1424.940510888</v>
+        <v>-1492.384352292</v>
       </c>
       <c r="P24">
-        <v>-4098.084725112</v>
+        <v>-4292.051121708</v>
       </c>
       <c r="Q24">
-        <v>-3948.084725112</v>
+        <v>-4142.051121708</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.099004608776774</v>
+        <v>0.09969557772192691</v>
       </c>
       <c r="T24">
-        <v>1.228743851657598</v>
+        <v>1.244701564016788</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01022843711965934</v>
+        <v>0.009783722462282842</v>
       </c>
       <c r="W24">
-        <v>0.2333881345271843</v>
+        <v>0.2334929982433937</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.03964510511495867</v>
+        <v>0.03792140489256912</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1304689844418643</v>
+        <v>0.1323689844418643</v>
       </c>
       <c r="C25">
-        <v>31581.98088844558</v>
+        <v>29438.421463248</v>
       </c>
       <c r="D25">
-        <v>47155.01088844558</v>
+        <v>46120.061463248</v>
       </c>
       <c r="E25">
-        <v>8940.030000000002</v>
+        <v>10048.64</v>
       </c>
       <c r="F25">
-        <v>25498.03</v>
+        <v>26606.64</v>
       </c>
       <c r="G25">
         <v>9925</v>
@@ -3471,37 +3471,37 @@
         <v>228</v>
       </c>
       <c r="M25">
-        <v>6012.435474000001</v>
+        <v>6273.845712000001</v>
       </c>
       <c r="N25">
-        <v>-5784.435474000001</v>
+        <v>-6045.845712000001</v>
       </c>
       <c r="O25">
-        <v>-1492.384352292</v>
+        <v>-1559.828193696</v>
       </c>
       <c r="P25">
-        <v>-4292.051121708</v>
+        <v>-4486.017518304001</v>
       </c>
       <c r="Q25">
-        <v>-4142.051121708</v>
+        <v>-4336.017518304001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09969557772192691</v>
+        <v>0.1004047300603733</v>
       </c>
       <c r="T25">
-        <v>1.244701564016788</v>
+        <v>1.261079216174904</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.009783722462282842</v>
+        <v>0.009376067359687726</v>
       </c>
       <c r="W25">
-        <v>0.2334929982433937</v>
+        <v>0.2335891233165856</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.03792140489256912</v>
+        <v>0.03634134635537878</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1323689844418643</v>
+        <v>0.1342689844418643</v>
       </c>
       <c r="C26">
-        <v>29438.421463248</v>
+        <v>27339.31612374566</v>
       </c>
       <c r="D26">
-        <v>46120.061463248</v>
+        <v>45129.56612374566</v>
       </c>
       <c r="E26">
-        <v>10048.64</v>
+        <v>11157.25</v>
       </c>
       <c r="F26">
-        <v>26606.64</v>
+        <v>27715.25</v>
       </c>
       <c r="G26">
         <v>9925</v>
@@ -3553,37 +3553,37 @@
         <v>228</v>
       </c>
       <c r="M26">
-        <v>6273.845712</v>
+        <v>6535.255950000001</v>
       </c>
       <c r="N26">
-        <v>-6045.845712</v>
+        <v>-6307.255950000001</v>
       </c>
       <c r="O26">
-        <v>-1559.828193696</v>
+        <v>-1627.2720351</v>
       </c>
       <c r="P26">
-        <v>-4486.017518304</v>
+        <v>-4679.9839149</v>
       </c>
       <c r="Q26">
-        <v>-4336.017518304</v>
+        <v>-4529.9839149</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1004047300603733</v>
+        <v>0.101132793127845</v>
       </c>
       <c r="T26">
-        <v>1.261079216174903</v>
+        <v>1.277893605723902</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.009376067359687726</v>
+        <v>0.009001024665300216</v>
       </c>
       <c r="W26">
-        <v>0.2335891233165856</v>
+        <v>0.2336775583839222</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.03634134635537878</v>
+        <v>0.03488769250116364</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1342689844418643</v>
+        <v>0.1361689844418643</v>
       </c>
       <c r="C27">
-        <v>27339.31612374566</v>
+        <v>25281.86094013869</v>
       </c>
       <c r="D27">
-        <v>45129.56612374566</v>
+        <v>44180.72094013869</v>
       </c>
       <c r="E27">
-        <v>11157.25</v>
+        <v>12265.86</v>
       </c>
       <c r="F27">
-        <v>27715.25</v>
+        <v>28823.86</v>
       </c>
       <c r="G27">
         <v>9925</v>
@@ -3635,37 +3635,37 @@
         <v>228</v>
       </c>
       <c r="M27">
-        <v>6535.255950000001</v>
+        <v>6796.666188</v>
       </c>
       <c r="N27">
-        <v>-6307.255950000001</v>
+        <v>-6568.666188</v>
       </c>
       <c r="O27">
-        <v>-1627.2720351</v>
+        <v>-1694.715876504</v>
       </c>
       <c r="P27">
-        <v>-4679.9839149</v>
+        <v>-4873.950311496</v>
       </c>
       <c r="Q27">
-        <v>-4529.9839149</v>
+        <v>-4723.950311496</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.101132793127845</v>
+        <v>0.1018805335755185</v>
       </c>
       <c r="T27">
-        <v>1.277893605723902</v>
+        <v>1.295162438233685</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.009001024665300216</v>
+        <v>0.008654831408942517</v>
       </c>
       <c r="W27">
-        <v>0.2336775583839222</v>
+        <v>0.2337591907537714</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.03488769250116364</v>
+        <v>0.03354585817419575</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1361689844418643</v>
+        <v>0.1380689844418643</v>
       </c>
       <c r="C28">
-        <v>25281.86094013869</v>
+        <v>23263.48293636106</v>
       </c>
       <c r="D28">
-        <v>44180.72094013869</v>
+        <v>43270.95293636106</v>
       </c>
       <c r="E28">
-        <v>12265.86</v>
+        <v>13374.47</v>
       </c>
       <c r="F28">
-        <v>28823.86</v>
+        <v>29932.47</v>
       </c>
       <c r="G28">
         <v>9925</v>
@@ -3717,37 +3717,37 @@
         <v>228</v>
       </c>
       <c r="M28">
-        <v>6796.666188</v>
+        <v>7058.076426000001</v>
       </c>
       <c r="N28">
-        <v>-6568.666188</v>
+        <v>-6830.076426000001</v>
       </c>
       <c r="O28">
-        <v>-1694.715876504</v>
+        <v>-1762.159717908</v>
       </c>
       <c r="P28">
-        <v>-4873.950311496</v>
+        <v>-5067.916708092001</v>
       </c>
       <c r="Q28">
-        <v>-4723.950311496</v>
+        <v>-4917.916708092001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1018805335755185</v>
+        <v>0.1026487600628544</v>
       </c>
       <c r="T28">
-        <v>1.295162438233685</v>
+        <v>1.312904389442365</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.008654831408942517</v>
+        <v>0.008334282097500201</v>
       </c>
       <c r="W28">
-        <v>0.2337591907537714</v>
+        <v>0.2338347762814095</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.03354585817419575</v>
+        <v>0.03230341898255895</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1380689844418643</v>
+        <v>0.1399689844418643</v>
       </c>
       <c r="C29">
-        <v>23263.48293636106</v>
+        <v>21281.81679089692</v>
       </c>
       <c r="D29">
-        <v>43270.95293636106</v>
+        <v>42397.89679089692</v>
       </c>
       <c r="E29">
-        <v>13374.47</v>
+        <v>14483.08</v>
       </c>
       <c r="F29">
-        <v>29932.47</v>
+        <v>31041.08</v>
       </c>
       <c r="G29">
         <v>9925</v>
@@ -3799,37 +3799,37 @@
         <v>228</v>
       </c>
       <c r="M29">
-        <v>7058.076426000001</v>
+        <v>7319.486664000001</v>
       </c>
       <c r="N29">
-        <v>-6830.076426000001</v>
+        <v>-7091.486664000001</v>
       </c>
       <c r="O29">
-        <v>-1762.159717908</v>
+        <v>-1829.603559312</v>
       </c>
       <c r="P29">
-        <v>-5067.916708092001</v>
+        <v>-5261.883104688</v>
       </c>
       <c r="Q29">
-        <v>-4917.916708092001</v>
+        <v>-5111.883104688</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1026487600628544</v>
+        <v>0.1034383261748385</v>
       </c>
       <c r="T29">
-        <v>1.312904389442365</v>
+        <v>1.331139172629065</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.008334282097500201</v>
+        <v>0.008036629165446622</v>
       </c>
       <c r="W29">
-        <v>0.2338347762814095</v>
+        <v>0.2339049628427877</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.03230341898255895</v>
+        <v>0.03114972544746752</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1399689844418643</v>
+        <v>0.1418689844418643</v>
       </c>
       <c r="C30">
-        <v>21281.81679089692</v>
+        <v>19334.68430238813</v>
       </c>
       <c r="D30">
-        <v>42397.89679089692</v>
+        <v>41559.37430238813</v>
       </c>
       <c r="E30">
-        <v>14483.08</v>
+        <v>15591.69</v>
       </c>
       <c r="F30">
-        <v>31041.08</v>
+        <v>32149.69</v>
       </c>
       <c r="G30">
         <v>9925</v>
@@ -3881,37 +3881,37 @@
         <v>228</v>
       </c>
       <c r="M30">
-        <v>7319.486664000001</v>
+        <v>7580.896902</v>
       </c>
       <c r="N30">
-        <v>-7091.486664000001</v>
+        <v>-7352.896902</v>
       </c>
       <c r="O30">
-        <v>-1829.603559312</v>
+        <v>-1897.047400716</v>
       </c>
       <c r="P30">
-        <v>-5261.883104688</v>
+        <v>-5455.849501284</v>
       </c>
       <c r="Q30">
-        <v>-5111.883104688</v>
+        <v>-5305.849501284</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1034383261748385</v>
+        <v>0.1042501335857517</v>
       </c>
       <c r="T30">
-        <v>1.331139172629065</v>
+        <v>1.349887611680179</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.008036629165446622</v>
+        <v>0.007759504021810531</v>
       </c>
       <c r="W30">
-        <v>0.2339049628427877</v>
+        <v>0.2339703089516571</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.03114972544746752</v>
+        <v>0.03007559698376172</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1418689844418642</v>
+        <v>0.1437689844418643</v>
       </c>
       <c r="C31">
-        <v>19334.68430238816</v>
+        <v>17420.0762446927</v>
       </c>
       <c r="D31">
-        <v>41559.37430238815</v>
+        <v>40753.3762446927</v>
       </c>
       <c r="E31">
-        <v>15591.69</v>
+        <v>16700.3</v>
       </c>
       <c r="F31">
-        <v>32149.69</v>
+        <v>33258.3</v>
       </c>
       <c r="G31">
         <v>9925</v>
@@ -3963,37 +3963,37 @@
         <v>228</v>
       </c>
       <c r="M31">
-        <v>7580.896902</v>
+        <v>7842.307139999999</v>
       </c>
       <c r="N31">
-        <v>-7352.896902</v>
+        <v>-7614.307139999999</v>
       </c>
       <c r="O31">
-        <v>-1897.047400716</v>
+        <v>-1964.49124212</v>
       </c>
       <c r="P31">
-        <v>-5455.849501284</v>
+        <v>-5649.815897879999</v>
       </c>
       <c r="Q31">
-        <v>-5305.849501284</v>
+        <v>-5499.815897879999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1042501335857517</v>
+        <v>0.1050851354941196</v>
       </c>
       <c r="T31">
-        <v>1.349887611680179</v>
+        <v>1.369171720418467</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.007759504021810531</v>
+        <v>0.007500853887750182</v>
       </c>
       <c r="W31">
-        <v>0.2339703089516571</v>
+        <v>0.2340312986532685</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.03007559698376172</v>
+        <v>0.02907307708430307</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1437689844418643</v>
+        <v>0.1456689844418643</v>
       </c>
       <c r="C32">
-        <v>17420.0762446927</v>
+        <v>15536.13629318017</v>
       </c>
       <c r="D32">
-        <v>40753.3762446927</v>
+        <v>39978.04629318017</v>
       </c>
       <c r="E32">
-        <v>16700.3</v>
+        <v>17808.91</v>
       </c>
       <c r="F32">
-        <v>33258.3</v>
+        <v>34366.91</v>
       </c>
       <c r="G32">
         <v>9925</v>
@@ -4045,37 +4045,37 @@
         <v>228</v>
       </c>
       <c r="M32">
-        <v>7842.307139999999</v>
+        <v>8103.717377999999</v>
       </c>
       <c r="N32">
-        <v>-7614.307139999999</v>
+        <v>-7875.717377999999</v>
       </c>
       <c r="O32">
-        <v>-1964.49124212</v>
+        <v>-2031.935083524</v>
       </c>
       <c r="P32">
-        <v>-5649.815897879999</v>
+        <v>-5843.782294475999</v>
       </c>
       <c r="Q32">
-        <v>-5499.815897879999</v>
+        <v>-5693.782294475999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1050851354941196</v>
+        <v>0.1059443403563532</v>
       </c>
       <c r="T32">
-        <v>1.369171720418467</v>
+        <v>1.389014788830329</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.007500853887750182</v>
+        <v>0.007258890859113079</v>
       </c>
       <c r="W32">
-        <v>0.2340312986532685</v>
+        <v>0.2340883535354211</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.02907307708430307</v>
+        <v>0.02813523588803524</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1456689844418643</v>
+        <v>0.1475689844418643</v>
       </c>
       <c r="C33">
-        <v>15536.13629318017</v>
+        <v>13681.14675157794</v>
       </c>
       <c r="D33">
-        <v>39978.04629318017</v>
+        <v>39231.66675157795</v>
       </c>
       <c r="E33">
-        <v>17808.91</v>
+        <v>18917.52</v>
       </c>
       <c r="F33">
-        <v>34366.91</v>
+        <v>35475.52</v>
       </c>
       <c r="G33">
         <v>9925</v>
@@ -4127,37 +4127,37 @@
         <v>228</v>
       </c>
       <c r="M33">
-        <v>8103.717377999999</v>
+        <v>8365.127616000002</v>
       </c>
       <c r="N33">
-        <v>-7875.717377999999</v>
+        <v>-8137.127616000002</v>
       </c>
       <c r="O33">
-        <v>-2031.935083524</v>
+        <v>-2099.378924928</v>
       </c>
       <c r="P33">
-        <v>-5843.782294475999</v>
+        <v>-6037.748691072002</v>
       </c>
       <c r="Q33">
-        <v>-5693.782294475999</v>
+        <v>-5887.748691072002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1059443403563532</v>
+        <v>0.106828815949829</v>
       </c>
       <c r="T33">
-        <v>1.389014788830329</v>
+        <v>1.409441476901363</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.007258890859113079</v>
+        <v>0.007032050519765793</v>
       </c>
       <c r="W33">
-        <v>0.2340883535354211</v>
+        <v>0.2341418424874392</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.02813523588803524</v>
+        <v>0.02725600976653408</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1475689844418643</v>
+        <v>0.1494689844418643</v>
       </c>
       <c r="C34">
-        <v>13681.14675157794</v>
+        <v>11853.51584837039</v>
       </c>
       <c r="D34">
-        <v>39231.66675157795</v>
+        <v>38512.6458483704</v>
       </c>
       <c r="E34">
-        <v>18917.52</v>
+        <v>20026.13</v>
       </c>
       <c r="F34">
-        <v>35475.52</v>
+        <v>36584.13</v>
       </c>
       <c r="G34">
         <v>9925</v>
@@ -4209,37 +4209,37 @@
         <v>228</v>
       </c>
       <c r="M34">
-        <v>8365.127616000002</v>
+        <v>8626.537854000002</v>
       </c>
       <c r="N34">
-        <v>-8137.127616000002</v>
+        <v>-8398.537854000002</v>
       </c>
       <c r="O34">
-        <v>-2099.378924928</v>
+        <v>-2166.822766332</v>
       </c>
       <c r="P34">
-        <v>-6037.748691072002</v>
+        <v>-6231.715087668002</v>
       </c>
       <c r="Q34">
-        <v>-5887.748691072002</v>
+        <v>-6081.715087668002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.106828815949829</v>
+        <v>0.1077396937998265</v>
       </c>
       <c r="T34">
-        <v>1.409441476901363</v>
+        <v>1.430477916855114</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.007032050519765793</v>
+        <v>0.006818958079772891</v>
       </c>
       <c r="W34">
-        <v>0.2341418424874392</v>
+        <v>0.2341920896847896</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.02725600976653408</v>
+        <v>0.02643007007663911</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1494689844418643</v>
+        <v>0.1513689844418643</v>
       </c>
       <c r="C35">
-        <v>11853.51584837039</v>
+        <v>10051.76640501239</v>
       </c>
       <c r="D35">
-        <v>38512.6458483704</v>
+        <v>37819.5064050124</v>
       </c>
       <c r="E35">
-        <v>20026.13</v>
+        <v>21134.74000000001</v>
       </c>
       <c r="F35">
-        <v>36584.13</v>
+        <v>37692.74000000001</v>
       </c>
       <c r="G35">
         <v>9925</v>
@@ -4291,37 +4291,37 @@
         <v>228</v>
       </c>
       <c r="M35">
-        <v>8626.537854000002</v>
+        <v>8887.948092000002</v>
       </c>
       <c r="N35">
-        <v>-8398.537854000002</v>
+        <v>-8659.948092000002</v>
       </c>
       <c r="O35">
-        <v>-2166.822766332</v>
+        <v>-2234.266607736001</v>
       </c>
       <c r="P35">
-        <v>-6231.715087668002</v>
+        <v>-6425.681484264001</v>
       </c>
       <c r="Q35">
-        <v>-6081.715087668002</v>
+        <v>-6275.681484264001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1077396937998265</v>
+        <v>0.1086781740089147</v>
       </c>
       <c r="T35">
-        <v>1.430477916855114</v>
+        <v>1.452151824686253</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.006818958079772891</v>
+        <v>0.006618400489191334</v>
       </c>
       <c r="W35">
-        <v>0.2341920896847896</v>
+        <v>0.2342393811646487</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.02643007007663911</v>
+        <v>0.02565271507438505</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1513689844418643</v>
+        <v>0.1532689844418643</v>
       </c>
       <c r="C36">
-        <v>10051.76640501239</v>
+        <v>8274.525706186025</v>
       </c>
       <c r="D36">
-        <v>37819.5064050124</v>
+        <v>37150.87570618603</v>
       </c>
       <c r="E36">
-        <v>21134.74000000001</v>
+        <v>22243.35000000001</v>
       </c>
       <c r="F36">
-        <v>37692.74000000001</v>
+        <v>38801.35000000001</v>
       </c>
       <c r="G36">
         <v>9925</v>
@@ -4373,37 +4373,37 @@
         <v>228</v>
       </c>
       <c r="M36">
-        <v>8887.948092000002</v>
+        <v>9149.358330000001</v>
       </c>
       <c r="N36">
-        <v>-8659.948092000002</v>
+        <v>-8921.358330000001</v>
       </c>
       <c r="O36">
-        <v>-2234.266607736001</v>
+        <v>-2301.71044914</v>
       </c>
       <c r="P36">
-        <v>-6425.681484264001</v>
+        <v>-6619.64788086</v>
       </c>
       <c r="Q36">
-        <v>-6275.681484264001</v>
+        <v>-6469.64788086</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1086781740089147</v>
+        <v>0.1096455305321288</v>
       </c>
       <c r="T36">
-        <v>1.452151824686253</v>
+        <v>1.474492621989118</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.006618400489191334</v>
+        <v>0.006429303332357298</v>
       </c>
       <c r="W36">
-        <v>0.2342393811646487</v>
+        <v>0.2342839702742302</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.02565271507438505</v>
+        <v>0.02491978035797404</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1532689844418643</v>
+        <v>0.1551689844418643</v>
       </c>
       <c r="C37">
-        <v>8274.525706186025</v>
+        <v>6520.516425924121</v>
       </c>
       <c r="D37">
-        <v>37150.87570618603</v>
+        <v>36505.47642592413</v>
       </c>
       <c r="E37">
-        <v>22243.35000000001</v>
+        <v>23351.96000000001</v>
       </c>
       <c r="F37">
-        <v>38801.35000000001</v>
+        <v>39909.96000000001</v>
       </c>
       <c r="G37">
         <v>9925</v>
@@ -4455,37 +4455,37 @@
         <v>228</v>
       </c>
       <c r="M37">
-        <v>9149.358330000001</v>
+        <v>9410.768568000001</v>
       </c>
       <c r="N37">
-        <v>-8921.358330000001</v>
+        <v>-9182.768568000001</v>
       </c>
       <c r="O37">
-        <v>-2301.71044914</v>
+        <v>-2369.154290544001</v>
       </c>
       <c r="P37">
-        <v>-6619.64788086</v>
+        <v>-6813.614277456001</v>
       </c>
       <c r="Q37">
-        <v>-6469.64788086</v>
+        <v>-6663.614277456001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1096455305321288</v>
+        <v>0.1106431169466933</v>
       </c>
       <c r="T37">
-        <v>1.474492621989118</v>
+        <v>1.497531569207698</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.006429303332357298</v>
+        <v>0.00625071157312515</v>
       </c>
       <c r="W37">
-        <v>0.2342839702742302</v>
+        <v>0.2343260822110571</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.02491978035797404</v>
+        <v>0.02422756423691919</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1551689844418643</v>
+        <v>0.1570689844418642</v>
       </c>
       <c r="C38">
-        <v>6520.516425924128</v>
+        <v>4788.548483392588</v>
       </c>
       <c r="D38">
-        <v>36505.47642592413</v>
+        <v>35882.11848339259</v>
       </c>
       <c r="E38">
-        <v>23351.96</v>
+        <v>24460.57</v>
       </c>
       <c r="F38">
-        <v>39909.96</v>
+        <v>41018.57</v>
       </c>
       <c r="G38">
         <v>9925</v>
@@ -4537,37 +4537,37 @@
         <v>228</v>
       </c>
       <c r="M38">
-        <v>9410.768568</v>
+        <v>9672.178806</v>
       </c>
       <c r="N38">
-        <v>-9182.768568</v>
+        <v>-9444.178806</v>
       </c>
       <c r="O38">
-        <v>-2369.154290544</v>
+        <v>-2436.598131948</v>
       </c>
       <c r="P38">
-        <v>-6813.614277455999</v>
+        <v>-7007.580674052</v>
       </c>
       <c r="Q38">
-        <v>-6663.614277455999</v>
+        <v>-6857.580674052</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1106431169466933</v>
+        <v>0.111672372771244</v>
       </c>
       <c r="T38">
-        <v>1.497531569207698</v>
+        <v>1.521301911576074</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.006250711573125151</v>
+        <v>0.006081773422500146</v>
       </c>
       <c r="W38">
-        <v>0.2343260822110571</v>
+        <v>0.2343659178269745</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.02422756423691919</v>
+        <v>0.02357276520348894</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1570689844418642</v>
+        <v>0.1589689844418643</v>
       </c>
       <c r="C39">
-        <v>4788.548483392588</v>
+        <v>3077.511719074762</v>
       </c>
       <c r="D39">
-        <v>35882.11848339259</v>
+        <v>35279.69171907476</v>
       </c>
       <c r="E39">
-        <v>24460.57</v>
+        <v>25569.18</v>
       </c>
       <c r="F39">
-        <v>41018.57</v>
+        <v>42127.18</v>
       </c>
       <c r="G39">
         <v>9925</v>
@@ -4619,37 +4619,37 @@
         <v>228</v>
       </c>
       <c r="M39">
-        <v>9672.178806</v>
+        <v>9933.589044</v>
       </c>
       <c r="N39">
-        <v>-9444.178806</v>
+        <v>-9705.589044</v>
       </c>
       <c r="O39">
-        <v>-2436.598131948</v>
+        <v>-2504.041973352</v>
       </c>
       <c r="P39">
-        <v>-7007.580674052</v>
+        <v>-7201.547070648</v>
       </c>
       <c r="Q39">
-        <v>-6857.580674052</v>
+        <v>-7051.547070648</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.111672372771244</v>
+        <v>0.1127348303965866</v>
       </c>
       <c r="T39">
-        <v>1.521301911576074</v>
+        <v>1.54583903918214</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.006081773422500146</v>
+        <v>0.005921726753486985</v>
       </c>
       <c r="W39">
-        <v>0.2343659178269745</v>
+        <v>0.2344036568315278</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.02357276520348894</v>
+        <v>0.0229524292770813</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1589689844418643</v>
+        <v>0.1608689844418643</v>
       </c>
       <c r="C40">
-        <v>3077.511719074762</v>
+        <v>1386.369296533849</v>
       </c>
       <c r="D40">
-        <v>35279.69171907476</v>
+        <v>34697.15929653385</v>
       </c>
       <c r="E40">
-        <v>25569.18</v>
+        <v>26677.79</v>
       </c>
       <c r="F40">
-        <v>42127.18</v>
+        <v>43235.79</v>
       </c>
       <c r="G40">
         <v>9925</v>
@@ -4701,37 +4701,37 @@
         <v>228</v>
       </c>
       <c r="M40">
-        <v>9933.589044</v>
+        <v>10194.999282</v>
       </c>
       <c r="N40">
-        <v>-9705.589044</v>
+        <v>-9966.999282000001</v>
       </c>
       <c r="O40">
-        <v>-2504.041973352</v>
+        <v>-2571.485814756</v>
       </c>
       <c r="P40">
-        <v>-7201.547070648</v>
+        <v>-7395.513467244</v>
       </c>
       <c r="Q40">
-        <v>-7051.547070648</v>
+        <v>-7245.513467244</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1127348303965866</v>
+        <v>0.11383212269817</v>
       </c>
       <c r="T40">
-        <v>1.54583903918214</v>
+        <v>1.57118066277529</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.005921726753486985</v>
+        <v>0.005769887605961677</v>
       </c>
       <c r="W40">
-        <v>0.2344036568315278</v>
+        <v>0.2344394605025142</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.0229524292770813</v>
+        <v>0.02236390544946387</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1608689844418643</v>
+        <v>0.1627689844418643</v>
       </c>
       <c r="C41">
-        <v>1386.369296533849</v>
+        <v>-285.8482527492743</v>
       </c>
       <c r="D41">
-        <v>34697.15929653385</v>
+        <v>34133.55174725073</v>
       </c>
       <c r="E41">
-        <v>26677.79</v>
+        <v>27786.4</v>
       </c>
       <c r="F41">
-        <v>43235.79</v>
+        <v>44344.4</v>
       </c>
       <c r="G41">
         <v>9925</v>
@@ -4783,37 +4783,37 @@
         <v>228</v>
       </c>
       <c r="M41">
-        <v>10194.999282</v>
+        <v>10456.40952</v>
       </c>
       <c r="N41">
-        <v>-9966.999282000001</v>
+        <v>-10228.40952</v>
       </c>
       <c r="O41">
-        <v>-2571.485814756</v>
+        <v>-2638.92965616</v>
       </c>
       <c r="P41">
-        <v>-7395.513467244</v>
+        <v>-7589.479863840001</v>
       </c>
       <c r="Q41">
-        <v>-7245.513467244</v>
+        <v>-7439.479863840001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.11383212269817</v>
+        <v>0.1149659914098062</v>
       </c>
       <c r="T41">
-        <v>1.57118066277529</v>
+        <v>1.597367007154878</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.005769887605961677</v>
+        <v>0.005625640415812635</v>
       </c>
       <c r="W41">
-        <v>0.2344394605025142</v>
+        <v>0.2344734739899514</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.02236390544946387</v>
+        <v>0.02180480781322724</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1627689844418643</v>
+        <v>0.1646689844418643</v>
       </c>
       <c r="C42">
-        <v>-285.8482527492743</v>
+        <v>-1940.048413414734</v>
       </c>
       <c r="D42">
-        <v>34133.55174725073</v>
+        <v>33587.96158658527</v>
       </c>
       <c r="E42">
-        <v>27786.4</v>
+        <v>28895.01</v>
       </c>
       <c r="F42">
-        <v>44344.4</v>
+        <v>45453.01</v>
       </c>
       <c r="G42">
         <v>9925</v>
@@ -4865,37 +4865,37 @@
         <v>228</v>
       </c>
       <c r="M42">
-        <v>10456.40952</v>
+        <v>10717.819758</v>
       </c>
       <c r="N42">
-        <v>-10228.40952</v>
+        <v>-10489.819758</v>
       </c>
       <c r="O42">
-        <v>-2638.92965616</v>
+        <v>-2706.373497564</v>
       </c>
       <c r="P42">
-        <v>-7589.479863840001</v>
+        <v>-7783.446260436001</v>
       </c>
       <c r="Q42">
-        <v>-7439.479863840001</v>
+        <v>-7633.446260436001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1149659914098062</v>
+        <v>0.1161382963489554</v>
       </c>
       <c r="T42">
-        <v>1.597367007154878</v>
+        <v>1.6244410242253</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.005625640415812635</v>
+        <v>0.005488429673963546</v>
       </c>
       <c r="W42">
-        <v>0.2344734739899514</v>
+        <v>0.2345058282828794</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.02180480781322724</v>
+        <v>0.02127298323241689</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1646689844418643</v>
+        <v>0.1665689844418643</v>
       </c>
       <c r="C43">
-        <v>-1940.048413414734</v>
+        <v>-3577.081562035586</v>
       </c>
       <c r="D43">
-        <v>33587.96158658527</v>
+        <v>33059.53843796442</v>
       </c>
       <c r="E43">
-        <v>28895.01</v>
+        <v>30003.62</v>
       </c>
       <c r="F43">
-        <v>45453.01</v>
+        <v>46561.62</v>
       </c>
       <c r="G43">
         <v>9925</v>
@@ -4947,37 +4947,37 @@
         <v>228</v>
       </c>
       <c r="M43">
-        <v>10717.819758</v>
+        <v>10979.229996</v>
       </c>
       <c r="N43">
-        <v>-10489.819758</v>
+        <v>-10751.229996</v>
       </c>
       <c r="O43">
-        <v>-2706.373497564</v>
+        <v>-2773.817338968001</v>
       </c>
       <c r="P43">
-        <v>-7783.446260436001</v>
+        <v>-7977.412657032001</v>
       </c>
       <c r="Q43">
-        <v>-7633.446260436001</v>
+        <v>-7827.412657032001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1161382963489554</v>
+        <v>0.1173510255963512</v>
       </c>
       <c r="T43">
-        <v>1.6244410242253</v>
+        <v>1.652448628091253</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.005488429673963546</v>
+        <v>0.005357752776964414</v>
       </c>
       <c r="W43">
-        <v>0.2345058282828794</v>
+        <v>0.2345366418951918</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.02127298323241689</v>
+        <v>0.02076648363164502</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1665689844418643</v>
+        <v>0.1684689844418643</v>
       </c>
       <c r="C44">
-        <v>-3577.081562035579</v>
+        <v>-5197.745389805707</v>
       </c>
       <c r="D44">
-        <v>33059.53843796442</v>
+        <v>32547.48461019429</v>
       </c>
       <c r="E44">
-        <v>30003.62</v>
+        <v>31112.23</v>
       </c>
       <c r="F44">
-        <v>46561.62</v>
+        <v>47670.23</v>
       </c>
       <c r="G44">
         <v>9925</v>
@@ -5029,37 +5029,37 @@
         <v>228</v>
       </c>
       <c r="M44">
-        <v>10979.229996</v>
+        <v>11240.640234</v>
       </c>
       <c r="N44">
-        <v>-10751.229996</v>
+        <v>-11012.640234</v>
       </c>
       <c r="O44">
-        <v>-2773.817338968</v>
+        <v>-2841.261180372</v>
       </c>
       <c r="P44">
-        <v>-7977.412657032</v>
+        <v>-8171.379053627999</v>
       </c>
       <c r="Q44">
-        <v>-7827.412657032</v>
+        <v>-8021.379053627999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1173510255963512</v>
+        <v>0.1186063067471644</v>
       </c>
       <c r="T44">
-        <v>1.652448628091253</v>
+        <v>1.681438954899871</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.005357752776964415</v>
+        <v>0.005233153875174546</v>
       </c>
       <c r="W44">
-        <v>0.2345366418951918</v>
+        <v>0.2345660223162339</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.02076648363164502</v>
+        <v>0.02028354215183936</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1684689844418643</v>
+        <v>0.1703689844418643</v>
       </c>
       <c r="C45">
-        <v>-5197.745389805707</v>
+        <v>-6802.788920483079</v>
       </c>
       <c r="D45">
-        <v>32547.48461019429</v>
+        <v>32051.05107951692</v>
       </c>
       <c r="E45">
-        <v>31112.23</v>
+        <v>32220.84</v>
       </c>
       <c r="F45">
-        <v>47670.23</v>
+        <v>48778.84</v>
       </c>
       <c r="G45">
         <v>9925</v>
@@ -5111,37 +5111,37 @@
         <v>228</v>
       </c>
       <c r="M45">
-        <v>11240.640234</v>
+        <v>11502.050472</v>
       </c>
       <c r="N45">
-        <v>-11012.640234</v>
+        <v>-11274.050472</v>
       </c>
       <c r="O45">
-        <v>-2841.261180372</v>
+        <v>-2908.705021776</v>
       </c>
       <c r="P45">
-        <v>-8171.379053627999</v>
+        <v>-8365.345450224</v>
       </c>
       <c r="Q45">
-        <v>-8021.379053627999</v>
+        <v>-8215.345450224</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1186063067471644</v>
+        <v>0.1199064193676495</v>
       </c>
       <c r="T45">
-        <v>1.681438954899871</v>
+        <v>1.711464650523083</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.005233153875174546</v>
+        <v>0.005114218559829668</v>
       </c>
       <c r="W45">
-        <v>0.2345660223162339</v>
+        <v>0.2345940672635922</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.02028354215183936</v>
+        <v>0.01982255255747933</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1703689844418643</v>
+        <v>0.1722689844418643</v>
       </c>
       <c r="C46">
-        <v>-6802.788920483079</v>
+        <v>-8392.916166152725</v>
       </c>
       <c r="D46">
-        <v>32051.05107951692</v>
+        <v>31569.53383384728</v>
       </c>
       <c r="E46">
-        <v>32220.84</v>
+        <v>33329.45</v>
       </c>
       <c r="F46">
-        <v>48778.84</v>
+        <v>49887.45</v>
       </c>
       <c r="G46">
         <v>9925</v>
@@ -5193,37 +5193,37 @@
         <v>228</v>
       </c>
       <c r="M46">
-        <v>11502.050472</v>
+        <v>11763.46071</v>
       </c>
       <c r="N46">
-        <v>-11274.050472</v>
+        <v>-11535.46071</v>
       </c>
       <c r="O46">
-        <v>-2908.705021776</v>
+        <v>-2976.14886318</v>
       </c>
       <c r="P46">
-        <v>-8365.345450224</v>
+        <v>-8559.311846820001</v>
       </c>
       <c r="Q46">
-        <v>-8215.345450224</v>
+        <v>-8409.311846820001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1199064193676495</v>
+        <v>0.1212538088106977</v>
       </c>
       <c r="T46">
-        <v>1.711464650523083</v>
+        <v>1.742582189623503</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.005114218559829668</v>
+        <v>0.00500056925850012</v>
       </c>
       <c r="W46">
-        <v>0.2345940672635922</v>
+        <v>0.2346208657688457</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.01982255255747933</v>
+        <v>0.0193820513895353</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1722689844418643</v>
+        <v>0.1741689844418643</v>
       </c>
       <c r="C47">
-        <v>-8392.916166152725</v>
+        <v>-9968.789458334293</v>
       </c>
       <c r="D47">
-        <v>31569.53383384728</v>
+        <v>31102.27054166571</v>
       </c>
       <c r="E47">
-        <v>33329.45</v>
+        <v>34438.06</v>
       </c>
       <c r="F47">
-        <v>49887.45</v>
+        <v>50996.06</v>
       </c>
       <c r="G47">
         <v>9925</v>
@@ -5275,37 +5275,37 @@
         <v>228</v>
       </c>
       <c r="M47">
-        <v>11763.46071</v>
+        <v>12024.870948</v>
       </c>
       <c r="N47">
-        <v>-11535.46071</v>
+        <v>-11796.870948</v>
       </c>
       <c r="O47">
-        <v>-2976.14886318</v>
+        <v>-3043.592704584</v>
       </c>
       <c r="P47">
-        <v>-8559.311846820001</v>
+        <v>-8753.278243416002</v>
       </c>
       <c r="Q47">
-        <v>-8409.311846820001</v>
+        <v>-8603.278243416002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1212538088106977</v>
+        <v>0.1226511015664513</v>
       </c>
       <c r="T47">
-        <v>1.742582189623503</v>
+        <v>1.774852230172087</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.00500056925850012</v>
+        <v>0.004891861231141421</v>
       </c>
       <c r="W47">
-        <v>0.2346208657688457</v>
+        <v>0.2346464991216969</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.0193820513895353</v>
+        <v>0.01896070244628456</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1741689844418643</v>
+        <v>0.1760689844418643</v>
       </c>
       <c r="C48">
-        <v>-9968.789458334293</v>
+        <v>-11531.0324875803</v>
       </c>
       <c r="D48">
-        <v>31102.27054166571</v>
+        <v>30648.6375124197</v>
       </c>
       <c r="E48">
-        <v>34438.06</v>
+        <v>35546.67000000001</v>
       </c>
       <c r="F48">
-        <v>50996.06</v>
+        <v>52104.67000000001</v>
       </c>
       <c r="G48">
         <v>9925</v>
@@ -5357,37 +5357,37 @@
         <v>228</v>
       </c>
       <c r="M48">
-        <v>12024.870948</v>
+        <v>12286.281186</v>
       </c>
       <c r="N48">
-        <v>-11796.870948</v>
+        <v>-12058.281186</v>
       </c>
       <c r="O48">
-        <v>-3043.592704584</v>
+        <v>-3111.036545988</v>
       </c>
       <c r="P48">
-        <v>-8753.278243416002</v>
+        <v>-8947.244640012002</v>
       </c>
       <c r="Q48">
-        <v>-8603.278243416002</v>
+        <v>-8797.244640012002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1226511015664513</v>
+        <v>0.124101122350724</v>
       </c>
       <c r="T48">
-        <v>1.774852230172087</v>
+        <v>1.808340008099862</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.004891861231141421</v>
+        <v>0.004787779077287349</v>
       </c>
       <c r="W48">
-        <v>0.2346464991216969</v>
+        <v>0.2346710416935757</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.01896070244628456</v>
+        <v>0.01855728324529982</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1760689844418643</v>
+        <v>0.1779689844418643</v>
       </c>
       <c r="C49">
-        <v>-11531.0324875803</v>
+        <v>-13080.2330808992</v>
       </c>
       <c r="D49">
-        <v>30648.6375124197</v>
+        <v>30208.0469191008</v>
       </c>
       <c r="E49">
-        <v>35546.67000000001</v>
+        <v>36655.28000000001</v>
       </c>
       <c r="F49">
-        <v>52104.67000000001</v>
+        <v>53213.28000000001</v>
       </c>
       <c r="G49">
         <v>9925</v>
@@ -5439,37 +5439,37 @@
         <v>228</v>
       </c>
       <c r="M49">
-        <v>12286.281186</v>
+        <v>12547.691424</v>
       </c>
       <c r="N49">
-        <v>-12058.281186</v>
+        <v>-12319.691424</v>
       </c>
       <c r="O49">
-        <v>-3111.036545988</v>
+        <v>-3178.480387392001</v>
       </c>
       <c r="P49">
-        <v>-8947.244640012002</v>
+        <v>-9141.211036608001</v>
       </c>
       <c r="Q49">
-        <v>-8797.244640012002</v>
+        <v>-8991.211036608001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.124101122350724</v>
+        <v>0.125606913165161</v>
       </c>
       <c r="T49">
-        <v>1.808340008099862</v>
+        <v>1.843115777486398</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.004787779077287349</v>
+        <v>0.004688033679843863</v>
       </c>
       <c r="W49">
-        <v>0.2346710416935757</v>
+        <v>0.2346945616582928</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.01855728324529982</v>
+        <v>0.01817067317768939</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1779689844418643</v>
+        <v>0.1798689844418643</v>
       </c>
       <c r="C50">
-        <v>-13080.2330808992</v>
+        <v>-14616.94574301178</v>
       </c>
       <c r="D50">
-        <v>30208.0469191008</v>
+        <v>29779.94425698822</v>
       </c>
       <c r="E50">
-        <v>36655.28</v>
+        <v>37763.89</v>
       </c>
       <c r="F50">
-        <v>53213.28</v>
+        <v>54321.89</v>
       </c>
       <c r="G50">
         <v>9925</v>
@@ -5521,37 +5521,37 @@
         <v>228</v>
       </c>
       <c r="M50">
-        <v>12547.691424</v>
+        <v>12809.101662</v>
       </c>
       <c r="N50">
-        <v>-12319.691424</v>
+        <v>-12581.101662</v>
       </c>
       <c r="O50">
-        <v>-3178.480387392</v>
+        <v>-3245.924228796001</v>
       </c>
       <c r="P50">
-        <v>-9141.211036608001</v>
+        <v>-9335.177433204</v>
       </c>
       <c r="Q50">
-        <v>-8991.211036608001</v>
+        <v>-9185.177433204</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.125606913165161</v>
+        <v>0.127171754599772</v>
       </c>
       <c r="T50">
-        <v>1.843115777486397</v>
+        <v>1.87925530253515</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.004688033679843863</v>
+        <v>0.004592359523112355</v>
       </c>
       <c r="W50">
-        <v>0.2346945616582928</v>
+        <v>0.2347171216244501</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.01817067317768939</v>
+        <v>0.01779984311283855</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1798689844418643</v>
+        <v>0.1817689844418643</v>
       </c>
       <c r="C51">
-        <v>-14616.94574301178</v>
+        <v>-16141.69398454193</v>
       </c>
       <c r="D51">
-        <v>29779.94425698822</v>
+        <v>29363.80601545808</v>
       </c>
       <c r="E51">
-        <v>37763.89</v>
+        <v>38872.5</v>
       </c>
       <c r="F51">
-        <v>54321.89</v>
+        <v>55430.5</v>
       </c>
       <c r="G51">
         <v>9925</v>
@@ -5603,37 +5603,37 @@
         <v>228</v>
       </c>
       <c r="M51">
-        <v>12809.101662</v>
+        <v>13070.5119</v>
       </c>
       <c r="N51">
-        <v>-12581.101662</v>
+        <v>-12842.5119</v>
       </c>
       <c r="O51">
-        <v>-3245.924228796001</v>
+        <v>-3313.368070200001</v>
       </c>
       <c r="P51">
-        <v>-9335.177433204</v>
+        <v>-9529.143829800001</v>
       </c>
       <c r="Q51">
-        <v>-9185.177433204</v>
+        <v>-9379.143829800001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.127171754599772</v>
+        <v>0.1287991896917674</v>
       </c>
       <c r="T51">
-        <v>1.87925530253515</v>
+        <v>1.916840408585853</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.004592359523112355</v>
+        <v>0.004500512332650108</v>
       </c>
       <c r="W51">
-        <v>0.2347171216244501</v>
+        <v>0.2347387791919611</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.01779984311283855</v>
+        <v>0.01744384625058182</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1817689844418643</v>
+        <v>0.1836689844418643</v>
       </c>
       <c r="C52">
-        <v>-16141.69398454193</v>
+        <v>-17654.97245769585</v>
       </c>
       <c r="D52">
-        <v>29363.80601545808</v>
+        <v>28959.13754230415</v>
       </c>
       <c r="E52">
-        <v>38872.5</v>
+        <v>39981.11</v>
       </c>
       <c r="F52">
-        <v>55430.5</v>
+        <v>56539.11</v>
       </c>
       <c r="G52">
         <v>9925</v>
@@ -5685,37 +5685,37 @@
         <v>228</v>
       </c>
       <c r="M52">
-        <v>13070.5119</v>
+        <v>13331.922138</v>
       </c>
       <c r="N52">
-        <v>-12842.5119</v>
+        <v>-13103.922138</v>
       </c>
       <c r="O52">
-        <v>-3313.368070200001</v>
+        <v>-3380.811911604</v>
       </c>
       <c r="P52">
-        <v>-9529.143829800001</v>
+        <v>-9723.110226396</v>
       </c>
       <c r="Q52">
-        <v>-9379.143829800001</v>
+        <v>-9573.110226396</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1287991896917674</v>
+        <v>0.1304930507058852</v>
       </c>
       <c r="T52">
-        <v>1.916840408585853</v>
+        <v>1.95595960059781</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.004500512332650108</v>
+        <v>0.004412266992794224</v>
       </c>
       <c r="W52">
-        <v>0.2347387791919611</v>
+        <v>0.2347595874430991</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.01744384625058182</v>
+        <v>0.01710181004958999</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1836689844418643</v>
+        <v>0.1855689844418643</v>
       </c>
       <c r="C53">
-        <v>-17654.97245769585</v>
+        <v>-19157.24891774847</v>
       </c>
       <c r="D53">
-        <v>28959.13754230415</v>
+        <v>28565.47108225154</v>
       </c>
       <c r="E53">
-        <v>39981.11</v>
+        <v>41089.72</v>
       </c>
       <c r="F53">
-        <v>56539.11</v>
+        <v>57647.72</v>
       </c>
       <c r="G53">
         <v>9925</v>
@@ -5767,37 +5767,37 @@
         <v>228</v>
       </c>
       <c r="M53">
-        <v>13331.922138</v>
+        <v>13593.332376</v>
       </c>
       <c r="N53">
-        <v>-13103.922138</v>
+        <v>-13365.332376</v>
       </c>
       <c r="O53">
-        <v>-3380.811911604</v>
+        <v>-3448.255753008</v>
       </c>
       <c r="P53">
-        <v>-9723.110226396</v>
+        <v>-9917.076622992001</v>
       </c>
       <c r="Q53">
-        <v>-9573.110226396</v>
+        <v>-9767.076622992001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1304930507058852</v>
+        <v>0.1322574892622577</v>
       </c>
       <c r="T53">
-        <v>1.95595960059781</v>
+        <v>1.996708758943597</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.004412266992794224</v>
+        <v>0.004327415704471258</v>
       </c>
       <c r="W53">
-        <v>0.2347595874430991</v>
+        <v>0.2347795953768857</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.01710181004958999</v>
+        <v>0.01677292908709793</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1855689844418643</v>
+        <v>0.1874689844418643</v>
       </c>
       <c r="C54">
-        <v>-19157.24891774847</v>
+        <v>-20648.9660266905</v>
       </c>
       <c r="D54">
-        <v>28565.47108225154</v>
+        <v>28182.3639733095</v>
       </c>
       <c r="E54">
-        <v>41089.72</v>
+        <v>42198.33</v>
       </c>
       <c r="F54">
-        <v>57647.72</v>
+        <v>58756.33</v>
       </c>
       <c r="G54">
         <v>9925</v>
@@ -5849,37 +5849,37 @@
         <v>228</v>
       </c>
       <c r="M54">
-        <v>13593.332376</v>
+        <v>13854.742614</v>
       </c>
       <c r="N54">
-        <v>-13365.332376</v>
+        <v>-13626.742614</v>
       </c>
       <c r="O54">
-        <v>-3448.255753008</v>
+        <v>-3515.699594412</v>
       </c>
       <c r="P54">
-        <v>-9917.076622992001</v>
+        <v>-10111.043019588</v>
       </c>
       <c r="Q54">
-        <v>-9767.076622992001</v>
+        <v>-9961.043019588</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1322574892622577</v>
+        <v>0.1340970103103909</v>
       </c>
       <c r="T54">
-        <v>1.996708758943597</v>
+        <v>2.039191924027504</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.004327415704471258</v>
+        <v>0.004245766351556705</v>
       </c>
       <c r="W54">
-        <v>0.2347795953768857</v>
+        <v>0.2347988482943029</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.01677292908709793</v>
+        <v>0.016456458726964</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1874689844418643</v>
+        <v>0.1893689844418643</v>
       </c>
       <c r="C55">
-        <v>-20648.9660266905</v>
+        <v>-22130.54301365816</v>
       </c>
       <c r="D55">
-        <v>28182.3639733095</v>
+        <v>27809.39698634184</v>
       </c>
       <c r="E55">
-        <v>42198.33</v>
+        <v>43306.94</v>
       </c>
       <c r="F55">
-        <v>58756.33</v>
+        <v>59864.94</v>
       </c>
       <c r="G55">
         <v>9925</v>
@@ -5931,37 +5931,37 @@
         <v>228</v>
       </c>
       <c r="M55">
-        <v>13854.742614</v>
+        <v>14116.152852</v>
       </c>
       <c r="N55">
-        <v>-13626.742614</v>
+        <v>-13888.152852</v>
       </c>
       <c r="O55">
-        <v>-3515.699594412</v>
+        <v>-3583.143435816</v>
       </c>
       <c r="P55">
-        <v>-10111.043019588</v>
+        <v>-10305.009416184</v>
       </c>
       <c r="Q55">
-        <v>-9961.043019588</v>
+        <v>-10155.009416184</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1340970103103909</v>
+        <v>0.1360165105345298</v>
       </c>
       <c r="T55">
-        <v>2.039191924027504</v>
+        <v>2.083522183245493</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.004245766351556705</v>
+        <v>0.0041671410487501</v>
       </c>
       <c r="W55">
-        <v>0.2347988482943029</v>
+        <v>0.2348173881407047</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.016456458726964</v>
+        <v>0.01615170949127942</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1893689844418643</v>
+        <v>0.1912689844418643</v>
       </c>
       <c r="C56">
-        <v>-22130.54301365816</v>
+        <v>-23602.37720523946</v>
       </c>
       <c r="D56">
-        <v>27809.39698634184</v>
+        <v>27446.17279476054</v>
       </c>
       <c r="E56">
-        <v>43306.94</v>
+        <v>44415.55</v>
       </c>
       <c r="F56">
-        <v>59864.94</v>
+        <v>60973.55</v>
       </c>
       <c r="G56">
         <v>9925</v>
@@ -6013,37 +6013,37 @@
         <v>228</v>
       </c>
       <c r="M56">
-        <v>14116.152852</v>
+        <v>14377.56309</v>
       </c>
       <c r="N56">
-        <v>-13888.152852</v>
+        <v>-14149.56309</v>
       </c>
       <c r="O56">
-        <v>-3583.143435816</v>
+        <v>-3650.58727722</v>
       </c>
       <c r="P56">
-        <v>-10305.009416184</v>
+        <v>-10498.97581278</v>
       </c>
       <c r="Q56">
-        <v>-10155.009416184</v>
+        <v>-10348.97581278</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1360165105345298</v>
+        <v>0.1380213218797416</v>
       </c>
       <c r="T56">
-        <v>2.083522183245493</v>
+        <v>2.129822676206504</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0041671410487501</v>
+        <v>0.004091374847863734</v>
       </c>
       <c r="W56">
-        <v>0.2348173881407047</v>
+        <v>0.2348352538108738</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.01615170949127942</v>
+        <v>0.01585804204598351</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1912689844418643</v>
+        <v>0.1931689844418643</v>
       </c>
       <c r="C57">
-        <v>-23602.37720523946</v>
+        <v>-25064.84543740105</v>
       </c>
       <c r="D57">
-        <v>27446.17279476054</v>
+        <v>27092.31456259896</v>
       </c>
       <c r="E57">
-        <v>44415.55</v>
+        <v>45524.16</v>
       </c>
       <c r="F57">
-        <v>60973.55</v>
+        <v>62082.16</v>
       </c>
       <c r="G57">
         <v>9925</v>
@@ -6095,37 +6095,37 @@
         <v>228</v>
       </c>
       <c r="M57">
-        <v>14377.56309</v>
+        <v>14638.973328</v>
       </c>
       <c r="N57">
-        <v>-14149.56309</v>
+        <v>-14410.973328</v>
       </c>
       <c r="O57">
-        <v>-3650.58727722</v>
+        <v>-3718.031118624001</v>
       </c>
       <c r="P57">
-        <v>-10498.97581278</v>
+        <v>-10692.942209376</v>
       </c>
       <c r="Q57">
-        <v>-10348.97581278</v>
+        <v>-10542.942209376</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1380213218797416</v>
+        <v>0.1401172610133721</v>
       </c>
       <c r="T57">
-        <v>2.129822676206504</v>
+        <v>2.178227737029379</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.004091374847863734</v>
+        <v>0.004018314582723311</v>
       </c>
       <c r="W57">
-        <v>0.2348352538108738</v>
+        <v>0.2348524814213939</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.01585804204598351</v>
+        <v>0.01557486272373376</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1931689844418643</v>
+        <v>0.1950689844418643</v>
       </c>
       <c r="C58">
-        <v>-25064.84543740105</v>
+        <v>-26518.30535958288</v>
       </c>
       <c r="D58">
-        <v>27092.31456259896</v>
+        <v>26747.46464041713</v>
       </c>
       <c r="E58">
-        <v>45524.16</v>
+        <v>46632.77</v>
       </c>
       <c r="F58">
-        <v>62082.16</v>
+        <v>63190.77</v>
       </c>
       <c r="G58">
         <v>9925</v>
@@ -6177,37 +6177,37 @@
         <v>228</v>
       </c>
       <c r="M58">
-        <v>14638.973328</v>
+        <v>14900.383566</v>
       </c>
       <c r="N58">
-        <v>-14410.973328</v>
+        <v>-14672.383566</v>
       </c>
       <c r="O58">
-        <v>-3718.031118624001</v>
+        <v>-3785.474960028001</v>
       </c>
       <c r="P58">
-        <v>-10692.942209376</v>
+        <v>-10886.908605972</v>
       </c>
       <c r="Q58">
-        <v>-10542.942209376</v>
+        <v>-10736.908605972</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1401172610133721</v>
+        <v>0.1423106856881017</v>
       </c>
       <c r="T58">
-        <v>2.178227737029379</v>
+        <v>2.228884196030062</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.004018314582723311</v>
+        <v>0.003947817835657989</v>
       </c>
       <c r="W58">
-        <v>0.2348524814213939</v>
+        <v>0.2348691045543519</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.01557486272373376</v>
+        <v>0.0153016195180542</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1950689844418643</v>
+        <v>0.1969689844418643</v>
       </c>
       <c r="C59">
-        <v>-26518.30535958288</v>
+        <v>-27963.09664044831</v>
       </c>
       <c r="D59">
-        <v>26747.46464041713</v>
+        <v>26411.28335955169</v>
       </c>
       <c r="E59">
-        <v>46632.77</v>
+        <v>47741.38</v>
       </c>
       <c r="F59">
-        <v>63190.77</v>
+        <v>64299.38</v>
       </c>
       <c r="G59">
         <v>9925</v>
@@ -6259,37 +6259,37 @@
         <v>228</v>
       </c>
       <c r="M59">
-        <v>14900.383566</v>
+        <v>15161.793804</v>
       </c>
       <c r="N59">
-        <v>-14672.383566</v>
+        <v>-14933.793804</v>
       </c>
       <c r="O59">
-        <v>-3785.474960028001</v>
+        <v>-3852.918801432</v>
       </c>
       <c r="P59">
-        <v>-10886.908605972</v>
+        <v>-11080.875002568</v>
       </c>
       <c r="Q59">
-        <v>-10736.908605972</v>
+        <v>-10930.875002568</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1423106856881017</v>
+        <v>0.144608559156866</v>
       </c>
       <c r="T59">
-        <v>2.228884196030062</v>
+        <v>2.281952867364112</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.003947817835657989</v>
+        <v>0.003879752010905266</v>
       </c>
       <c r="W59">
-        <v>0.2348691045543519</v>
+        <v>0.2348851544758285</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.0153016195180542</v>
+        <v>0.01503779849188092</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1969689844418642</v>
+        <v>0.1988689844418643</v>
       </c>
       <c r="C60">
-        <v>-27963.0966404483</v>
+        <v>-29399.54208383433</v>
       </c>
       <c r="D60">
-        <v>26411.2833595517</v>
+        <v>26083.44791616567</v>
       </c>
       <c r="E60">
-        <v>47741.38</v>
+        <v>48849.99</v>
       </c>
       <c r="F60">
-        <v>64299.38</v>
+        <v>65407.99</v>
       </c>
       <c r="G60">
         <v>9925</v>
@@ -6341,37 +6341,37 @@
         <v>228</v>
       </c>
       <c r="M60">
-        <v>15161.793804</v>
+        <v>15423.204042</v>
       </c>
       <c r="N60">
-        <v>-14933.793804</v>
+        <v>-15195.204042</v>
       </c>
       <c r="O60">
-        <v>-3852.918801432</v>
+        <v>-3920.362642836</v>
       </c>
       <c r="P60">
-        <v>-11080.875002568</v>
+        <v>-11274.841399164</v>
       </c>
       <c r="Q60">
-        <v>-10930.875002568</v>
+        <v>-11124.841399164</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.144608559156866</v>
+        <v>0.1470185240143505</v>
       </c>
       <c r="T60">
-        <v>2.281952867364111</v>
+        <v>2.337610254372991</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.003879752010905266</v>
+        <v>0.003813993502245855</v>
       </c>
       <c r="W60">
-        <v>0.2348851544758285</v>
+        <v>0.2349006603321704</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.01503779849188092</v>
+        <v>0.01478292055134056</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1988689844418643</v>
+        <v>0.2007689844418643</v>
       </c>
       <c r="C61">
-        <v>-29399.54208383433</v>
+        <v>-30827.94866260914</v>
       </c>
       <c r="D61">
-        <v>26083.44791616567</v>
+        <v>25763.65133739085</v>
       </c>
       <c r="E61">
-        <v>48849.99</v>
+        <v>49958.59999999999</v>
       </c>
       <c r="F61">
-        <v>65407.99</v>
+        <v>66516.59999999999</v>
       </c>
       <c r="G61">
         <v>9925</v>
@@ -6423,37 +6423,37 @@
         <v>228</v>
       </c>
       <c r="M61">
-        <v>15423.204042</v>
+        <v>15684.61428</v>
       </c>
       <c r="N61">
-        <v>-15195.204042</v>
+        <v>-15456.61428</v>
       </c>
       <c r="O61">
-        <v>-3920.362642836</v>
+        <v>-3987.806484239999</v>
       </c>
       <c r="P61">
-        <v>-11274.841399164</v>
+        <v>-11468.80779576</v>
       </c>
       <c r="Q61">
-        <v>-11124.841399164</v>
+        <v>-11318.80779576</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1470185240143505</v>
+        <v>0.1495489871147093</v>
       </c>
       <c r="T61">
-        <v>2.337610254372991</v>
+        <v>2.396050510732317</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.003813993502245855</v>
+        <v>0.003750426943875091</v>
       </c>
       <c r="W61">
-        <v>0.2349006603321704</v>
+        <v>0.2349156493266343</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.01478292055134056</v>
+        <v>0.01453653854215153</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2007689844418643</v>
+        <v>0.2026689844418643</v>
       </c>
       <c r="C62">
-        <v>-30827.94866260914</v>
+        <v>-32248.60847739699</v>
       </c>
       <c r="D62">
-        <v>25763.65133739085</v>
+        <v>25451.60152260301</v>
       </c>
       <c r="E62">
-        <v>49958.59999999999</v>
+        <v>51067.20999999999</v>
       </c>
       <c r="F62">
-        <v>66516.59999999999</v>
+        <v>67625.20999999999</v>
       </c>
       <c r="G62">
         <v>9925</v>
@@ -6505,37 +6505,37 @@
         <v>228</v>
       </c>
       <c r="M62">
-        <v>15684.61428</v>
+        <v>15946.024518</v>
       </c>
       <c r="N62">
-        <v>-15456.61428</v>
+        <v>-15718.024518</v>
       </c>
       <c r="O62">
-        <v>-3987.806484239999</v>
+        <v>-4055.250325644</v>
       </c>
       <c r="P62">
-        <v>-11468.80779576</v>
+        <v>-11662.774192356</v>
       </c>
       <c r="Q62">
-        <v>-11318.80779576</v>
+        <v>-11512.774192356</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1495489871147093</v>
+        <v>0.152209217553548</v>
       </c>
       <c r="T62">
-        <v>2.396050510732317</v>
+        <v>2.457487703315197</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.003750426943875091</v>
+        <v>0.003688944534959106</v>
       </c>
       <c r="W62">
-        <v>0.2349156493266343</v>
+        <v>0.2349301468786566</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.01453653854215153</v>
+        <v>0.0142982346316245</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2026689844418643</v>
+        <v>0.2045689844418643</v>
       </c>
       <c r="C63">
-        <v>-32248.60847739699</v>
+        <v>-33661.79964646439</v>
       </c>
       <c r="D63">
-        <v>25451.60152260301</v>
+        <v>25147.0203535356</v>
       </c>
       <c r="E63">
-        <v>51067.20999999999</v>
+        <v>52175.81999999999</v>
       </c>
       <c r="F63">
-        <v>67625.20999999999</v>
+        <v>68733.81999999999</v>
       </c>
       <c r="G63">
         <v>9925</v>
@@ -6587,37 +6587,37 @@
         <v>228</v>
       </c>
       <c r="M63">
-        <v>15946.024518</v>
+        <v>16207.434756</v>
       </c>
       <c r="N63">
-        <v>-15718.024518</v>
+        <v>-15979.434756</v>
       </c>
       <c r="O63">
-        <v>-4055.250325644</v>
+        <v>-4122.694167048</v>
       </c>
       <c r="P63">
-        <v>-11662.774192356</v>
+        <v>-11856.740588952</v>
       </c>
       <c r="Q63">
-        <v>-11512.774192356</v>
+        <v>-11706.740588952</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.152209217553548</v>
+        <v>0.1550094601207466</v>
       </c>
       <c r="T63">
-        <v>2.457487703315197</v>
+        <v>2.522158432349807</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.003688944534959106</v>
+        <v>0.003629445429556539</v>
       </c>
       <c r="W63">
-        <v>0.2349301468786566</v>
+        <v>0.2349441767677106</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.0142982346316245</v>
+        <v>0.01406761794401756</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2045689844418643</v>
+        <v>0.2064689844418643</v>
       </c>
       <c r="C64">
-        <v>-33661.79964646439</v>
+        <v>-35067.78713246578</v>
       </c>
       <c r="D64">
-        <v>25147.0203535356</v>
+        <v>24849.64286753423</v>
       </c>
       <c r="E64">
-        <v>52175.81999999999</v>
+        <v>53284.43000000001</v>
       </c>
       <c r="F64">
-        <v>68733.81999999999</v>
+        <v>69842.43000000001</v>
       </c>
       <c r="G64">
         <v>9925</v>
@@ -6669,37 +6669,37 @@
         <v>228</v>
       </c>
       <c r="M64">
-        <v>16207.434756</v>
+        <v>16468.844994</v>
       </c>
       <c r="N64">
-        <v>-15979.434756</v>
+        <v>-16240.844994</v>
       </c>
       <c r="O64">
-        <v>-4122.694167048</v>
+        <v>-4190.138008452001</v>
       </c>
       <c r="P64">
-        <v>-11856.740588952</v>
+        <v>-12050.706985548</v>
       </c>
       <c r="Q64">
-        <v>-11706.740588952</v>
+        <v>-11900.706985548</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1550094601207466</v>
+        <v>0.1579610671510371</v>
       </c>
       <c r="T64">
-        <v>2.522158432349807</v>
+        <v>2.590324876467369</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.003629445429556539</v>
+        <v>0.003571835184642943</v>
       </c>
       <c r="W64">
-        <v>0.2349441767677106</v>
+        <v>0.2349577612634612</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.01406761794401756</v>
+        <v>0.01384432242109668</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2064689844418643</v>
+        <v>0.2083689844418643</v>
       </c>
       <c r="C65">
-        <v>-35067.78713246578</v>
+        <v>-36466.82351121456</v>
       </c>
       <c r="D65">
-        <v>24849.64286753423</v>
+        <v>24559.21648878545</v>
       </c>
       <c r="E65">
-        <v>53284.43000000001</v>
+        <v>54393.04000000001</v>
       </c>
       <c r="F65">
-        <v>69842.43000000001</v>
+        <v>70951.04000000001</v>
       </c>
       <c r="G65">
         <v>9925</v>
@@ -6751,37 +6751,37 @@
         <v>228</v>
       </c>
       <c r="M65">
-        <v>16468.844994</v>
+        <v>16730.255232</v>
       </c>
       <c r="N65">
-        <v>-16240.844994</v>
+        <v>-16502.255232</v>
       </c>
       <c r="O65">
-        <v>-4190.138008452001</v>
+        <v>-4257.581849856001</v>
       </c>
       <c r="P65">
-        <v>-12050.706985548</v>
+        <v>-12244.673382144</v>
       </c>
       <c r="Q65">
-        <v>-11900.706985548</v>
+        <v>-12094.673382144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1579610671510371</v>
+        <v>0.161076652349677</v>
       </c>
       <c r="T65">
-        <v>2.590324876467369</v>
+        <v>2.66227834525813</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.003571835184642943</v>
+        <v>0.003516025259882896</v>
       </c>
       <c r="W65">
-        <v>0.2349577612634612</v>
+        <v>0.2349709212437196</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.01384432242109668</v>
+        <v>0.01362800488326699</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2083689844418643</v>
+        <v>0.2102689844418643</v>
       </c>
       <c r="C66">
-        <v>-36466.82351121456</v>
+        <v>-37859.14968716739</v>
       </c>
       <c r="D66">
-        <v>24559.21648878545</v>
+        <v>24275.50031283262</v>
       </c>
       <c r="E66">
-        <v>54393.04000000001</v>
+        <v>55501.65000000001</v>
       </c>
       <c r="F66">
-        <v>70951.04000000001</v>
+        <v>72059.65000000001</v>
       </c>
       <c r="G66">
         <v>9925</v>
@@ -6833,37 +6833,37 @@
         <v>228</v>
       </c>
       <c r="M66">
-        <v>16730.255232</v>
+        <v>16991.66547</v>
       </c>
       <c r="N66">
-        <v>-16502.255232</v>
+        <v>-16763.66547</v>
       </c>
       <c r="O66">
-        <v>-4257.581849856001</v>
+        <v>-4325.025691260001</v>
       </c>
       <c r="P66">
-        <v>-12244.673382144</v>
+        <v>-12438.63977874</v>
       </c>
       <c r="Q66">
-        <v>-12094.673382144</v>
+        <v>-12288.63977874</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.161076652349677</v>
+        <v>0.1643702709882392</v>
       </c>
       <c r="T66">
-        <v>2.66227834525813</v>
+        <v>2.738343440836934</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.003516025259882896</v>
+        <v>0.003461932563577006</v>
       </c>
       <c r="W66">
-        <v>0.2349709212437196</v>
+        <v>0.2349836763015086</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.01362800488326699</v>
+        <v>0.01341834326967828</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2102689844418643</v>
+        <v>0.2121689844418643</v>
       </c>
       <c r="C67">
-        <v>-37859.14968716739</v>
+        <v>-39244.99555988199</v>
       </c>
       <c r="D67">
-        <v>24275.50031283262</v>
+        <v>23998.26444011802</v>
       </c>
       <c r="E67">
-        <v>55501.65000000001</v>
+        <v>56610.26000000001</v>
       </c>
       <c r="F67">
-        <v>72059.65000000001</v>
+        <v>73168.26000000001</v>
       </c>
       <c r="G67">
         <v>9925</v>
@@ -6915,37 +6915,37 @@
         <v>228</v>
       </c>
       <c r="M67">
-        <v>16991.66547</v>
+        <v>17253.075708</v>
       </c>
       <c r="N67">
-        <v>-16763.66547</v>
+        <v>-17025.075708</v>
       </c>
       <c r="O67">
-        <v>-4325.025691260001</v>
+        <v>-4392.469532664001</v>
       </c>
       <c r="P67">
-        <v>-12438.63977874</v>
+        <v>-12632.606175336</v>
       </c>
       <c r="Q67">
-        <v>-12288.63977874</v>
+        <v>-12482.606175336</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1643702709882392</v>
+        <v>0.167857631899658</v>
       </c>
       <c r="T67">
-        <v>2.738343440836934</v>
+        <v>2.818882953802726</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.003461932563577006</v>
+        <v>0.003409479039886445</v>
       </c>
       <c r="W67">
-        <v>0.2349836763015086</v>
+        <v>0.2349960448423948</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.01341834326967828</v>
+        <v>0.01321503503831956</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2121689844418643</v>
+        <v>0.2140689844418643</v>
       </c>
       <c r="C68">
-        <v>-39244.99555988199</v>
+        <v>-40624.58064532311</v>
       </c>
       <c r="D68">
-        <v>23998.26444011802</v>
+        <v>23727.2893546769</v>
       </c>
       <c r="E68">
-        <v>56610.26000000001</v>
+        <v>57718.87000000001</v>
       </c>
       <c r="F68">
-        <v>73168.26000000001</v>
+        <v>74276.87000000001</v>
       </c>
       <c r="G68">
         <v>9925</v>
@@ -6997,37 +6997,37 @@
         <v>228</v>
       </c>
       <c r="M68">
-        <v>17253.075708</v>
+        <v>17514.485946</v>
       </c>
       <c r="N68">
-        <v>-17025.075708</v>
+        <v>-17286.485946</v>
       </c>
       <c r="O68">
-        <v>-4392.469532664001</v>
+        <v>-4459.913374068001</v>
       </c>
       <c r="P68">
-        <v>-12632.606175336</v>
+        <v>-12826.572571932</v>
       </c>
       <c r="Q68">
-        <v>-12482.606175336</v>
+        <v>-12676.572571932</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.167857631899658</v>
+        <v>0.1715563480178295</v>
       </c>
       <c r="T68">
-        <v>2.818882953802726</v>
+        <v>2.904303649372506</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.003409479039886445</v>
+        <v>0.003358591293022468</v>
       </c>
       <c r="W68">
-        <v>0.2349960448423948</v>
+        <v>0.2350080441731053</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.01321503503831956</v>
+        <v>0.01301779570938943</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2140689844418643</v>
+        <v>0.2159689844418643</v>
       </c>
       <c r="C69">
-        <v>-40624.58064532311</v>
+        <v>-41998.11465554594</v>
       </c>
       <c r="D69">
-        <v>23727.2893546769</v>
+        <v>23462.36534445407</v>
       </c>
       <c r="E69">
-        <v>57718.87000000001</v>
+        <v>58827.48000000001</v>
       </c>
       <c r="F69">
-        <v>74276.87000000001</v>
+        <v>75385.48000000001</v>
       </c>
       <c r="G69">
         <v>9925</v>
@@ -7079,37 +7079,37 @@
         <v>228</v>
       </c>
       <c r="M69">
-        <v>17514.485946</v>
+        <v>17775.896184</v>
       </c>
       <c r="N69">
-        <v>-17286.485946</v>
+        <v>-17547.896184</v>
       </c>
       <c r="O69">
-        <v>-4459.913374068001</v>
+        <v>-4527.357215472001</v>
       </c>
       <c r="P69">
-        <v>-12826.572571932</v>
+        <v>-13020.538968528</v>
       </c>
       <c r="Q69">
-        <v>-12676.572571932</v>
+        <v>-12870.538968528</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1715563480178295</v>
+        <v>0.1754862338933867</v>
       </c>
       <c r="T69">
-        <v>2.904303649372506</v>
+        <v>2.995063138415397</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.003358591293022468</v>
+        <v>0.003309200244595667</v>
       </c>
       <c r="W69">
-        <v>0.2350080441731053</v>
+        <v>0.2350196905823244</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.01301779570938943</v>
+        <v>0.01282635753719252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2159689844418643</v>
+        <v>0.2178689844418643</v>
       </c>
       <c r="C70">
-        <v>-41998.11465554594</v>
+        <v>-43365.79803997406</v>
       </c>
       <c r="D70">
-        <v>23462.36534445407</v>
+        <v>23203.29196002595</v>
       </c>
       <c r="E70">
-        <v>58827.48000000001</v>
+        <v>59936.09000000001</v>
       </c>
       <c r="F70">
-        <v>75385.48000000001</v>
+        <v>76494.09000000001</v>
       </c>
       <c r="G70">
         <v>9925</v>
@@ -7161,37 +7161,37 @@
         <v>228</v>
       </c>
       <c r="M70">
-        <v>17775.896184</v>
+        <v>18037.30642200001</v>
       </c>
       <c r="N70">
-        <v>-17547.896184</v>
+        <v>-17809.30642200001</v>
       </c>
       <c r="O70">
-        <v>-4527.357215472001</v>
+        <v>-4594.801056876002</v>
       </c>
       <c r="P70">
-        <v>-13020.538968528</v>
+        <v>-13214.505365124</v>
       </c>
       <c r="Q70">
-        <v>-12870.538968528</v>
+        <v>-13064.505365124</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1754862338933867</v>
+        <v>0.1796696607931733</v>
       </c>
       <c r="T70">
-        <v>2.995063138415397</v>
+        <v>3.091678078364281</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.003309200244595667</v>
+        <v>0.003261240820760947</v>
       </c>
       <c r="W70">
-        <v>0.2350196905823244</v>
+        <v>0.2350309994144646</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.01282635753719252</v>
+        <v>0.01264046829752308</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2178689844418643</v>
+        <v>0.2197689844418643</v>
       </c>
       <c r="C71">
-        <v>-43365.79803997406</v>
+        <v>-44727.82249120793</v>
       </c>
       <c r="D71">
-        <v>23203.29196002595</v>
+        <v>22949.87750879208</v>
       </c>
       <c r="E71">
-        <v>59936.09000000001</v>
+        <v>61044.70000000001</v>
       </c>
       <c r="F71">
-        <v>76494.09000000001</v>
+        <v>77602.70000000001</v>
       </c>
       <c r="G71">
         <v>9925</v>
@@ -7243,37 +7243,37 @@
         <v>228</v>
       </c>
       <c r="M71">
-        <v>18037.30642200001</v>
+        <v>18298.71666</v>
       </c>
       <c r="N71">
-        <v>-17809.30642200001</v>
+        <v>-18070.71666</v>
       </c>
       <c r="O71">
-        <v>-4594.801056876002</v>
+        <v>-4662.244898280001</v>
       </c>
       <c r="P71">
-        <v>-13214.505365124</v>
+        <v>-13408.47176172</v>
       </c>
       <c r="Q71">
-        <v>-13064.505365124</v>
+        <v>-13258.47176172</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1796696607931733</v>
+        <v>0.1841319828196124</v>
       </c>
       <c r="T71">
-        <v>3.091678078364281</v>
+        <v>3.194734014309756</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.003261240820760947</v>
+        <v>0.003214651666178649</v>
       </c>
       <c r="W71">
-        <v>0.2350309994144646</v>
+        <v>0.2350419851371151</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.01264046829752308</v>
+        <v>0.01245989017898697</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2197689844418643</v>
+        <v>0.2216689844418643</v>
       </c>
       <c r="C72">
-        <v>-44727.82249120793</v>
+        <v>-46084.3714180465</v>
       </c>
       <c r="D72">
-        <v>22949.87750879208</v>
+        <v>22701.93858195351</v>
       </c>
       <c r="E72">
-        <v>61044.70000000001</v>
+        <v>62153.31000000001</v>
       </c>
       <c r="F72">
-        <v>77602.70000000001</v>
+        <v>78711.31000000001</v>
       </c>
       <c r="G72">
         <v>9925</v>
@@ -7325,37 +7325,37 @@
         <v>228</v>
       </c>
       <c r="M72">
-        <v>18298.71666</v>
+        <v>18560.126898</v>
       </c>
       <c r="N72">
-        <v>-18070.71666</v>
+        <v>-18332.126898</v>
       </c>
       <c r="O72">
-        <v>-4662.244898280001</v>
+        <v>-4729.688739684001</v>
       </c>
       <c r="P72">
-        <v>-13408.47176172</v>
+        <v>-13602.438158316</v>
       </c>
       <c r="Q72">
-        <v>-13258.47176172</v>
+        <v>-13452.438158316</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1841319828196124</v>
+        <v>0.1889020511927025</v>
       </c>
       <c r="T72">
-        <v>3.194734014309756</v>
+        <v>3.304897256182507</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.003214651666178649</v>
+        <v>0.003169374882147963</v>
       </c>
       <c r="W72">
-        <v>0.2350419851371151</v>
+        <v>0.2350526614027895</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.01245989017898697</v>
+        <v>0.01228439876801535</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2216689844418643</v>
+        <v>0.2235689844418643</v>
       </c>
       <c r="C73">
-        <v>-46084.37141804649</v>
+        <v>-47435.62038817471</v>
       </c>
       <c r="D73">
-        <v>22701.93858195351</v>
+        <v>22459.29961182529</v>
       </c>
       <c r="E73">
-        <v>62153.31</v>
+        <v>63261.92</v>
       </c>
       <c r="F73">
-        <v>78711.31</v>
+        <v>79819.92</v>
       </c>
       <c r="G73">
         <v>9925</v>
@@ -7407,37 +7407,37 @@
         <v>228</v>
       </c>
       <c r="M73">
-        <v>18560.126898</v>
+        <v>18821.537136</v>
       </c>
       <c r="N73">
-        <v>-18332.126898</v>
+        <v>-18593.537136</v>
       </c>
       <c r="O73">
-        <v>-4729.688739684</v>
+        <v>-4797.132581088</v>
       </c>
       <c r="P73">
-        <v>-13602.438158316</v>
+        <v>-13796.404554912</v>
       </c>
       <c r="Q73">
-        <v>-13452.438158316</v>
+        <v>-13646.404554912</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1889020511927025</v>
+        <v>0.194012838735299</v>
       </c>
       <c r="T73">
-        <v>3.304897256182506</v>
+        <v>3.422929301046167</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.003169374882147964</v>
+        <v>0.003125355786562575</v>
       </c>
       <c r="W73">
-        <v>0.2350526614027895</v>
+        <v>0.2350630411055286</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.01228439876801535</v>
+        <v>0.01211378211845959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2235689844418643</v>
+        <v>0.2254689844418643</v>
       </c>
       <c r="C74">
-        <v>-47435.62038817471</v>
+        <v>-48781.73754276251</v>
       </c>
       <c r="D74">
-        <v>22459.29961182529</v>
+        <v>22221.79245723749</v>
       </c>
       <c r="E74">
-        <v>63261.92</v>
+        <v>64370.53</v>
       </c>
       <c r="F74">
-        <v>79819.92</v>
+        <v>80928.53</v>
       </c>
       <c r="G74">
         <v>9925</v>
@@ -7489,37 +7489,37 @@
         <v>228</v>
       </c>
       <c r="M74">
-        <v>18821.537136</v>
+        <v>19082.947374</v>
       </c>
       <c r="N74">
-        <v>-18593.537136</v>
+        <v>-18854.947374</v>
       </c>
       <c r="O74">
-        <v>-4797.132581088</v>
+        <v>-4864.576422492</v>
       </c>
       <c r="P74">
-        <v>-13796.404554912</v>
+        <v>-13990.370951508</v>
       </c>
       <c r="Q74">
-        <v>-13646.404554912</v>
+        <v>-13840.370951508</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.194012838735299</v>
+        <v>0.1995022031329027</v>
       </c>
       <c r="T74">
-        <v>3.422929301046167</v>
+        <v>3.549704460344173</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.003125355786562575</v>
+        <v>0.003082542693595965</v>
       </c>
       <c r="W74">
-        <v>0.2350630411055286</v>
+        <v>0.2350731364328501</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.01211378211845959</v>
+        <v>0.0119478398976588</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2254689844418643</v>
+        <v>0.2273689844418643</v>
       </c>
       <c r="C75">
-        <v>-48781.73754276251</v>
+        <v>-50122.88398503287</v>
       </c>
       <c r="D75">
-        <v>22221.79245723749</v>
+        <v>21989.25601496714</v>
       </c>
       <c r="E75">
-        <v>64370.53</v>
+        <v>65479.14</v>
       </c>
       <c r="F75">
-        <v>80928.53</v>
+        <v>82037.14</v>
       </c>
       <c r="G75">
         <v>9925</v>
@@ -7571,37 +7571,37 @@
         <v>228</v>
       </c>
       <c r="M75">
-        <v>19082.947374</v>
+        <v>19344.357612</v>
       </c>
       <c r="N75">
-        <v>-18854.947374</v>
+        <v>-19116.357612</v>
       </c>
       <c r="O75">
-        <v>-4864.576422492</v>
+        <v>-4932.020263896</v>
       </c>
       <c r="P75">
-        <v>-13990.370951508</v>
+        <v>-14184.337348104</v>
       </c>
       <c r="Q75">
-        <v>-13840.370951508</v>
+        <v>-14034.337348104</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1995022031329027</v>
+        <v>0.205413826330322</v>
       </c>
       <c r="T75">
-        <v>3.549704460344173</v>
+        <v>3.686231554972795</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.003082542693595965</v>
+        <v>0.003040886711250073</v>
       </c>
       <c r="W75">
-        <v>0.2350731364328501</v>
+        <v>0.2350829589134873</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0119478398976588</v>
+        <v>0.01178638260174447</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2273689844418643</v>
+        <v>0.2292689844418643</v>
       </c>
       <c r="C76">
-        <v>-50122.88398503287</v>
+        <v>-51459.21414468565</v>
       </c>
       <c r="D76">
-        <v>21989.25601496714</v>
+        <v>21761.53585531435</v>
       </c>
       <c r="E76">
-        <v>65479.14</v>
+        <v>66587.75</v>
       </c>
       <c r="F76">
-        <v>82037.14</v>
+        <v>83145.75</v>
       </c>
       <c r="G76">
         <v>9925</v>
@@ -7653,37 +7653,37 @@
         <v>228</v>
       </c>
       <c r="M76">
-        <v>19344.357612</v>
+        <v>19605.76785</v>
       </c>
       <c r="N76">
-        <v>-19116.357612</v>
+        <v>-19377.76785</v>
       </c>
       <c r="O76">
-        <v>-4932.020263896</v>
+        <v>-4999.4641053</v>
       </c>
       <c r="P76">
-        <v>-14184.337348104</v>
+        <v>-14378.3037447</v>
       </c>
       <c r="Q76">
-        <v>-14034.337348104</v>
+        <v>-14228.3037447</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.205413826330322</v>
+        <v>0.2117983793835349</v>
       </c>
       <c r="T76">
-        <v>3.686231554972795</v>
+        <v>3.833680817171707</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.003040886711250073</v>
+        <v>0.003000341555100072</v>
       </c>
       <c r="W76">
-        <v>0.2350829589134873</v>
+        <v>0.2350925194613074</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.01178638260174447</v>
+        <v>0.01162923083372125</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2292689844418643</v>
+        <v>0.2311689844418643</v>
       </c>
       <c r="C77">
-        <v>-51459.21414468565</v>
+        <v>-52790.87611991006</v>
       </c>
       <c r="D77">
-        <v>21761.53585531435</v>
+        <v>21538.48388008995</v>
       </c>
       <c r="E77">
-        <v>66587.75</v>
+        <v>67696.36</v>
       </c>
       <c r="F77">
-        <v>83145.75</v>
+        <v>84254.36</v>
       </c>
       <c r="G77">
         <v>9925</v>
@@ -7735,37 +7735,37 @@
         <v>228</v>
       </c>
       <c r="M77">
-        <v>19605.76785</v>
+        <v>19867.178088</v>
       </c>
       <c r="N77">
-        <v>-19377.76785</v>
+        <v>-19639.178088</v>
       </c>
       <c r="O77">
-        <v>-4999.4641053</v>
+        <v>-5066.907946704</v>
       </c>
       <c r="P77">
-        <v>-14378.3037447</v>
+        <v>-14572.270141296</v>
       </c>
       <c r="Q77">
-        <v>-14228.3037447</v>
+        <v>-14422.270141296</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2117983793835349</v>
+        <v>0.2187149785245155</v>
       </c>
       <c r="T77">
-        <v>3.833680817171707</v>
+        <v>3.993417517887194</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.003000341555100072</v>
+        <v>0.002960863376743493</v>
       </c>
       <c r="W77">
-        <v>0.2350925194613074</v>
+        <v>0.2351018284157639</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.01162923083372125</v>
+        <v>0.01147621463854065</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2311689844418643</v>
+        <v>0.2330689844418643</v>
       </c>
       <c r="C78">
-        <v>-52790.87611991006</v>
+        <v>-54118.0119985767</v>
       </c>
       <c r="D78">
-        <v>21538.48388008995</v>
+        <v>21319.9580014233</v>
       </c>
       <c r="E78">
-        <v>67696.36</v>
+        <v>68804.97</v>
       </c>
       <c r="F78">
-        <v>84254.36</v>
+        <v>85362.97</v>
       </c>
       <c r="G78">
         <v>9925</v>
@@ -7817,37 +7817,37 @@
         <v>228</v>
       </c>
       <c r="M78">
-        <v>19867.178088</v>
+        <v>20128.588326</v>
       </c>
       <c r="N78">
-        <v>-19639.178088</v>
+        <v>-19900.588326</v>
       </c>
       <c r="O78">
-        <v>-5066.907946704</v>
+        <v>-5134.351788108001</v>
       </c>
       <c r="P78">
-        <v>-14572.270141296</v>
+        <v>-14766.236537892</v>
       </c>
       <c r="Q78">
-        <v>-14422.270141296</v>
+        <v>-14616.236537892</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2187149785245155</v>
+        <v>0.2262330210690597</v>
       </c>
       <c r="T78">
-        <v>3.993417517887194</v>
+        <v>4.167044366490986</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.002960863376743493</v>
+        <v>0.002922410605616953</v>
       </c>
       <c r="W78">
-        <v>0.2351018284157639</v>
+        <v>0.2351108955791955</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.01147621463854065</v>
+        <v>0.01132717288998819</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2330689844418643</v>
+        <v>0.2349689844418643</v>
       </c>
       <c r="C79">
-        <v>-54118.0119985767</v>
+        <v>-55440.75816007391</v>
       </c>
       <c r="D79">
-        <v>21319.9580014233</v>
+        <v>21105.82183992609</v>
       </c>
       <c r="E79">
-        <v>68804.97</v>
+        <v>69913.58</v>
       </c>
       <c r="F79">
-        <v>85362.97</v>
+        <v>86471.58</v>
       </c>
       <c r="G79">
         <v>9925</v>
@@ -7899,37 +7899,37 @@
         <v>228</v>
       </c>
       <c r="M79">
-        <v>20128.588326</v>
+        <v>20389.998564</v>
       </c>
       <c r="N79">
-        <v>-19900.588326</v>
+        <v>-20161.998564</v>
       </c>
       <c r="O79">
-        <v>-5134.351788108001</v>
+        <v>-5201.795629512</v>
       </c>
       <c r="P79">
-        <v>-14766.236537892</v>
+        <v>-14960.202934488</v>
       </c>
       <c r="Q79">
-        <v>-14616.236537892</v>
+        <v>-14810.202934488</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2262330210690597</v>
+        <v>0.2344345220267442</v>
       </c>
       <c r="T79">
-        <v>4.167044366490986</v>
+        <v>4.356455474058758</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.002922410605616953</v>
+        <v>0.002884943802980839</v>
       </c>
       <c r="W79">
-        <v>0.2351108955791955</v>
+        <v>0.2351197302512571</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.01132717288998819</v>
+        <v>0.01118195272473188</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2349689844418643</v>
+        <v>0.2368689844418643</v>
       </c>
       <c r="C80">
-        <v>-55440.75816007391</v>
+        <v>-56759.24555913477</v>
       </c>
       <c r="D80">
-        <v>21105.82183992609</v>
+        <v>20895.94444086523</v>
       </c>
       <c r="E80">
-        <v>69913.58</v>
+        <v>71022.19</v>
       </c>
       <c r="F80">
-        <v>86471.58</v>
+        <v>87580.19</v>
       </c>
       <c r="G80">
         <v>9925</v>
@@ -7981,37 +7981,37 @@
         <v>228</v>
       </c>
       <c r="M80">
-        <v>20389.998564</v>
+        <v>20651.408802</v>
       </c>
       <c r="N80">
-        <v>-20161.998564</v>
+        <v>-20423.408802</v>
       </c>
       <c r="O80">
-        <v>-5201.795629512</v>
+        <v>-5269.239470916001</v>
       </c>
       <c r="P80">
-        <v>-14960.202934488</v>
+        <v>-15154.169331084</v>
       </c>
       <c r="Q80">
-        <v>-14810.202934488</v>
+        <v>-15004.169331084</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2344345220267442</v>
+        <v>0.243417118313732</v>
       </c>
       <c r="T80">
-        <v>4.356455474058758</v>
+        <v>4.563905734728223</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.002884943802980839</v>
+        <v>0.002848425526993739</v>
       </c>
       <c r="W80">
-        <v>0.2351197302512571</v>
+        <v>0.2351283412607349</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.01118195272473188</v>
+        <v>0.01104040901935555</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2368689844418643</v>
+        <v>0.2387689844418643</v>
       </c>
       <c r="C81">
-        <v>-56759.24555913477</v>
+        <v>-58073.5999928969</v>
       </c>
       <c r="D81">
-        <v>20895.94444086523</v>
+        <v>20690.20000710311</v>
       </c>
       <c r="E81">
-        <v>71022.19</v>
+        <v>72130.8</v>
       </c>
       <c r="F81">
-        <v>87580.19</v>
+        <v>88688.8</v>
       </c>
       <c r="G81">
         <v>9925</v>
@@ -8063,37 +8063,37 @@
         <v>228</v>
       </c>
       <c r="M81">
-        <v>20651.408802</v>
+        <v>20912.81904</v>
       </c>
       <c r="N81">
-        <v>-20423.408802</v>
+        <v>-20684.81904</v>
       </c>
       <c r="O81">
-        <v>-5269.239470916001</v>
+        <v>-5336.68331232</v>
       </c>
       <c r="P81">
-        <v>-15154.169331084</v>
+        <v>-15348.13572768</v>
       </c>
       <c r="Q81">
-        <v>-15004.169331084</v>
+        <v>-15198.13572768</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.243417118313732</v>
+        <v>0.2532979742294186</v>
       </c>
       <c r="T81">
-        <v>4.563905734728223</v>
+        <v>4.792101021464634</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.002848425526993739</v>
+        <v>0.002812820207906317</v>
       </c>
       <c r="W81">
-        <v>0.2351283412607349</v>
+        <v>0.2351367369949757</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.01104040901935555</v>
+        <v>0.01090240390661368</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2387689844418643</v>
+        <v>0.2406689844418643</v>
       </c>
       <c r="C82">
-        <v>-58073.5999928969</v>
+        <v>-59383.94235233876</v>
       </c>
       <c r="D82">
-        <v>20690.20000710311</v>
+        <v>20488.46764766124</v>
       </c>
       <c r="E82">
-        <v>72130.8</v>
+        <v>73239.41</v>
       </c>
       <c r="F82">
-        <v>88688.8</v>
+        <v>89797.41</v>
       </c>
       <c r="G82">
         <v>9925</v>
@@ -8145,37 +8145,37 @@
         <v>228</v>
       </c>
       <c r="M82">
-        <v>20912.81904</v>
+        <v>21174.229278</v>
       </c>
       <c r="N82">
-        <v>-20684.81904</v>
+        <v>-20946.229278</v>
       </c>
       <c r="O82">
-        <v>-5336.68331232</v>
+        <v>-5404.127153724001</v>
       </c>
       <c r="P82">
-        <v>-15348.13572768</v>
+        <v>-15542.102124276</v>
       </c>
       <c r="Q82">
-        <v>-15198.13572768</v>
+        <v>-15392.102124276</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2532979742294186</v>
+        <v>0.2642189202414933</v>
       </c>
       <c r="T82">
-        <v>4.792101021464634</v>
+        <v>5.044316864699615</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.002812820207906317</v>
+        <v>0.002778094032500066</v>
       </c>
       <c r="W82">
-        <v>0.2351367369949757</v>
+        <v>0.2351449254271365</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.01090240390661368</v>
+        <v>0.01076780632751961</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2406689844418643</v>
+        <v>0.2425689844418643</v>
       </c>
       <c r="C83">
-        <v>-59383.94235233876</v>
+        <v>-60690.38885914889</v>
       </c>
       <c r="D83">
-        <v>20488.46764766124</v>
+        <v>20290.63114085111</v>
       </c>
       <c r="E83">
-        <v>73239.41</v>
+        <v>74348.02</v>
       </c>
       <c r="F83">
-        <v>89797.41</v>
+        <v>90906.02</v>
       </c>
       <c r="G83">
         <v>9925</v>
@@ -8227,37 +8227,37 @@
         <v>228</v>
       </c>
       <c r="M83">
-        <v>21174.229278</v>
+        <v>21435.639516</v>
       </c>
       <c r="N83">
-        <v>-20946.229278</v>
+        <v>-21207.639516</v>
       </c>
       <c r="O83">
-        <v>-5404.127153724001</v>
+        <v>-5471.570995128001</v>
       </c>
       <c r="P83">
-        <v>-15542.102124276</v>
+        <v>-15736.068520872</v>
       </c>
       <c r="Q83">
-        <v>-15392.102124276</v>
+        <v>-15586.068520872</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2642189202414933</v>
+        <v>0.276353304699354</v>
       </c>
       <c r="T83">
-        <v>5.044316864699615</v>
+        <v>5.324556690516261</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.002778094032500066</v>
+        <v>0.002744214836981773</v>
       </c>
       <c r="W83">
-        <v>0.2351449254271365</v>
+        <v>0.2351529141414397</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.01076780632751961</v>
+        <v>0.01063649161620839</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2425689844418643</v>
+        <v>0.2444689844418643</v>
       </c>
       <c r="C84">
-        <v>-60690.38885914889</v>
+        <v>-61993.05128900314</v>
       </c>
       <c r="D84">
-        <v>20290.63114085111</v>
+        <v>20096.57871099687</v>
       </c>
       <c r="E84">
-        <v>74348.02</v>
+        <v>75456.63</v>
       </c>
       <c r="F84">
-        <v>90906.02</v>
+        <v>92014.63</v>
       </c>
       <c r="G84">
         <v>9925</v>
@@ -8309,37 +8309,37 @@
         <v>228</v>
       </c>
       <c r="M84">
-        <v>21435.639516</v>
+        <v>21697.049754</v>
       </c>
       <c r="N84">
-        <v>-21207.639516</v>
+        <v>-21469.049754</v>
       </c>
       <c r="O84">
-        <v>-5471.570995128001</v>
+        <v>-5539.014836532001</v>
       </c>
       <c r="P84">
-        <v>-15736.068520872</v>
+        <v>-15930.034917468</v>
       </c>
       <c r="Q84">
-        <v>-15586.068520872</v>
+        <v>-15780.034917468</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.276353304699354</v>
+        <v>0.2899152637993161</v>
       </c>
       <c r="T84">
-        <v>5.324556690516261</v>
+        <v>5.637765907605454</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.002744214836981773</v>
+        <v>0.002711152007620547</v>
       </c>
       <c r="W84">
-        <v>0.2351529141414397</v>
+        <v>0.2351607103566031</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01063649161620839</v>
+        <v>0.01050834111480836</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2444689844418643</v>
+        <v>0.2463689844418643</v>
       </c>
       <c r="C85">
-        <v>-61993.05128900314</v>
+        <v>-63292.03718215106</v>
       </c>
       <c r="D85">
-        <v>20096.57871099687</v>
+        <v>19906.20281784894</v>
       </c>
       <c r="E85">
-        <v>75456.63</v>
+        <v>76565.24000000001</v>
       </c>
       <c r="F85">
-        <v>92014.63</v>
+        <v>93123.24000000001</v>
       </c>
       <c r="G85">
         <v>9925</v>
@@ -8391,37 +8391,37 @@
         <v>228</v>
       </c>
       <c r="M85">
-        <v>21697.049754</v>
+        <v>21958.459992</v>
       </c>
       <c r="N85">
-        <v>-21469.049754</v>
+        <v>-21730.459992</v>
       </c>
       <c r="O85">
-        <v>-5539.014836532001</v>
+        <v>-5606.458677936002</v>
       </c>
       <c r="P85">
-        <v>-15930.034917468</v>
+        <v>-16124.001314064</v>
       </c>
       <c r="Q85">
-        <v>-15780.034917468</v>
+        <v>-15974.001314064</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2899152637993161</v>
+        <v>0.3051724677867734</v>
       </c>
       <c r="T85">
-        <v>5.637765907605454</v>
+        <v>5.990126276830796</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.002711152007620547</v>
+        <v>0.002678876388482207</v>
       </c>
       <c r="W85">
-        <v>0.2351607103566031</v>
+        <v>0.2351683209475959</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.01050834111480836</v>
+        <v>0.01038324181582251</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2463689844418643</v>
+        <v>0.2482689844418643</v>
       </c>
       <c r="C86">
-        <v>-63292.03718215105</v>
+        <v>-64587.45004214551</v>
       </c>
       <c r="D86">
-        <v>19906.20281784894</v>
+        <v>19719.39995785448</v>
       </c>
       <c r="E86">
-        <v>76565.23999999999</v>
+        <v>77673.84999999999</v>
       </c>
       <c r="F86">
-        <v>93123.23999999999</v>
+        <v>94231.84999999999</v>
       </c>
       <c r="G86">
         <v>9925</v>
@@ -8473,37 +8473,37 @@
         <v>228</v>
       </c>
       <c r="M86">
-        <v>21958.459992</v>
+        <v>22219.87023</v>
       </c>
       <c r="N86">
-        <v>-21730.459992</v>
+        <v>-21991.87023</v>
       </c>
       <c r="O86">
-        <v>-5606.458677936</v>
+        <v>-5673.90251934</v>
       </c>
       <c r="P86">
-        <v>-16124.001314064</v>
+        <v>-16317.96771066</v>
       </c>
       <c r="Q86">
-        <v>-15974.001314064</v>
+        <v>-16167.96771066</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3051724677867732</v>
+        <v>0.3224639656392248</v>
       </c>
       <c r="T86">
-        <v>5.990126276830791</v>
+        <v>6.389468028619511</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.002678876388482208</v>
+        <v>0.002647360195676535</v>
       </c>
       <c r="W86">
-        <v>0.2351683209475959</v>
+        <v>0.2351757524658595</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.01038324181582251</v>
+        <v>0.01026108602975406</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2482689844418643</v>
+        <v>0.2501689844418643</v>
       </c>
       <c r="C87">
-        <v>-64587.45004214551</v>
+        <v>-65879.38952348655</v>
       </c>
       <c r="D87">
-        <v>19719.39995785448</v>
+        <v>19536.07047651345</v>
       </c>
       <c r="E87">
-        <v>77673.84999999999</v>
+        <v>78782.45999999999</v>
       </c>
       <c r="F87">
-        <v>94231.84999999999</v>
+        <v>95340.45999999999</v>
       </c>
       <c r="G87">
         <v>9925</v>
@@ -8555,37 +8555,37 @@
         <v>228</v>
       </c>
       <c r="M87">
-        <v>22219.87023</v>
+        <v>22481.280468</v>
       </c>
       <c r="N87">
-        <v>-21991.87023</v>
+        <v>-22253.280468</v>
       </c>
       <c r="O87">
-        <v>-5673.90251934</v>
+        <v>-5741.346360744</v>
       </c>
       <c r="P87">
-        <v>-16317.96771066</v>
+        <v>-16511.934107256</v>
       </c>
       <c r="Q87">
-        <v>-16167.96771066</v>
+        <v>-16361.934107256</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3224639656392248</v>
+        <v>0.342225677470598</v>
       </c>
       <c r="T87">
-        <v>6.389468028619511</v>
+        <v>6.845858602092333</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.002647360195676535</v>
+        <v>0.002616576937587273</v>
       </c>
       <c r="W87">
-        <v>0.2351757524658595</v>
+        <v>0.2351830111581169</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.01026108602975406</v>
+        <v>0.01014177107591963</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2501689844418643</v>
+        <v>0.2520689844418643</v>
       </c>
       <c r="C88">
-        <v>-65879.38952348655</v>
+        <v>-67167.9516088949</v>
       </c>
       <c r="D88">
-        <v>19536.07047651345</v>
+        <v>19356.11839110509</v>
       </c>
       <c r="E88">
-        <v>78782.45999999999</v>
+        <v>79891.06999999999</v>
       </c>
       <c r="F88">
-        <v>95340.45999999999</v>
+        <v>96449.06999999999</v>
       </c>
       <c r="G88">
         <v>9925</v>
@@ -8637,37 +8637,37 @@
         <v>228</v>
       </c>
       <c r="M88">
-        <v>22481.280468</v>
+        <v>22742.690706</v>
       </c>
       <c r="N88">
-        <v>-22253.280468</v>
+        <v>-22514.690706</v>
       </c>
       <c r="O88">
-        <v>-5741.346360744</v>
+        <v>-5808.790202147999</v>
       </c>
       <c r="P88">
-        <v>-16511.934107256</v>
+        <v>-16705.900503852</v>
       </c>
       <c r="Q88">
-        <v>-16361.934107256</v>
+        <v>-16555.900503852</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.342225677470598</v>
+        <v>0.365027652660644</v>
       </c>
       <c r="T88">
-        <v>6.845858602092333</v>
+        <v>7.372463109945589</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.002616576937587273</v>
+        <v>0.002586501340603511</v>
       </c>
       <c r="W88">
-        <v>0.2351830111581169</v>
+        <v>0.2351901029838857</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.01014177107591963</v>
+        <v>0.0100251989945872</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2520689844418643</v>
+        <v>0.2539689844418643</v>
       </c>
       <c r="C89">
-        <v>-67167.9516088949</v>
+        <v>-68453.22877687722</v>
       </c>
       <c r="D89">
-        <v>19356.11839110509</v>
+        <v>19179.45122312278</v>
       </c>
       <c r="E89">
-        <v>79891.06999999999</v>
+        <v>80999.68000000001</v>
       </c>
       <c r="F89">
-        <v>96449.06999999999</v>
+        <v>97557.68000000001</v>
       </c>
       <c r="G89">
         <v>9925</v>
@@ -8719,37 +8719,37 @@
         <v>228</v>
       </c>
       <c r="M89">
-        <v>22742.690706</v>
+        <v>23004.100944</v>
       </c>
       <c r="N89">
-        <v>-22514.690706</v>
+        <v>-22776.100944</v>
       </c>
       <c r="O89">
-        <v>-5808.790202147999</v>
+        <v>-5876.234043552001</v>
       </c>
       <c r="P89">
-        <v>-16705.900503852</v>
+        <v>-16899.866900448</v>
       </c>
       <c r="Q89">
-        <v>-16555.900503852</v>
+        <v>-16749.866900448</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.365027652660644</v>
+        <v>0.391629957049031</v>
       </c>
       <c r="T89">
-        <v>7.372463109945589</v>
+        <v>7.986835035774389</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.002586501340603511</v>
+        <v>0.002557109279914834</v>
       </c>
       <c r="W89">
-        <v>0.2351901029838857</v>
+        <v>0.2351970336317961</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.0100251989945872</v>
+        <v>0.009911276278739667</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2539689844418643</v>
+        <v>0.2558689844418643</v>
       </c>
       <c r="C90">
-        <v>-68453.22877687722</v>
+        <v>-69735.31016019807</v>
       </c>
       <c r="D90">
-        <v>19179.45122312278</v>
+        <v>19005.97983980194</v>
       </c>
       <c r="E90">
-        <v>80999.68000000001</v>
+        <v>82108.29000000001</v>
       </c>
       <c r="F90">
-        <v>97557.68000000001</v>
+        <v>98666.29000000001</v>
       </c>
       <c r="G90">
         <v>9925</v>
@@ -8801,37 +8801,37 @@
         <v>228</v>
       </c>
       <c r="M90">
-        <v>23004.100944</v>
+        <v>23265.511182</v>
       </c>
       <c r="N90">
-        <v>-22776.100944</v>
+        <v>-23037.511182</v>
       </c>
       <c r="O90">
-        <v>-5876.234043552001</v>
+        <v>-5943.677884956001</v>
       </c>
       <c r="P90">
-        <v>-16899.866900448</v>
+        <v>-17093.833297044</v>
       </c>
       <c r="Q90">
-        <v>-16749.866900448</v>
+        <v>-16943.833297044</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.391629957049031</v>
+        <v>0.4230690440534884</v>
       </c>
       <c r="T90">
-        <v>7.986835035774389</v>
+        <v>8.712910948117516</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.002557109279914834</v>
+        <v>0.002528377714971971</v>
       </c>
       <c r="W90">
-        <v>0.2351970336317961</v>
+        <v>0.2352038085348096</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.009911276278739667</v>
+        <v>0.009799913623922407</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2558689844418643</v>
+        <v>0.2577689844418642</v>
       </c>
       <c r="C91">
-        <v>-69735.31016019807</v>
+        <v>-71014.2816958289</v>
       </c>
       <c r="D91">
-        <v>19005.97983980194</v>
+        <v>18835.6183041711</v>
       </c>
       <c r="E91">
-        <v>82108.29000000001</v>
+        <v>83216.90000000001</v>
       </c>
       <c r="F91">
-        <v>98666.29000000001</v>
+        <v>99774.90000000001</v>
       </c>
       <c r="G91">
         <v>9925</v>
@@ -8883,37 +8883,37 @@
         <v>228</v>
       </c>
       <c r="M91">
-        <v>23265.511182</v>
+        <v>23526.92142</v>
       </c>
       <c r="N91">
-        <v>-23037.511182</v>
+        <v>-23298.92142</v>
       </c>
       <c r="O91">
-        <v>-5943.677884956001</v>
+        <v>-6011.121726360001</v>
       </c>
       <c r="P91">
-        <v>-17093.833297044</v>
+        <v>-17287.79969364</v>
       </c>
       <c r="Q91">
-        <v>-16943.833297044</v>
+        <v>-17137.79969364</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4230690440534884</v>
+        <v>0.4607959484588373</v>
       </c>
       <c r="T91">
-        <v>8.712910948117516</v>
+        <v>9.584202042929268</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.002528377714971971</v>
+        <v>0.00250028462925006</v>
       </c>
       <c r="W91">
-        <v>0.2352038085348096</v>
+        <v>0.2352104328844228</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.009799913623922407</v>
+        <v>0.009691025694767652</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2577689844418642</v>
+        <v>0.2596689844418643</v>
       </c>
       <c r="C92">
-        <v>-71014.2816958289</v>
+        <v>-72290.22626690436</v>
       </c>
       <c r="D92">
-        <v>18835.6183041711</v>
+        <v>18668.28373309565</v>
       </c>
       <c r="E92">
-        <v>83216.90000000001</v>
+        <v>84325.51000000001</v>
       </c>
       <c r="F92">
-        <v>99774.90000000001</v>
+        <v>100883.51</v>
       </c>
       <c r="G92">
         <v>9925</v>
@@ -8965,37 +8965,37 @@
         <v>228</v>
       </c>
       <c r="M92">
-        <v>23526.92142</v>
+        <v>23788.331658</v>
       </c>
       <c r="N92">
-        <v>-23298.92142</v>
+        <v>-23560.331658</v>
       </c>
       <c r="O92">
-        <v>-6011.121726360001</v>
+        <v>-6078.565567764001</v>
       </c>
       <c r="P92">
-        <v>-17287.79969364</v>
+        <v>-17481.766090236</v>
       </c>
       <c r="Q92">
-        <v>-17137.79969364</v>
+        <v>-17331.766090236</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4607959484588373</v>
+        <v>0.506906609398708</v>
       </c>
       <c r="T92">
-        <v>9.584202042929268</v>
+        <v>10.64911338103252</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.00250028462925006</v>
+        <v>0.002472808973983576</v>
       </c>
       <c r="W92">
-        <v>0.2352104328844228</v>
+        <v>0.2352169116439347</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.009691025694767652</v>
+        <v>0.009584530906913136</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2596689844418643</v>
+        <v>0.2615689844418643</v>
       </c>
       <c r="C93">
-        <v>-72290.22626690436</v>
+        <v>-73563.22383717835</v>
       </c>
       <c r="D93">
-        <v>18668.28373309565</v>
+        <v>18503.89616282166</v>
       </c>
       <c r="E93">
-        <v>84325.51000000001</v>
+        <v>85434.12000000001</v>
       </c>
       <c r="F93">
-        <v>100883.51</v>
+        <v>101992.12</v>
       </c>
       <c r="G93">
         <v>9925</v>
@@ -9047,37 +9047,37 @@
         <v>228</v>
       </c>
       <c r="M93">
-        <v>23788.331658</v>
+        <v>24049.741896</v>
       </c>
       <c r="N93">
-        <v>-23560.331658</v>
+        <v>-23821.741896</v>
       </c>
       <c r="O93">
-        <v>-6078.565567764001</v>
+        <v>-6146.009409168001</v>
       </c>
       <c r="P93">
-        <v>-17481.766090236</v>
+        <v>-17675.732486832</v>
       </c>
       <c r="Q93">
-        <v>-17331.766090236</v>
+        <v>-17525.732486832</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.506906609398708</v>
+        <v>0.5645449355735468</v>
       </c>
       <c r="T93">
-        <v>10.64911338103252</v>
+        <v>11.98025255366159</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.002472808973983576</v>
+        <v>0.002445930615570711</v>
       </c>
       <c r="W93">
-        <v>0.2352169116439347</v>
+        <v>0.2352232495608484</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.009584530906913136</v>
+        <v>0.00948035122314228</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2615689844418643</v>
+        <v>0.2634689844418643</v>
       </c>
       <c r="C94">
-        <v>-73563.22383717835</v>
+        <v>-74833.35157843813</v>
       </c>
       <c r="D94">
-        <v>18503.89616282166</v>
+        <v>18342.37842156188</v>
       </c>
       <c r="E94">
-        <v>85434.12000000001</v>
+        <v>86542.73000000001</v>
       </c>
       <c r="F94">
-        <v>101992.12</v>
+        <v>103100.73</v>
       </c>
       <c r="G94">
         <v>9925</v>
@@ -9129,37 +9129,37 @@
         <v>228</v>
       </c>
       <c r="M94">
-        <v>24049.741896</v>
+        <v>24311.152134</v>
       </c>
       <c r="N94">
-        <v>-23821.741896</v>
+        <v>-24083.152134</v>
       </c>
       <c r="O94">
-        <v>-6146.009409168001</v>
+        <v>-6213.453250572001</v>
       </c>
       <c r="P94">
-        <v>-17675.732486832</v>
+        <v>-17869.698883428</v>
       </c>
       <c r="Q94">
-        <v>-17525.732486832</v>
+        <v>-17719.698883428</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5645449355735468</v>
+        <v>0.6386513549411963</v>
       </c>
       <c r="T94">
-        <v>11.98025255366159</v>
+        <v>13.69171720418468</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.002445930615570711</v>
+        <v>0.002419630286371026</v>
       </c>
       <c r="W94">
-        <v>0.2352232495608484</v>
+        <v>0.2352294511784737</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.00948035122314228</v>
+        <v>0.009378411962678412</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2634689844418643</v>
+        <v>0.2653689844418642</v>
       </c>
       <c r="C95">
-        <v>-74833.35157843813</v>
+        <v>-76100.6839913033</v>
       </c>
       <c r="D95">
-        <v>18342.37842156188</v>
+        <v>18183.65600869671</v>
       </c>
       <c r="E95">
-        <v>86542.73000000001</v>
+        <v>87651.34000000001</v>
       </c>
       <c r="F95">
-        <v>103100.73</v>
+        <v>104209.34</v>
       </c>
       <c r="G95">
         <v>9925</v>
@@ -9211,37 +9211,37 @@
         <v>228</v>
       </c>
       <c r="M95">
-        <v>24311.152134</v>
+        <v>24572.562372</v>
       </c>
       <c r="N95">
-        <v>-24083.152134</v>
+        <v>-24344.562372</v>
       </c>
       <c r="O95">
-        <v>-6213.453250572001</v>
+        <v>-6280.897091976001</v>
       </c>
       <c r="P95">
-        <v>-17869.698883428</v>
+        <v>-18063.665280024</v>
       </c>
       <c r="Q95">
-        <v>-17719.698883428</v>
+        <v>-17913.665280024</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6386513549411963</v>
+        <v>0.7374599140980626</v>
       </c>
       <c r="T95">
-        <v>13.69171720418468</v>
+        <v>15.97367007154879</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.002419630286371026</v>
+        <v>0.002393889538643675</v>
       </c>
       <c r="W95">
-        <v>0.2352294511784737</v>
+        <v>0.2352355208467878</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.009378411962678412</v>
+        <v>0.009278641622649908</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2653689844418642</v>
+        <v>0.2672689844418643</v>
       </c>
       <c r="C96">
-        <v>-76100.6839913033</v>
+        <v>-77365.29301980652</v>
       </c>
       <c r="D96">
-        <v>18183.65600869671</v>
+        <v>18027.6569801935</v>
       </c>
       <c r="E96">
-        <v>87651.34000000001</v>
+        <v>88759.95000000001</v>
       </c>
       <c r="F96">
-        <v>104209.34</v>
+        <v>105317.95</v>
       </c>
       <c r="G96">
         <v>9925</v>
@@ -9293,37 +9293,37 @@
         <v>228</v>
       </c>
       <c r="M96">
-        <v>24572.562372</v>
+        <v>24833.97261</v>
       </c>
       <c r="N96">
-        <v>-24344.562372</v>
+        <v>-24605.97261</v>
       </c>
       <c r="O96">
-        <v>-6280.897091976001</v>
+        <v>-6348.340933380001</v>
       </c>
       <c r="P96">
-        <v>-18063.665280024</v>
+        <v>-18257.63167662</v>
       </c>
       <c r="Q96">
-        <v>-17913.665280024</v>
+        <v>-18107.63167662</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7374599140980626</v>
+        <v>0.8757918969176756</v>
       </c>
       <c r="T96">
-        <v>15.97367007154879</v>
+        <v>19.16840408585856</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.002393889538643675</v>
+        <v>0.002368690701394793</v>
       </c>
       <c r="W96">
-        <v>0.2352355208467878</v>
+        <v>0.2352414627326111</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.009278641622649908</v>
+        <v>0.009180971710832542</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2672689844418643</v>
+        <v>0.2691689844418643</v>
       </c>
       <c r="C97">
-        <v>-77365.29301980652</v>
+        <v>-78627.24816012649</v>
       </c>
       <c r="D97">
-        <v>18027.6569801935</v>
+        <v>17874.31183987352</v>
       </c>
       <c r="E97">
-        <v>88759.95000000001</v>
+        <v>89868.56000000001</v>
       </c>
       <c r="F97">
-        <v>105317.95</v>
+        <v>106426.56</v>
       </c>
       <c r="G97">
         <v>9925</v>
@@ -9375,37 +9375,37 @@
         <v>228</v>
       </c>
       <c r="M97">
-        <v>24833.97261</v>
+        <v>25095.382848</v>
       </c>
       <c r="N97">
-        <v>-24605.97261</v>
+        <v>-24867.382848</v>
       </c>
       <c r="O97">
-        <v>-6348.340933380001</v>
+        <v>-6415.784774784001</v>
       </c>
       <c r="P97">
-        <v>-18257.63167662</v>
+        <v>-18451.598073216</v>
       </c>
       <c r="Q97">
-        <v>-18107.63167662</v>
+        <v>-18301.598073216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8757918969176756</v>
+        <v>1.083289871147095</v>
       </c>
       <c r="T97">
-        <v>19.16840408585856</v>
+        <v>23.96050510732321</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.002368690701394793</v>
+        <v>0.002344016839921931</v>
       </c>
       <c r="W97">
-        <v>0.2352414627326111</v>
+        <v>0.2352472808291464</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.009180971710832542</v>
+        <v>0.009085336588844695</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2691689844418643</v>
+        <v>0.2710689844418643</v>
       </c>
       <c r="C98">
-        <v>-78627.24816012647</v>
+        <v>-79886.61656381842</v>
       </c>
       <c r="D98">
-        <v>17874.31183987352</v>
+        <v>17723.55343618158</v>
       </c>
       <c r="E98">
-        <v>89868.56</v>
+        <v>90977.17</v>
       </c>
       <c r="F98">
-        <v>106426.56</v>
+        <v>107535.17</v>
       </c>
       <c r="G98">
         <v>9925</v>
@@ -9457,37 +9457,37 @@
         <v>228</v>
       </c>
       <c r="M98">
-        <v>25095.382848</v>
+        <v>25356.793086</v>
       </c>
       <c r="N98">
-        <v>-24867.382848</v>
+        <v>-25128.793086</v>
       </c>
       <c r="O98">
-        <v>-6415.784774784001</v>
+        <v>-6483.228616188</v>
       </c>
       <c r="P98">
-        <v>-18451.598073216</v>
+        <v>-18645.564469812</v>
       </c>
       <c r="Q98">
-        <v>-18301.598073216</v>
+        <v>-18495.564469812</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.083289871147092</v>
+        <v>1.429119828196123</v>
       </c>
       <c r="T98">
-        <v>23.96050510732315</v>
+        <v>31.94734014309753</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002344016839921931</v>
+        <v>0.00231985171786088</v>
       </c>
       <c r="W98">
-        <v>0.2352472808291464</v>
+        <v>0.2352529789649284</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.009085336588844695</v>
+        <v>0.008991673325042138</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2710689844418643</v>
+        <v>0.2729689844418643</v>
       </c>
       <c r="C99">
-        <v>-79886.61656381842</v>
+        <v>-81143.46313586403</v>
       </c>
       <c r="D99">
-        <v>17723.55343618158</v>
+        <v>17575.31686413597</v>
       </c>
       <c r="E99">
-        <v>90977.17</v>
+        <v>92085.78</v>
       </c>
       <c r="F99">
-        <v>107535.17</v>
+        <v>108643.78</v>
       </c>
       <c r="G99">
         <v>9925</v>
@@ -9539,37 +9539,37 @@
         <v>228</v>
       </c>
       <c r="M99">
-        <v>25356.793086</v>
+        <v>25618.203324</v>
       </c>
       <c r="N99">
-        <v>-25128.793086</v>
+        <v>-25390.203324</v>
       </c>
       <c r="O99">
-        <v>-6483.228616188</v>
+        <v>-6550.672457592001</v>
       </c>
       <c r="P99">
-        <v>-18645.564469812</v>
+        <v>-18839.530866408</v>
       </c>
       <c r="Q99">
-        <v>-18495.564469812</v>
+        <v>-18689.530866408</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.429119828196123</v>
+        <v>2.120779742294184</v>
       </c>
       <c r="T99">
-        <v>31.94734014309753</v>
+        <v>47.92101021464629</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00231985171786088</v>
+        <v>0.002296179761556178</v>
       </c>
       <c r="W99">
-        <v>0.2352529789649284</v>
+        <v>0.2352585608122251</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.008991673325042138</v>
+        <v>0.008899921556419277</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2729689844418643</v>
+        <v>0.2748689844418643</v>
       </c>
       <c r="C100">
-        <v>-81143.46313586403</v>
+        <v>-82397.85062784192</v>
       </c>
       <c r="D100">
-        <v>17575.31686413597</v>
+        <v>17429.53937215808</v>
       </c>
       <c r="E100">
-        <v>92085.78</v>
+        <v>93194.39</v>
       </c>
       <c r="F100">
-        <v>108643.78</v>
+        <v>109752.39</v>
       </c>
       <c r="G100">
         <v>9925</v>
@@ -9621,37 +9621,37 @@
         <v>228</v>
       </c>
       <c r="M100">
-        <v>25618.203324</v>
+        <v>25879.613562</v>
       </c>
       <c r="N100">
-        <v>-25390.203324</v>
+        <v>-25651.613562</v>
       </c>
       <c r="O100">
-        <v>-6550.672457592001</v>
+        <v>-6618.116298996001</v>
       </c>
       <c r="P100">
-        <v>-18839.530866408</v>
+        <v>-19033.497263004</v>
       </c>
       <c r="Q100">
-        <v>-18689.530866408</v>
+        <v>-18883.497263004</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.120779742294184</v>
+        <v>4.195759484588368</v>
       </c>
       <c r="T100">
-        <v>47.92101021464629</v>
+        <v>95.84202042929259</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002296179761556178</v>
+        <v>0.002272986026590964</v>
       </c>
       <c r="W100">
-        <v>0.2352585608122251</v>
+        <v>0.2352640298949299</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.008899921556419277</v>
+        <v>0.008810023358879704</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2748689844418643</v>
-      </c>
-      <c r="C101">
-        <v>-82397.85062784192</v>
-      </c>
-      <c r="D101">
-        <v>17429.53937215808</v>
-      </c>
-      <c r="E101">
-        <v>93194.39</v>
-      </c>
-      <c r="F101">
-        <v>109752.39</v>
-      </c>
-      <c r="G101">
-        <v>9925</v>
-      </c>
-      <c r="H101">
-        <v>94303</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>378</v>
-      </c>
-      <c r="K101">
-        <v>150</v>
-      </c>
-      <c r="L101">
-        <v>228</v>
-      </c>
-      <c r="M101">
-        <v>25879.613562</v>
-      </c>
-      <c r="N101">
-        <v>-25651.613562</v>
-      </c>
-      <c r="O101">
-        <v>-6618.116298996001</v>
-      </c>
-      <c r="P101">
-        <v>-19033.497263004</v>
-      </c>
-      <c r="Q101">
-        <v>-18883.497263004</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.195759484588368</v>
-      </c>
-      <c r="T101">
-        <v>95.84202042929259</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.002272986026590964</v>
-      </c>
-      <c r="W101">
-        <v>0.2352640298949299</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.008810023358879704</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
